--- a/jogos_2025-07-19.xlsx
+++ b/jogos_2025-07-19.xlsx
@@ -235,15 +235,15 @@
     <t>Japan J1 League</t>
   </si>
   <si>
+    <t>South Korea K League 1</t>
+  </si>
+  <si>
+    <t>South Korea K League 2</t>
+  </si>
+  <si>
     <t>China China League One</t>
   </si>
   <si>
-    <t>South Korea K League 2</t>
-  </si>
-  <si>
-    <t>South Korea K League 1</t>
-  </si>
-  <si>
     <t>China Chinese Super League</t>
   </si>
   <si>
@@ -268,12 +268,12 @@
     <t>Estonia Meistriliiga</t>
   </si>
   <si>
+    <t>Chile Primera B</t>
+  </si>
+  <si>
     <t>Chile Primera División</t>
   </si>
   <si>
-    <t>Chile Primera B</t>
-  </si>
-  <si>
     <t>Argentina Primera División</t>
   </si>
   <si>
@@ -289,12 +289,12 @@
     <t>Canada Canadian Premier League</t>
   </si>
   <si>
+    <t>USA USL Championship</t>
+  </si>
+  <si>
     <t>Brazil Serie C</t>
   </si>
   <si>
-    <t>USA USL Championship</t>
-  </si>
-  <si>
     <t>USA MLS</t>
   </si>
   <si>
@@ -316,34 +316,37 @@
     <t>Sutherland Sharks</t>
   </si>
   <si>
+    <t>Shonan Bellmare</t>
+  </si>
+  <si>
+    <t>Gangwon</t>
+  </si>
+  <si>
+    <t>Seoul E-Land</t>
+  </si>
+  <si>
+    <t>Pohang Steelers</t>
+  </si>
+  <si>
+    <t>Yanbian Longding</t>
+  </si>
+  <si>
+    <t>Jeonnam Dragons</t>
+  </si>
+  <si>
+    <t>Gimpo Citizen</t>
+  </si>
+  <si>
     <t>Tokyo</t>
   </si>
   <si>
-    <t>Yanbian Longding</t>
-  </si>
-  <si>
-    <t>Jeonnam Dragons</t>
-  </si>
-  <si>
-    <t>Pohang Steelers</t>
-  </si>
-  <si>
-    <t>Shonan Bellmare</t>
-  </si>
-  <si>
-    <t>Gangwon</t>
+    <t>Jeju United</t>
   </si>
   <si>
     <t>Hwaseong</t>
   </si>
   <si>
-    <t>Jeju United</t>
-  </si>
-  <si>
-    <t>Gimpo Citizen</t>
-  </si>
-  <si>
-    <t>Seoul E-Land</t>
+    <t>Shenyang Urban</t>
   </si>
   <si>
     <t>Suzhou Dongwu</t>
@@ -352,9 +355,6 @@
     <t>Dalian Zhixing</t>
   </si>
   <si>
-    <t>Shenyang Urban</t>
-  </si>
-  <si>
     <t>Hebei Kungfu</t>
   </si>
   <si>
@@ -364,48 +364,48 @@
     <t>Sichuan Jiuniu</t>
   </si>
   <si>
+    <t>Henan Jianye</t>
+  </si>
+  <si>
     <t>KFUM</t>
   </si>
   <si>
-    <t>Henan Jianye</t>
-  </si>
-  <si>
     <t>Östersunds FK</t>
   </si>
   <si>
+    <t>Öster</t>
+  </si>
+  <si>
     <t>Umeå</t>
   </si>
   <si>
-    <t>Öster</t>
+    <t>Yelimay Semey</t>
+  </si>
+  <si>
+    <t>Kairat</t>
   </si>
   <si>
     <t>Djurgården</t>
   </si>
   <si>
-    <t>Yelimay Semey</t>
-  </si>
-  <si>
     <t>Oddevold</t>
   </si>
   <si>
-    <t>Kairat</t>
+    <t>VPS</t>
   </si>
   <si>
     <t>Molde</t>
   </si>
   <si>
-    <t>VPS</t>
-  </si>
-  <si>
     <t>Breidablik</t>
   </si>
   <si>
+    <t>Sandviken</t>
+  </si>
+  <si>
     <t>Okzhetpes</t>
   </si>
   <si>
-    <t>Sandviken</t>
-  </si>
-  <si>
     <t>Degerfors</t>
   </si>
   <si>
@@ -415,12 +415,12 @@
     <t>Harju Jalgpallikool</t>
   </si>
   <si>
+    <t>Cobreloa</t>
+  </si>
+  <si>
     <t>Unión Española</t>
   </si>
   <si>
-    <t>Cobreloa</t>
-  </si>
-  <si>
     <t>San Lorenzo</t>
   </si>
   <si>
@@ -433,90 +433,90 @@
     <t>Goiás</t>
   </si>
   <si>
+    <t>Colo-Colo</t>
+  </si>
+  <si>
+    <t>Deportes Santa Cruz</t>
+  </si>
+  <si>
     <t>Fortaleza</t>
   </si>
   <si>
-    <t>Deportes Santa Cruz</t>
-  </si>
-  <si>
-    <t>Colo-Colo</t>
-  </si>
-  <si>
     <t>Lanús</t>
   </si>
   <si>
+    <t>Defensores Unidos</t>
+  </si>
+  <si>
+    <t>Chaco For Ever</t>
+  </si>
+  <si>
+    <t>Deportivo Morón</t>
+  </si>
+  <si>
+    <t>Estudiantes Río Cuarto</t>
+  </si>
+  <si>
+    <t>Tristán Suárez</t>
+  </si>
+  <si>
+    <t>York9 FC</t>
+  </si>
+  <si>
+    <t>Deportivo Maipú</t>
+  </si>
+  <si>
+    <t>Arsenal de Sarandí</t>
+  </si>
+  <si>
+    <t>Alvarado</t>
+  </si>
+  <si>
+    <t>Atlanta</t>
+  </si>
+  <si>
+    <t>All Boys</t>
+  </si>
+  <si>
+    <t>Deportivo Madryn</t>
+  </si>
+  <si>
+    <t>Rhode Island</t>
+  </si>
+  <si>
+    <t>Ituano</t>
+  </si>
+  <si>
+    <t>ABC</t>
+  </si>
+  <si>
+    <t>Colón</t>
+  </si>
+  <si>
+    <t>Estudiantes Caseros</t>
+  </si>
+  <si>
+    <t>Temperley</t>
+  </si>
+  <si>
+    <t>Colegiales</t>
+  </si>
+  <si>
     <t>Gimnasia y Tiro</t>
   </si>
   <si>
-    <t>Arsenal de Sarandí</t>
-  </si>
-  <si>
-    <t>York9 FC</t>
-  </si>
-  <si>
-    <t>Tristán Suárez</t>
-  </si>
-  <si>
-    <t>Colegiales</t>
-  </si>
-  <si>
-    <t>All Boys</t>
-  </si>
-  <si>
-    <t>Estudiantes Río Cuarto</t>
-  </si>
-  <si>
-    <t>Defensores Unidos</t>
-  </si>
-  <si>
-    <t>Estudiantes Caseros</t>
-  </si>
-  <si>
-    <t>Deportivo Maipú</t>
-  </si>
-  <si>
-    <t>Ituano</t>
-  </si>
-  <si>
-    <t>Temperley</t>
-  </si>
-  <si>
-    <t>Alvarado</t>
-  </si>
-  <si>
-    <t>Colón</t>
-  </si>
-  <si>
-    <t>Chaco For Ever</t>
-  </si>
-  <si>
-    <t>Atlanta</t>
-  </si>
-  <si>
-    <t>Deportivo Morón</t>
-  </si>
-  <si>
-    <t>ABC</t>
-  </si>
-  <si>
-    <t>Rhode Island</t>
-  </si>
-  <si>
-    <t>Deportivo Madryn</t>
-  </si>
-  <si>
     <t>Vasco da Gama</t>
   </si>
   <si>
+    <t>Avaí</t>
+  </si>
+  <si>
     <t>Coritiba</t>
   </si>
   <si>
     <t>Mirassol</t>
   </si>
   <si>
-    <t>Avaí</t>
-  </si>
-  <si>
     <t>Coquimbo Unido</t>
   </si>
   <si>
@@ -532,28 +532,34 @@
     <t>Ponte Preta</t>
   </si>
   <si>
+    <t>Crown Legacy</t>
+  </si>
+  <si>
+    <t>Concepción</t>
+  </si>
+  <si>
+    <t>Loudoun United</t>
+  </si>
+  <si>
     <t>Chattanooga FC</t>
   </si>
   <si>
-    <t>Loudoun United</t>
-  </si>
-  <si>
-    <t>Concepción</t>
-  </si>
-  <si>
-    <t>Crown Legacy</t>
+    <t>Carolina Core</t>
+  </si>
+  <si>
+    <t>Atlanta United FC</t>
   </si>
   <si>
     <t>Columbus Crew</t>
   </si>
   <si>
+    <t>Montreal Impact</t>
+  </si>
+  <si>
     <t>Volta Redonda</t>
   </si>
   <si>
-    <t>Montreal Impact</t>
-  </si>
-  <si>
-    <t>Carolina Core</t>
+    <t>Charleston Battery</t>
   </si>
   <si>
     <t>New York RB</t>
@@ -562,22 +568,22 @@
     <t>New England Revolution</t>
   </si>
   <si>
-    <t>Atlanta United FC</t>
-  </si>
-  <si>
-    <t>Charleston Battery</t>
-  </si>
-  <si>
     <t>São Paulo</t>
   </si>
   <si>
+    <t>Birmingham Legion</t>
+  </si>
+  <si>
+    <t>Louisville City</t>
+  </si>
+  <si>
     <t>Instituto</t>
   </si>
   <si>
-    <t>Louisville City</t>
-  </si>
-  <si>
-    <t>Birmingham Legion</t>
+    <t>Seattle Sounders</t>
+  </si>
+  <si>
+    <t>FC Dallas</t>
   </si>
   <si>
     <t>Nashville SC</t>
@@ -586,12 +592,6 @@
     <t>Sporting KC</t>
   </si>
   <si>
-    <t>FC Dallas</t>
-  </si>
-  <si>
-    <t>Seattle Sounders</t>
-  </si>
-  <si>
     <t>Houston Dynamo</t>
   </si>
   <si>
@@ -601,12 +601,12 @@
     <t>Orange County SC</t>
   </si>
   <si>
+    <t>Portland Timbers</t>
+  </si>
+  <si>
     <t>Los Angeles FC</t>
   </si>
   <si>
-    <t>Portland Timbers</t>
-  </si>
-  <si>
     <t>San Diego</t>
   </si>
   <si>
@@ -625,34 +625,37 @@
     <t>Blacktown City</t>
   </si>
   <si>
+    <t>Cerezo Osaka</t>
+  </si>
+  <si>
+    <t>Daejeon Citizen</t>
+  </si>
+  <si>
+    <t>Seongnam</t>
+  </si>
+  <si>
+    <t>Jeonbuk Motors</t>
+  </si>
+  <si>
+    <t>Qingdao Red Lions</t>
+  </si>
+  <si>
+    <t>Suwon Bluewings</t>
+  </si>
+  <si>
+    <t>Ansan Greeners</t>
+  </si>
+  <si>
     <t>Urawa Reds</t>
   </si>
   <si>
-    <t>Qingdao Red Lions</t>
-  </si>
-  <si>
-    <t>Suwon Bluewings</t>
-  </si>
-  <si>
-    <t>Jeonbuk Motors</t>
-  </si>
-  <si>
-    <t>Cerezo Osaka</t>
-  </si>
-  <si>
-    <t>Daejeon Citizen</t>
+    <t>Anyang</t>
   </si>
   <si>
     <t>Busan I'Park</t>
   </si>
   <si>
-    <t>Anyang</t>
-  </si>
-  <si>
-    <t>Ansan Greeners</t>
-  </si>
-  <si>
-    <t>Seongnam</t>
+    <t>Chongqing Tongliang Long</t>
   </si>
   <si>
     <t>Dongguan United</t>
@@ -661,9 +664,6 @@
     <t>Shandong Luneng</t>
   </si>
   <si>
-    <t>Chongqing Tongliang Long</t>
-  </si>
-  <si>
     <t>Nantong Zhiyun</t>
   </si>
   <si>
@@ -673,48 +673,48 @@
     <t>Qingdao Jonoon</t>
   </si>
   <si>
+    <t>Meizhou Hakka</t>
+  </si>
+  <si>
     <t>Brann</t>
   </si>
   <si>
-    <t>Meizhou Hakka</t>
-  </si>
-  <si>
     <t>Falkenberg</t>
   </si>
   <si>
+    <t>Malmö FF</t>
+  </si>
+  <si>
     <t>Örebro</t>
   </si>
   <si>
-    <t>Malmö FF</t>
+    <t>Zhenys</t>
+  </si>
+  <si>
+    <t>Kaisar</t>
   </si>
   <si>
     <t>Elfsborg</t>
   </si>
   <si>
-    <t>Zhenys</t>
-  </si>
-  <si>
     <t>Örgryte</t>
   </si>
   <si>
-    <t>Kaisar</t>
+    <t>KuPS</t>
   </si>
   <si>
     <t>Strømsgodset</t>
   </si>
   <si>
-    <t>KuPS</t>
-  </si>
-  <si>
     <t>Vestri</t>
   </si>
   <si>
+    <t>Västerås SK</t>
+  </si>
+  <si>
     <t>Ulytau</t>
   </si>
   <si>
-    <t>Västerås SK</t>
-  </si>
-  <si>
     <t>GAIS</t>
   </si>
   <si>
@@ -724,12 +724,12 @@
     <t>Tallinna FC Levadia</t>
   </si>
   <si>
+    <t>San Marcos</t>
+  </si>
+  <si>
     <t>Unión La Calera</t>
   </si>
   <si>
-    <t>San Marcos</t>
-  </si>
-  <si>
     <t>Gimnasia La Plata</t>
   </si>
   <si>
@@ -742,90 +742,90 @@
     <t>Cuiabá</t>
   </si>
   <si>
+    <t>La Serena</t>
+  </si>
+  <si>
+    <t>Recoleta</t>
+  </si>
+  <si>
     <t>Bahia</t>
   </si>
   <si>
-    <t>Recoleta</t>
-  </si>
-  <si>
-    <t>La Serena</t>
-  </si>
-  <si>
     <t>Rosario Central</t>
   </si>
   <si>
+    <t>Agropecuario</t>
+  </si>
+  <si>
+    <t>Almirante Brown</t>
+  </si>
+  <si>
+    <t>Chacarita Juniors</t>
+  </si>
+  <si>
+    <t>Nueva Chicago</t>
+  </si>
+  <si>
+    <t>Los Andes</t>
+  </si>
+  <si>
+    <t>Vancouver FC</t>
+  </si>
+  <si>
+    <t>Club Atlético Güemes</t>
+  </si>
+  <si>
+    <t>San Miguel</t>
+  </si>
+  <si>
+    <t>Ferro Carril Oeste</t>
+  </si>
+  <si>
+    <t>Racing Córdoba</t>
+  </si>
+  <si>
+    <t>Almagro</t>
+  </si>
+  <si>
+    <t>Patronato</t>
+  </si>
+  <si>
+    <t>Hartford Athletic</t>
+  </si>
+  <si>
+    <t>Botafogo PB</t>
+  </si>
+  <si>
+    <t>Maringá</t>
+  </si>
+  <si>
+    <t>Gimnasia Mendoza</t>
+  </si>
+  <si>
+    <t>San Telmo</t>
+  </si>
+  <si>
+    <t>Gimnasia Jujuy</t>
+  </si>
+  <si>
+    <t>Quilmes</t>
+  </si>
+  <si>
     <t>San Martín Tucumán</t>
   </si>
   <si>
-    <t>San Miguel</t>
-  </si>
-  <si>
-    <t>Vancouver FC</t>
-  </si>
-  <si>
-    <t>Los Andes</t>
-  </si>
-  <si>
-    <t>Quilmes</t>
-  </si>
-  <si>
-    <t>Almagro</t>
-  </si>
-  <si>
-    <t>Nueva Chicago</t>
-  </si>
-  <si>
-    <t>Agropecuario</t>
-  </si>
-  <si>
-    <t>San Telmo</t>
-  </si>
-  <si>
-    <t>Club Atlético Güemes</t>
-  </si>
-  <si>
-    <t>Botafogo PB</t>
-  </si>
-  <si>
-    <t>Gimnasia Jujuy</t>
-  </si>
-  <si>
-    <t>Ferro Carril Oeste</t>
-  </si>
-  <si>
-    <t>Gimnasia Mendoza</t>
-  </si>
-  <si>
-    <t>Almirante Brown</t>
-  </si>
-  <si>
-    <t>Racing Córdoba</t>
-  </si>
-  <si>
-    <t>Chacarita Juniors</t>
-  </si>
-  <si>
-    <t>Maringá</t>
-  </si>
-  <si>
-    <t>Hartford Athletic</t>
-  </si>
-  <si>
-    <t>Patronato</t>
-  </si>
-  <si>
     <t>Grêmio</t>
   </si>
   <si>
+    <t>Vila Nova</t>
+  </si>
+  <si>
     <t>Paysandu</t>
   </si>
   <si>
     <t>Santos</t>
   </si>
   <si>
-    <t>Vila Nova</t>
-  </si>
-  <si>
     <t>Deportes Iquique</t>
   </si>
   <si>
@@ -841,28 +841,34 @@
     <t>Floresta</t>
   </si>
   <si>
+    <t>Philadelphia Union II</t>
+  </si>
+  <si>
+    <t>Antofagasta</t>
+  </si>
+  <si>
+    <t>Oakland Roots</t>
+  </si>
+  <si>
     <t>Inter Miami II</t>
   </si>
   <si>
-    <t>Oakland Roots</t>
-  </si>
-  <si>
-    <t>Antofagasta</t>
-  </si>
-  <si>
-    <t>Philadelphia Union II</t>
+    <t>Atlanta United II</t>
+  </si>
+  <si>
+    <t>Charlotte</t>
   </si>
   <si>
     <t>DC United</t>
   </si>
   <si>
+    <t>Chicago Fire</t>
+  </si>
+  <si>
     <t>Atlético PR</t>
   </si>
   <si>
-    <t>Chicago Fire</t>
-  </si>
-  <si>
-    <t>Atlanta United II</t>
+    <t>Miami FC II</t>
   </si>
   <si>
     <t>Inter Miami</t>
@@ -871,22 +877,22 @@
     <t>Orlando City</t>
   </si>
   <si>
-    <t>Charlotte</t>
-  </si>
-  <si>
-    <t>Miami FC II</t>
-  </si>
-  <si>
     <t>Corinthians</t>
   </si>
   <si>
+    <t>Colorado Springs</t>
+  </si>
+  <si>
+    <t>Tulsa Roughnecks</t>
+  </si>
+  <si>
     <t>River Plate</t>
   </si>
   <si>
-    <t>Tulsa Roughnecks</t>
-  </si>
-  <si>
-    <t>Colorado Springs</t>
+    <t>SJ Earthquakes</t>
+  </si>
+  <si>
+    <t>St. Louis City</t>
   </si>
   <si>
     <t>Toronto</t>
@@ -895,12 +901,6 @@
     <t>New York City</t>
   </si>
   <si>
-    <t>St. Louis City</t>
-  </si>
-  <si>
-    <t>SJ Earthquakes</t>
-  </si>
-  <si>
     <t>Philadelphia Union</t>
   </si>
   <si>
@@ -910,10 +910,10 @@
     <t>Las Vegas Lights</t>
   </si>
   <si>
+    <t>Minnesota United</t>
+  </si>
+  <si>
     <t>LA Galaxy</t>
-  </si>
-  <si>
-    <t>Minnesota United</t>
   </si>
   <si>
     <t>Vancouver Whitecaps</t>
@@ -1443,22 +1443,22 @@
         <v>301</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="P2">
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R2">
         <v>0</v>
@@ -1491,10 +1491,10 @@
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -1559,13 +1559,13 @@
         <v>301</v>
       </c>
       <c r="L3">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="M3">
         <v>4</v>
       </c>
       <c r="N3">
-        <v>2.75</v>
+        <v>2.22</v>
       </c>
       <c r="O3">
         <v>2</v>
@@ -1577,16 +1577,16 @@
         <v>1.8</v>
       </c>
       <c r="R3">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="S3">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="T3">
         <v>2.06</v>
       </c>
       <c r="U3">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="V3">
         <v>4.33</v>
@@ -1604,22 +1604,22 @@
         <v>1.07</v>
       </c>
       <c r="AA3">
-        <v>5.25</v>
+        <v>5.8</v>
       </c>
       <c r="AB3">
         <v>1.37</v>
       </c>
       <c r="AC3">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="AD3">
         <v>2.1</v>
       </c>
       <c r="AE3">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AF3">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AG3">
         <v>3.03</v>
@@ -1696,16 +1696,16 @@
         <v>1.24</v>
       </c>
       <c r="S4">
-        <v>3.36</v>
+        <v>3.3</v>
       </c>
       <c r="T4">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="U4">
         <v>1.57</v>
       </c>
       <c r="V4">
-        <v>5.1</v>
+        <v>5.15</v>
       </c>
       <c r="W4">
         <v>1.13</v>
@@ -1717,10 +1717,10 @@
         <v>12</v>
       </c>
       <c r="Z4">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AA4">
-        <v>4.55</v>
+        <v>4.5</v>
       </c>
       <c r="AB4">
         <v>1.57</v>
@@ -1729,13 +1729,13 @@
         <v>2.35</v>
       </c>
       <c r="AD4">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="AE4">
         <v>1.5</v>
       </c>
       <c r="AF4">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG4">
         <v>2.51</v>
@@ -1791,13 +1791,13 @@
         <v>301</v>
       </c>
       <c r="L5">
-        <v>3.05</v>
+        <v>2.87</v>
       </c>
       <c r="M5">
-        <v>4</v>
+        <v>3.56</v>
       </c>
       <c r="N5">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="O5">
         <v>2.3</v>
@@ -1907,13 +1907,13 @@
         <v>301</v>
       </c>
       <c r="L6">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="M6">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="N6">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="O6">
         <v>1.33</v>
@@ -1931,16 +1931,16 @@
         <v>3.3</v>
       </c>
       <c r="T6">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="U6">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="V6">
         <v>5</v>
       </c>
       <c r="W6">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="X6">
         <v>1.01</v>
@@ -1958,13 +1958,13 @@
         <v>1.57</v>
       </c>
       <c r="AC6">
+        <v>2.26</v>
+      </c>
+      <c r="AD6">
         <v>2.3</v>
       </c>
-      <c r="AD6">
-        <v>2.28</v>
-      </c>
       <c r="AE6">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AF6">
         <v>1.67</v>
@@ -1976,7 +1976,7 @@
         <v>4</v>
       </c>
       <c r="AI6">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AJ6" t="s">
         <v>303</v>
@@ -2023,76 +2023,76 @@
         <v>301</v>
       </c>
       <c r="L7">
-        <v>2.4</v>
+        <v>2.74</v>
       </c>
       <c r="M7">
-        <v>3.26</v>
+        <v>3.41</v>
       </c>
       <c r="N7">
-        <v>2.52</v>
+        <v>2.16</v>
       </c>
       <c r="O7">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="P7">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="Q7">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="R7">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="S7">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="T7">
+        <v>2.45</v>
+      </c>
+      <c r="U7">
+        <v>1.48</v>
+      </c>
+      <c r="V7">
+        <v>6</v>
+      </c>
+      <c r="W7">
+        <v>1.12</v>
+      </c>
+      <c r="X7">
+        <v>1.05</v>
+      </c>
+      <c r="Y7">
+        <v>9.5</v>
+      </c>
+      <c r="Z7">
+        <v>1.25</v>
+      </c>
+      <c r="AA7">
+        <v>3.95</v>
+      </c>
+      <c r="AB7">
+        <v>1.65</v>
+      </c>
+      <c r="AC7">
+        <v>2</v>
+      </c>
+      <c r="AD7">
         <v>2.8</v>
       </c>
-      <c r="U7">
-        <v>1.38</v>
-      </c>
-      <c r="V7">
-        <v>7</v>
-      </c>
-      <c r="W7">
-        <v>1.08</v>
-      </c>
-      <c r="X7">
-        <v>1.06</v>
-      </c>
-      <c r="Y7">
-        <v>8.5</v>
-      </c>
-      <c r="Z7">
-        <v>1.3</v>
-      </c>
-      <c r="AA7">
-        <v>3.35</v>
-      </c>
-      <c r="AB7">
-        <v>1.87</v>
-      </c>
-      <c r="AC7">
-        <v>1.83</v>
-      </c>
-      <c r="AD7">
-        <v>3.4</v>
-      </c>
       <c r="AE7">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="AF7">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AG7">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AH7">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="AI7">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AJ7" t="s">
         <v>303</v>
@@ -2139,76 +2139,76 @@
         <v>301</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AJ8" t="s">
         <v>303</v>
@@ -2255,40 +2255,40 @@
         <v>301</v>
       </c>
       <c r="L9">
-        <v>3.74</v>
+        <v>1.83</v>
       </c>
       <c r="M9">
-        <v>3.5</v>
+        <v>3.11</v>
       </c>
       <c r="N9">
-        <v>1.77</v>
+        <v>3.97</v>
       </c>
       <c r="O9">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="P9">
-        <v>13.75</v>
+        <v>12</v>
       </c>
       <c r="Q9">
-        <v>1.67</v>
+        <v>2.31</v>
       </c>
       <c r="R9">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="S9">
-        <v>3.3</v>
+        <v>3.01</v>
       </c>
       <c r="T9">
-        <v>2.45</v>
+        <v>2.84</v>
       </c>
       <c r="U9">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="V9">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="W9">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="X9">
         <v>1.01</v>
@@ -2297,34 +2297,34 @@
         <v>11</v>
       </c>
       <c r="Z9">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AA9">
-        <v>4.05</v>
+        <v>3.6</v>
       </c>
       <c r="AB9">
-        <v>1.65</v>
+        <v>1.87</v>
       </c>
       <c r="AC9">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AD9">
-        <v>2.69</v>
+        <v>3.2</v>
       </c>
       <c r="AE9">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AF9">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG9">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AH9">
-        <v>5.15</v>
+        <v>6.5</v>
       </c>
       <c r="AI9">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AJ9" t="s">
         <v>303</v>
@@ -2344,7 +2344,7 @@
         <v>43</v>
       </c>
       <c r="C10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D10" t="s">
         <v>94</v>
@@ -2460,7 +2460,7 @@
         <v>43</v>
       </c>
       <c r="C11" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D11" t="s">
         <v>94</v>
@@ -2487,76 +2487,76 @@
         <v>301</v>
       </c>
       <c r="L11">
-        <v>2.74</v>
+        <v>1.41</v>
       </c>
       <c r="M11">
-        <v>3.41</v>
+        <v>3.82</v>
       </c>
       <c r="N11">
-        <v>2.16</v>
+        <v>5.93</v>
       </c>
       <c r="O11">
-        <v>2.1</v>
+        <v>1.38</v>
       </c>
       <c r="P11">
-        <v>9.5</v>
+        <v>8.9</v>
       </c>
       <c r="Q11">
-        <v>1.9</v>
+        <v>3.58</v>
       </c>
       <c r="R11">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S11">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="T11">
-        <v>2.45</v>
+        <v>2.68</v>
       </c>
       <c r="U11">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="V11">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="W11">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X11">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>9.5</v>
+        <v>8.9</v>
       </c>
       <c r="Z11">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AA11">
-        <v>3.95</v>
+        <v>3.4</v>
       </c>
       <c r="AB11">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AC11">
+        <v>1.85</v>
+      </c>
+      <c r="AD11">
+        <v>2.97</v>
+      </c>
+      <c r="AE11">
+        <v>1.3</v>
+      </c>
+      <c r="AF11">
         <v>2</v>
       </c>
-      <c r="AD11">
-        <v>2.8</v>
-      </c>
-      <c r="AE11">
-        <v>1.42</v>
-      </c>
-      <c r="AF11">
-        <v>1.55</v>
-      </c>
       <c r="AG11">
-        <v>2.25</v>
+        <v>1.73</v>
       </c>
       <c r="AH11">
-        <v>5</v>
+        <v>5.55</v>
       </c>
       <c r="AI11">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AJ11" t="s">
         <v>303</v>
@@ -2576,7 +2576,7 @@
         <v>43</v>
       </c>
       <c r="C12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D12" t="s">
         <v>94</v>
@@ -2603,73 +2603,73 @@
         <v>301</v>
       </c>
       <c r="L12">
-        <v>2.29</v>
+        <v>3.74</v>
       </c>
       <c r="M12">
-        <v>3.12</v>
+        <v>3.5</v>
       </c>
       <c r="N12">
-        <v>2.75</v>
+        <v>1.77</v>
       </c>
       <c r="O12">
+        <v>2.25</v>
+      </c>
+      <c r="P12">
+        <v>13.75</v>
+      </c>
+      <c r="Q12">
+        <v>1.67</v>
+      </c>
+      <c r="R12">
+        <v>1.3</v>
+      </c>
+      <c r="S12">
+        <v>3.3</v>
+      </c>
+      <c r="T12">
+        <v>2.45</v>
+      </c>
+      <c r="U12">
+        <v>1.5</v>
+      </c>
+      <c r="V12">
+        <v>6</v>
+      </c>
+      <c r="W12">
+        <v>1.12</v>
+      </c>
+      <c r="X12">
+        <v>1.01</v>
+      </c>
+      <c r="Y12">
+        <v>11</v>
+      </c>
+      <c r="Z12">
+        <v>1.16</v>
+      </c>
+      <c r="AA12">
+        <v>4.05</v>
+      </c>
+      <c r="AB12">
+        <v>1.65</v>
+      </c>
+      <c r="AC12">
         <v>2</v>
       </c>
-      <c r="P12">
-        <v>8</v>
-      </c>
-      <c r="Q12">
-        <v>2.1</v>
-      </c>
-      <c r="R12">
-        <v>1.42</v>
-      </c>
-      <c r="S12">
-        <v>2.65</v>
-      </c>
-      <c r="T12">
-        <v>2.88</v>
-      </c>
-      <c r="U12">
+      <c r="AD12">
+        <v>2.69</v>
+      </c>
+      <c r="AE12">
         <v>1.36</v>
       </c>
-      <c r="V12">
-        <v>7</v>
-      </c>
-      <c r="W12">
-        <v>1.08</v>
-      </c>
-      <c r="X12">
-        <v>1.07</v>
-      </c>
-      <c r="Y12">
-        <v>8</v>
-      </c>
-      <c r="Z12">
-        <v>1.33</v>
-      </c>
-      <c r="AA12">
-        <v>3.25</v>
-      </c>
-      <c r="AB12">
-        <v>1.93</v>
-      </c>
-      <c r="AC12">
-        <v>1.77</v>
-      </c>
-      <c r="AD12">
-        <v>3.45</v>
-      </c>
-      <c r="AE12">
-        <v>1.3</v>
-      </c>
       <c r="AF12">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AG12">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AH12">
-        <v>6.5</v>
+        <v>5.15</v>
       </c>
       <c r="AI12">
         <v>1.1</v>
@@ -2719,76 +2719,76 @@
         <v>301</v>
       </c>
       <c r="L13">
-        <v>3.41</v>
+        <v>1.74</v>
       </c>
       <c r="M13">
-        <v>3.32</v>
+        <v>3.28</v>
       </c>
       <c r="N13">
-        <v>1.9</v>
+        <v>4.2</v>
       </c>
       <c r="O13">
-        <v>2.42</v>
+        <v>1.53</v>
       </c>
       <c r="P13">
-        <v>7.1</v>
+        <v>6.75</v>
       </c>
       <c r="Q13">
-        <v>1.78</v>
+        <v>3.18</v>
       </c>
       <c r="R13">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="S13">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="T13">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="U13">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="V13">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W13">
+        <v>1.02</v>
+      </c>
+      <c r="X13">
         <v>1.05</v>
       </c>
-      <c r="X13">
-        <v>1.04</v>
-      </c>
       <c r="Y13">
-        <v>7.1</v>
+        <v>8</v>
       </c>
       <c r="Z13">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AA13">
-        <v>2.52</v>
+        <v>2.75</v>
       </c>
       <c r="AB13">
+        <v>2.3</v>
+      </c>
+      <c r="AC13">
+        <v>1.5</v>
+      </c>
+      <c r="AD13">
+        <v>4.8</v>
+      </c>
+      <c r="AE13">
+        <v>1.14</v>
+      </c>
+      <c r="AF13">
         <v>2.2</v>
       </c>
-      <c r="AC13">
-        <v>1.53</v>
-      </c>
-      <c r="AD13">
-        <v>4.3</v>
-      </c>
-      <c r="AE13">
-        <v>1.15</v>
-      </c>
-      <c r="AF13">
-        <v>2.05</v>
-      </c>
       <c r="AG13">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AH13">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AI13">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AJ13" t="s">
         <v>303</v>
@@ -2808,7 +2808,7 @@
         <v>43</v>
       </c>
       <c r="C14" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D14" t="s">
         <v>94</v>
@@ -2835,34 +2835,34 @@
         <v>301</v>
       </c>
       <c r="L14">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="M14">
-        <v>3.03</v>
+        <v>3.26</v>
       </c>
       <c r="N14">
-        <v>2.79</v>
+        <v>2.52</v>
       </c>
       <c r="O14">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="P14">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="Q14">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="R14">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S14">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="T14">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="U14">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="V14">
         <v>7</v>
@@ -2871,40 +2871,40 @@
         <v>1.08</v>
       </c>
       <c r="X14">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y14">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="Z14">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AA14">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="AB14">
+        <v>1.87</v>
+      </c>
+      <c r="AC14">
+        <v>1.83</v>
+      </c>
+      <c r="AD14">
+        <v>3.4</v>
+      </c>
+      <c r="AE14">
+        <v>1.3</v>
+      </c>
+      <c r="AF14">
+        <v>1.7</v>
+      </c>
+      <c r="AG14">
         <v>2</v>
       </c>
-      <c r="AC14">
-        <v>1.65</v>
-      </c>
-      <c r="AD14">
-        <v>3.8</v>
-      </c>
-      <c r="AE14">
-        <v>1.25</v>
-      </c>
-      <c r="AF14">
-        <v>1.77</v>
-      </c>
-      <c r="AG14">
-        <v>1.9</v>
-      </c>
       <c r="AH14">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="AI14">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AJ14" t="s">
         <v>303</v>
@@ -2924,7 +2924,7 @@
         <v>43</v>
       </c>
       <c r="C15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D15" t="s">
         <v>94</v>
@@ -2951,76 +2951,76 @@
         <v>301</v>
       </c>
       <c r="L15">
-        <v>1.74</v>
+        <v>2.32</v>
       </c>
       <c r="M15">
-        <v>3.28</v>
+        <v>3.03</v>
       </c>
       <c r="N15">
-        <v>4.2</v>
+        <v>2.79</v>
       </c>
       <c r="O15">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="P15">
-        <v>6.75</v>
+        <v>8</v>
       </c>
       <c r="Q15">
-        <v>3.18</v>
+        <v>2.25</v>
       </c>
       <c r="R15">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="S15">
-        <v>2.56</v>
+        <v>2.65</v>
       </c>
       <c r="T15">
-        <v>3.34</v>
+        <v>2.88</v>
       </c>
       <c r="U15">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="V15">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="W15">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X15">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y15">
         <v>8</v>
       </c>
       <c r="Z15">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AA15">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AB15">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AC15">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AD15">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="AE15">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AF15">
-        <v>2.2</v>
+        <v>1.77</v>
       </c>
       <c r="AG15">
-        <v>1.62</v>
+        <v>1.9</v>
       </c>
       <c r="AH15">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="AI15">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AJ15" t="s">
         <v>303</v>
@@ -3067,76 +3067,76 @@
         <v>301</v>
       </c>
       <c r="L16">
-        <v>1.83</v>
+        <v>3.41</v>
       </c>
       <c r="M16">
-        <v>3.11</v>
+        <v>3.32</v>
       </c>
       <c r="N16">
-        <v>3.97</v>
+        <v>1.9</v>
       </c>
       <c r="O16">
-        <v>1.67</v>
+        <v>2.42</v>
       </c>
       <c r="P16">
-        <v>12</v>
+        <v>7.1</v>
       </c>
       <c r="Q16">
-        <v>2.31</v>
+        <v>1.78</v>
       </c>
       <c r="R16">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="S16">
-        <v>3.01</v>
+        <v>2.62</v>
       </c>
       <c r="T16">
-        <v>2.84</v>
+        <v>3.25</v>
       </c>
       <c r="U16">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="V16">
-        <v>6.5</v>
+        <v>10</v>
       </c>
       <c r="W16">
         <v>1.05</v>
       </c>
       <c r="X16">
+        <v>1.04</v>
+      </c>
+      <c r="Y16">
+        <v>7.1</v>
+      </c>
+      <c r="Z16">
+        <v>1.41</v>
+      </c>
+      <c r="AA16">
+        <v>2.52</v>
+      </c>
+      <c r="AB16">
+        <v>2.2</v>
+      </c>
+      <c r="AC16">
+        <v>1.53</v>
+      </c>
+      <c r="AD16">
+        <v>4.3</v>
+      </c>
+      <c r="AE16">
+        <v>1.15</v>
+      </c>
+      <c r="AF16">
+        <v>2.05</v>
+      </c>
+      <c r="AG16">
+        <v>1.73</v>
+      </c>
+      <c r="AH16">
+        <v>8.4</v>
+      </c>
+      <c r="AI16">
         <v>1.01</v>
-      </c>
-      <c r="Y16">
-        <v>11</v>
-      </c>
-      <c r="Z16">
-        <v>1.25</v>
-      </c>
-      <c r="AA16">
-        <v>3.6</v>
-      </c>
-      <c r="AB16">
-        <v>1.87</v>
-      </c>
-      <c r="AC16">
-        <v>1.83</v>
-      </c>
-      <c r="AD16">
-        <v>3.2</v>
-      </c>
-      <c r="AE16">
-        <v>1.3</v>
-      </c>
-      <c r="AF16">
-        <v>1.67</v>
-      </c>
-      <c r="AG16">
-        <v>2.1</v>
-      </c>
-      <c r="AH16">
-        <v>6.5</v>
-      </c>
-      <c r="AI16">
-        <v>1.08</v>
       </c>
       <c r="AJ16" t="s">
         <v>303</v>
@@ -3156,7 +3156,7 @@
         <v>44</v>
       </c>
       <c r="C17" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D17" t="s">
         <v>94</v>
@@ -3183,76 +3183,76 @@
         <v>301</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="M17">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH17">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AI17">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AJ17" t="s">
         <v>303</v>
@@ -3272,7 +3272,7 @@
         <v>44</v>
       </c>
       <c r="C18" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D18" t="s">
         <v>94</v>
@@ -3299,76 +3299,76 @@
         <v>301</v>
       </c>
       <c r="L18">
-        <v>3.1</v>
+        <v>1.75</v>
       </c>
       <c r="M18">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="N18">
-        <v>2.09</v>
+        <v>4.5</v>
       </c>
       <c r="O18">
-        <v>2.4</v>
+        <v>1.53</v>
       </c>
       <c r="P18">
-        <v>18.75</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q18">
-        <v>1.57</v>
+        <v>2.88</v>
       </c>
       <c r="R18">
+        <v>1.42</v>
+      </c>
+      <c r="S18">
+        <v>2.62</v>
+      </c>
+      <c r="T18">
+        <v>3</v>
+      </c>
+      <c r="U18">
+        <v>1.33</v>
+      </c>
+      <c r="V18">
+        <v>7.5</v>
+      </c>
+      <c r="W18">
+        <v>1.06</v>
+      </c>
+      <c r="X18">
+        <v>1.05</v>
+      </c>
+      <c r="Y18">
+        <v>8</v>
+      </c>
+      <c r="Z18">
+        <v>1.36</v>
+      </c>
+      <c r="AA18">
+        <v>2.9</v>
+      </c>
+      <c r="AB18">
+        <v>2.1</v>
+      </c>
+      <c r="AC18">
+        <v>1.65</v>
+      </c>
+      <c r="AD18">
+        <v>3.6</v>
+      </c>
+      <c r="AE18">
         <v>1.25</v>
       </c>
-      <c r="S18">
-        <v>3.75</v>
-      </c>
-      <c r="T18">
-        <v>2.25</v>
-      </c>
-      <c r="U18">
-        <v>1.57</v>
-      </c>
-      <c r="V18">
-        <v>5.5</v>
-      </c>
-      <c r="W18">
-        <v>1.14</v>
-      </c>
-      <c r="X18">
-        <v>1.01</v>
-      </c>
-      <c r="Y18">
-        <v>13</v>
-      </c>
-      <c r="Z18">
-        <v>1.1</v>
-      </c>
-      <c r="AA18">
-        <v>5</v>
-      </c>
-      <c r="AB18">
-        <v>1.58</v>
-      </c>
-      <c r="AC18">
-        <v>2.4</v>
-      </c>
-      <c r="AD18">
-        <v>2.35</v>
-      </c>
-      <c r="AE18">
-        <v>1.57</v>
-      </c>
       <c r="AF18">
-        <v>1.53</v>
+        <v>2</v>
       </c>
       <c r="AG18">
-        <v>2.38</v>
+        <v>1.73</v>
       </c>
       <c r="AH18">
-        <v>4.05</v>
+        <v>7</v>
       </c>
       <c r="AI18">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="AJ18" t="s">
         <v>303</v>
@@ -3388,7 +3388,7 @@
         <v>44</v>
       </c>
       <c r="C19" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D19" t="s">
         <v>94</v>
@@ -3415,76 +3415,76 @@
         <v>301</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>18.75</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH19">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AI19">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AJ19" t="s">
         <v>303</v>
@@ -3504,7 +3504,7 @@
         <v>45</v>
       </c>
       <c r="C20" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D20" t="s">
         <v>94</v>
@@ -3531,76 +3531,76 @@
         <v>301</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M20">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH20">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AI20">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AJ20" t="s">
         <v>303</v>
@@ -3852,7 +3852,7 @@
         <v>47</v>
       </c>
       <c r="C23" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D23" t="s">
         <v>94</v>
@@ -3879,76 +3879,76 @@
         <v>301</v>
       </c>
       <c r="L23">
-        <v>2.88</v>
+        <v>1.45</v>
       </c>
       <c r="M23">
-        <v>3.11</v>
+        <v>4.8</v>
       </c>
       <c r="N23">
-        <v>2.22</v>
+        <v>5.8</v>
       </c>
       <c r="O23">
-        <v>2.15</v>
+        <v>1.33</v>
       </c>
       <c r="P23">
-        <v>8.5</v>
+        <v>22</v>
       </c>
       <c r="Q23">
-        <v>1.93</v>
+        <v>3.25</v>
       </c>
       <c r="R23">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="S23">
-        <v>2.7</v>
+        <v>4</v>
       </c>
       <c r="T23">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="U23">
-        <v>1.38</v>
+        <v>1.67</v>
       </c>
       <c r="V23">
-        <v>7.3</v>
+        <v>4.5</v>
       </c>
       <c r="W23">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="X23">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>8.5</v>
+        <v>17</v>
       </c>
       <c r="Z23">
-        <v>1.3</v>
+        <v>1.08</v>
       </c>
       <c r="AA23">
-        <v>3.45</v>
+        <v>5.55</v>
       </c>
       <c r="AB23">
-        <v>1.89</v>
+        <v>1.48</v>
       </c>
       <c r="AC23">
-        <v>1.81</v>
+        <v>2.6</v>
       </c>
       <c r="AD23">
-        <v>3.2</v>
+        <v>2.21</v>
       </c>
       <c r="AE23">
-        <v>1.33</v>
+        <v>1.66</v>
       </c>
       <c r="AF23">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG23">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AH23">
-        <v>6.25</v>
+        <v>3.44</v>
       </c>
       <c r="AI23">
-        <v>1.11</v>
+        <v>1.23</v>
       </c>
       <c r="AJ23" t="s">
         <v>303</v>
@@ -3968,7 +3968,7 @@
         <v>47</v>
       </c>
       <c r="C24" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D24" t="s">
         <v>94</v>
@@ -3995,76 +3995,76 @@
         <v>301</v>
       </c>
       <c r="L24">
-        <v>1.45</v>
+        <v>2.88</v>
       </c>
       <c r="M24">
-        <v>4.8</v>
+        <v>3.11</v>
       </c>
       <c r="N24">
-        <v>5.8</v>
+        <v>2.22</v>
       </c>
       <c r="O24">
+        <v>2.15</v>
+      </c>
+      <c r="P24">
+        <v>8.5</v>
+      </c>
+      <c r="Q24">
+        <v>1.93</v>
+      </c>
+      <c r="R24">
+        <v>1.4</v>
+      </c>
+      <c r="S24">
+        <v>2.7</v>
+      </c>
+      <c r="T24">
+        <v>2.8</v>
+      </c>
+      <c r="U24">
+        <v>1.38</v>
+      </c>
+      <c r="V24">
+        <v>7.3</v>
+      </c>
+      <c r="W24">
+        <v>1.03</v>
+      </c>
+      <c r="X24">
+        <v>1.06</v>
+      </c>
+      <c r="Y24">
+        <v>8.5</v>
+      </c>
+      <c r="Z24">
+        <v>1.3</v>
+      </c>
+      <c r="AA24">
+        <v>3.45</v>
+      </c>
+      <c r="AB24">
+        <v>1.89</v>
+      </c>
+      <c r="AC24">
+        <v>1.81</v>
+      </c>
+      <c r="AD24">
+        <v>3.2</v>
+      </c>
+      <c r="AE24">
         <v>1.33</v>
       </c>
-      <c r="P24">
-        <v>22</v>
-      </c>
-      <c r="Q24">
-        <v>3.25</v>
-      </c>
-      <c r="R24">
-        <v>1.22</v>
-      </c>
-      <c r="S24">
-        <v>4</v>
-      </c>
-      <c r="T24">
-        <v>2.1</v>
-      </c>
-      <c r="U24">
-        <v>1.67</v>
-      </c>
-      <c r="V24">
-        <v>4.5</v>
-      </c>
-      <c r="W24">
-        <v>1.18</v>
-      </c>
-      <c r="X24">
-        <v>1.01</v>
-      </c>
-      <c r="Y24">
-        <v>17</v>
-      </c>
-      <c r="Z24">
-        <v>1.08</v>
-      </c>
-      <c r="AA24">
-        <v>5.55</v>
-      </c>
-      <c r="AB24">
-        <v>1.48</v>
-      </c>
-      <c r="AC24">
-        <v>2.6</v>
-      </c>
-      <c r="AD24">
-        <v>2.21</v>
-      </c>
-      <c r="AE24">
-        <v>1.66</v>
-      </c>
       <c r="AF24">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG24">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AH24">
-        <v>3.44</v>
+        <v>6.25</v>
       </c>
       <c r="AI24">
-        <v>1.23</v>
+        <v>1.11</v>
       </c>
       <c r="AJ24" t="s">
         <v>303</v>
@@ -4200,7 +4200,7 @@
         <v>48</v>
       </c>
       <c r="C26" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D26" t="s">
         <v>94</v>
@@ -4227,76 +4227,76 @@
         <v>301</v>
       </c>
       <c r="L26">
-        <v>2.73</v>
+        <v>5.9</v>
       </c>
       <c r="M26">
-        <v>3.29</v>
+        <v>4.2</v>
       </c>
       <c r="N26">
-        <v>2.23</v>
+        <v>1.4</v>
       </c>
       <c r="O26">
-        <v>2.2</v>
+        <v>3.35</v>
       </c>
       <c r="P26">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q26">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="R26">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S26">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T26">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="U26">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="V26">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="W26">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X26">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y26">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z26">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AA26">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="AB26">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AC26">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AD26">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="AE26">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AF26">
-        <v>1.57</v>
+        <v>1.77</v>
       </c>
       <c r="AG26">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="AH26">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="AI26">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AJ26" t="s">
         <v>303</v>
@@ -4316,7 +4316,7 @@
         <v>48</v>
       </c>
       <c r="C27" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D27" t="s">
         <v>94</v>
@@ -4343,76 +4343,76 @@
         <v>301</v>
       </c>
       <c r="L27">
-        <v>5.9</v>
+        <v>2.73</v>
       </c>
       <c r="M27">
-        <v>4.2</v>
+        <v>3.29</v>
       </c>
       <c r="N27">
-        <v>1.4</v>
+        <v>2.23</v>
       </c>
       <c r="O27">
-        <v>3.35</v>
+        <v>2.2</v>
       </c>
       <c r="P27">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q27">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="R27">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S27">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T27">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="U27">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="V27">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="W27">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X27">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y27">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Z27">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AA27">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="AB27">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AC27">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AD27">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="AE27">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AF27">
-        <v>1.77</v>
+        <v>1.57</v>
       </c>
       <c r="AG27">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="AH27">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="AI27">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AJ27" t="s">
         <v>303</v>
@@ -4432,7 +4432,7 @@
         <v>48</v>
       </c>
       <c r="C28" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D28" t="s">
         <v>94</v>
@@ -4459,76 +4459,76 @@
         <v>301</v>
       </c>
       <c r="L28">
-        <v>2.09</v>
+        <v>1.88</v>
       </c>
       <c r="M28">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="N28">
-        <v>2.98</v>
+        <v>4.52</v>
       </c>
       <c r="O28">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="P28">
-        <v>10.5</v>
+        <v>6.7</v>
       </c>
       <c r="Q28">
-        <v>2.3</v>
+        <v>2.89</v>
       </c>
       <c r="R28">
-        <v>1.33</v>
+        <v>1.49</v>
       </c>
       <c r="S28">
-        <v>3.25</v>
+        <v>2.4</v>
       </c>
       <c r="T28">
-        <v>2.63</v>
+        <v>3.14</v>
       </c>
       <c r="U28">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="V28">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="W28">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="X28">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y28">
-        <v>11</v>
+        <v>7.5</v>
       </c>
       <c r="Z28">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="AA28">
-        <v>3.64</v>
+        <v>2.8</v>
       </c>
       <c r="AB28">
-        <v>1.77</v>
+        <v>2.2</v>
       </c>
       <c r="AC28">
-        <v>1.93</v>
+        <v>1.62</v>
       </c>
       <c r="AD28">
-        <v>2.88</v>
+        <v>3.74</v>
       </c>
       <c r="AE28">
-        <v>1.34</v>
+        <v>1.19</v>
       </c>
       <c r="AF28">
-        <v>1.67</v>
+        <v>1.97</v>
       </c>
       <c r="AG28">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="AH28">
-        <v>5.3</v>
+        <v>8</v>
       </c>
       <c r="AI28">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="AJ28" t="s">
         <v>303</v>
@@ -4575,76 +4575,76 @@
         <v>301</v>
       </c>
       <c r="L29">
-        <v>1.88</v>
+        <v>1.18</v>
       </c>
       <c r="M29">
-        <v>3.22</v>
+        <v>5</v>
       </c>
       <c r="N29">
-        <v>4.52</v>
+        <v>13</v>
       </c>
       <c r="O29">
-        <v>1.61</v>
+        <v>1.23</v>
       </c>
       <c r="P29">
-        <v>6.7</v>
+        <v>7.9</v>
       </c>
       <c r="Q29">
-        <v>2.89</v>
+        <v>5.65</v>
       </c>
       <c r="R29">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="S29">
-        <v>2.4</v>
+        <v>2.76</v>
       </c>
       <c r="T29">
-        <v>3.14</v>
+        <v>2.6</v>
       </c>
       <c r="U29">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="V29">
-        <v>8.5</v>
+        <v>6.05</v>
       </c>
       <c r="W29">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X29">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="Z29">
-        <v>1.38</v>
+        <v>1.24</v>
       </c>
       <c r="AA29">
-        <v>2.7</v>
+        <v>3.34</v>
       </c>
       <c r="AB29">
-        <v>2.22</v>
+        <v>1.8</v>
       </c>
       <c r="AC29">
-        <v>1.63</v>
+        <v>1.91</v>
       </c>
       <c r="AD29">
-        <v>3.8</v>
+        <v>2.83</v>
       </c>
       <c r="AE29">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="AF29">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AG29">
-        <v>1.73</v>
+        <v>1.48</v>
       </c>
       <c r="AH29">
-        <v>8</v>
+        <v>5.5</v>
       </c>
       <c r="AI29">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AJ29" t="s">
         <v>303</v>
@@ -4664,7 +4664,7 @@
         <v>48</v>
       </c>
       <c r="C30" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D30" t="s">
         <v>94</v>
@@ -4691,76 +4691,76 @@
         <v>301</v>
       </c>
       <c r="L30">
-        <v>2.57</v>
+        <v>2.09</v>
       </c>
       <c r="M30">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="N30">
-        <v>2.34</v>
+        <v>2.98</v>
       </c>
       <c r="O30">
-        <v>2.05</v>
+        <v>1.67</v>
       </c>
       <c r="P30">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Q30">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="R30">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S30">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="T30">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="U30">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="V30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W30">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X30">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z30">
         <v>1.22</v>
       </c>
       <c r="AA30">
-        <v>4.33</v>
+        <v>3.64</v>
       </c>
       <c r="AB30">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="AC30">
+        <v>1.93</v>
+      </c>
+      <c r="AD30">
+        <v>2.88</v>
+      </c>
+      <c r="AE30">
+        <v>1.34</v>
+      </c>
+      <c r="AF30">
+        <v>1.67</v>
+      </c>
+      <c r="AG30">
         <v>2.1</v>
       </c>
-      <c r="AD30">
-        <v>2.26</v>
-      </c>
-      <c r="AE30">
-        <v>1.51</v>
-      </c>
-      <c r="AF30">
-        <v>1.57</v>
-      </c>
-      <c r="AG30">
-        <v>2.25</v>
-      </c>
       <c r="AH30">
-        <v>4.75</v>
+        <v>5.3</v>
       </c>
       <c r="AI30">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AJ30" t="s">
         <v>303</v>
@@ -4780,7 +4780,7 @@
         <v>48</v>
       </c>
       <c r="C31" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D31" t="s">
         <v>94</v>
@@ -4807,76 +4807,76 @@
         <v>301</v>
       </c>
       <c r="L31">
+        <v>2.57</v>
+      </c>
+      <c r="M31">
+        <v>3.3</v>
+      </c>
+      <c r="N31">
+        <v>2.34</v>
+      </c>
+      <c r="O31">
+        <v>2.05</v>
+      </c>
+      <c r="P31">
+        <v>10</v>
+      </c>
+      <c r="Q31">
+        <v>1.8</v>
+      </c>
+      <c r="R31">
         <v>1.3</v>
       </c>
-      <c r="M31">
-        <v>4.52</v>
-      </c>
-      <c r="N31">
-        <v>14</v>
-      </c>
-      <c r="O31">
-        <v>1.23</v>
-      </c>
-      <c r="P31">
-        <v>7.9</v>
-      </c>
-      <c r="Q31">
-        <v>5.65</v>
-      </c>
-      <c r="R31">
-        <v>1.36</v>
-      </c>
       <c r="S31">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="T31">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="U31">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="V31">
-        <v>6.3</v>
+        <v>6</v>
       </c>
       <c r="W31">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="X31">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y31">
         <v>10</v>
       </c>
       <c r="Z31">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AA31">
-        <v>3.4</v>
+        <v>4.33</v>
       </c>
       <c r="AB31">
-        <v>1.93</v>
+        <v>1.65</v>
       </c>
       <c r="AC31">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AD31">
-        <v>2.97</v>
+        <v>2.26</v>
       </c>
       <c r="AE31">
-        <v>1.3</v>
+        <v>1.51</v>
       </c>
       <c r="AF31">
-        <v>2.5</v>
+        <v>1.57</v>
       </c>
       <c r="AG31">
-        <v>1.48</v>
+        <v>2.25</v>
       </c>
       <c r="AH31">
-        <v>5.75</v>
+        <v>4.75</v>
       </c>
       <c r="AI31">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="AJ31" t="s">
         <v>303</v>
@@ -4896,7 +4896,7 @@
         <v>49</v>
       </c>
       <c r="C32" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D32" t="s">
         <v>94</v>
@@ -4923,76 +4923,76 @@
         <v>301</v>
       </c>
       <c r="L32">
-        <v>1.47</v>
+        <v>2.81</v>
       </c>
       <c r="M32">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="N32">
-        <v>4.9</v>
+        <v>2.33</v>
       </c>
       <c r="O32">
-        <v>1.39</v>
+        <v>2.3</v>
       </c>
       <c r="P32">
-        <v>25</v>
+        <v>13.75</v>
       </c>
       <c r="Q32">
-        <v>3</v>
+        <v>1.67</v>
       </c>
       <c r="R32">
-        <v>1.16</v>
+        <v>1.31</v>
       </c>
       <c r="S32">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="T32">
-        <v>2.03</v>
+        <v>2.45</v>
       </c>
       <c r="U32">
-        <v>1.7</v>
+        <v>1.43</v>
       </c>
       <c r="V32">
-        <v>4.4</v>
+        <v>5.75</v>
       </c>
       <c r="W32">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X32">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y32">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="Z32">
-        <v>1.06</v>
+        <v>1.19</v>
       </c>
       <c r="AA32">
-        <v>6.25</v>
+        <v>3.8</v>
       </c>
       <c r="AB32">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="AC32">
+        <v>2.06</v>
+      </c>
+      <c r="AD32">
+        <v>2.78</v>
+      </c>
+      <c r="AE32">
+        <v>1.38</v>
+      </c>
+      <c r="AF32">
+        <v>1.63</v>
+      </c>
+      <c r="AG32">
         <v>2.2</v>
       </c>
-      <c r="AD32">
-        <v>2.22</v>
-      </c>
-      <c r="AE32">
-        <v>1.66</v>
-      </c>
-      <c r="AF32">
-        <v>1.51</v>
-      </c>
-      <c r="AG32">
-        <v>2.39</v>
-      </c>
       <c r="AH32">
-        <v>3.25</v>
+        <v>5</v>
       </c>
       <c r="AI32">
-        <v>1.27</v>
+        <v>1.13</v>
       </c>
       <c r="AJ32" t="s">
         <v>303</v>
@@ -5012,7 +5012,7 @@
         <v>49</v>
       </c>
       <c r="C33" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D33" t="s">
         <v>94</v>
@@ -5039,76 +5039,76 @@
         <v>301</v>
       </c>
       <c r="L33">
+        <v>1.47</v>
+      </c>
+      <c r="M33">
+        <v>4.2</v>
+      </c>
+      <c r="N33">
+        <v>4.9</v>
+      </c>
+      <c r="O33">
+        <v>1.39</v>
+      </c>
+      <c r="P33">
+        <v>25</v>
+      </c>
+      <c r="Q33">
         <v>3</v>
       </c>
-      <c r="M33">
-        <v>3.65</v>
-      </c>
-      <c r="N33">
-        <v>2.12</v>
-      </c>
-      <c r="O33">
-        <v>2.3</v>
-      </c>
-      <c r="P33">
-        <v>13.75</v>
-      </c>
-      <c r="Q33">
-        <v>1.67</v>
-      </c>
       <c r="R33">
-        <v>1.31</v>
+        <v>1.16</v>
       </c>
       <c r="S33">
-        <v>2.9</v>
+        <v>4.1</v>
       </c>
       <c r="T33">
-        <v>2.45</v>
+        <v>2.03</v>
       </c>
       <c r="U33">
-        <v>1.46</v>
+        <v>1.7</v>
       </c>
       <c r="V33">
-        <v>5.75</v>
+        <v>4.4</v>
       </c>
       <c r="W33">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X33">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="Z33">
-        <v>1.19</v>
+        <v>1.06</v>
       </c>
       <c r="AA33">
-        <v>3.75</v>
+        <v>6.25</v>
       </c>
       <c r="AB33">
-        <v>1.76</v>
+        <v>1.55</v>
       </c>
       <c r="AC33">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AD33">
-        <v>2.77</v>
+        <v>2.22</v>
       </c>
       <c r="AE33">
-        <v>1.42</v>
+        <v>1.66</v>
       </c>
       <c r="AF33">
-        <v>1.63</v>
+        <v>1.51</v>
       </c>
       <c r="AG33">
-        <v>2.23</v>
+        <v>2.39</v>
       </c>
       <c r="AH33">
-        <v>5</v>
+        <v>3.25</v>
       </c>
       <c r="AI33">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AJ33" t="s">
         <v>303</v>
@@ -5155,13 +5155,13 @@
         <v>301</v>
       </c>
       <c r="L34">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="M34">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="N34">
-        <v>6.5</v>
+        <v>6.74</v>
       </c>
       <c r="O34">
         <v>1.37</v>
@@ -5176,13 +5176,13 @@
         <v>1.25</v>
       </c>
       <c r="S34">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="T34">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="U34">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="V34">
         <v>4.2</v>
@@ -5194,34 +5194,34 @@
         <v>1.02</v>
       </c>
       <c r="Y34">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Z34">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AA34">
         <v>5</v>
       </c>
       <c r="AB34">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AC34">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="AD34">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AE34">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AF34">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG34">
         <v>2.2</v>
       </c>
       <c r="AH34">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="AI34">
         <v>1.25</v>
@@ -5244,7 +5244,7 @@
         <v>50</v>
       </c>
       <c r="C35" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D35" t="s">
         <v>94</v>
@@ -5271,76 +5271,76 @@
         <v>301</v>
       </c>
       <c r="L35">
-        <v>1.91</v>
+        <v>2.65</v>
       </c>
       <c r="M35">
-        <v>3.22</v>
+        <v>3.32</v>
       </c>
       <c r="N35">
+        <v>2.27</v>
+      </c>
+      <c r="O35">
+        <v>2.05</v>
+      </c>
+      <c r="P35">
+        <v>11</v>
+      </c>
+      <c r="Q35">
+        <v>1.8</v>
+      </c>
+      <c r="R35">
+        <v>1.3</v>
+      </c>
+      <c r="S35">
+        <v>3.4</v>
+      </c>
+      <c r="T35">
+        <v>2.5</v>
+      </c>
+      <c r="U35">
+        <v>1.5</v>
+      </c>
+      <c r="V35">
+        <v>6</v>
+      </c>
+      <c r="W35">
+        <v>1.13</v>
+      </c>
+      <c r="X35">
+        <v>1.04</v>
+      </c>
+      <c r="Y35">
+        <v>11</v>
+      </c>
+      <c r="Z35">
+        <v>1.22</v>
+      </c>
+      <c r="AA35">
         <v>4.33</v>
       </c>
-      <c r="O35">
+      <c r="AB35">
+        <v>1.62</v>
+      </c>
+      <c r="AC35">
+        <v>2.15</v>
+      </c>
+      <c r="AD35">
+        <v>2.15</v>
+      </c>
+      <c r="AE35">
+        <v>1.6</v>
+      </c>
+      <c r="AF35">
         <v>1.57</v>
       </c>
-      <c r="P35">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="Q35">
-        <v>2.74</v>
-      </c>
-      <c r="R35">
-        <v>1.45</v>
-      </c>
-      <c r="S35">
-        <v>2.55</v>
-      </c>
-      <c r="T35">
-        <v>3.04</v>
-      </c>
-      <c r="U35">
-        <v>1.33</v>
-      </c>
-      <c r="V35">
-        <v>8.4</v>
-      </c>
-      <c r="W35">
-        <v>1.01</v>
-      </c>
-      <c r="X35">
-        <v>1.01</v>
-      </c>
-      <c r="Y35">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="Z35">
-        <v>1.28</v>
-      </c>
-      <c r="AA35">
-        <v>3.08</v>
-      </c>
-      <c r="AB35">
-        <v>2.06</v>
-      </c>
-      <c r="AC35">
-        <v>1.73</v>
-      </c>
-      <c r="AD35">
-        <v>3.5</v>
-      </c>
-      <c r="AE35">
-        <v>1.22</v>
-      </c>
-      <c r="AF35">
-        <v>1.85</v>
-      </c>
       <c r="AG35">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="AH35">
-        <v>7.3</v>
+        <v>4.5</v>
       </c>
       <c r="AI35">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="AJ35" t="s">
         <v>303</v>
@@ -5360,7 +5360,7 @@
         <v>50</v>
       </c>
       <c r="C36" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D36" t="s">
         <v>94</v>
@@ -5387,76 +5387,76 @@
         <v>301</v>
       </c>
       <c r="L36">
-        <v>2.65</v>
+        <v>1.91</v>
       </c>
       <c r="M36">
-        <v>3.32</v>
+        <v>3.22</v>
       </c>
       <c r="N36">
-        <v>2.27</v>
+        <v>4.33</v>
       </c>
       <c r="O36">
-        <v>2.05</v>
+        <v>1.57</v>
       </c>
       <c r="P36">
-        <v>11</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q36">
-        <v>1.8</v>
+        <v>2.74</v>
       </c>
       <c r="R36">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="S36">
-        <v>3.4</v>
+        <v>2.58</v>
       </c>
       <c r="T36">
-        <v>2.5</v>
+        <v>2.93</v>
       </c>
       <c r="U36">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="V36">
-        <v>6</v>
+        <v>8.1</v>
       </c>
       <c r="W36">
-        <v>1.13</v>
+        <v>1.02</v>
       </c>
       <c r="X36">
+        <v>1.01</v>
+      </c>
+      <c r="Y36">
+        <v>9</v>
+      </c>
+      <c r="Z36">
+        <v>1.27</v>
+      </c>
+      <c r="AA36">
+        <v>3.14</v>
+      </c>
+      <c r="AB36">
+        <v>1.97</v>
+      </c>
+      <c r="AC36">
+        <v>1.75</v>
+      </c>
+      <c r="AD36">
+        <v>3.34</v>
+      </c>
+      <c r="AE36">
+        <v>1.24</v>
+      </c>
+      <c r="AF36">
+        <v>1.82</v>
+      </c>
+      <c r="AG36">
+        <v>1.94</v>
+      </c>
+      <c r="AH36">
+        <v>6.95</v>
+      </c>
+      <c r="AI36">
         <v>1.04</v>
-      </c>
-      <c r="Y36">
-        <v>11</v>
-      </c>
-      <c r="Z36">
-        <v>1.22</v>
-      </c>
-      <c r="AA36">
-        <v>4.33</v>
-      </c>
-      <c r="AB36">
-        <v>1.62</v>
-      </c>
-      <c r="AC36">
-        <v>2.15</v>
-      </c>
-      <c r="AD36">
-        <v>2.15</v>
-      </c>
-      <c r="AE36">
-        <v>1.6</v>
-      </c>
-      <c r="AF36">
-        <v>1.57</v>
-      </c>
-      <c r="AG36">
-        <v>2.25</v>
-      </c>
-      <c r="AH36">
-        <v>4.5</v>
-      </c>
-      <c r="AI36">
-        <v>1.2</v>
       </c>
       <c r="AJ36" t="s">
         <v>303</v>
@@ -5732,13 +5732,13 @@
         <v>0</v>
       </c>
       <c r="K39" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L39">
         <v>7.65</v>
       </c>
       <c r="M39">
-        <v>6.35</v>
+        <v>6.5</v>
       </c>
       <c r="N39">
         <v>1.26</v>
@@ -5851,76 +5851,76 @@
         <v>301</v>
       </c>
       <c r="L40">
-        <v>2.53</v>
+        <v>2.11</v>
       </c>
       <c r="M40">
-        <v>3.21</v>
+        <v>3</v>
       </c>
       <c r="N40">
-        <v>2.85</v>
+        <v>3.25</v>
       </c>
       <c r="O40">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="P40">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="Q40">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="R40">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="S40">
-        <v>2.63</v>
+        <v>2.76</v>
       </c>
       <c r="T40">
-        <v>3.25</v>
+        <v>2.84</v>
       </c>
       <c r="U40">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="V40">
+        <v>6.5</v>
+      </c>
+      <c r="W40">
+        <v>1.08</v>
+      </c>
+      <c r="X40">
+        <v>1.01</v>
+      </c>
+      <c r="Y40">
         <v>9</v>
       </c>
-      <c r="W40">
-        <v>1.07</v>
-      </c>
-      <c r="X40">
-        <v>1.03</v>
-      </c>
-      <c r="Y40">
-        <v>7.4</v>
-      </c>
       <c r="Z40">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AA40">
-        <v>2.84</v>
+        <v>3.2</v>
       </c>
       <c r="AB40">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AC40">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AD40">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="AE40">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AF40">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AG40">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AH40">
-        <v>7.1</v>
+        <v>6</v>
       </c>
       <c r="AI40">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AJ40" t="s">
         <v>303</v>
@@ -5967,76 +5967,76 @@
         <v>301</v>
       </c>
       <c r="L41">
-        <v>2.05</v>
+        <v>2.53</v>
       </c>
       <c r="M41">
-        <v>3.14</v>
+        <v>3.21</v>
       </c>
       <c r="N41">
-        <v>3.19</v>
+        <v>2.85</v>
       </c>
       <c r="O41">
+        <v>1.83</v>
+      </c>
+      <c r="P41">
+        <v>7.4</v>
+      </c>
+      <c r="Q41">
+        <v>2.2</v>
+      </c>
+      <c r="R41">
+        <v>1.44</v>
+      </c>
+      <c r="S41">
+        <v>2.63</v>
+      </c>
+      <c r="T41">
+        <v>3.25</v>
+      </c>
+      <c r="U41">
+        <v>1.33</v>
+      </c>
+      <c r="V41">
+        <v>9</v>
+      </c>
+      <c r="W41">
+        <v>1.07</v>
+      </c>
+      <c r="X41">
+        <v>1.03</v>
+      </c>
+      <c r="Y41">
+        <v>7.4</v>
+      </c>
+      <c r="Z41">
+        <v>1.33</v>
+      </c>
+      <c r="AA41">
+        <v>2.84</v>
+      </c>
+      <c r="AB41">
+        <v>2.15</v>
+      </c>
+      <c r="AC41">
         <v>1.67</v>
       </c>
-      <c r="P41">
-        <v>8.4</v>
-      </c>
-      <c r="Q41">
-        <v>2.5</v>
-      </c>
-      <c r="R41">
-        <v>1.39</v>
-      </c>
-      <c r="S41">
-        <v>2.76</v>
-      </c>
-      <c r="T41">
-        <v>2.84</v>
-      </c>
-      <c r="U41">
-        <v>1.37</v>
-      </c>
-      <c r="V41">
-        <v>7</v>
-      </c>
-      <c r="W41">
-        <v>1.06</v>
-      </c>
-      <c r="X41">
-        <v>1.01</v>
-      </c>
-      <c r="Y41">
-        <v>9</v>
-      </c>
-      <c r="Z41">
-        <v>1.3</v>
-      </c>
-      <c r="AA41">
-        <v>3.08</v>
-      </c>
-      <c r="AB41">
-        <v>1.94</v>
-      </c>
-      <c r="AC41">
-        <v>1.76</v>
-      </c>
       <c r="AD41">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="AE41">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AF41">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AG41">
-        <v>2.01</v>
+        <v>1.83</v>
       </c>
       <c r="AH41">
-        <v>6.2</v>
+        <v>7.1</v>
       </c>
       <c r="AI41">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AJ41" t="s">
         <v>303</v>
@@ -6431,13 +6431,13 @@
         <v>301</v>
       </c>
       <c r="L45">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="M45">
-        <v>3.06</v>
+        <v>3.15</v>
       </c>
       <c r="N45">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="O45">
         <v>1.57</v>
@@ -6449,13 +6449,13 @@
         <v>3.1</v>
       </c>
       <c r="R45">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="S45">
         <v>2.15</v>
       </c>
       <c r="T45">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="U45">
         <v>1.25</v>
@@ -6473,16 +6473,16 @@
         <v>6.2</v>
       </c>
       <c r="Z45">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AA45">
-        <v>2.43</v>
+        <v>2.36</v>
       </c>
       <c r="AB45">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AC45">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AD45">
         <v>4.75</v>
@@ -6494,7 +6494,7 @@
         <v>2.1</v>
       </c>
       <c r="AG45">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AH45">
         <v>9.5</v>
@@ -6520,7 +6520,7 @@
         <v>56</v>
       </c>
       <c r="C46" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D46" t="s">
         <v>94</v>
@@ -6547,76 +6547,76 @@
         <v>301</v>
       </c>
       <c r="L46">
-        <v>2.4</v>
+        <v>1.34</v>
       </c>
       <c r="M46">
-        <v>2.96</v>
+        <v>4.96</v>
       </c>
       <c r="N46">
+        <v>8.35</v>
+      </c>
+      <c r="O46">
+        <v>1.25</v>
+      </c>
+      <c r="P46">
+        <v>15.25</v>
+      </c>
+      <c r="Q46">
+        <v>4.33</v>
+      </c>
+      <c r="R46">
+        <v>1.3</v>
+      </c>
+      <c r="S46">
+        <v>3.4</v>
+      </c>
+      <c r="T46">
+        <v>2.5</v>
+      </c>
+      <c r="U46">
+        <v>1.5</v>
+      </c>
+      <c r="V46">
+        <v>6</v>
+      </c>
+      <c r="W46">
+        <v>1.13</v>
+      </c>
+      <c r="X46">
+        <v>1.01</v>
+      </c>
+      <c r="Y46">
+        <v>11</v>
+      </c>
+      <c r="Z46">
+        <v>1.17</v>
+      </c>
+      <c r="AA46">
+        <v>4</v>
+      </c>
+      <c r="AB46">
+        <v>1.73</v>
+      </c>
+      <c r="AC46">
+        <v>2.08</v>
+      </c>
+      <c r="AD46">
         <v>2.75</v>
       </c>
-      <c r="O46">
-        <v>1.95</v>
-      </c>
-      <c r="P46">
-        <v>7</v>
-      </c>
-      <c r="Q46">
-        <v>2.15</v>
-      </c>
-      <c r="R46">
-        <v>1.46</v>
-      </c>
-      <c r="S46">
-        <v>2.45</v>
-      </c>
-      <c r="T46">
-        <v>3.14</v>
-      </c>
-      <c r="U46">
-        <v>1.31</v>
-      </c>
-      <c r="V46">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="W46">
-        <v>1.05</v>
-      </c>
-      <c r="X46">
-        <v>1.03</v>
-      </c>
-      <c r="Y46">
-        <v>7.2</v>
-      </c>
-      <c r="Z46">
-        <v>1.4</v>
-      </c>
-      <c r="AA46">
-        <v>2.9</v>
-      </c>
-      <c r="AB46">
-        <v>2.3</v>
-      </c>
-      <c r="AC46">
-        <v>1.57</v>
-      </c>
-      <c r="AD46">
-        <v>4.05</v>
-      </c>
       <c r="AE46">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AF46">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AG46">
-        <v>1.86</v>
+        <v>1.67</v>
       </c>
       <c r="AH46">
-        <v>8.5</v>
+        <v>5.3</v>
       </c>
       <c r="AI46">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AJ46" t="s">
         <v>303</v>
@@ -6636,7 +6636,7 @@
         <v>56</v>
       </c>
       <c r="C47" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D47" t="s">
         <v>94</v>
@@ -6663,13 +6663,13 @@
         <v>301</v>
       </c>
       <c r="L47">
-        <v>2.67</v>
+        <v>2.74</v>
       </c>
       <c r="M47">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="N47">
-        <v>2.43</v>
+        <v>2.7</v>
       </c>
       <c r="O47">
         <v>1.91</v>
@@ -6681,16 +6681,16 @@
         <v>2.2</v>
       </c>
       <c r="R47">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="S47">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="T47">
         <v>3.1</v>
       </c>
       <c r="U47">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V47">
         <v>8</v>
@@ -6699,7 +6699,7 @@
         <v>1.05</v>
       </c>
       <c r="X47">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y47">
         <v>8</v>
@@ -6711,10 +6711,10 @@
         <v>2.78</v>
       </c>
       <c r="AB47">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AC47">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AD47">
         <v>3.8</v>
@@ -6723,7 +6723,7 @@
         <v>1.2</v>
       </c>
       <c r="AF47">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG47">
         <v>1.85</v>
@@ -6732,7 +6732,7 @@
         <v>7</v>
       </c>
       <c r="AI47">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AJ47" t="s">
         <v>303</v>
@@ -6752,7 +6752,7 @@
         <v>56</v>
       </c>
       <c r="C48" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D48" t="s">
         <v>94</v>
@@ -6779,76 +6779,76 @@
         <v>301</v>
       </c>
       <c r="L48">
-        <v>1.34</v>
+        <v>2.4</v>
       </c>
       <c r="M48">
-        <v>4.96</v>
+        <v>2.96</v>
       </c>
       <c r="N48">
-        <v>8.35</v>
+        <v>2.75</v>
       </c>
       <c r="O48">
-        <v>1.25</v>
+        <v>1.95</v>
       </c>
       <c r="P48">
-        <v>15.25</v>
+        <v>7</v>
       </c>
       <c r="Q48">
-        <v>4.33</v>
+        <v>2.15</v>
       </c>
       <c r="R48">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="S48">
-        <v>3.4</v>
+        <v>2.45</v>
       </c>
       <c r="T48">
-        <v>2.5</v>
+        <v>3.14</v>
       </c>
       <c r="U48">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="V48">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W48">
-        <v>1.13</v>
+        <v>1.02</v>
       </c>
       <c r="X48">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y48">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="Z48">
-        <v>1.17</v>
+        <v>1.4</v>
       </c>
       <c r="AA48">
-        <v>4</v>
+        <v>2.85</v>
       </c>
       <c r="AB48">
-        <v>1.73</v>
+        <v>2.25</v>
       </c>
       <c r="AC48">
-        <v>2.08</v>
+        <v>1.63</v>
       </c>
       <c r="AD48">
-        <v>2.75</v>
+        <v>4.05</v>
       </c>
       <c r="AE48">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AF48">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="AG48">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AH48">
-        <v>5.3</v>
+        <v>8.5</v>
       </c>
       <c r="AI48">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="AJ48" t="s">
         <v>303</v>
@@ -7124,7 +7124,7 @@
         <v>0</v>
       </c>
       <c r="K51" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L51">
         <v>0</v>
@@ -7216,7 +7216,7 @@
         <v>58</v>
       </c>
       <c r="C52" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D52" t="s">
         <v>94</v>
@@ -7240,43 +7240,43 @@
         <v>0</v>
       </c>
       <c r="K52" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L52">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M52">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N52">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O52">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="P52">
         <v>0</v>
       </c>
       <c r="Q52">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R52">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S52">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T52">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U52">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V52">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W52">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X52">
         <v>0</v>
@@ -7291,10 +7291,10 @@
         <v>0</v>
       </c>
       <c r="AB52">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC52">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD52">
         <v>0</v>
@@ -7303,10 +7303,10 @@
         <v>0</v>
       </c>
       <c r="AF52">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG52">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH52">
         <v>0</v>
@@ -7564,7 +7564,7 @@
         <v>58</v>
       </c>
       <c r="C55" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D55" t="s">
         <v>94</v>
@@ -7591,40 +7591,40 @@
         <v>301</v>
       </c>
       <c r="L55">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M55">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N55">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O55">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="P55">
         <v>0</v>
       </c>
       <c r="Q55">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R55">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S55">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T55">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U55">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V55">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W55">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X55">
         <v>0</v>
@@ -7639,10 +7639,10 @@
         <v>0</v>
       </c>
       <c r="AB55">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC55">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD55">
         <v>0</v>
@@ -7651,10 +7651,10 @@
         <v>0</v>
       </c>
       <c r="AF55">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG55">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH55">
         <v>0</v>
@@ -7936,7 +7936,7 @@
         <v>0</v>
       </c>
       <c r="K58" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L58">
         <v>0</v>
@@ -8144,7 +8144,7 @@
         <v>58</v>
       </c>
       <c r="C60" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D60" t="s">
         <v>94</v>
@@ -8171,76 +8171,76 @@
         <v>301</v>
       </c>
       <c r="L60">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M60">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N60">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O60">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="P60">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="Q60">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="R60">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S60">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T60">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U60">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V60">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="W60">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X60">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y60">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="Z60">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AA60">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AB60">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AC60">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AD60">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE60">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF60">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG60">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AH60">
-        <v>9.75</v>
+        <v>0</v>
       </c>
       <c r="AI60">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AJ60" t="s">
         <v>303</v>
@@ -8376,7 +8376,7 @@
         <v>58</v>
       </c>
       <c r="C62" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D62" t="s">
         <v>94</v>
@@ -8403,76 +8403,76 @@
         <v>301</v>
       </c>
       <c r="L62">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M62">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N62">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O62">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="P62">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q62">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R62">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S62">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T62">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U62">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V62">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W62">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X62">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y62">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z62">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AA62">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB62">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC62">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD62">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AE62">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF62">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG62">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH62">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="AI62">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AJ62" t="s">
         <v>303</v>
@@ -8492,7 +8492,7 @@
         <v>58</v>
       </c>
       <c r="C63" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D63" t="s">
         <v>94</v>
@@ -8519,76 +8519,76 @@
         <v>301</v>
       </c>
       <c r="L63">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M63">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N63">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O63">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="P63">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="Q63">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R63">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S63">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T63">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U63">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V63">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W63">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X63">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y63">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="Z63">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA63">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB63">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC63">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AD63">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AE63">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF63">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG63">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH63">
-        <v>0</v>
+        <v>9.75</v>
       </c>
       <c r="AI63">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AJ63" t="s">
         <v>303</v>
@@ -8608,7 +8608,7 @@
         <v>58</v>
       </c>
       <c r="C64" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D64" t="s">
         <v>94</v>
@@ -8632,79 +8632,79 @@
         <v>0</v>
       </c>
       <c r="K64" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L64">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M64">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N64">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O64">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="P64">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q64">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R64">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S64">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="T64">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U64">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V64">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W64">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X64">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y64">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z64">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AA64">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AB64">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AC64">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD64">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AE64">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF64">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG64">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH64">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AI64">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AJ64" t="s">
         <v>303</v>
@@ -8956,7 +8956,7 @@
         <v>58</v>
       </c>
       <c r="C67" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D67" t="s">
         <v>94</v>
@@ -8983,76 +8983,76 @@
         <v>301</v>
       </c>
       <c r="L67">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M67">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N67">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O67">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="P67">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q67">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R67">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S67">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T67">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U67">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V67">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W67">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X67">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y67">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="Z67">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AA67">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB67">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC67">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD67">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AE67">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AF67">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG67">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH67">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AI67">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AJ67" t="s">
         <v>303</v>
@@ -9072,7 +9072,7 @@
         <v>58</v>
       </c>
       <c r="C68" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D68" t="s">
         <v>94</v>
@@ -9099,76 +9099,76 @@
         <v>301</v>
       </c>
       <c r="L68">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="M68">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N68">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O68">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="P68">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Q68">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R68">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S68">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T68">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U68">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V68">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W68">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X68">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y68">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Z68">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AA68">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AB68">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AC68">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AD68">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AE68">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AF68">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG68">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH68">
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="AI68">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AJ68" t="s">
         <v>303</v>
@@ -9331,13 +9331,13 @@
         <v>301</v>
       </c>
       <c r="L70">
-        <v>2.29</v>
+        <v>1.95</v>
       </c>
       <c r="M70">
-        <v>3.02</v>
+        <v>3.11</v>
       </c>
       <c r="N70">
-        <v>2.84</v>
+        <v>3.7</v>
       </c>
       <c r="O70">
         <v>1.67</v>
@@ -9349,13 +9349,13 @@
         <v>2.5</v>
       </c>
       <c r="R70">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="S70">
-        <v>2.68</v>
+        <v>2.52</v>
       </c>
       <c r="T70">
-        <v>3.14</v>
+        <v>3.34</v>
       </c>
       <c r="U70">
         <v>1.29</v>
@@ -9364,43 +9364,43 @@
         <v>8.6</v>
       </c>
       <c r="W70">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X70">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Y70">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="Z70">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AA70">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AB70">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="AC70">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AD70">
-        <v>4.25</v>
+        <v>4.8</v>
       </c>
       <c r="AE70">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AF70">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AG70">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AH70">
         <v>8.6</v>
       </c>
       <c r="AI70">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AJ70" t="s">
         <v>303</v>
@@ -9447,76 +9447,76 @@
         <v>301</v>
       </c>
       <c r="L71">
-        <v>1.6</v>
+        <v>2.18</v>
       </c>
       <c r="M71">
-        <v>3.31</v>
+        <v>2.88</v>
       </c>
       <c r="N71">
-        <v>5.2</v>
+        <v>3.8</v>
       </c>
       <c r="O71">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="P71">
-        <v>6.5</v>
+        <v>5.75</v>
       </c>
       <c r="Q71">
-        <v>3.3</v>
+        <v>2.37</v>
       </c>
       <c r="R71">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="S71">
-        <v>2.47</v>
+        <v>2.38</v>
       </c>
       <c r="T71">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="U71">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="V71">
-        <v>8.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="W71">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X71">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Y71">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="Z71">
+        <v>1.57</v>
+      </c>
+      <c r="AA71">
+        <v>2.39</v>
+      </c>
+      <c r="AB71">
+        <v>2.62</v>
+      </c>
+      <c r="AC71">
         <v>1.4</v>
       </c>
-      <c r="AA71">
-        <v>2.66</v>
-      </c>
-      <c r="AB71">
-        <v>2.3</v>
-      </c>
-      <c r="AC71">
-        <v>1.5</v>
-      </c>
       <c r="AD71">
-        <v>4.45</v>
+        <v>5.1</v>
       </c>
       <c r="AE71">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF71">
-        <v>2.58</v>
+        <v>2.19</v>
       </c>
       <c r="AG71">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AH71">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AI71">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AJ71" t="s">
         <v>303</v>
@@ -9536,7 +9536,7 @@
         <v>60</v>
       </c>
       <c r="C72" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D72" t="s">
         <v>94</v>
@@ -9563,73 +9563,73 @@
         <v>301</v>
       </c>
       <c r="L72">
-        <v>2.56</v>
+        <v>1.65</v>
       </c>
       <c r="M72">
-        <v>2.84</v>
+        <v>3.54</v>
       </c>
       <c r="N72">
-        <v>2.65</v>
+        <v>6</v>
       </c>
       <c r="O72">
-        <v>1.95</v>
+        <v>1.5</v>
       </c>
       <c r="P72">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="Q72">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="R72">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="S72">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="T72">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U72">
         <v>1.29</v>
       </c>
       <c r="V72">
-        <v>8.1</v>
+        <v>8.9</v>
       </c>
       <c r="W72">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X72">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="Y72">
-        <v>6.45</v>
+        <v>7</v>
       </c>
       <c r="Z72">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AA72">
-        <v>2.56</v>
+        <v>2.65</v>
       </c>
       <c r="AB72">
+        <v>2.42</v>
+      </c>
+      <c r="AC72">
+        <v>1.54</v>
+      </c>
+      <c r="AD72">
+        <v>4.5</v>
+      </c>
+      <c r="AE72">
+        <v>1.14</v>
+      </c>
+      <c r="AF72">
         <v>2.3</v>
       </c>
-      <c r="AC72">
-        <v>1.55</v>
-      </c>
-      <c r="AD72">
-        <v>4.75</v>
-      </c>
-      <c r="AE72">
-        <v>1.16</v>
-      </c>
-      <c r="AF72">
-        <v>2</v>
-      </c>
       <c r="AG72">
-        <v>1.79</v>
+        <v>1.53</v>
       </c>
       <c r="AH72">
-        <v>8.300000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AI72">
         <v>1.05</v>
@@ -9652,7 +9652,7 @@
         <v>60</v>
       </c>
       <c r="C73" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D73" t="s">
         <v>94</v>
@@ -9679,76 +9679,76 @@
         <v>301</v>
       </c>
       <c r="L73">
-        <v>1.88</v>
+        <v>2.6</v>
       </c>
       <c r="M73">
-        <v>2.93</v>
+        <v>2.97</v>
       </c>
       <c r="N73">
-        <v>4.1</v>
+        <v>2.9</v>
       </c>
       <c r="O73">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="P73">
-        <v>5.75</v>
+        <v>6.75</v>
       </c>
       <c r="Q73">
-        <v>2.37</v>
+        <v>2.2</v>
       </c>
       <c r="R73">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="S73">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="T73">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="U73">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="V73">
-        <v>11.5</v>
+        <v>8.1</v>
       </c>
       <c r="W73">
         <v>1.03</v>
       </c>
       <c r="X73">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y73">
-        <v>5.75</v>
+        <v>6.5</v>
       </c>
       <c r="Z73">
+        <v>1.44</v>
+      </c>
+      <c r="AA73">
+        <v>2.6</v>
+      </c>
+      <c r="AB73">
+        <v>2.3</v>
+      </c>
+      <c r="AC73">
         <v>1.53</v>
       </c>
-      <c r="AA73">
-        <v>2.25</v>
-      </c>
-      <c r="AB73">
-        <v>2.6</v>
-      </c>
-      <c r="AC73">
-        <v>1.44</v>
-      </c>
       <c r="AD73">
-        <v>5.1</v>
+        <v>4.75</v>
       </c>
       <c r="AE73">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AF73">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AG73">
-        <v>1.57</v>
+        <v>1.79</v>
       </c>
       <c r="AH73">
-        <v>10</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AI73">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AJ73" t="s">
         <v>303</v>
@@ -9768,7 +9768,7 @@
         <v>60</v>
       </c>
       <c r="C74" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D74" t="s">
         <v>94</v>
@@ -10116,7 +10116,7 @@
         <v>62</v>
       </c>
       <c r="C77" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D77" t="s">
         <v>94</v>
@@ -10143,13 +10143,13 @@
         <v>301</v>
       </c>
       <c r="L77">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="M77">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="N77">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O77">
         <v>1.49</v>
@@ -10170,7 +10170,7 @@
         <v>2.75</v>
       </c>
       <c r="U77">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="V77">
         <v>7.25</v>
@@ -10191,10 +10191,10 @@
         <v>3.2</v>
       </c>
       <c r="AB77">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AC77">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AD77">
         <v>3.35</v>
@@ -10232,7 +10232,7 @@
         <v>62</v>
       </c>
       <c r="C78" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D78" t="s">
         <v>94</v>
@@ -10259,13 +10259,13 @@
         <v>301</v>
       </c>
       <c r="L78">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="M78">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="N78">
-        <v>5.5</v>
+        <v>5.46</v>
       </c>
       <c r="O78">
         <v>1.49</v>
@@ -10277,58 +10277,58 @@
         <v>3.5</v>
       </c>
       <c r="R78">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="S78">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="T78">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="U78">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="V78">
-        <v>9.5</v>
+        <v>8.9</v>
       </c>
       <c r="W78">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X78">
         <v>1.09</v>
       </c>
       <c r="Y78">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="Z78">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AA78">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="AB78">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AC78">
         <v>1.5</v>
       </c>
       <c r="AD78">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AE78">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF78">
         <v>2.4</v>
       </c>
       <c r="AG78">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AH78">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="AI78">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AJ78" t="s">
         <v>303</v>
@@ -10375,22 +10375,22 @@
         <v>301</v>
       </c>
       <c r="L79">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M79">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N79">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O79">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="P79">
         <v>0</v>
       </c>
       <c r="Q79">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R79">
         <v>0</v>
@@ -10423,10 +10423,10 @@
         <v>0</v>
       </c>
       <c r="AB79">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC79">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD79">
         <v>0</v>
@@ -10464,7 +10464,7 @@
         <v>63</v>
       </c>
       <c r="C80" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="D80" t="s">
         <v>94</v>
@@ -10491,76 +10491,76 @@
         <v>301</v>
       </c>
       <c r="L80">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="M80">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="N80">
-        <v>3.45</v>
+        <v>3.39</v>
       </c>
       <c r="O80">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="P80">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q80">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="R80">
+        <v>1.42</v>
+      </c>
+      <c r="S80">
+        <v>2.62</v>
+      </c>
+      <c r="T80">
+        <v>3</v>
+      </c>
+      <c r="U80">
+        <v>1.33</v>
+      </c>
+      <c r="V80">
+        <v>7.6</v>
+      </c>
+      <c r="W80">
+        <v>1.06</v>
+      </c>
+      <c r="X80">
+        <v>1.01</v>
+      </c>
+      <c r="Y80">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="Z80">
+        <v>1.3</v>
+      </c>
+      <c r="AA80">
+        <v>3</v>
+      </c>
+      <c r="AB80">
+        <v>2.1</v>
+      </c>
+      <c r="AC80">
+        <v>1.68</v>
+      </c>
+      <c r="AD80">
+        <v>3.6</v>
+      </c>
+      <c r="AE80">
         <v>1.25</v>
       </c>
-      <c r="S80">
-        <v>3.55</v>
-      </c>
-      <c r="T80">
-        <v>2.45</v>
-      </c>
-      <c r="U80">
-        <v>1.5</v>
-      </c>
-      <c r="V80">
-        <v>6</v>
-      </c>
-      <c r="W80">
-        <v>1.13</v>
-      </c>
-      <c r="X80">
-        <v>1.04</v>
-      </c>
-      <c r="Y80">
-        <v>13</v>
-      </c>
-      <c r="Z80">
-        <v>1.18</v>
-      </c>
-      <c r="AA80">
-        <v>4</v>
-      </c>
-      <c r="AB80">
-        <v>1.74</v>
-      </c>
-      <c r="AC80">
-        <v>1.97</v>
-      </c>
-      <c r="AD80">
-        <v>2.83</v>
-      </c>
-      <c r="AE80">
-        <v>1.4</v>
-      </c>
       <c r="AF80">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AG80">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AH80">
-        <v>5</v>
+        <v>7.6</v>
       </c>
       <c r="AI80">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AJ80" t="s">
         <v>303</v>
@@ -10580,7 +10580,7 @@
         <v>63</v>
       </c>
       <c r="C81" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="D81" t="s">
         <v>94</v>
@@ -10607,76 +10607,76 @@
         <v>301</v>
       </c>
       <c r="L81">
-        <v>2.14</v>
+        <v>1.6</v>
       </c>
       <c r="M81">
-        <v>3.14</v>
+        <v>4.2</v>
       </c>
       <c r="N81">
-        <v>3</v>
+        <v>3.74</v>
       </c>
       <c r="O81">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="P81">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q81">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="R81">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="S81">
-        <v>2.62</v>
+        <v>3.55</v>
       </c>
       <c r="T81">
-        <v>3.04</v>
+        <v>2.45</v>
       </c>
       <c r="U81">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="V81">
-        <v>7.6</v>
+        <v>5.95</v>
       </c>
       <c r="W81">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X81">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y81">
-        <v>8.699999999999999</v>
+        <v>13</v>
       </c>
       <c r="Z81">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AA81">
-        <v>2.97</v>
+        <v>4</v>
       </c>
       <c r="AB81">
+        <v>1.72</v>
+      </c>
+      <c r="AC81">
+        <v>2.01</v>
+      </c>
+      <c r="AD81">
+        <v>2.83</v>
+      </c>
+      <c r="AE81">
+        <v>1.38</v>
+      </c>
+      <c r="AF81">
+        <v>1.73</v>
+      </c>
+      <c r="AG81">
         <v>2.1</v>
       </c>
-      <c r="AC81">
-        <v>1.67</v>
-      </c>
-      <c r="AD81">
-        <v>3.68</v>
-      </c>
-      <c r="AE81">
-        <v>1.2</v>
-      </c>
-      <c r="AF81">
-        <v>1.85</v>
-      </c>
-      <c r="AG81">
-        <v>1.83</v>
-      </c>
       <c r="AH81">
-        <v>7.6</v>
+        <v>5</v>
       </c>
       <c r="AI81">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="AJ81" t="s">
         <v>303</v>
@@ -10723,22 +10723,22 @@
         <v>301</v>
       </c>
       <c r="L82">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M82">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N82">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O82">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="P82">
         <v>0</v>
       </c>
       <c r="Q82">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R82">
         <v>0</v>
@@ -10771,10 +10771,10 @@
         <v>0</v>
       </c>
       <c r="AB82">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC82">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD82">
         <v>0</v>
@@ -10812,7 +10812,7 @@
         <v>64</v>
       </c>
       <c r="C83" t="s">
-        <v>93</v>
+        <v>70</v>
       </c>
       <c r="D83" t="s">
         <v>94</v>
@@ -10839,76 +10839,76 @@
         <v>301</v>
       </c>
       <c r="L83">
-        <v>1.45</v>
+        <v>1.87</v>
       </c>
       <c r="M83">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="N83">
-        <v>6</v>
+        <v>3.46</v>
       </c>
       <c r="O83">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="P83">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Q83">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="R83">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S83">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="T83">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U83">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="V83">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="W83">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X83">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y83">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Z83">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AA83">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AB83">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="AC83">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AD83">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE83">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF83">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG83">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH83">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AI83">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AJ83" t="s">
         <v>303</v>
@@ -10928,7 +10928,7 @@
         <v>64</v>
       </c>
       <c r="C84" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="D84" t="s">
         <v>94</v>
@@ -10955,76 +10955,76 @@
         <v>301</v>
       </c>
       <c r="L84">
-        <v>2.97</v>
+        <v>2.11</v>
       </c>
       <c r="M84">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="N84">
-        <v>2.17</v>
+        <v>3.08</v>
       </c>
       <c r="O84">
-        <v>2.3</v>
+        <v>1.67</v>
       </c>
       <c r="P84">
-        <v>6</v>
+        <v>12.5</v>
       </c>
       <c r="Q84">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="R84">
-        <v>1.6</v>
+        <v>1.22</v>
       </c>
       <c r="S84">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="T84">
-        <v>3.6</v>
+        <v>2.1</v>
       </c>
       <c r="U84">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="V84">
-        <v>8.699999999999999</v>
+        <v>4.5</v>
       </c>
       <c r="W84">
+        <v>1.18</v>
+      </c>
+      <c r="X84">
         <v>1.01</v>
       </c>
-      <c r="X84">
-        <v>1.11</v>
-      </c>
       <c r="Y84">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="Z84">
-        <v>1.48</v>
+        <v>1.17</v>
       </c>
       <c r="AA84">
-        <v>2.37</v>
+        <v>5</v>
       </c>
       <c r="AB84">
-        <v>2.52</v>
+        <v>1.44</v>
       </c>
       <c r="AC84">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="AD84">
-        <v>4.7</v>
+        <v>2.05</v>
       </c>
       <c r="AE84">
-        <v>1.15</v>
+        <v>1.7</v>
       </c>
       <c r="AF84">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="AG84">
-        <v>1.69</v>
+        <v>2.75</v>
       </c>
       <c r="AH84">
-        <v>11.5</v>
+        <v>3.65</v>
       </c>
       <c r="AI84">
-        <v>1.04</v>
+        <v>1.28</v>
       </c>
       <c r="AJ84" t="s">
         <v>303</v>
@@ -11071,22 +11071,22 @@
         <v>301</v>
       </c>
       <c r="L85">
-        <v>2.63</v>
+        <v>1.45</v>
       </c>
       <c r="M85">
+        <v>3.8</v>
+      </c>
+      <c r="N85">
+        <v>6</v>
+      </c>
+      <c r="O85">
+        <v>1.36</v>
+      </c>
+      <c r="P85">
+        <v>14</v>
+      </c>
+      <c r="Q85">
         <v>3.1</v>
-      </c>
-      <c r="N85">
-        <v>2.4</v>
-      </c>
-      <c r="O85">
-        <v>2.05</v>
-      </c>
-      <c r="P85">
-        <v>11.5</v>
-      </c>
-      <c r="Q85">
-        <v>1.8</v>
       </c>
       <c r="R85">
         <v>1.25</v>
@@ -11095,22 +11095,22 @@
         <v>3.75</v>
       </c>
       <c r="T85">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="U85">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="V85">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="W85">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X85">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y85">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="Z85">
         <v>1.17</v>
@@ -11125,16 +11125,16 @@
         <v>2.4</v>
       </c>
       <c r="AD85">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AE85">
         <v>1.61</v>
       </c>
       <c r="AF85">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AG85">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="AH85">
         <v>3.8</v>
@@ -11160,7 +11160,7 @@
         <v>64</v>
       </c>
       <c r="C86" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="D86" t="s">
         <v>94</v>
@@ -11187,76 +11187,76 @@
         <v>301</v>
       </c>
       <c r="L86">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="M86">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N86">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O86">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P86">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Q86">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R86">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S86">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T86">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U86">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V86">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W86">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X86">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y86">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z86">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AA86">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB86">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC86">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD86">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE86">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF86">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG86">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH86">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AI86">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AJ86" t="s">
         <v>303</v>
@@ -11276,7 +11276,7 @@
         <v>64</v>
       </c>
       <c r="C87" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="D87" t="s">
         <v>94</v>
@@ -11303,76 +11303,76 @@
         <v>301</v>
       </c>
       <c r="L87">
-        <v>2.98</v>
+        <v>3.14</v>
       </c>
       <c r="M87">
-        <v>3.07</v>
+        <v>3.12</v>
       </c>
       <c r="N87">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="O87">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="P87">
+        <v>6</v>
+      </c>
+      <c r="Q87">
+        <v>1.91</v>
+      </c>
+      <c r="R87">
+        <v>1.6</v>
+      </c>
+      <c r="S87">
+        <v>2.25</v>
+      </c>
+      <c r="T87">
+        <v>3.6</v>
+      </c>
+      <c r="U87">
+        <v>1.25</v>
+      </c>
+      <c r="V87">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="W87">
+        <v>1.01</v>
+      </c>
+      <c r="X87">
+        <v>1.11</v>
+      </c>
+      <c r="Y87">
+        <v>6</v>
+      </c>
+      <c r="Z87">
+        <v>1.53</v>
+      </c>
+      <c r="AA87">
+        <v>2.45</v>
+      </c>
+      <c r="AB87">
+        <v>2.65</v>
+      </c>
+      <c r="AC87">
+        <v>1.48</v>
+      </c>
+      <c r="AD87">
+        <v>4.9</v>
+      </c>
+      <c r="AE87">
+        <v>1.15</v>
+      </c>
+      <c r="AF87">
+        <v>2.05</v>
+      </c>
+      <c r="AG87">
+        <v>1.68</v>
+      </c>
+      <c r="AH87">
         <v>11.5</v>
       </c>
-      <c r="Q87">
-        <v>1.73</v>
-      </c>
-      <c r="R87">
-        <v>1.25</v>
-      </c>
-      <c r="S87">
-        <v>3.75</v>
-      </c>
-      <c r="T87">
-        <v>2.25</v>
-      </c>
-      <c r="U87">
-        <v>1.57</v>
-      </c>
-      <c r="V87">
-        <v>5.5</v>
-      </c>
-      <c r="W87">
-        <v>1.14</v>
-      </c>
-      <c r="X87">
-        <v>1.01</v>
-      </c>
-      <c r="Y87">
-        <v>17</v>
-      </c>
-      <c r="Z87">
-        <v>1.18</v>
-      </c>
-      <c r="AA87">
-        <v>4.75</v>
-      </c>
-      <c r="AB87">
-        <v>1.53</v>
-      </c>
-      <c r="AC87">
-        <v>2.35</v>
-      </c>
-      <c r="AD87">
-        <v>2.25</v>
-      </c>
-      <c r="AE87">
-        <v>1.57</v>
-      </c>
-      <c r="AF87">
-        <v>1.44</v>
-      </c>
-      <c r="AG87">
-        <v>2.63</v>
-      </c>
-      <c r="AH87">
-        <v>4</v>
-      </c>
       <c r="AI87">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="AJ87" t="s">
         <v>303</v>
@@ -11392,7 +11392,7 @@
         <v>64</v>
       </c>
       <c r="C88" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D88" t="s">
         <v>94</v>
@@ -11419,76 +11419,76 @@
         <v>301</v>
       </c>
       <c r="L88">
-        <v>2.47</v>
+        <v>1.3</v>
       </c>
       <c r="M88">
-        <v>3.07</v>
+        <v>4.75</v>
       </c>
       <c r="N88">
-        <v>2.57</v>
+        <v>6.4</v>
       </c>
       <c r="O88">
-        <v>2.05</v>
+        <v>1.28</v>
       </c>
       <c r="P88">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="Q88">
-        <v>1.83</v>
+        <v>3.35</v>
       </c>
       <c r="R88">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="S88">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="T88">
+        <v>2.22</v>
+      </c>
+      <c r="U88">
+        <v>1.75</v>
+      </c>
+      <c r="V88">
+        <v>4.3</v>
+      </c>
+      <c r="W88">
+        <v>1.2</v>
+      </c>
+      <c r="X88">
+        <v>1.02</v>
+      </c>
+      <c r="Y88">
+        <v>16.5</v>
+      </c>
+      <c r="Z88">
+        <v>1.15</v>
+      </c>
+      <c r="AA88">
+        <v>5.5</v>
+      </c>
+      <c r="AB88">
+        <v>1.42</v>
+      </c>
+      <c r="AC88">
         <v>2.5</v>
       </c>
-      <c r="U88">
-        <v>1.5</v>
-      </c>
-      <c r="V88">
-        <v>6.5</v>
-      </c>
-      <c r="W88">
-        <v>1.11</v>
-      </c>
-      <c r="X88">
-        <v>1</v>
-      </c>
-      <c r="Y88">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="Z88">
+      <c r="AD88">
+        <v>2.2</v>
+      </c>
+      <c r="AE88">
+        <v>1.6</v>
+      </c>
+      <c r="AF88">
+        <v>1.67</v>
+      </c>
+      <c r="AG88">
+        <v>2</v>
+      </c>
+      <c r="AH88">
+        <v>3.58</v>
+      </c>
+      <c r="AI88">
         <v>1.21</v>
-      </c>
-      <c r="AA88">
-        <v>3.74</v>
-      </c>
-      <c r="AB88">
-        <v>1.8</v>
-      </c>
-      <c r="AC88">
-        <v>1.91</v>
-      </c>
-      <c r="AD88">
-        <v>2.74</v>
-      </c>
-      <c r="AE88">
-        <v>1.37</v>
-      </c>
-      <c r="AF88">
-        <v>1.57</v>
-      </c>
-      <c r="AG88">
-        <v>2.25</v>
-      </c>
-      <c r="AH88">
-        <v>4.95</v>
-      </c>
-      <c r="AI88">
-        <v>1.11</v>
       </c>
       <c r="AJ88" t="s">
         <v>303</v>
@@ -11535,40 +11535,40 @@
         <v>301</v>
       </c>
       <c r="L89">
-        <v>2.11</v>
+        <v>2.98</v>
       </c>
       <c r="M89">
-        <v>3.12</v>
+        <v>3.07</v>
       </c>
       <c r="N89">
-        <v>3.08</v>
+        <v>2.18</v>
       </c>
       <c r="O89">
-        <v>1.67</v>
+        <v>2.2</v>
       </c>
       <c r="P89">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Q89">
-        <v>2.2</v>
+        <v>1.73</v>
       </c>
       <c r="R89">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="S89">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="T89">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="U89">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="V89">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="W89">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="X89">
         <v>1.01</v>
@@ -11577,34 +11577,34 @@
         <v>17</v>
       </c>
       <c r="Z89">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AA89">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="AB89">
+        <v>1.53</v>
+      </c>
+      <c r="AC89">
+        <v>2.35</v>
+      </c>
+      <c r="AD89">
+        <v>2.25</v>
+      </c>
+      <c r="AE89">
+        <v>1.57</v>
+      </c>
+      <c r="AF89">
         <v>1.44</v>
       </c>
-      <c r="AC89">
-        <v>2.6</v>
-      </c>
-      <c r="AD89">
-        <v>2.05</v>
-      </c>
-      <c r="AE89">
-        <v>1.7</v>
-      </c>
-      <c r="AF89">
-        <v>1.4</v>
-      </c>
       <c r="AG89">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="AH89">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="AI89">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AJ89" t="s">
         <v>303</v>
@@ -11624,7 +11624,7 @@
         <v>64</v>
       </c>
       <c r="C90" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D90" t="s">
         <v>94</v>
@@ -11651,76 +11651,76 @@
         <v>301</v>
       </c>
       <c r="L90">
-        <v>1.24</v>
+        <v>2.47</v>
       </c>
       <c r="M90">
-        <v>7</v>
+        <v>3.07</v>
       </c>
       <c r="N90">
-        <v>6.6</v>
+        <v>2.57</v>
       </c>
       <c r="O90">
-        <v>1.28</v>
+        <v>2.05</v>
       </c>
       <c r="P90">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="Q90">
-        <v>3.35</v>
+        <v>1.83</v>
       </c>
       <c r="R90">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="S90">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="T90">
-        <v>2.22</v>
+        <v>2.5</v>
       </c>
       <c r="U90">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="V90">
-        <v>4.3</v>
+        <v>6.5</v>
       </c>
       <c r="W90">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="X90">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y90">
-        <v>16.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Z90">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="AA90">
-        <v>5.5</v>
+        <v>3.74</v>
       </c>
       <c r="AB90">
-        <v>1.42</v>
+        <v>1.8</v>
       </c>
       <c r="AC90">
-        <v>2.5</v>
+        <v>1.91</v>
       </c>
       <c r="AD90">
-        <v>2.1</v>
+        <v>2.74</v>
       </c>
       <c r="AE90">
-        <v>1.66</v>
+        <v>1.37</v>
       </c>
       <c r="AF90">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AG90">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AH90">
-        <v>3.58</v>
+        <v>4.95</v>
       </c>
       <c r="AI90">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="AJ90" t="s">
         <v>303</v>
@@ -11767,13 +11767,13 @@
         <v>301</v>
       </c>
       <c r="L91">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="M91">
-        <v>2.96</v>
+        <v>3.13</v>
       </c>
       <c r="N91">
-        <v>2.87</v>
+        <v>3.1</v>
       </c>
       <c r="O91">
         <v>1.83</v>
@@ -11803,19 +11803,19 @@
         <v>1.05</v>
       </c>
       <c r="X91">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y91">
         <v>6.5</v>
       </c>
       <c r="Z91">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AA91">
-        <v>2.6</v>
+        <v>2.49</v>
       </c>
       <c r="AB91">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="AC91">
         <v>1.5</v>
@@ -11856,7 +11856,7 @@
         <v>65</v>
       </c>
       <c r="C92" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D92" t="s">
         <v>94</v>
@@ -11883,76 +11883,76 @@
         <v>301</v>
       </c>
       <c r="L92">
-        <v>4</v>
+        <v>2.43</v>
       </c>
       <c r="M92">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="N92">
+        <v>2.53</v>
+      </c>
+      <c r="O92">
+        <v>1.83</v>
+      </c>
+      <c r="P92">
+        <v>0</v>
+      </c>
+      <c r="Q92">
+        <v>2.1</v>
+      </c>
+      <c r="R92">
+        <v>1.36</v>
+      </c>
+      <c r="S92">
+        <v>2.95</v>
+      </c>
+      <c r="T92">
+        <v>2.8</v>
+      </c>
+      <c r="U92">
+        <v>1.4</v>
+      </c>
+      <c r="V92">
+        <v>7.3</v>
+      </c>
+      <c r="W92">
+        <v>1.08</v>
+      </c>
+      <c r="X92">
+        <v>1.02</v>
+      </c>
+      <c r="Y92">
+        <v>10</v>
+      </c>
+      <c r="Z92">
+        <v>1.23</v>
+      </c>
+      <c r="AA92">
+        <v>3.4</v>
+      </c>
+      <c r="AB92">
+        <v>1.92</v>
+      </c>
+      <c r="AC92">
+        <v>1.86</v>
+      </c>
+      <c r="AD92">
+        <v>3.25</v>
+      </c>
+      <c r="AE92">
+        <v>1.31</v>
+      </c>
+      <c r="AF92">
+        <v>1.73</v>
+      </c>
+      <c r="AG92">
         <v>2</v>
       </c>
-      <c r="O92">
-        <v>2.65</v>
-      </c>
-      <c r="P92">
-        <v>6.5</v>
-      </c>
-      <c r="Q92">
-        <v>1.75</v>
-      </c>
-      <c r="R92">
-        <v>1.5</v>
-      </c>
-      <c r="S92">
-        <v>2.4</v>
-      </c>
-      <c r="T92">
-        <v>3.2</v>
-      </c>
-      <c r="U92">
-        <v>1.3</v>
-      </c>
-      <c r="V92">
-        <v>8</v>
-      </c>
-      <c r="W92">
-        <v>1.05</v>
-      </c>
-      <c r="X92">
-        <v>1.1</v>
-      </c>
-      <c r="Y92">
-        <v>6.5</v>
-      </c>
-      <c r="Z92">
-        <v>1.48</v>
-      </c>
-      <c r="AA92">
-        <v>2.65</v>
-      </c>
-      <c r="AB92">
-        <v>2.4</v>
-      </c>
-      <c r="AC92">
-        <v>1.55</v>
-      </c>
-      <c r="AD92">
-        <v>4.5</v>
-      </c>
-      <c r="AE92">
-        <v>1.2</v>
-      </c>
-      <c r="AF92">
-        <v>2.05</v>
-      </c>
-      <c r="AG92">
-        <v>1.7</v>
-      </c>
       <c r="AH92">
-        <v>9</v>
+        <v>5.8</v>
       </c>
       <c r="AI92">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AJ92" t="s">
         <v>303</v>
@@ -11972,7 +11972,7 @@
         <v>65</v>
       </c>
       <c r="C93" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D93" t="s">
         <v>94</v>
@@ -11999,13 +11999,13 @@
         <v>301</v>
       </c>
       <c r="L93">
-        <v>1.61</v>
+        <v>1.43</v>
       </c>
       <c r="M93">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="N93">
-        <v>4.6</v>
+        <v>6.5</v>
       </c>
       <c r="O93">
         <v>1.33</v>
@@ -12020,7 +12020,7 @@
         <v>1.3</v>
       </c>
       <c r="S93">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="T93">
         <v>2.4</v>
@@ -12032,7 +12032,7 @@
         <v>5.5</v>
       </c>
       <c r="W93">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X93">
         <v>1.01</v>
@@ -12056,7 +12056,7 @@
         <v>2.59</v>
       </c>
       <c r="AE93">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AF93">
         <v>1.8</v>
@@ -12088,7 +12088,7 @@
         <v>65</v>
       </c>
       <c r="C94" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D94" t="s">
         <v>94</v>
@@ -12115,76 +12115,76 @@
         <v>301</v>
       </c>
       <c r="L94">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="M94">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N94">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="O94">
-        <v>1.83</v>
+        <v>2.65</v>
       </c>
       <c r="P94">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Q94">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="R94">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="S94">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="T94">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="U94">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="V94">
-        <v>7.3</v>
+        <v>8</v>
       </c>
       <c r="W94">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X94">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="Y94">
+        <v>6.5</v>
+      </c>
+      <c r="Z94">
+        <v>1.48</v>
+      </c>
+      <c r="AA94">
+        <v>2.65</v>
+      </c>
+      <c r="AB94">
+        <v>2.4</v>
+      </c>
+      <c r="AC94">
+        <v>1.55</v>
+      </c>
+      <c r="AD94">
+        <v>4.5</v>
+      </c>
+      <c r="AE94">
+        <v>1.2</v>
+      </c>
+      <c r="AF94">
+        <v>2.05</v>
+      </c>
+      <c r="AG94">
+        <v>1.7</v>
+      </c>
+      <c r="AH94">
         <v>9</v>
       </c>
-      <c r="Z94">
-        <v>1.24</v>
-      </c>
-      <c r="AA94">
-        <v>3.4</v>
-      </c>
-      <c r="AB94">
-        <v>1.9</v>
-      </c>
-      <c r="AC94">
-        <v>1.81</v>
-      </c>
-      <c r="AD94">
-        <v>3.25</v>
-      </c>
-      <c r="AE94">
-        <v>1.31</v>
-      </c>
-      <c r="AF94">
-        <v>1.73</v>
-      </c>
-      <c r="AG94">
-        <v>2</v>
-      </c>
-      <c r="AH94">
-        <v>5.8</v>
-      </c>
       <c r="AI94">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AJ94" t="s">
         <v>303</v>
@@ -12231,76 +12231,76 @@
         <v>301</v>
       </c>
       <c r="L95">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="M95">
-        <v>3.79</v>
+        <v>3.65</v>
       </c>
       <c r="N95">
         <v>4.9</v>
       </c>
       <c r="O95">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="P95">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="Q95">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="R95">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="S95">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="T95">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="U95">
-        <v>1.49</v>
+        <v>1.67</v>
       </c>
       <c r="V95">
-        <v>5.75</v>
+        <v>4.5</v>
       </c>
       <c r="W95">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="X95">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y95">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="Z95">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="AA95">
-        <v>3.7</v>
+        <v>5.25</v>
       </c>
       <c r="AB95">
-        <v>1.7</v>
+        <v>1.45</v>
       </c>
       <c r="AC95">
-        <v>2</v>
+        <v>2.55</v>
       </c>
       <c r="AD95">
-        <v>2.75</v>
+        <v>2.1</v>
       </c>
       <c r="AE95">
-        <v>1.39</v>
+        <v>1.67</v>
       </c>
       <c r="AF95">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="AG95">
-        <v>1.83</v>
+        <v>2.5</v>
       </c>
       <c r="AH95">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="AI95">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="AJ95" t="s">
         <v>303</v>
@@ -12347,76 +12347,76 @@
         <v>301</v>
       </c>
       <c r="L96">
-        <v>2.63</v>
+        <v>2.15</v>
       </c>
       <c r="M96">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N96">
-        <v>2.4</v>
+        <v>2.93</v>
       </c>
       <c r="O96">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="P96">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="Q96">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="R96">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="S96">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="T96">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="U96">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="V96">
+        <v>6</v>
+      </c>
+      <c r="W96">
+        <v>1.13</v>
+      </c>
+      <c r="X96">
+        <v>1.04</v>
+      </c>
+      <c r="Y96">
+        <v>10</v>
+      </c>
+      <c r="Z96">
+        <v>1.2</v>
+      </c>
+      <c r="AA96">
+        <v>4.33</v>
+      </c>
+      <c r="AB96">
+        <v>1.62</v>
+      </c>
+      <c r="AC96">
+        <v>2.15</v>
+      </c>
+      <c r="AD96">
+        <v>2.55</v>
+      </c>
+      <c r="AE96">
+        <v>1.5</v>
+      </c>
+      <c r="AF96">
+        <v>1.53</v>
+      </c>
+      <c r="AG96">
+        <v>2.38</v>
+      </c>
+      <c r="AH96">
         <v>4.5</v>
       </c>
-      <c r="W96">
-        <v>1.18</v>
-      </c>
-      <c r="X96">
-        <v>1.01</v>
-      </c>
-      <c r="Y96">
-        <v>17</v>
-      </c>
-      <c r="Z96">
-        <v>1.15</v>
-      </c>
-      <c r="AA96">
-        <v>5.25</v>
-      </c>
-      <c r="AB96">
-        <v>1.4</v>
-      </c>
-      <c r="AC96">
-        <v>2.75</v>
-      </c>
-      <c r="AD96">
-        <v>2.1</v>
-      </c>
-      <c r="AE96">
-        <v>1.65</v>
-      </c>
-      <c r="AF96">
-        <v>1.4</v>
-      </c>
-      <c r="AG96">
-        <v>2.75</v>
-      </c>
-      <c r="AH96">
-        <v>3.5</v>
-      </c>
       <c r="AI96">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AJ96" t="s">
         <v>303</v>
@@ -12463,76 +12463,76 @@
         <v>301</v>
       </c>
       <c r="L97">
-        <v>2.15</v>
+        <v>1.53</v>
       </c>
       <c r="M97">
+        <v>3.79</v>
+      </c>
+      <c r="N97">
+        <v>4.9</v>
+      </c>
+      <c r="O97">
+        <v>1.43</v>
+      </c>
+      <c r="P97">
+        <v>10.5</v>
+      </c>
+      <c r="Q97">
         <v>3.2</v>
       </c>
-      <c r="N97">
-        <v>2.93</v>
-      </c>
-      <c r="O97">
-        <v>1.67</v>
-      </c>
-      <c r="P97">
-        <v>11.5</v>
-      </c>
-      <c r="Q97">
-        <v>2.2</v>
-      </c>
       <c r="R97">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S97">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="T97">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="U97">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="V97">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="W97">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X97">
         <v>1.04</v>
       </c>
       <c r="Y97">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Z97">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AA97">
-        <v>4.33</v>
+        <v>3.7</v>
       </c>
       <c r="AB97">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AC97">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AD97">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="AE97">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="AF97">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="AG97">
-        <v>2.38</v>
+        <v>1.83</v>
       </c>
       <c r="AH97">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AI97">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AJ97" t="s">
         <v>303</v>
@@ -12579,22 +12579,22 @@
         <v>301</v>
       </c>
       <c r="L98">
-        <v>1.56</v>
+        <v>2.63</v>
       </c>
       <c r="M98">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="N98">
-        <v>4.9</v>
+        <v>2.4</v>
       </c>
       <c r="O98">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="P98">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Q98">
-        <v>2.88</v>
+        <v>1.8</v>
       </c>
       <c r="R98">
         <v>1.22</v>
@@ -12615,10 +12615,10 @@
         <v>1.18</v>
       </c>
       <c r="X98">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y98">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z98">
         <v>1.15</v>
@@ -12627,25 +12627,25 @@
         <v>5.25</v>
       </c>
       <c r="AB98">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AC98">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="AD98">
         <v>2.1</v>
       </c>
       <c r="AE98">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AF98">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AG98">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="AH98">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AI98">
         <v>1.28</v>
@@ -12900,7 +12900,7 @@
         <v>68</v>
       </c>
       <c r="C101" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D101" t="s">
         <v>94</v>
@@ -12927,13 +12927,13 @@
         <v>301</v>
       </c>
       <c r="L101">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="M101">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="N101">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="O101">
         <v>1.44</v>
@@ -12948,19 +12948,19 @@
         <v>1.33</v>
       </c>
       <c r="S101">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="T101">
         <v>2.83</v>
       </c>
       <c r="U101">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="V101">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="W101">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X101">
         <v>1</v>
@@ -12975,10 +12975,10 @@
         <v>3.5</v>
       </c>
       <c r="AB101">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AC101">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AD101">
         <v>3.3</v>
@@ -13043,22 +13043,22 @@
         <v>301</v>
       </c>
       <c r="L102">
-        <v>1.52</v>
+        <v>2.4</v>
       </c>
       <c r="M102">
-        <v>3.74</v>
+        <v>3.1</v>
       </c>
       <c r="N102">
-        <v>5.1</v>
+        <v>2.63</v>
       </c>
       <c r="O102">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="P102">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="Q102">
-        <v>3</v>
+        <v>2.05</v>
       </c>
       <c r="R102">
         <v>1.25</v>
@@ -13067,16 +13067,16 @@
         <v>3.75</v>
       </c>
       <c r="T102">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="U102">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="V102">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="W102">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X102">
         <v>1.01</v>
@@ -13085,34 +13085,34 @@
         <v>17</v>
       </c>
       <c r="Z102">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AA102">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="AB102">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AC102">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="AD102">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AE102">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AF102">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="AG102">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="AH102">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="AI102">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AJ102" t="s">
         <v>303</v>
@@ -13159,22 +13159,22 @@
         <v>301</v>
       </c>
       <c r="L103">
-        <v>2.4</v>
+        <v>1.52</v>
       </c>
       <c r="M103">
-        <v>3.1</v>
+        <v>3.74</v>
       </c>
       <c r="N103">
-        <v>2.63</v>
+        <v>5.1</v>
       </c>
       <c r="O103">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="P103">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="Q103">
-        <v>2.05</v>
+        <v>3</v>
       </c>
       <c r="R103">
         <v>1.25</v>
@@ -13183,16 +13183,16 @@
         <v>3.75</v>
       </c>
       <c r="T103">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="U103">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="V103">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="W103">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X103">
         <v>1.01</v>
@@ -13201,34 +13201,34 @@
         <v>17</v>
       </c>
       <c r="Z103">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AA103">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="AB103">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="AC103">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="AD103">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AE103">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AF103">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="AG103">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="AH103">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="AI103">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AJ103" t="s">
         <v>303</v>

--- a/jogos_2025-07-19.xlsx
+++ b/jogos_2025-07-19.xlsx
@@ -235,12 +235,12 @@
     <t>Japan J1 League</t>
   </si>
   <si>
+    <t>South Korea K League 2</t>
+  </si>
+  <si>
     <t>South Korea K League 1</t>
   </si>
   <si>
-    <t>South Korea K League 2</t>
-  </si>
-  <si>
     <t>China China League One</t>
   </si>
   <si>
@@ -250,21 +250,21 @@
     <t>Norway Eliteserien</t>
   </si>
   <si>
+    <t>Kazakhstan Kazakhstan Premier League</t>
+  </si>
+  <si>
+    <t>Sweden Allsvenskan</t>
+  </si>
+  <si>
     <t>Sweden Superettan</t>
   </si>
   <si>
-    <t>Sweden Allsvenskan</t>
-  </si>
-  <si>
-    <t>Kazakhstan Kazakhstan Premier League</t>
+    <t>Iceland Úrvalsdeild</t>
   </si>
   <si>
     <t>Finland Veikkausliiga</t>
   </si>
   <si>
-    <t>Iceland Úrvalsdeild</t>
-  </si>
-  <si>
     <t>Estonia Meistriliiga</t>
   </si>
   <si>
@@ -280,21 +280,21 @@
     <t>Argentina Prim B Nacional</t>
   </si>
   <si>
+    <t>Brazil Serie A</t>
+  </si>
+  <si>
     <t>Brazil Serie B</t>
   </si>
   <si>
-    <t>Brazil Serie A</t>
+    <t>USA USL Championship</t>
+  </si>
+  <si>
+    <t>Brazil Serie C</t>
   </si>
   <si>
     <t>Canada Canadian Premier League</t>
   </si>
   <si>
-    <t>USA USL Championship</t>
-  </si>
-  <si>
-    <t>Brazil Serie C</t>
-  </si>
-  <si>
     <t>USA MLS</t>
   </si>
   <si>
@@ -316,36 +316,36 @@
     <t>Sutherland Sharks</t>
   </si>
   <si>
+    <t>Tokyo</t>
+  </si>
+  <si>
     <t>Shonan Bellmare</t>
   </si>
   <si>
+    <t>Gimpo Citizen</t>
+  </si>
+  <si>
+    <t>Jeonnam Dragons</t>
+  </si>
+  <si>
+    <t>Jeju United</t>
+  </si>
+  <si>
     <t>Gangwon</t>
   </si>
   <si>
+    <t>Hwaseong</t>
+  </si>
+  <si>
+    <t>Pohang Steelers</t>
+  </si>
+  <si>
+    <t>Yanbian Longding</t>
+  </si>
+  <si>
     <t>Seoul E-Land</t>
   </si>
   <si>
-    <t>Pohang Steelers</t>
-  </si>
-  <si>
-    <t>Yanbian Longding</t>
-  </si>
-  <si>
-    <t>Jeonnam Dragons</t>
-  </si>
-  <si>
-    <t>Gimpo Citizen</t>
-  </si>
-  <si>
-    <t>Tokyo</t>
-  </si>
-  <si>
-    <t>Jeju United</t>
-  </si>
-  <si>
-    <t>Hwaseong</t>
-  </si>
-  <si>
     <t>Shenyang Urban</t>
   </si>
   <si>
@@ -358,37 +358,40 @@
     <t>Hebei Kungfu</t>
   </si>
   <si>
+    <t>Sichuan Jiuniu</t>
+  </si>
+  <si>
     <t>Beijing Guoan</t>
   </si>
   <si>
-    <t>Sichuan Jiuniu</t>
+    <t>KFUM</t>
   </si>
   <si>
     <t>Henan Jianye</t>
   </si>
   <si>
-    <t>KFUM</t>
+    <t>Yelimay Semey</t>
+  </si>
+  <si>
+    <t>Öster</t>
   </si>
   <si>
     <t>Östersunds FK</t>
   </si>
   <si>
-    <t>Öster</t>
+    <t>Kairat</t>
   </si>
   <si>
     <t>Umeå</t>
   </si>
   <si>
-    <t>Yelimay Semey</t>
-  </si>
-  <si>
-    <t>Kairat</t>
+    <t>Oddevold</t>
   </si>
   <si>
     <t>Djurgården</t>
   </si>
   <si>
-    <t>Oddevold</t>
+    <t>Breidablik</t>
   </si>
   <si>
     <t>VPS</t>
@@ -397,9 +400,6 @@
     <t>Molde</t>
   </si>
   <si>
-    <t>Breidablik</t>
-  </si>
-  <si>
     <t>Sandviken</t>
   </si>
   <si>
@@ -409,12 +409,12 @@
     <t>Degerfors</t>
   </si>
   <si>
+    <t>Harju Jalgpallikool</t>
+  </si>
+  <si>
     <t>Viking</t>
   </si>
   <si>
-    <t>Harju Jalgpallikool</t>
-  </si>
-  <si>
     <t>Cobreloa</t>
   </si>
   <si>
@@ -424,10 +424,13 @@
     <t>San Lorenzo</t>
   </si>
   <si>
+    <t>Club Atlético Mitre</t>
+  </si>
+  <si>
     <t>Talleres Remedios</t>
   </si>
   <si>
-    <t>Club Atlético Mitre</t>
+    <t>Fortaleza</t>
   </si>
   <si>
     <t>Goiás</t>
@@ -439,145 +442,148 @@
     <t>Deportes Santa Cruz</t>
   </si>
   <si>
-    <t>Fortaleza</t>
-  </si>
-  <si>
     <t>Lanús</t>
   </si>
   <si>
+    <t>Estudiantes Caseros</t>
+  </si>
+  <si>
+    <t>Deportivo Madryn</t>
+  </si>
+  <si>
+    <t>Colegiales</t>
+  </si>
+  <si>
+    <t>Colón</t>
+  </si>
+  <si>
+    <t>Tristán Suárez</t>
+  </si>
+  <si>
+    <t>Estudiantes Río Cuarto</t>
+  </si>
+  <si>
     <t>Defensores Unidos</t>
   </si>
   <si>
     <t>Chaco For Ever</t>
   </si>
   <si>
+    <t>Atlanta</t>
+  </si>
+  <si>
+    <t>Deportivo Maipú</t>
+  </si>
+  <si>
+    <t>All Boys</t>
+  </si>
+  <si>
+    <t>Temperley</t>
+  </si>
+  <si>
+    <t>Alvarado</t>
+  </si>
+  <si>
+    <t>Rhode Island</t>
+  </si>
+  <si>
+    <t>Gimnasia y Tiro</t>
+  </si>
+  <si>
     <t>Deportivo Morón</t>
   </si>
   <si>
-    <t>Estudiantes Río Cuarto</t>
-  </si>
-  <si>
-    <t>Tristán Suárez</t>
+    <t>Ituano</t>
+  </si>
+  <si>
+    <t>Arsenal de Sarandí</t>
+  </si>
+  <si>
+    <t>ABC</t>
   </si>
   <si>
     <t>York9 FC</t>
   </si>
   <si>
-    <t>Deportivo Maipú</t>
-  </si>
-  <si>
-    <t>Arsenal de Sarandí</t>
-  </si>
-  <si>
-    <t>Alvarado</t>
-  </si>
-  <si>
-    <t>Atlanta</t>
-  </si>
-  <si>
-    <t>All Boys</t>
-  </si>
-  <si>
-    <t>Deportivo Madryn</t>
-  </si>
-  <si>
-    <t>Rhode Island</t>
-  </si>
-  <si>
-    <t>Ituano</t>
-  </si>
-  <si>
-    <t>ABC</t>
-  </si>
-  <si>
-    <t>Colón</t>
-  </si>
-  <si>
-    <t>Estudiantes Caseros</t>
-  </si>
-  <si>
-    <t>Temperley</t>
-  </si>
-  <si>
-    <t>Colegiales</t>
-  </si>
-  <si>
-    <t>Gimnasia y Tiro</t>
-  </si>
-  <si>
     <t>Vasco da Gama</t>
   </si>
   <si>
+    <t>Coritiba</t>
+  </si>
+  <si>
+    <t>Mirassol</t>
+  </si>
+  <si>
+    <t>Coquimbo Unido</t>
+  </si>
+  <si>
     <t>Avaí</t>
   </si>
   <si>
-    <t>Coritiba</t>
-  </si>
-  <si>
-    <t>Mirassol</t>
-  </si>
-  <si>
-    <t>Coquimbo Unido</t>
+    <t>Godoy Cruz</t>
   </si>
   <si>
     <t>Platense</t>
   </si>
   <si>
-    <t>Godoy Cruz</t>
+    <t>Ponte Preta</t>
   </si>
   <si>
     <t>Londrina</t>
   </si>
   <si>
-    <t>Ponte Preta</t>
-  </si>
-  <si>
     <t>Crown Legacy</t>
   </si>
   <si>
+    <t>Loudoun United</t>
+  </si>
+  <si>
     <t>Concepción</t>
   </si>
   <si>
-    <t>Loudoun United</t>
-  </si>
-  <si>
     <t>Chattanooga FC</t>
   </si>
   <si>
+    <t>Montreal Impact</t>
+  </si>
+  <si>
     <t>Carolina Core</t>
   </si>
   <si>
+    <t>Volta Redonda</t>
+  </si>
+  <si>
+    <t>Columbus Crew</t>
+  </si>
+  <si>
+    <t>New York RB</t>
+  </si>
+  <si>
+    <t>New England Revolution</t>
+  </si>
+  <si>
+    <t>Charleston Battery</t>
+  </si>
+  <si>
     <t>Atlanta United FC</t>
   </si>
   <si>
-    <t>Columbus Crew</t>
-  </si>
-  <si>
-    <t>Montreal Impact</t>
-  </si>
-  <si>
-    <t>Volta Redonda</t>
-  </si>
-  <si>
-    <t>Charleston Battery</t>
-  </si>
-  <si>
-    <t>New York RB</t>
-  </si>
-  <si>
-    <t>New England Revolution</t>
+    <t>Instituto</t>
+  </si>
+  <si>
+    <t>Louisville City</t>
+  </si>
+  <si>
+    <t>Birmingham Legion</t>
   </si>
   <si>
     <t>São Paulo</t>
   </si>
   <si>
-    <t>Birmingham Legion</t>
-  </si>
-  <si>
-    <t>Louisville City</t>
-  </si>
-  <si>
-    <t>Instituto</t>
+    <t>Sporting KC</t>
+  </si>
+  <si>
+    <t>Nashville SC</t>
   </si>
   <si>
     <t>Seattle Sounders</t>
@@ -586,12 +592,6 @@
     <t>FC Dallas</t>
   </si>
   <si>
-    <t>Nashville SC</t>
-  </si>
-  <si>
-    <t>Sporting KC</t>
-  </si>
-  <si>
     <t>Houston Dynamo</t>
   </si>
   <si>
@@ -625,36 +625,36 @@
     <t>Blacktown City</t>
   </si>
   <si>
+    <t>Urawa Reds</t>
+  </si>
+  <si>
     <t>Cerezo Osaka</t>
   </si>
   <si>
+    <t>Ansan Greeners</t>
+  </si>
+  <si>
+    <t>Suwon Bluewings</t>
+  </si>
+  <si>
+    <t>Anyang</t>
+  </si>
+  <si>
     <t>Daejeon Citizen</t>
   </si>
   <si>
+    <t>Busan I'Park</t>
+  </si>
+  <si>
+    <t>Jeonbuk Motors</t>
+  </si>
+  <si>
+    <t>Qingdao Red Lions</t>
+  </si>
+  <si>
     <t>Seongnam</t>
   </si>
   <si>
-    <t>Jeonbuk Motors</t>
-  </si>
-  <si>
-    <t>Qingdao Red Lions</t>
-  </si>
-  <si>
-    <t>Suwon Bluewings</t>
-  </si>
-  <si>
-    <t>Ansan Greeners</t>
-  </si>
-  <si>
-    <t>Urawa Reds</t>
-  </si>
-  <si>
-    <t>Anyang</t>
-  </si>
-  <si>
-    <t>Busan I'Park</t>
-  </si>
-  <si>
     <t>Chongqing Tongliang Long</t>
   </si>
   <si>
@@ -667,37 +667,40 @@
     <t>Nantong Zhiyun</t>
   </si>
   <si>
+    <t>Qingdao Jonoon</t>
+  </si>
+  <si>
     <t>Shanghai Shenhua</t>
   </si>
   <si>
-    <t>Qingdao Jonoon</t>
+    <t>Brann</t>
   </si>
   <si>
     <t>Meizhou Hakka</t>
   </si>
   <si>
-    <t>Brann</t>
+    <t>Zhenys</t>
+  </si>
+  <si>
+    <t>Malmö FF</t>
   </si>
   <si>
     <t>Falkenberg</t>
   </si>
   <si>
-    <t>Malmö FF</t>
+    <t>Kaisar</t>
   </si>
   <si>
     <t>Örebro</t>
   </si>
   <si>
-    <t>Zhenys</t>
-  </si>
-  <si>
-    <t>Kaisar</t>
+    <t>Örgryte</t>
   </si>
   <si>
     <t>Elfsborg</t>
   </si>
   <si>
-    <t>Örgryte</t>
+    <t>Vestri</t>
   </si>
   <si>
     <t>KuPS</t>
@@ -706,9 +709,6 @@
     <t>Strømsgodset</t>
   </si>
   <si>
-    <t>Vestri</t>
-  </si>
-  <si>
     <t>Västerås SK</t>
   </si>
   <si>
@@ -718,12 +718,12 @@
     <t>GAIS</t>
   </si>
   <si>
+    <t>Tallinna FC Levadia</t>
+  </si>
+  <si>
     <t>FK Bodo - Glimt</t>
   </si>
   <si>
-    <t>Tallinna FC Levadia</t>
-  </si>
-  <si>
     <t>San Marcos</t>
   </si>
   <si>
@@ -733,10 +733,13 @@
     <t>Gimnasia La Plata</t>
   </si>
   <si>
+    <t>Central Norte</t>
+  </si>
+  <si>
     <t>Defensores de Belgrano</t>
   </si>
   <si>
-    <t>Central Norte</t>
+    <t>Bahia</t>
   </si>
   <si>
     <t>Cuiabá</t>
@@ -748,157 +751,154 @@
     <t>Recoleta</t>
   </si>
   <si>
-    <t>Bahia</t>
-  </si>
-  <si>
     <t>Rosario Central</t>
   </si>
   <si>
+    <t>San Telmo</t>
+  </si>
+  <si>
+    <t>Patronato</t>
+  </si>
+  <si>
+    <t>Quilmes</t>
+  </si>
+  <si>
+    <t>Gimnasia Mendoza</t>
+  </si>
+  <si>
+    <t>Los Andes</t>
+  </si>
+  <si>
+    <t>Nueva Chicago</t>
+  </si>
+  <si>
     <t>Agropecuario</t>
   </si>
   <si>
     <t>Almirante Brown</t>
   </si>
   <si>
+    <t>Racing Córdoba</t>
+  </si>
+  <si>
+    <t>Club Atlético Güemes</t>
+  </si>
+  <si>
+    <t>Almagro</t>
+  </si>
+  <si>
+    <t>Gimnasia Jujuy</t>
+  </si>
+  <si>
+    <t>Ferro Carril Oeste</t>
+  </si>
+  <si>
+    <t>Hartford Athletic</t>
+  </si>
+  <si>
+    <t>San Martín Tucumán</t>
+  </si>
+  <si>
     <t>Chacarita Juniors</t>
   </si>
   <si>
-    <t>Nueva Chicago</t>
-  </si>
-  <si>
-    <t>Los Andes</t>
+    <t>Botafogo PB</t>
+  </si>
+  <si>
+    <t>San Miguel</t>
+  </si>
+  <si>
+    <t>Maringá</t>
   </si>
   <si>
     <t>Vancouver FC</t>
   </si>
   <si>
-    <t>Club Atlético Güemes</t>
-  </si>
-  <si>
-    <t>San Miguel</t>
-  </si>
-  <si>
-    <t>Ferro Carril Oeste</t>
-  </si>
-  <si>
-    <t>Racing Córdoba</t>
-  </si>
-  <si>
-    <t>Almagro</t>
-  </si>
-  <si>
-    <t>Patronato</t>
-  </si>
-  <si>
-    <t>Hartford Athletic</t>
-  </si>
-  <si>
-    <t>Botafogo PB</t>
-  </si>
-  <si>
-    <t>Maringá</t>
-  </si>
-  <si>
-    <t>Gimnasia Mendoza</t>
-  </si>
-  <si>
-    <t>San Telmo</t>
-  </si>
-  <si>
-    <t>Gimnasia Jujuy</t>
-  </si>
-  <si>
-    <t>Quilmes</t>
-  </si>
-  <si>
-    <t>San Martín Tucumán</t>
-  </si>
-  <si>
     <t>Grêmio</t>
   </si>
   <si>
+    <t>Paysandu</t>
+  </si>
+  <si>
+    <t>Santos</t>
+  </si>
+  <si>
+    <t>Deportes Iquique</t>
+  </si>
+  <si>
     <t>Vila Nova</t>
   </si>
   <si>
-    <t>Paysandu</t>
-  </si>
-  <si>
-    <t>Santos</t>
-  </si>
-  <si>
-    <t>Deportes Iquique</t>
+    <t>Sarmiento</t>
   </si>
   <si>
     <t>Vélez Sarsfield</t>
   </si>
   <si>
-    <t>Sarmiento</t>
+    <t>Floresta</t>
   </si>
   <si>
     <t>Itabaiana</t>
   </si>
   <si>
-    <t>Floresta</t>
-  </si>
-  <si>
     <t>Philadelphia Union II</t>
   </si>
   <si>
+    <t>Oakland Roots</t>
+  </si>
+  <si>
     <t>Antofagasta</t>
   </si>
   <si>
-    <t>Oakland Roots</t>
-  </si>
-  <si>
     <t>Inter Miami II</t>
   </si>
   <si>
+    <t>Chicago Fire</t>
+  </si>
+  <si>
     <t>Atlanta United II</t>
   </si>
   <si>
+    <t>Atlético PR</t>
+  </si>
+  <si>
+    <t>DC United</t>
+  </si>
+  <si>
+    <t>Inter Miami</t>
+  </si>
+  <si>
+    <t>Orlando City</t>
+  </si>
+  <si>
+    <t>Miami FC II</t>
+  </si>
+  <si>
     <t>Charlotte</t>
   </si>
   <si>
-    <t>DC United</t>
-  </si>
-  <si>
-    <t>Chicago Fire</t>
-  </si>
-  <si>
-    <t>Atlético PR</t>
-  </si>
-  <si>
-    <t>Miami FC II</t>
-  </si>
-  <si>
-    <t>Inter Miami</t>
-  </si>
-  <si>
-    <t>Orlando City</t>
+    <t>River Plate</t>
+  </si>
+  <si>
+    <t>Tulsa Roughnecks</t>
+  </si>
+  <si>
+    <t>Colorado Springs</t>
   </si>
   <si>
     <t>Corinthians</t>
   </si>
   <si>
-    <t>Colorado Springs</t>
-  </si>
-  <si>
-    <t>Tulsa Roughnecks</t>
-  </si>
-  <si>
-    <t>River Plate</t>
+    <t>New York City</t>
+  </si>
+  <si>
+    <t>Toronto</t>
   </si>
   <si>
     <t>SJ Earthquakes</t>
   </si>
   <si>
     <t>St. Louis City</t>
-  </si>
-  <si>
-    <t>Toronto</t>
-  </si>
-  <si>
-    <t>New York City</t>
   </si>
   <si>
     <t>Philadelphia Union</t>
@@ -2023,76 +2023,76 @@
         <v>301</v>
       </c>
       <c r="L7">
-        <v>2.74</v>
+        <v>2.4</v>
       </c>
       <c r="M7">
-        <v>3.41</v>
+        <v>3.26</v>
       </c>
       <c r="N7">
-        <v>2.16</v>
+        <v>2.52</v>
       </c>
       <c r="O7">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="P7">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="Q7">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="R7">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="S7">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="T7">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="U7">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="V7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W7">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X7">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y7">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="Z7">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AA7">
-        <v>3.95</v>
+        <v>3.35</v>
       </c>
       <c r="AB7">
-        <v>1.65</v>
+        <v>1.87</v>
       </c>
       <c r="AC7">
+        <v>1.83</v>
+      </c>
+      <c r="AD7">
+        <v>3.4</v>
+      </c>
+      <c r="AE7">
+        <v>1.3</v>
+      </c>
+      <c r="AF7">
+        <v>1.7</v>
+      </c>
+      <c r="AG7">
         <v>2</v>
       </c>
-      <c r="AD7">
-        <v>2.8</v>
-      </c>
-      <c r="AE7">
-        <v>1.42</v>
-      </c>
-      <c r="AF7">
-        <v>1.55</v>
-      </c>
-      <c r="AG7">
-        <v>2.25</v>
-      </c>
       <c r="AH7">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="AI7">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AJ7" t="s">
         <v>303</v>
@@ -2112,7 +2112,7 @@
         <v>43</v>
       </c>
       <c r="C8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D8" t="s">
         <v>94</v>
@@ -2139,76 +2139,76 @@
         <v>301</v>
       </c>
       <c r="L8">
-        <v>2.29</v>
+        <v>2.74</v>
       </c>
       <c r="M8">
-        <v>3.12</v>
+        <v>3.41</v>
       </c>
       <c r="N8">
-        <v>2.75</v>
+        <v>2.16</v>
       </c>
       <c r="O8">
+        <v>2.1</v>
+      </c>
+      <c r="P8">
+        <v>9.5</v>
+      </c>
+      <c r="Q8">
+        <v>1.9</v>
+      </c>
+      <c r="R8">
+        <v>1.33</v>
+      </c>
+      <c r="S8">
+        <v>3</v>
+      </c>
+      <c r="T8">
+        <v>2.45</v>
+      </c>
+      <c r="U8">
+        <v>1.48</v>
+      </c>
+      <c r="V8">
+        <v>6</v>
+      </c>
+      <c r="W8">
+        <v>1.12</v>
+      </c>
+      <c r="X8">
+        <v>1.05</v>
+      </c>
+      <c r="Y8">
+        <v>9.5</v>
+      </c>
+      <c r="Z8">
+        <v>1.25</v>
+      </c>
+      <c r="AA8">
+        <v>3.95</v>
+      </c>
+      <c r="AB8">
+        <v>1.65</v>
+      </c>
+      <c r="AC8">
         <v>2</v>
       </c>
-      <c r="P8">
-        <v>8</v>
-      </c>
-      <c r="Q8">
-        <v>2.1</v>
-      </c>
-      <c r="R8">
+      <c r="AD8">
+        <v>2.8</v>
+      </c>
+      <c r="AE8">
         <v>1.42</v>
       </c>
-      <c r="S8">
-        <v>2.65</v>
-      </c>
-      <c r="T8">
-        <v>2.88</v>
-      </c>
-      <c r="U8">
-        <v>1.36</v>
-      </c>
-      <c r="V8">
-        <v>7</v>
-      </c>
-      <c r="W8">
-        <v>1.08</v>
-      </c>
-      <c r="X8">
-        <v>1.07</v>
-      </c>
-      <c r="Y8">
-        <v>8</v>
-      </c>
-      <c r="Z8">
-        <v>1.33</v>
-      </c>
-      <c r="AA8">
-        <v>3.25</v>
-      </c>
-      <c r="AB8">
-        <v>1.93</v>
-      </c>
-      <c r="AC8">
-        <v>1.77</v>
-      </c>
-      <c r="AD8">
-        <v>3.45</v>
-      </c>
-      <c r="AE8">
-        <v>1.3</v>
-      </c>
       <c r="AF8">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AG8">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AH8">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="AI8">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AJ8" t="s">
         <v>303</v>
@@ -2228,7 +2228,7 @@
         <v>43</v>
       </c>
       <c r="C9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D9" t="s">
         <v>94</v>
@@ -2255,76 +2255,76 @@
         <v>301</v>
       </c>
       <c r="L9">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="M9">
-        <v>3.11</v>
+        <v>3.28</v>
       </c>
       <c r="N9">
-        <v>3.97</v>
+        <v>4.2</v>
       </c>
       <c r="O9">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="P9">
-        <v>12</v>
+        <v>6.75</v>
       </c>
       <c r="Q9">
-        <v>2.31</v>
+        <v>3.18</v>
       </c>
       <c r="R9">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="S9">
-        <v>3.01</v>
+        <v>2.56</v>
       </c>
       <c r="T9">
-        <v>2.84</v>
+        <v>3.34</v>
       </c>
       <c r="U9">
+        <v>1.28</v>
+      </c>
+      <c r="V9">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="W9">
+        <v>1.02</v>
+      </c>
+      <c r="X9">
+        <v>1.05</v>
+      </c>
+      <c r="Y9">
+        <v>8</v>
+      </c>
+      <c r="Z9">
         <v>1.4</v>
       </c>
-      <c r="V9">
-        <v>6.5</v>
-      </c>
-      <c r="W9">
-        <v>1.05</v>
-      </c>
-      <c r="X9">
-        <v>1.01</v>
-      </c>
-      <c r="Y9">
-        <v>11</v>
-      </c>
-      <c r="Z9">
-        <v>1.25</v>
-      </c>
       <c r="AA9">
-        <v>3.6</v>
+        <v>2.75</v>
       </c>
       <c r="AB9">
-        <v>1.87</v>
+        <v>2.3</v>
       </c>
       <c r="AC9">
-        <v>1.83</v>
+        <v>1.5</v>
       </c>
       <c r="AD9">
-        <v>3.2</v>
+        <v>4.8</v>
       </c>
       <c r="AE9">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AF9">
-        <v>1.67</v>
+        <v>2.2</v>
       </c>
       <c r="AG9">
-        <v>2.1</v>
+        <v>1.62</v>
       </c>
       <c r="AH9">
-        <v>6.5</v>
+        <v>9</v>
       </c>
       <c r="AI9">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AJ9" t="s">
         <v>303</v>
@@ -2371,76 +2371,76 @@
         <v>301</v>
       </c>
       <c r="L10">
-        <v>2.85</v>
+        <v>3.74</v>
       </c>
       <c r="M10">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="N10">
-        <v>2.3</v>
+        <v>1.77</v>
       </c>
       <c r="O10">
         <v>2.25</v>
       </c>
       <c r="P10">
-        <v>7</v>
+        <v>13.75</v>
       </c>
       <c r="Q10">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="R10">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="S10">
+        <v>3.3</v>
+      </c>
+      <c r="T10">
         <v>2.45</v>
       </c>
-      <c r="T10">
-        <v>3.2</v>
-      </c>
       <c r="U10">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="V10">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="W10">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X10">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="Z10">
-        <v>1.42</v>
+        <v>1.16</v>
       </c>
       <c r="AA10">
-        <v>2.8</v>
+        <v>4.05</v>
       </c>
       <c r="AB10">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="AC10">
-        <v>1.61</v>
+        <v>2</v>
       </c>
       <c r="AD10">
-        <v>4.2</v>
+        <v>2.69</v>
       </c>
       <c r="AE10">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AF10">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AG10">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AH10">
-        <v>8.5</v>
+        <v>5.15</v>
       </c>
       <c r="AI10">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AJ10" t="s">
         <v>303</v>
@@ -2460,7 +2460,7 @@
         <v>43</v>
       </c>
       <c r="C11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D11" t="s">
         <v>94</v>
@@ -2487,73 +2487,73 @@
         <v>301</v>
       </c>
       <c r="L11">
-        <v>1.41</v>
+        <v>2.32</v>
       </c>
       <c r="M11">
-        <v>3.82</v>
+        <v>3.03</v>
       </c>
       <c r="N11">
-        <v>5.93</v>
+        <v>2.79</v>
       </c>
       <c r="O11">
+        <v>1.91</v>
+      </c>
+      <c r="P11">
+        <v>8</v>
+      </c>
+      <c r="Q11">
+        <v>2.25</v>
+      </c>
+      <c r="R11">
+        <v>1.42</v>
+      </c>
+      <c r="S11">
+        <v>2.65</v>
+      </c>
+      <c r="T11">
+        <v>2.88</v>
+      </c>
+      <c r="U11">
+        <v>1.36</v>
+      </c>
+      <c r="V11">
+        <v>7</v>
+      </c>
+      <c r="W11">
+        <v>1.08</v>
+      </c>
+      <c r="X11">
+        <v>1.07</v>
+      </c>
+      <c r="Y11">
+        <v>8</v>
+      </c>
+      <c r="Z11">
         <v>1.38</v>
       </c>
-      <c r="P11">
-        <v>8.9</v>
-      </c>
-      <c r="Q11">
-        <v>3.58</v>
-      </c>
-      <c r="R11">
-        <v>1.36</v>
-      </c>
-      <c r="S11">
-        <v>2.8</v>
-      </c>
-      <c r="T11">
-        <v>2.68</v>
-      </c>
-      <c r="U11">
-        <v>1.39</v>
-      </c>
-      <c r="V11">
-        <v>6.25</v>
-      </c>
-      <c r="W11">
-        <v>1.06</v>
-      </c>
-      <c r="X11">
-        <v>1.01</v>
-      </c>
-      <c r="Y11">
-        <v>8.9</v>
-      </c>
-      <c r="Z11">
-        <v>1.29</v>
-      </c>
       <c r="AA11">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="AB11">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AC11">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AD11">
-        <v>2.97</v>
+        <v>3.8</v>
       </c>
       <c r="AE11">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AF11">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="AG11">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="AH11">
-        <v>5.55</v>
+        <v>7.5</v>
       </c>
       <c r="AI11">
         <v>1.08</v>
@@ -2603,73 +2603,73 @@
         <v>301</v>
       </c>
       <c r="L12">
-        <v>3.74</v>
+        <v>2.29</v>
       </c>
       <c r="M12">
-        <v>3.5</v>
+        <v>3.12</v>
       </c>
       <c r="N12">
+        <v>2.75</v>
+      </c>
+      <c r="O12">
+        <v>2</v>
+      </c>
+      <c r="P12">
+        <v>8</v>
+      </c>
+      <c r="Q12">
+        <v>2.1</v>
+      </c>
+      <c r="R12">
+        <v>1.42</v>
+      </c>
+      <c r="S12">
+        <v>2.65</v>
+      </c>
+      <c r="T12">
+        <v>2.88</v>
+      </c>
+      <c r="U12">
+        <v>1.36</v>
+      </c>
+      <c r="V12">
+        <v>7</v>
+      </c>
+      <c r="W12">
+        <v>1.08</v>
+      </c>
+      <c r="X12">
+        <v>1.07</v>
+      </c>
+      <c r="Y12">
+        <v>8</v>
+      </c>
+      <c r="Z12">
+        <v>1.33</v>
+      </c>
+      <c r="AA12">
+        <v>3.25</v>
+      </c>
+      <c r="AB12">
+        <v>1.93</v>
+      </c>
+      <c r="AC12">
         <v>1.77</v>
       </c>
-      <c r="O12">
-        <v>2.25</v>
-      </c>
-      <c r="P12">
-        <v>13.75</v>
-      </c>
-      <c r="Q12">
-        <v>1.67</v>
-      </c>
-      <c r="R12">
+      <c r="AD12">
+        <v>3.45</v>
+      </c>
+      <c r="AE12">
         <v>1.3</v>
       </c>
-      <c r="S12">
-        <v>3.3</v>
-      </c>
-      <c r="T12">
-        <v>2.45</v>
-      </c>
-      <c r="U12">
-        <v>1.5</v>
-      </c>
-      <c r="V12">
-        <v>6</v>
-      </c>
-      <c r="W12">
-        <v>1.12</v>
-      </c>
-      <c r="X12">
-        <v>1.01</v>
-      </c>
-      <c r="Y12">
-        <v>11</v>
-      </c>
-      <c r="Z12">
-        <v>1.16</v>
-      </c>
-      <c r="AA12">
-        <v>4.05</v>
-      </c>
-      <c r="AB12">
-        <v>1.65</v>
-      </c>
-      <c r="AC12">
+      <c r="AF12">
+        <v>1.7</v>
+      </c>
+      <c r="AG12">
         <v>2</v>
       </c>
-      <c r="AD12">
-        <v>2.69</v>
-      </c>
-      <c r="AE12">
-        <v>1.36</v>
-      </c>
-      <c r="AF12">
-        <v>1.62</v>
-      </c>
-      <c r="AG12">
-        <v>2.2</v>
-      </c>
       <c r="AH12">
-        <v>5.15</v>
+        <v>6.5</v>
       </c>
       <c r="AI12">
         <v>1.1</v>
@@ -2692,7 +2692,7 @@
         <v>43</v>
       </c>
       <c r="C13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D13" t="s">
         <v>94</v>
@@ -2719,76 +2719,76 @@
         <v>301</v>
       </c>
       <c r="L13">
-        <v>1.74</v>
+        <v>3.41</v>
       </c>
       <c r="M13">
-        <v>3.28</v>
+        <v>3.32</v>
       </c>
       <c r="N13">
-        <v>4.2</v>
+        <v>1.9</v>
       </c>
       <c r="O13">
+        <v>2.42</v>
+      </c>
+      <c r="P13">
+        <v>7.1</v>
+      </c>
+      <c r="Q13">
+        <v>1.78</v>
+      </c>
+      <c r="R13">
+        <v>1.44</v>
+      </c>
+      <c r="S13">
+        <v>2.62</v>
+      </c>
+      <c r="T13">
+        <v>3.25</v>
+      </c>
+      <c r="U13">
+        <v>1.3</v>
+      </c>
+      <c r="V13">
+        <v>10</v>
+      </c>
+      <c r="W13">
+        <v>1.05</v>
+      </c>
+      <c r="X13">
+        <v>1.04</v>
+      </c>
+      <c r="Y13">
+        <v>7.1</v>
+      </c>
+      <c r="Z13">
+        <v>1.41</v>
+      </c>
+      <c r="AA13">
+        <v>2.52</v>
+      </c>
+      <c r="AB13">
+        <v>2.2</v>
+      </c>
+      <c r="AC13">
         <v>1.53</v>
       </c>
-      <c r="P13">
-        <v>6.75</v>
-      </c>
-      <c r="Q13">
-        <v>3.18</v>
-      </c>
-      <c r="R13">
-        <v>1.48</v>
-      </c>
-      <c r="S13">
-        <v>2.56</v>
-      </c>
-      <c r="T13">
-        <v>3.34</v>
-      </c>
-      <c r="U13">
-        <v>1.28</v>
-      </c>
-      <c r="V13">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="W13">
-        <v>1.02</v>
-      </c>
-      <c r="X13">
-        <v>1.05</v>
-      </c>
-      <c r="Y13">
-        <v>8</v>
-      </c>
-      <c r="Z13">
-        <v>1.4</v>
-      </c>
-      <c r="AA13">
-        <v>2.75</v>
-      </c>
-      <c r="AB13">
-        <v>2.3</v>
-      </c>
-      <c r="AC13">
-        <v>1.5</v>
-      </c>
       <c r="AD13">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="AE13">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF13">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AG13">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AH13">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AI13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AJ13" t="s">
         <v>303</v>
@@ -2808,7 +2808,7 @@
         <v>43</v>
       </c>
       <c r="C14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D14" t="s">
         <v>94</v>
@@ -2835,76 +2835,76 @@
         <v>301</v>
       </c>
       <c r="L14">
-        <v>2.4</v>
+        <v>2.85</v>
       </c>
       <c r="M14">
-        <v>3.26</v>
+        <v>3</v>
       </c>
       <c r="N14">
-        <v>2.52</v>
+        <v>2.3</v>
       </c>
       <c r="O14">
+        <v>2.25</v>
+      </c>
+      <c r="P14">
+        <v>7</v>
+      </c>
+      <c r="Q14">
+        <v>1.95</v>
+      </c>
+      <c r="R14">
+        <v>1.48</v>
+      </c>
+      <c r="S14">
+        <v>2.45</v>
+      </c>
+      <c r="T14">
+        <v>3.2</v>
+      </c>
+      <c r="U14">
+        <v>1.3</v>
+      </c>
+      <c r="V14">
+        <v>7.5</v>
+      </c>
+      <c r="W14">
+        <v>1.07</v>
+      </c>
+      <c r="X14">
+        <v>1.09</v>
+      </c>
+      <c r="Y14">
+        <v>7</v>
+      </c>
+      <c r="Z14">
+        <v>1.42</v>
+      </c>
+      <c r="AA14">
+        <v>2.8</v>
+      </c>
+      <c r="AB14">
         <v>2.05</v>
       </c>
-      <c r="P14">
+      <c r="AC14">
+        <v>1.61</v>
+      </c>
+      <c r="AD14">
+        <v>4.2</v>
+      </c>
+      <c r="AE14">
+        <v>1.22</v>
+      </c>
+      <c r="AF14">
+        <v>1.85</v>
+      </c>
+      <c r="AG14">
+        <v>1.8</v>
+      </c>
+      <c r="AH14">
         <v>8.5</v>
       </c>
-      <c r="Q14">
-        <v>2.05</v>
-      </c>
-      <c r="R14">
-        <v>1.4</v>
-      </c>
-      <c r="S14">
-        <v>2.75</v>
-      </c>
-      <c r="T14">
-        <v>2.8</v>
-      </c>
-      <c r="U14">
-        <v>1.38</v>
-      </c>
-      <c r="V14">
-        <v>7</v>
-      </c>
-      <c r="W14">
-        <v>1.08</v>
-      </c>
-      <c r="X14">
+      <c r="AI14">
         <v>1.06</v>
-      </c>
-      <c r="Y14">
-        <v>8.5</v>
-      </c>
-      <c r="Z14">
-        <v>1.3</v>
-      </c>
-      <c r="AA14">
-        <v>3.35</v>
-      </c>
-      <c r="AB14">
-        <v>1.87</v>
-      </c>
-      <c r="AC14">
-        <v>1.83</v>
-      </c>
-      <c r="AD14">
-        <v>3.4</v>
-      </c>
-      <c r="AE14">
-        <v>1.3</v>
-      </c>
-      <c r="AF14">
-        <v>1.7</v>
-      </c>
-      <c r="AG14">
-        <v>2</v>
-      </c>
-      <c r="AH14">
-        <v>6.5</v>
-      </c>
-      <c r="AI14">
-        <v>1.1</v>
       </c>
       <c r="AJ14" t="s">
         <v>303</v>
@@ -2924,7 +2924,7 @@
         <v>43</v>
       </c>
       <c r="C15" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D15" t="s">
         <v>94</v>
@@ -2951,73 +2951,73 @@
         <v>301</v>
       </c>
       <c r="L15">
-        <v>2.32</v>
+        <v>1.41</v>
       </c>
       <c r="M15">
-        <v>3.03</v>
+        <v>3.82</v>
       </c>
       <c r="N15">
-        <v>2.79</v>
+        <v>5.93</v>
       </c>
       <c r="O15">
-        <v>1.91</v>
+        <v>1.38</v>
       </c>
       <c r="P15">
-        <v>8</v>
+        <v>8.9</v>
       </c>
       <c r="Q15">
-        <v>2.25</v>
+        <v>3.58</v>
       </c>
       <c r="R15">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="S15">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="T15">
-        <v>2.88</v>
+        <v>2.68</v>
       </c>
       <c r="U15">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="V15">
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="W15">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X15">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>8</v>
+        <v>8.9</v>
       </c>
       <c r="Z15">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AA15">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="AB15">
+        <v>1.85</v>
+      </c>
+      <c r="AC15">
+        <v>1.85</v>
+      </c>
+      <c r="AD15">
+        <v>2.97</v>
+      </c>
+      <c r="AE15">
+        <v>1.3</v>
+      </c>
+      <c r="AF15">
         <v>2</v>
       </c>
-      <c r="AC15">
-        <v>1.65</v>
-      </c>
-      <c r="AD15">
-        <v>3.8</v>
-      </c>
-      <c r="AE15">
-        <v>1.25</v>
-      </c>
-      <c r="AF15">
-        <v>1.77</v>
-      </c>
       <c r="AG15">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AH15">
-        <v>7.5</v>
+        <v>5.55</v>
       </c>
       <c r="AI15">
         <v>1.08</v>
@@ -3040,7 +3040,7 @@
         <v>43</v>
       </c>
       <c r="C16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D16" t="s">
         <v>94</v>
@@ -3067,76 +3067,76 @@
         <v>301</v>
       </c>
       <c r="L16">
-        <v>3.41</v>
+        <v>1.83</v>
       </c>
       <c r="M16">
-        <v>3.32</v>
+        <v>3.11</v>
       </c>
       <c r="N16">
-        <v>1.9</v>
+        <v>3.97</v>
       </c>
       <c r="O16">
-        <v>2.42</v>
+        <v>1.67</v>
       </c>
       <c r="P16">
-        <v>7.1</v>
+        <v>12</v>
       </c>
       <c r="Q16">
-        <v>1.78</v>
+        <v>2.31</v>
       </c>
       <c r="R16">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="S16">
-        <v>2.62</v>
+        <v>3.01</v>
       </c>
       <c r="T16">
-        <v>3.25</v>
+        <v>2.84</v>
       </c>
       <c r="U16">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="V16">
-        <v>10</v>
+        <v>6.5</v>
       </c>
       <c r="W16">
         <v>1.05</v>
       </c>
       <c r="X16">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>7.1</v>
+        <v>11</v>
       </c>
       <c r="Z16">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="AA16">
-        <v>2.52</v>
+        <v>3.6</v>
       </c>
       <c r="AB16">
-        <v>2.2</v>
+        <v>1.87</v>
       </c>
       <c r="AC16">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="AD16">
-        <v>4.3</v>
+        <v>3.2</v>
       </c>
       <c r="AE16">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AF16">
-        <v>2.05</v>
+        <v>1.67</v>
       </c>
       <c r="AG16">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="AH16">
-        <v>8.4</v>
+        <v>6.5</v>
       </c>
       <c r="AI16">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AJ16" t="s">
         <v>303</v>
@@ -3647,40 +3647,40 @@
         <v>301</v>
       </c>
       <c r="L21">
-        <v>2.45</v>
+        <v>1.9</v>
       </c>
       <c r="M21">
-        <v>3.05</v>
+        <v>3.74</v>
       </c>
       <c r="N21">
-        <v>3</v>
+        <v>3.78</v>
       </c>
       <c r="O21">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="P21">
         <v>9.1</v>
       </c>
       <c r="Q21">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="R21">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="S21">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="T21">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="U21">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="V21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W21">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X21">
         <v>1</v>
@@ -3689,34 +3689,34 @@
         <v>9.1</v>
       </c>
       <c r="Z21">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AA21">
-        <v>3.88</v>
+        <v>3.15</v>
       </c>
       <c r="AB21">
-        <v>1.68</v>
+        <v>1.97</v>
       </c>
       <c r="AC21">
-        <v>2.19</v>
+        <v>1.85</v>
       </c>
       <c r="AD21">
-        <v>2.53</v>
+        <v>3.22</v>
       </c>
       <c r="AE21">
-        <v>1.41</v>
+        <v>1.26</v>
       </c>
       <c r="AF21">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AG21">
-        <v>2.38</v>
+        <v>1.95</v>
       </c>
       <c r="AH21">
-        <v>4.55</v>
+        <v>6.05</v>
       </c>
       <c r="AI21">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AJ21" t="s">
         <v>303</v>
@@ -3763,40 +3763,40 @@
         <v>301</v>
       </c>
       <c r="L22">
-        <v>1.9</v>
+        <v>2.45</v>
       </c>
       <c r="M22">
-        <v>3.74</v>
+        <v>3.05</v>
       </c>
       <c r="N22">
-        <v>3.78</v>
+        <v>3</v>
       </c>
       <c r="O22">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="P22">
         <v>9.1</v>
       </c>
       <c r="Q22">
+        <v>2.05</v>
+      </c>
+      <c r="R22">
+        <v>1.3</v>
+      </c>
+      <c r="S22">
+        <v>3.4</v>
+      </c>
+      <c r="T22">
         <v>2.5</v>
       </c>
-      <c r="R22">
-        <v>1.36</v>
-      </c>
-      <c r="S22">
-        <v>3</v>
-      </c>
-      <c r="T22">
-        <v>2.75</v>
-      </c>
       <c r="U22">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="V22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W22">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X22">
         <v>1</v>
@@ -3805,34 +3805,34 @@
         <v>9.1</v>
       </c>
       <c r="Z22">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AA22">
-        <v>3.15</v>
+        <v>3.88</v>
       </c>
       <c r="AB22">
-        <v>1.97</v>
+        <v>1.68</v>
       </c>
       <c r="AC22">
-        <v>1.85</v>
+        <v>2.19</v>
       </c>
       <c r="AD22">
-        <v>3.22</v>
+        <v>2.53</v>
       </c>
       <c r="AE22">
-        <v>1.26</v>
+        <v>1.41</v>
       </c>
       <c r="AF22">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AG22">
-        <v>1.95</v>
+        <v>2.38</v>
       </c>
       <c r="AH22">
-        <v>6.05</v>
+        <v>4.55</v>
       </c>
       <c r="AI22">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AJ22" t="s">
         <v>303</v>
@@ -3852,7 +3852,7 @@
         <v>47</v>
       </c>
       <c r="C23" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D23" t="s">
         <v>94</v>
@@ -3879,76 +3879,76 @@
         <v>301</v>
       </c>
       <c r="L23">
-        <v>1.45</v>
+        <v>2.88</v>
       </c>
       <c r="M23">
-        <v>4.8</v>
+        <v>3.11</v>
       </c>
       <c r="N23">
-        <v>5.8</v>
+        <v>2.22</v>
       </c>
       <c r="O23">
+        <v>2.15</v>
+      </c>
+      <c r="P23">
+        <v>8.5</v>
+      </c>
+      <c r="Q23">
+        <v>1.93</v>
+      </c>
+      <c r="R23">
+        <v>1.4</v>
+      </c>
+      <c r="S23">
+        <v>2.7</v>
+      </c>
+      <c r="T23">
+        <v>2.8</v>
+      </c>
+      <c r="U23">
+        <v>1.38</v>
+      </c>
+      <c r="V23">
+        <v>7.3</v>
+      </c>
+      <c r="W23">
+        <v>1.03</v>
+      </c>
+      <c r="X23">
+        <v>1.06</v>
+      </c>
+      <c r="Y23">
+        <v>8.5</v>
+      </c>
+      <c r="Z23">
+        <v>1.3</v>
+      </c>
+      <c r="AA23">
+        <v>3.45</v>
+      </c>
+      <c r="AB23">
+        <v>1.89</v>
+      </c>
+      <c r="AC23">
+        <v>1.81</v>
+      </c>
+      <c r="AD23">
+        <v>3.2</v>
+      </c>
+      <c r="AE23">
         <v>1.33</v>
       </c>
-      <c r="P23">
-        <v>22</v>
-      </c>
-      <c r="Q23">
-        <v>3.25</v>
-      </c>
-      <c r="R23">
-        <v>1.22</v>
-      </c>
-      <c r="S23">
-        <v>4</v>
-      </c>
-      <c r="T23">
-        <v>2.1</v>
-      </c>
-      <c r="U23">
-        <v>1.67</v>
-      </c>
-      <c r="V23">
-        <v>4.5</v>
-      </c>
-      <c r="W23">
-        <v>1.18</v>
-      </c>
-      <c r="X23">
-        <v>1.01</v>
-      </c>
-      <c r="Y23">
-        <v>17</v>
-      </c>
-      <c r="Z23">
-        <v>1.08</v>
-      </c>
-      <c r="AA23">
-        <v>5.55</v>
-      </c>
-      <c r="AB23">
-        <v>1.48</v>
-      </c>
-      <c r="AC23">
-        <v>2.6</v>
-      </c>
-      <c r="AD23">
-        <v>2.21</v>
-      </c>
-      <c r="AE23">
-        <v>1.66</v>
-      </c>
       <c r="AF23">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG23">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AH23">
-        <v>3.44</v>
+        <v>6.25</v>
       </c>
       <c r="AI23">
-        <v>1.23</v>
+        <v>1.11</v>
       </c>
       <c r="AJ23" t="s">
         <v>303</v>
@@ -3968,7 +3968,7 @@
         <v>47</v>
       </c>
       <c r="C24" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D24" t="s">
         <v>94</v>
@@ -3995,76 +3995,76 @@
         <v>301</v>
       </c>
       <c r="L24">
-        <v>2.88</v>
+        <v>1.45</v>
       </c>
       <c r="M24">
-        <v>3.11</v>
+        <v>4.8</v>
       </c>
       <c r="N24">
-        <v>2.22</v>
+        <v>5.8</v>
       </c>
       <c r="O24">
-        <v>2.15</v>
+        <v>1.33</v>
       </c>
       <c r="P24">
-        <v>8.5</v>
+        <v>22</v>
       </c>
       <c r="Q24">
-        <v>1.93</v>
+        <v>3.25</v>
       </c>
       <c r="R24">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="S24">
-        <v>2.7</v>
+        <v>4</v>
       </c>
       <c r="T24">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="U24">
-        <v>1.38</v>
+        <v>1.67</v>
       </c>
       <c r="V24">
-        <v>7.3</v>
+        <v>4.5</v>
       </c>
       <c r="W24">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="X24">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>8.5</v>
+        <v>17</v>
       </c>
       <c r="Z24">
-        <v>1.3</v>
+        <v>1.08</v>
       </c>
       <c r="AA24">
-        <v>3.45</v>
+        <v>5.55</v>
       </c>
       <c r="AB24">
-        <v>1.89</v>
+        <v>1.48</v>
       </c>
       <c r="AC24">
-        <v>1.81</v>
+        <v>2.6</v>
       </c>
       <c r="AD24">
-        <v>3.2</v>
+        <v>2.21</v>
       </c>
       <c r="AE24">
-        <v>1.33</v>
+        <v>1.66</v>
       </c>
       <c r="AF24">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG24">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AH24">
-        <v>6.25</v>
+        <v>3.44</v>
       </c>
       <c r="AI24">
-        <v>1.11</v>
+        <v>1.23</v>
       </c>
       <c r="AJ24" t="s">
         <v>303</v>
@@ -4111,76 +4111,76 @@
         <v>301</v>
       </c>
       <c r="L25">
+        <v>1.88</v>
+      </c>
+      <c r="M25">
+        <v>3.22</v>
+      </c>
+      <c r="N25">
+        <v>4.52</v>
+      </c>
+      <c r="O25">
+        <v>1.61</v>
+      </c>
+      <c r="P25">
+        <v>6.7</v>
+      </c>
+      <c r="Q25">
+        <v>2.89</v>
+      </c>
+      <c r="R25">
+        <v>1.49</v>
+      </c>
+      <c r="S25">
         <v>2.4</v>
       </c>
-      <c r="M25">
-        <v>3.15</v>
-      </c>
-      <c r="N25">
-        <v>2.6</v>
-      </c>
-      <c r="O25">
-        <v>1.8</v>
-      </c>
-      <c r="P25">
-        <v>9</v>
-      </c>
-      <c r="Q25">
-        <v>2.1</v>
-      </c>
-      <c r="R25">
-        <v>1.36</v>
-      </c>
-      <c r="S25">
-        <v>3</v>
-      </c>
       <c r="T25">
-        <v>2.63</v>
+        <v>3.14</v>
       </c>
       <c r="U25">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="V25">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="W25">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="X25">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y25">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="Z25">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AA25">
-        <v>3.55</v>
+        <v>2.8</v>
       </c>
       <c r="AB25">
-        <v>1.81</v>
+        <v>2.2</v>
       </c>
       <c r="AC25">
-        <v>1.89</v>
+        <v>1.62</v>
       </c>
       <c r="AD25">
-        <v>3.25</v>
+        <v>3.74</v>
       </c>
       <c r="AE25">
-        <v>1.35</v>
+        <v>1.19</v>
       </c>
       <c r="AF25">
-        <v>1.67</v>
+        <v>1.97</v>
       </c>
       <c r="AG25">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="AH25">
-        <v>6.25</v>
+        <v>8</v>
       </c>
       <c r="AI25">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="AJ25" t="s">
         <v>303</v>
@@ -4316,7 +4316,7 @@
         <v>48</v>
       </c>
       <c r="C27" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D27" t="s">
         <v>94</v>
@@ -4343,76 +4343,76 @@
         <v>301</v>
       </c>
       <c r="L27">
-        <v>2.73</v>
+        <v>2.4</v>
       </c>
       <c r="M27">
-        <v>3.29</v>
+        <v>3.15</v>
       </c>
       <c r="N27">
-        <v>2.23</v>
+        <v>2.6</v>
       </c>
       <c r="O27">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="P27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q27">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="R27">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S27">
+        <v>3</v>
+      </c>
+      <c r="T27">
+        <v>2.63</v>
+      </c>
+      <c r="U27">
+        <v>1.44</v>
+      </c>
+      <c r="V27">
+        <v>7</v>
+      </c>
+      <c r="W27">
+        <v>1.1</v>
+      </c>
+      <c r="X27">
+        <v>1.06</v>
+      </c>
+      <c r="Y27">
+        <v>9</v>
+      </c>
+      <c r="Z27">
+        <v>1.3</v>
+      </c>
+      <c r="AA27">
+        <v>3.55</v>
+      </c>
+      <c r="AB27">
+        <v>1.81</v>
+      </c>
+      <c r="AC27">
+        <v>1.89</v>
+      </c>
+      <c r="AD27">
         <v>3.25</v>
       </c>
-      <c r="T27">
-        <v>2.5</v>
-      </c>
-      <c r="U27">
-        <v>1.5</v>
-      </c>
-      <c r="V27">
-        <v>6</v>
-      </c>
-      <c r="W27">
-        <v>1.13</v>
-      </c>
-      <c r="X27">
-        <v>1.05</v>
-      </c>
-      <c r="Y27">
-        <v>10</v>
-      </c>
-      <c r="Z27">
-        <v>1.25</v>
-      </c>
-      <c r="AA27">
-        <v>4</v>
-      </c>
-      <c r="AB27">
-        <v>1.75</v>
-      </c>
-      <c r="AC27">
-        <v>2.04</v>
-      </c>
-      <c r="AD27">
-        <v>2.8</v>
-      </c>
       <c r="AE27">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AF27">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AG27">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AH27">
-        <v>5.25</v>
+        <v>6.25</v>
       </c>
       <c r="AI27">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AJ27" t="s">
         <v>303</v>
@@ -4432,7 +4432,7 @@
         <v>48</v>
       </c>
       <c r="C28" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D28" t="s">
         <v>94</v>
@@ -4459,76 +4459,76 @@
         <v>301</v>
       </c>
       <c r="L28">
-        <v>1.88</v>
+        <v>1.18</v>
       </c>
       <c r="M28">
-        <v>3.22</v>
+        <v>5</v>
       </c>
       <c r="N28">
-        <v>4.52</v>
+        <v>13</v>
       </c>
       <c r="O28">
-        <v>1.61</v>
+        <v>1.23</v>
       </c>
       <c r="P28">
-        <v>6.7</v>
+        <v>7.9</v>
       </c>
       <c r="Q28">
-        <v>2.89</v>
+        <v>5.65</v>
       </c>
       <c r="R28">
-        <v>1.49</v>
+        <v>1.33</v>
       </c>
       <c r="S28">
-        <v>2.4</v>
+        <v>2.76</v>
       </c>
       <c r="T28">
-        <v>3.14</v>
+        <v>2.6</v>
       </c>
       <c r="U28">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="V28">
-        <v>8.5</v>
+        <v>6.05</v>
       </c>
       <c r="W28">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X28">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="Z28">
-        <v>1.38</v>
+        <v>1.24</v>
       </c>
       <c r="AA28">
-        <v>2.8</v>
+        <v>3.34</v>
       </c>
       <c r="AB28">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AC28">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="AD28">
-        <v>3.74</v>
+        <v>2.83</v>
       </c>
       <c r="AE28">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="AF28">
-        <v>1.97</v>
+        <v>2.5</v>
       </c>
       <c r="AG28">
-        <v>1.73</v>
+        <v>1.48</v>
       </c>
       <c r="AH28">
-        <v>8</v>
+        <v>5.5</v>
       </c>
       <c r="AI28">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AJ28" t="s">
         <v>303</v>
@@ -4575,76 +4575,76 @@
         <v>301</v>
       </c>
       <c r="L29">
-        <v>1.18</v>
+        <v>2.73</v>
       </c>
       <c r="M29">
-        <v>5</v>
+        <v>3.29</v>
       </c>
       <c r="N29">
-        <v>13</v>
+        <v>2.23</v>
       </c>
       <c r="O29">
-        <v>1.23</v>
+        <v>2.2</v>
       </c>
       <c r="P29">
-        <v>7.9</v>
+        <v>10</v>
       </c>
       <c r="Q29">
-        <v>5.65</v>
+        <v>1.73</v>
       </c>
       <c r="R29">
         <v>1.33</v>
       </c>
       <c r="S29">
-        <v>2.76</v>
+        <v>3.25</v>
       </c>
       <c r="T29">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="U29">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="V29">
-        <v>6.05</v>
+        <v>6</v>
       </c>
       <c r="W29">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="X29">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y29">
         <v>10</v>
       </c>
       <c r="Z29">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AA29">
-        <v>3.34</v>
+        <v>4</v>
       </c>
       <c r="AB29">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC29">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="AD29">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="AE29">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AF29">
-        <v>2.5</v>
+        <v>1.57</v>
       </c>
       <c r="AG29">
-        <v>1.48</v>
+        <v>2.25</v>
       </c>
       <c r="AH29">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="AI29">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AJ29" t="s">
         <v>303</v>
@@ -4664,7 +4664,7 @@
         <v>48</v>
       </c>
       <c r="C30" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D30" t="s">
         <v>94</v>
@@ -4691,76 +4691,76 @@
         <v>301</v>
       </c>
       <c r="L30">
-        <v>2.09</v>
+        <v>2.57</v>
       </c>
       <c r="M30">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="N30">
-        <v>2.98</v>
+        <v>2.34</v>
       </c>
       <c r="O30">
-        <v>1.67</v>
+        <v>2.05</v>
       </c>
       <c r="P30">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Q30">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="R30">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S30">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="T30">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="U30">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="V30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W30">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X30">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y30">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Z30">
         <v>1.22</v>
       </c>
       <c r="AA30">
-        <v>3.64</v>
+        <v>4.33</v>
       </c>
       <c r="AB30">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="AC30">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AD30">
-        <v>2.88</v>
+        <v>2.26</v>
       </c>
       <c r="AE30">
-        <v>1.34</v>
+        <v>1.51</v>
       </c>
       <c r="AF30">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AG30">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AH30">
-        <v>5.3</v>
+        <v>4.75</v>
       </c>
       <c r="AI30">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="AJ30" t="s">
         <v>303</v>
@@ -4780,7 +4780,7 @@
         <v>48</v>
       </c>
       <c r="C31" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D31" t="s">
         <v>94</v>
@@ -4807,76 +4807,76 @@
         <v>301</v>
       </c>
       <c r="L31">
-        <v>2.57</v>
+        <v>2.09</v>
       </c>
       <c r="M31">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="N31">
-        <v>2.34</v>
+        <v>2.98</v>
       </c>
       <c r="O31">
-        <v>2.05</v>
+        <v>1.67</v>
       </c>
       <c r="P31">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Q31">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="R31">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S31">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="T31">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="U31">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="V31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W31">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X31">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y31">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z31">
         <v>1.22</v>
       </c>
       <c r="AA31">
-        <v>4.33</v>
+        <v>3.64</v>
       </c>
       <c r="AB31">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="AC31">
+        <v>1.93</v>
+      </c>
+      <c r="AD31">
+        <v>2.88</v>
+      </c>
+      <c r="AE31">
+        <v>1.34</v>
+      </c>
+      <c r="AF31">
+        <v>1.67</v>
+      </c>
+      <c r="AG31">
         <v>2.1</v>
       </c>
-      <c r="AD31">
-        <v>2.26</v>
-      </c>
-      <c r="AE31">
-        <v>1.51</v>
-      </c>
-      <c r="AF31">
-        <v>1.57</v>
-      </c>
-      <c r="AG31">
-        <v>2.25</v>
-      </c>
       <c r="AH31">
-        <v>4.75</v>
+        <v>5.3</v>
       </c>
       <c r="AI31">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AJ31" t="s">
         <v>303</v>
@@ -4923,76 +4923,76 @@
         <v>301</v>
       </c>
       <c r="L32">
-        <v>2.81</v>
+        <v>1.37</v>
       </c>
       <c r="M32">
-        <v>3.3</v>
+        <v>4.9</v>
       </c>
       <c r="N32">
-        <v>2.33</v>
+        <v>6.74</v>
       </c>
       <c r="O32">
-        <v>2.3</v>
+        <v>1.37</v>
       </c>
       <c r="P32">
-        <v>13.75</v>
+        <v>19.25</v>
       </c>
       <c r="Q32">
-        <v>1.67</v>
+        <v>3.1</v>
       </c>
       <c r="R32">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="S32">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="T32">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="U32">
-        <v>1.43</v>
+        <v>1.65</v>
       </c>
       <c r="V32">
-        <v>5.75</v>
+        <v>4.2</v>
       </c>
       <c r="W32">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="X32">
         <v>1.02</v>
       </c>
       <c r="Y32">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Z32">
-        <v>1.19</v>
+        <v>1.1</v>
       </c>
       <c r="AA32">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="AB32">
-        <v>1.73</v>
+        <v>1.43</v>
       </c>
       <c r="AC32">
-        <v>2.06</v>
+        <v>2.62</v>
       </c>
       <c r="AD32">
-        <v>2.78</v>
+        <v>2.18</v>
       </c>
       <c r="AE32">
-        <v>1.38</v>
+        <v>1.62</v>
       </c>
       <c r="AF32">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AG32">
         <v>2.2</v>
       </c>
       <c r="AH32">
-        <v>5</v>
+        <v>3.64</v>
       </c>
       <c r="AI32">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AJ32" t="s">
         <v>303</v>
@@ -5012,7 +5012,7 @@
         <v>49</v>
       </c>
       <c r="C33" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D33" t="s">
         <v>94</v>
@@ -5039,76 +5039,76 @@
         <v>301</v>
       </c>
       <c r="L33">
-        <v>1.47</v>
+        <v>2.81</v>
       </c>
       <c r="M33">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="N33">
-        <v>4.9</v>
+        <v>2.33</v>
       </c>
       <c r="O33">
-        <v>1.39</v>
+        <v>2.3</v>
       </c>
       <c r="P33">
-        <v>25</v>
+        <v>13.75</v>
       </c>
       <c r="Q33">
-        <v>3</v>
+        <v>1.67</v>
       </c>
       <c r="R33">
-        <v>1.16</v>
+        <v>1.31</v>
       </c>
       <c r="S33">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="T33">
-        <v>2.03</v>
+        <v>2.45</v>
       </c>
       <c r="U33">
-        <v>1.7</v>
+        <v>1.43</v>
       </c>
       <c r="V33">
-        <v>4.4</v>
+        <v>5.75</v>
       </c>
       <c r="W33">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X33">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y33">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="Z33">
-        <v>1.06</v>
+        <v>1.19</v>
       </c>
       <c r="AA33">
-        <v>6.25</v>
+        <v>3.8</v>
       </c>
       <c r="AB33">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="AC33">
+        <v>2.06</v>
+      </c>
+      <c r="AD33">
+        <v>2.78</v>
+      </c>
+      <c r="AE33">
+        <v>1.38</v>
+      </c>
+      <c r="AF33">
+        <v>1.63</v>
+      </c>
+      <c r="AG33">
         <v>2.2</v>
       </c>
-      <c r="AD33">
-        <v>2.22</v>
-      </c>
-      <c r="AE33">
-        <v>1.66</v>
-      </c>
-      <c r="AF33">
-        <v>1.51</v>
-      </c>
-      <c r="AG33">
-        <v>2.39</v>
-      </c>
       <c r="AH33">
-        <v>3.25</v>
+        <v>5</v>
       </c>
       <c r="AI33">
-        <v>1.27</v>
+        <v>1.13</v>
       </c>
       <c r="AJ33" t="s">
         <v>303</v>
@@ -5128,7 +5128,7 @@
         <v>49</v>
       </c>
       <c r="C34" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D34" t="s">
         <v>94</v>
@@ -5155,76 +5155,76 @@
         <v>301</v>
       </c>
       <c r="L34">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
       <c r="M34">
+        <v>4.2</v>
+      </c>
+      <c r="N34">
         <v>4.9</v>
       </c>
-      <c r="N34">
-        <v>6.74</v>
-      </c>
       <c r="O34">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="P34">
-        <v>19.25</v>
+        <v>25</v>
       </c>
       <c r="Q34">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R34">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="S34">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="T34">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="U34">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="V34">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="W34">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="X34">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="Z34">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AA34">
-        <v>5</v>
+        <v>6.25</v>
       </c>
       <c r="AB34">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="AC34">
-        <v>2.62</v>
+        <v>2.2</v>
       </c>
       <c r="AD34">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="AE34">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AF34">
-        <v>1.67</v>
+        <v>1.51</v>
       </c>
       <c r="AG34">
-        <v>2.2</v>
+        <v>2.39</v>
       </c>
       <c r="AH34">
-        <v>3.64</v>
+        <v>3.25</v>
       </c>
       <c r="AI34">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AJ34" t="s">
         <v>303</v>
@@ -5244,7 +5244,7 @@
         <v>50</v>
       </c>
       <c r="C35" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D35" t="s">
         <v>94</v>
@@ -5360,7 +5360,7 @@
         <v>50</v>
       </c>
       <c r="C36" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D36" t="s">
         <v>94</v>
@@ -5592,7 +5592,7 @@
         <v>52</v>
       </c>
       <c r="C38" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="D38" t="s">
         <v>94</v>
@@ -5616,79 +5616,79 @@
         <v>0</v>
       </c>
       <c r="K38" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L38">
-        <v>2.77</v>
+        <v>7.65</v>
       </c>
       <c r="M38">
-        <v>3.79</v>
+        <v>6.5</v>
       </c>
       <c r="N38">
-        <v>2.02</v>
+        <v>1.26</v>
       </c>
       <c r="O38">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P38">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Q38">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="R38">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S38">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="T38">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U38">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V38">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="W38">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X38">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y38">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="Z38">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AA38">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AB38">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AC38">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AD38">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE38">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF38">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AG38">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AH38">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AI38">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AJ38" t="s">
         <v>303</v>
@@ -5708,7 +5708,7 @@
         <v>52</v>
       </c>
       <c r="C39" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="D39" t="s">
         <v>94</v>
@@ -5732,79 +5732,79 @@
         <v>0</v>
       </c>
       <c r="K39" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L39">
-        <v>7.65</v>
+        <v>2.77</v>
       </c>
       <c r="M39">
-        <v>6.5</v>
+        <v>3.79</v>
       </c>
       <c r="N39">
-        <v>1.26</v>
+        <v>2.02</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="T39">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V39">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="W39">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X39">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Z39">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AA39">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AB39">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC39">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD39">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE39">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF39">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AG39">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AH39">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AI39">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AJ39" t="s">
         <v>303</v>
@@ -6431,73 +6431,73 @@
         <v>301</v>
       </c>
       <c r="L45">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="M45">
-        <v>3.15</v>
+        <v>2.96</v>
       </c>
       <c r="N45">
-        <v>4.3</v>
+        <v>2.75</v>
       </c>
       <c r="O45">
-        <v>1.57</v>
+        <v>1.95</v>
       </c>
       <c r="P45">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q45">
-        <v>3.1</v>
+        <v>2.15</v>
       </c>
       <c r="R45">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="S45">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="T45">
-        <v>3.42</v>
+        <v>3.14</v>
       </c>
       <c r="U45">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="V45">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W45">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X45">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y45">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="Z45">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AA45">
-        <v>2.36</v>
+        <v>2.85</v>
       </c>
       <c r="AB45">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="AC45">
-        <v>1.44</v>
+        <v>1.63</v>
       </c>
       <c r="AD45">
-        <v>4.75</v>
+        <v>4.05</v>
       </c>
       <c r="AE45">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AF45">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="AG45">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AH45">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="AI45">
         <v>1.02</v>
@@ -6520,7 +6520,7 @@
         <v>56</v>
       </c>
       <c r="C46" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D46" t="s">
         <v>94</v>
@@ -6547,76 +6547,76 @@
         <v>301</v>
       </c>
       <c r="L46">
-        <v>1.34</v>
+        <v>2</v>
       </c>
       <c r="M46">
-        <v>4.96</v>
+        <v>3.15</v>
       </c>
       <c r="N46">
-        <v>8.35</v>
+        <v>4.3</v>
       </c>
       <c r="O46">
+        <v>1.57</v>
+      </c>
+      <c r="P46">
+        <v>6</v>
+      </c>
+      <c r="Q46">
+        <v>3.1</v>
+      </c>
+      <c r="R46">
+        <v>1.6</v>
+      </c>
+      <c r="S46">
+        <v>2.15</v>
+      </c>
+      <c r="T46">
+        <v>3.42</v>
+      </c>
+      <c r="U46">
         <v>1.25</v>
       </c>
-      <c r="P46">
-        <v>15.25</v>
-      </c>
-      <c r="Q46">
-        <v>4.33</v>
-      </c>
-      <c r="R46">
-        <v>1.3</v>
-      </c>
-      <c r="S46">
-        <v>3.4</v>
-      </c>
-      <c r="T46">
+      <c r="V46">
+        <v>10</v>
+      </c>
+      <c r="W46">
+        <v>1.03</v>
+      </c>
+      <c r="X46">
+        <v>1.07</v>
+      </c>
+      <c r="Y46">
+        <v>6.2</v>
+      </c>
+      <c r="Z46">
+        <v>1.47</v>
+      </c>
+      <c r="AA46">
+        <v>2.36</v>
+      </c>
+      <c r="AB46">
         <v>2.5</v>
       </c>
-      <c r="U46">
-        <v>1.5</v>
-      </c>
-      <c r="V46">
-        <v>6</v>
-      </c>
-      <c r="W46">
-        <v>1.13</v>
-      </c>
-      <c r="X46">
-        <v>1.01</v>
-      </c>
-      <c r="Y46">
-        <v>11</v>
-      </c>
-      <c r="Z46">
-        <v>1.17</v>
-      </c>
-      <c r="AA46">
-        <v>4</v>
-      </c>
-      <c r="AB46">
-        <v>1.73</v>
-      </c>
       <c r="AC46">
-        <v>2.08</v>
+        <v>1.44</v>
       </c>
       <c r="AD46">
-        <v>2.75</v>
+        <v>4.75</v>
       </c>
       <c r="AE46">
-        <v>1.35</v>
+        <v>1.15</v>
       </c>
       <c r="AF46">
         <v>2.1</v>
       </c>
       <c r="AG46">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AH46">
-        <v>5.3</v>
+        <v>9.5</v>
       </c>
       <c r="AI46">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="AJ46" t="s">
         <v>303</v>
@@ -6636,7 +6636,7 @@
         <v>56</v>
       </c>
       <c r="C47" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D47" t="s">
         <v>94</v>
@@ -6663,76 +6663,76 @@
         <v>301</v>
       </c>
       <c r="L47">
-        <v>2.74</v>
+        <v>1.34</v>
       </c>
       <c r="M47">
-        <v>2.9</v>
+        <v>4.96</v>
       </c>
       <c r="N47">
-        <v>2.7</v>
+        <v>8.35</v>
       </c>
       <c r="O47">
-        <v>1.91</v>
+        <v>1.25</v>
       </c>
       <c r="P47">
-        <v>7.2</v>
+        <v>15.25</v>
       </c>
       <c r="Q47">
-        <v>2.2</v>
+        <v>4.33</v>
       </c>
       <c r="R47">
-        <v>1.46</v>
+        <v>1.3</v>
       </c>
       <c r="S47">
-        <v>2.52</v>
+        <v>3.4</v>
       </c>
       <c r="T47">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="U47">
-        <v>1.32</v>
+        <v>1.5</v>
       </c>
       <c r="V47">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="W47">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="X47">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y47">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="Z47">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="AA47">
-        <v>2.78</v>
+        <v>4</v>
       </c>
       <c r="AB47">
+        <v>1.73</v>
+      </c>
+      <c r="AC47">
+        <v>2.08</v>
+      </c>
+      <c r="AD47">
+        <v>2.75</v>
+      </c>
+      <c r="AE47">
+        <v>1.35</v>
+      </c>
+      <c r="AF47">
         <v>2.1</v>
       </c>
-      <c r="AC47">
-        <v>1.64</v>
-      </c>
-      <c r="AD47">
-        <v>3.8</v>
-      </c>
-      <c r="AE47">
-        <v>1.2</v>
-      </c>
-      <c r="AF47">
-        <v>1.85</v>
-      </c>
       <c r="AG47">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AH47">
-        <v>7</v>
+        <v>5.3</v>
       </c>
       <c r="AI47">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AJ47" t="s">
         <v>303</v>
@@ -6752,7 +6752,7 @@
         <v>56</v>
       </c>
       <c r="C48" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D48" t="s">
         <v>94</v>
@@ -6779,76 +6779,76 @@
         <v>301</v>
       </c>
       <c r="L48">
-        <v>2.4</v>
+        <v>2.74</v>
       </c>
       <c r="M48">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="N48">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="O48">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="P48">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="Q48">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="R48">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="S48">
-        <v>2.45</v>
+        <v>2.52</v>
       </c>
       <c r="T48">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="U48">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="V48">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="W48">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X48">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y48">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z48">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AA48">
-        <v>2.85</v>
+        <v>2.78</v>
       </c>
       <c r="AB48">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AC48">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AD48">
-        <v>4.05</v>
+        <v>3.8</v>
       </c>
       <c r="AE48">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF48">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="AG48">
         <v>1.85</v>
       </c>
       <c r="AH48">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="AI48">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AJ48" t="s">
         <v>303</v>
@@ -7008,7 +7008,7 @@
         <v>0</v>
       </c>
       <c r="K50" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L50">
         <v>0</v>
@@ -7124,7 +7124,7 @@
         <v>0</v>
       </c>
       <c r="K51" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L51">
         <v>0</v>
@@ -7240,7 +7240,7 @@
         <v>0</v>
       </c>
       <c r="K52" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L52">
         <v>0</v>
@@ -7564,7 +7564,7 @@
         <v>58</v>
       </c>
       <c r="C55" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D55" t="s">
         <v>94</v>
@@ -7591,40 +7591,40 @@
         <v>301</v>
       </c>
       <c r="L55">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M55">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N55">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O55">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="P55">
         <v>0</v>
       </c>
       <c r="Q55">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R55">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S55">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T55">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U55">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V55">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W55">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X55">
         <v>0</v>
@@ -7639,10 +7639,10 @@
         <v>0</v>
       </c>
       <c r="AB55">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC55">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD55">
         <v>0</v>
@@ -7651,10 +7651,10 @@
         <v>0</v>
       </c>
       <c r="AF55">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG55">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH55">
         <v>0</v>
@@ -7820,7 +7820,7 @@
         <v>0</v>
       </c>
       <c r="K57" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L57">
         <v>0</v>
@@ -8376,7 +8376,7 @@
         <v>58</v>
       </c>
       <c r="C62" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D62" t="s">
         <v>94</v>
@@ -8403,76 +8403,76 @@
         <v>301</v>
       </c>
       <c r="L62">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M62">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N62">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O62">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="P62">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Q62">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R62">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S62">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T62">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U62">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V62">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W62">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X62">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y62">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Z62">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AA62">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AB62">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC62">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD62">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AE62">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AF62">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG62">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH62">
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="AI62">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AJ62" t="s">
         <v>303</v>
@@ -8492,7 +8492,7 @@
         <v>58</v>
       </c>
       <c r="C63" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D63" t="s">
         <v>94</v>
@@ -8519,76 +8519,76 @@
         <v>301</v>
       </c>
       <c r="L63">
-        <v>1.96</v>
+        <v>1.75</v>
       </c>
       <c r="M63">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="N63">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="O63">
-        <v>1.71</v>
+        <v>1.53</v>
       </c>
       <c r="P63">
-        <v>6.75</v>
+        <v>9</v>
       </c>
       <c r="Q63">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="R63">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="S63">
-        <v>2.25</v>
+        <v>2.65</v>
       </c>
       <c r="T63">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="U63">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="V63">
-        <v>10</v>
+        <v>6.5</v>
       </c>
       <c r="W63">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X63">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y63">
-        <v>6.35</v>
+        <v>9</v>
       </c>
       <c r="Z63">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="AA63">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="AB63">
-        <v>2.38</v>
+        <v>1.95</v>
       </c>
       <c r="AC63">
-        <v>1.46</v>
+        <v>1.75</v>
       </c>
       <c r="AD63">
-        <v>4.6</v>
+        <v>3.34</v>
       </c>
       <c r="AE63">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AF63">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AG63">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AH63">
-        <v>9.75</v>
+        <v>6.55</v>
       </c>
       <c r="AI63">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AJ63" t="s">
         <v>303</v>
@@ -8608,7 +8608,7 @@
         <v>58</v>
       </c>
       <c r="C64" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D64" t="s">
         <v>94</v>
@@ -8635,76 +8635,76 @@
         <v>301</v>
       </c>
       <c r="L64">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M64">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N64">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O64">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="P64">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q64">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R64">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="S64">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="T64">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U64">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V64">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W64">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X64">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y64">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Z64">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AA64">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AB64">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AC64">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD64">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AE64">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AF64">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG64">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH64">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AI64">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AJ64" t="s">
         <v>303</v>
@@ -8748,7 +8748,7 @@
         <v>0</v>
       </c>
       <c r="K65" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L65">
         <v>0</v>
@@ -8840,7 +8840,7 @@
         <v>58</v>
       </c>
       <c r="C66" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D66" t="s">
         <v>94</v>
@@ -8864,79 +8864,79 @@
         <v>0</v>
       </c>
       <c r="K66" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L66">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M66">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N66">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O66">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="P66">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="Q66">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R66">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S66">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T66">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U66">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V66">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W66">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X66">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y66">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="Z66">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA66">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB66">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC66">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AD66">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AE66">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF66">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG66">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH66">
-        <v>0</v>
+        <v>9.75</v>
       </c>
       <c r="AI66">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AJ66" t="s">
         <v>303</v>
@@ -9072,7 +9072,7 @@
         <v>58</v>
       </c>
       <c r="C68" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D68" t="s">
         <v>94</v>
@@ -9099,76 +9099,76 @@
         <v>301</v>
       </c>
       <c r="L68">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M68">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N68">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O68">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="P68">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q68">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R68">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S68">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="T68">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U68">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V68">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W68">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X68">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y68">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z68">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AA68">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AB68">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AC68">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD68">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AE68">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF68">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG68">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH68">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AI68">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AJ68" t="s">
         <v>303</v>
@@ -9188,7 +9188,7 @@
         <v>58</v>
       </c>
       <c r="C69" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D69" t="s">
         <v>94</v>
@@ -9215,40 +9215,40 @@
         <v>301</v>
       </c>
       <c r="L69">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M69">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N69">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O69">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="P69">
         <v>0</v>
       </c>
       <c r="Q69">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R69">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S69">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T69">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U69">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V69">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W69">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X69">
         <v>0</v>
@@ -9263,10 +9263,10 @@
         <v>0</v>
       </c>
       <c r="AB69">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC69">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD69">
         <v>0</v>
@@ -9275,10 +9275,10 @@
         <v>0</v>
       </c>
       <c r="AF69">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG69">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH69">
         <v>0</v>
@@ -9304,7 +9304,7 @@
         <v>59</v>
       </c>
       <c r="C70" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D70" t="s">
         <v>94</v>
@@ -9420,7 +9420,7 @@
         <v>60</v>
       </c>
       <c r="C71" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D71" t="s">
         <v>94</v>
@@ -9447,76 +9447,76 @@
         <v>301</v>
       </c>
       <c r="L71">
-        <v>2.18</v>
+        <v>1.65</v>
       </c>
       <c r="M71">
-        <v>2.88</v>
+        <v>3.54</v>
       </c>
       <c r="N71">
-        <v>3.8</v>
+        <v>6</v>
       </c>
       <c r="O71">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="P71">
-        <v>5.75</v>
+        <v>6.5</v>
       </c>
       <c r="Q71">
-        <v>2.37</v>
+        <v>3.3</v>
       </c>
       <c r="R71">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="S71">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="T71">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="U71">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="V71">
-        <v>12</v>
+        <v>8.9</v>
       </c>
       <c r="W71">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X71">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="Y71">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z71">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AA71">
-        <v>2.39</v>
+        <v>2.65</v>
       </c>
       <c r="AB71">
-        <v>2.62</v>
+        <v>2.42</v>
       </c>
       <c r="AC71">
-        <v>1.4</v>
+        <v>1.54</v>
       </c>
       <c r="AD71">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="AE71">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF71">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="AG71">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AH71">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AI71">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AJ71" t="s">
         <v>303</v>
@@ -9563,28 +9563,28 @@
         <v>301</v>
       </c>
       <c r="L72">
-        <v>1.65</v>
+        <v>2.6</v>
       </c>
       <c r="M72">
-        <v>3.54</v>
+        <v>2.97</v>
       </c>
       <c r="N72">
-        <v>6</v>
+        <v>2.9</v>
       </c>
       <c r="O72">
-        <v>1.5</v>
+        <v>1.95</v>
       </c>
       <c r="P72">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
       <c r="Q72">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="R72">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="S72">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="T72">
         <v>3.3</v>
@@ -9593,46 +9593,46 @@
         <v>1.29</v>
       </c>
       <c r="V72">
-        <v>8.9</v>
+        <v>8.1</v>
       </c>
       <c r="W72">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X72">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="Y72">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="Z72">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AA72">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="AB72">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="AC72">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AD72">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="AE72">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AF72">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AG72">
-        <v>1.53</v>
+        <v>1.79</v>
       </c>
       <c r="AH72">
-        <v>11.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AI72">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AJ72" t="s">
         <v>303</v>
@@ -9652,7 +9652,7 @@
         <v>60</v>
       </c>
       <c r="C73" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D73" t="s">
         <v>94</v>
@@ -9679,76 +9679,76 @@
         <v>301</v>
       </c>
       <c r="L73">
-        <v>2.6</v>
+        <v>1.47</v>
       </c>
       <c r="M73">
-        <v>2.97</v>
+        <v>4.25</v>
       </c>
       <c r="N73">
-        <v>2.9</v>
+        <v>6.55</v>
       </c>
       <c r="O73">
+        <v>1.36</v>
+      </c>
+      <c r="P73">
+        <v>12</v>
+      </c>
+      <c r="Q73">
+        <v>3.5</v>
+      </c>
+      <c r="R73">
+        <v>1.36</v>
+      </c>
+      <c r="S73">
+        <v>3</v>
+      </c>
+      <c r="T73">
+        <v>2.63</v>
+      </c>
+      <c r="U73">
+        <v>1.44</v>
+      </c>
+      <c r="V73">
+        <v>7</v>
+      </c>
+      <c r="W73">
+        <v>1.1</v>
+      </c>
+      <c r="X73">
+        <v>1.01</v>
+      </c>
+      <c r="Y73">
+        <v>11</v>
+      </c>
+      <c r="Z73">
+        <v>1.22</v>
+      </c>
+      <c r="AA73">
+        <v>3.52</v>
+      </c>
+      <c r="AB73">
+        <v>1.85</v>
+      </c>
+      <c r="AC73">
         <v>1.95</v>
       </c>
-      <c r="P73">
-        <v>6.75</v>
-      </c>
-      <c r="Q73">
-        <v>2.2</v>
-      </c>
-      <c r="R73">
-        <v>1.49</v>
-      </c>
-      <c r="S73">
-        <v>2.55</v>
-      </c>
-      <c r="T73">
-        <v>3.3</v>
-      </c>
-      <c r="U73">
-        <v>1.29</v>
-      </c>
-      <c r="V73">
-        <v>8.1</v>
-      </c>
-      <c r="W73">
-        <v>1.03</v>
-      </c>
-      <c r="X73">
-        <v>1.06</v>
-      </c>
-      <c r="Y73">
-        <v>6.5</v>
-      </c>
-      <c r="Z73">
-        <v>1.44</v>
-      </c>
-      <c r="AA73">
-        <v>2.6</v>
-      </c>
-      <c r="AB73">
-        <v>2.3</v>
-      </c>
-      <c r="AC73">
-        <v>1.53</v>
-      </c>
       <c r="AD73">
-        <v>4.75</v>
+        <v>2.98</v>
       </c>
       <c r="AE73">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AF73">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AG73">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AH73">
-        <v>8.300000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="AI73">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AJ73" t="s">
         <v>303</v>
@@ -9768,7 +9768,7 @@
         <v>60</v>
       </c>
       <c r="C74" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D74" t="s">
         <v>94</v>
@@ -9795,76 +9795,76 @@
         <v>301</v>
       </c>
       <c r="L74">
-        <v>1.47</v>
+        <v>2.18</v>
       </c>
       <c r="M74">
-        <v>4.25</v>
+        <v>2.88</v>
       </c>
       <c r="N74">
-        <v>6.55</v>
+        <v>3.8</v>
       </c>
       <c r="O74">
-        <v>1.36</v>
+        <v>1.9</v>
       </c>
       <c r="P74">
+        <v>5.75</v>
+      </c>
+      <c r="Q74">
+        <v>2.37</v>
+      </c>
+      <c r="R74">
+        <v>1.59</v>
+      </c>
+      <c r="S74">
+        <v>2.38</v>
+      </c>
+      <c r="T74">
+        <v>3.8</v>
+      </c>
+      <c r="U74">
+        <v>1.22</v>
+      </c>
+      <c r="V74">
         <v>12</v>
       </c>
-      <c r="Q74">
-        <v>3.5</v>
-      </c>
-      <c r="R74">
-        <v>1.36</v>
-      </c>
-      <c r="S74">
-        <v>3</v>
-      </c>
-      <c r="T74">
-        <v>2.63</v>
-      </c>
-      <c r="U74">
-        <v>1.44</v>
-      </c>
-      <c r="V74">
-        <v>7</v>
-      </c>
       <c r="W74">
+        <v>1.02</v>
+      </c>
+      <c r="X74">
+        <v>1.07</v>
+      </c>
+      <c r="Y74">
+        <v>6</v>
+      </c>
+      <c r="Z74">
+        <v>1.57</v>
+      </c>
+      <c r="AA74">
+        <v>2.39</v>
+      </c>
+      <c r="AB74">
+        <v>2.62</v>
+      </c>
+      <c r="AC74">
+        <v>1.4</v>
+      </c>
+      <c r="AD74">
+        <v>5.1</v>
+      </c>
+      <c r="AE74">
         <v>1.1</v>
       </c>
-      <c r="X74">
-        <v>1.01</v>
-      </c>
-      <c r="Y74">
-        <v>11</v>
-      </c>
-      <c r="Z74">
-        <v>1.22</v>
-      </c>
-      <c r="AA74">
-        <v>3.52</v>
-      </c>
-      <c r="AB74">
-        <v>1.85</v>
-      </c>
-      <c r="AC74">
-        <v>1.95</v>
-      </c>
-      <c r="AD74">
-        <v>2.98</v>
-      </c>
-      <c r="AE74">
-        <v>1.3</v>
-      </c>
       <c r="AF74">
-        <v>1.91</v>
+        <v>2.19</v>
       </c>
       <c r="AG74">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AH74">
-        <v>5.8</v>
+        <v>10</v>
       </c>
       <c r="AI74">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AJ74" t="s">
         <v>303</v>
@@ -9911,70 +9911,70 @@
         <v>301</v>
       </c>
       <c r="L75">
-        <v>2.55</v>
+        <v>1.9</v>
       </c>
       <c r="M75">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="N75">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="O75">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="P75">
-        <v>5</v>
+        <v>6.25</v>
       </c>
       <c r="Q75">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="R75">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="S75">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="T75">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="U75">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="V75">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="W75">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X75">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="Y75">
-        <v>5</v>
+        <v>6.25</v>
       </c>
       <c r="Z75">
-        <v>1.77</v>
+        <v>1.53</v>
       </c>
       <c r="AA75">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="AB75">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="AC75">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AD75">
-        <v>7.5</v>
+        <v>5.25</v>
       </c>
       <c r="AE75">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AF75">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="AG75">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AH75">
         <v>10</v>
@@ -10027,70 +10027,70 @@
         <v>301</v>
       </c>
       <c r="L76">
-        <v>1.9</v>
+        <v>2.55</v>
       </c>
       <c r="M76">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="N76">
+        <v>3.1</v>
+      </c>
+      <c r="O76">
+        <v>1.95</v>
+      </c>
+      <c r="P76">
+        <v>5</v>
+      </c>
+      <c r="Q76">
+        <v>2.5</v>
+      </c>
+      <c r="R76">
+        <v>1.73</v>
+      </c>
+      <c r="S76">
+        <v>2</v>
+      </c>
+      <c r="T76">
         <v>4.5</v>
       </c>
-      <c r="O76">
-        <v>1.62</v>
-      </c>
-      <c r="P76">
-        <v>6.25</v>
-      </c>
-      <c r="Q76">
-        <v>3</v>
-      </c>
-      <c r="R76">
-        <v>1.57</v>
-      </c>
-      <c r="S76">
-        <v>2.25</v>
-      </c>
-      <c r="T76">
-        <v>3.75</v>
-      </c>
       <c r="U76">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="V76">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="W76">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X76">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="Y76">
-        <v>6.25</v>
+        <v>5</v>
       </c>
       <c r="Z76">
-        <v>1.53</v>
+        <v>1.77</v>
       </c>
       <c r="AA76">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="AB76">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="AC76">
+        <v>1.3</v>
+      </c>
+      <c r="AD76">
+        <v>7.5</v>
+      </c>
+      <c r="AE76">
+        <v>1.08</v>
+      </c>
+      <c r="AF76">
+        <v>2.63</v>
+      </c>
+      <c r="AG76">
         <v>1.44</v>
-      </c>
-      <c r="AD76">
-        <v>5.25</v>
-      </c>
-      <c r="AE76">
-        <v>1.15</v>
-      </c>
-      <c r="AF76">
-        <v>2.25</v>
-      </c>
-      <c r="AG76">
-        <v>1.57</v>
       </c>
       <c r="AH76">
         <v>10</v>
@@ -10116,7 +10116,7 @@
         <v>62</v>
       </c>
       <c r="C77" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D77" t="s">
         <v>94</v>
@@ -10143,76 +10143,76 @@
         <v>301</v>
       </c>
       <c r="L77">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="M77">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="N77">
-        <v>6</v>
+        <v>5.46</v>
       </c>
       <c r="O77">
         <v>1.49</v>
       </c>
       <c r="P77">
-        <v>8.75</v>
+        <v>6.5</v>
       </c>
       <c r="Q77">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="R77">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="S77">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="T77">
-        <v>2.75</v>
+        <v>3.35</v>
       </c>
       <c r="U77">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="V77">
-        <v>7.25</v>
+        <v>8.9</v>
       </c>
       <c r="W77">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X77">
+        <v>1.09</v>
+      </c>
+      <c r="Y77">
+        <v>6.5</v>
+      </c>
+      <c r="Z77">
+        <v>1.42</v>
+      </c>
+      <c r="AA77">
+        <v>2.5</v>
+      </c>
+      <c r="AB77">
+        <v>2.4</v>
+      </c>
+      <c r="AC77">
+        <v>1.5</v>
+      </c>
+      <c r="AD77">
+        <v>4.4</v>
+      </c>
+      <c r="AE77">
+        <v>1.18</v>
+      </c>
+      <c r="AF77">
+        <v>2.4</v>
+      </c>
+      <c r="AG77">
+        <v>1.5</v>
+      </c>
+      <c r="AH77">
+        <v>8.5</v>
+      </c>
+      <c r="AI77">
         <v>1.03</v>
-      </c>
-      <c r="Y77">
-        <v>9</v>
-      </c>
-      <c r="Z77">
-        <v>1.3</v>
-      </c>
-      <c r="AA77">
-        <v>3.2</v>
-      </c>
-      <c r="AB77">
-        <v>1.95</v>
-      </c>
-      <c r="AC77">
-        <v>1.75</v>
-      </c>
-      <c r="AD77">
-        <v>3.35</v>
-      </c>
-      <c r="AE77">
-        <v>1.29</v>
-      </c>
-      <c r="AF77">
-        <v>2</v>
-      </c>
-      <c r="AG77">
-        <v>1.73</v>
-      </c>
-      <c r="AH77">
-        <v>6.1</v>
-      </c>
-      <c r="AI77">
-        <v>1.09</v>
       </c>
       <c r="AJ77" t="s">
         <v>303</v>
@@ -10232,7 +10232,7 @@
         <v>62</v>
       </c>
       <c r="C78" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D78" t="s">
         <v>94</v>
@@ -10259,76 +10259,76 @@
         <v>301</v>
       </c>
       <c r="L78">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="M78">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="N78">
-        <v>5.46</v>
+        <v>6</v>
       </c>
       <c r="O78">
         <v>1.49</v>
       </c>
       <c r="P78">
-        <v>6.5</v>
+        <v>8.75</v>
       </c>
       <c r="Q78">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="R78">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="S78">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="T78">
+        <v>2.75</v>
+      </c>
+      <c r="U78">
+        <v>1.35</v>
+      </c>
+      <c r="V78">
+        <v>7.25</v>
+      </c>
+      <c r="W78">
+        <v>1.07</v>
+      </c>
+      <c r="X78">
+        <v>1.03</v>
+      </c>
+      <c r="Y78">
+        <v>9</v>
+      </c>
+      <c r="Z78">
+        <v>1.3</v>
+      </c>
+      <c r="AA78">
+        <v>3.2</v>
+      </c>
+      <c r="AB78">
+        <v>1.95</v>
+      </c>
+      <c r="AC78">
+        <v>1.75</v>
+      </c>
+      <c r="AD78">
         <v>3.35</v>
       </c>
-      <c r="U78">
-        <v>1.26</v>
-      </c>
-      <c r="V78">
-        <v>8.9</v>
-      </c>
-      <c r="W78">
-        <v>1.03</v>
-      </c>
-      <c r="X78">
+      <c r="AE78">
+        <v>1.29</v>
+      </c>
+      <c r="AF78">
+        <v>2</v>
+      </c>
+      <c r="AG78">
+        <v>1.73</v>
+      </c>
+      <c r="AH78">
+        <v>6.1</v>
+      </c>
+      <c r="AI78">
         <v>1.09</v>
-      </c>
-      <c r="Y78">
-        <v>6.5</v>
-      </c>
-      <c r="Z78">
-        <v>1.42</v>
-      </c>
-      <c r="AA78">
-        <v>2.5</v>
-      </c>
-      <c r="AB78">
-        <v>2.4</v>
-      </c>
-      <c r="AC78">
-        <v>1.5</v>
-      </c>
-      <c r="AD78">
-        <v>4.4</v>
-      </c>
-      <c r="AE78">
-        <v>1.18</v>
-      </c>
-      <c r="AF78">
-        <v>2.4</v>
-      </c>
-      <c r="AG78">
-        <v>1.5</v>
-      </c>
-      <c r="AH78">
-        <v>8.5</v>
-      </c>
-      <c r="AI78">
-        <v>1.03</v>
       </c>
       <c r="AJ78" t="s">
         <v>303</v>
@@ -10464,7 +10464,7 @@
         <v>63</v>
       </c>
       <c r="C80" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="D80" t="s">
         <v>94</v>
@@ -10491,76 +10491,76 @@
         <v>301</v>
       </c>
       <c r="L80">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="M80">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="N80">
-        <v>3.39</v>
+        <v>3.74</v>
       </c>
       <c r="O80">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="P80">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q80">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="R80">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="S80">
-        <v>2.62</v>
+        <v>3.55</v>
       </c>
       <c r="T80">
-        <v>3</v>
+        <v>2.45</v>
       </c>
       <c r="U80">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="V80">
-        <v>7.6</v>
+        <v>5.95</v>
       </c>
       <c r="W80">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X80">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y80">
-        <v>8.699999999999999</v>
+        <v>13</v>
       </c>
       <c r="Z80">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AA80">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB80">
+        <v>1.72</v>
+      </c>
+      <c r="AC80">
+        <v>2.01</v>
+      </c>
+      <c r="AD80">
+        <v>2.83</v>
+      </c>
+      <c r="AE80">
+        <v>1.38</v>
+      </c>
+      <c r="AF80">
+        <v>1.73</v>
+      </c>
+      <c r="AG80">
         <v>2.1</v>
       </c>
-      <c r="AC80">
-        <v>1.68</v>
-      </c>
-      <c r="AD80">
-        <v>3.6</v>
-      </c>
-      <c r="AE80">
-        <v>1.25</v>
-      </c>
-      <c r="AF80">
-        <v>1.85</v>
-      </c>
-      <c r="AG80">
-        <v>1.83</v>
-      </c>
       <c r="AH80">
-        <v>7.6</v>
+        <v>5</v>
       </c>
       <c r="AI80">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="AJ80" t="s">
         <v>303</v>
@@ -10580,7 +10580,7 @@
         <v>63</v>
       </c>
       <c r="C81" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="D81" t="s">
         <v>94</v>
@@ -10607,76 +10607,76 @@
         <v>301</v>
       </c>
       <c r="L81">
-        <v>1.6</v>
+        <v>1.91</v>
       </c>
       <c r="M81">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="N81">
-        <v>3.74</v>
+        <v>3.39</v>
       </c>
       <c r="O81">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="P81">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q81">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="R81">
+        <v>1.42</v>
+      </c>
+      <c r="S81">
+        <v>2.62</v>
+      </c>
+      <c r="T81">
+        <v>3</v>
+      </c>
+      <c r="U81">
+        <v>1.33</v>
+      </c>
+      <c r="V81">
+        <v>7.6</v>
+      </c>
+      <c r="W81">
+        <v>1.06</v>
+      </c>
+      <c r="X81">
+        <v>1.01</v>
+      </c>
+      <c r="Y81">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="Z81">
+        <v>1.3</v>
+      </c>
+      <c r="AA81">
+        <v>3</v>
+      </c>
+      <c r="AB81">
+        <v>2.1</v>
+      </c>
+      <c r="AC81">
+        <v>1.68</v>
+      </c>
+      <c r="AD81">
+        <v>3.6</v>
+      </c>
+      <c r="AE81">
         <v>1.25</v>
       </c>
-      <c r="S81">
-        <v>3.55</v>
-      </c>
-      <c r="T81">
-        <v>2.45</v>
-      </c>
-      <c r="U81">
-        <v>1.5</v>
-      </c>
-      <c r="V81">
-        <v>5.95</v>
-      </c>
-      <c r="W81">
+      <c r="AF81">
+        <v>1.85</v>
+      </c>
+      <c r="AG81">
+        <v>1.83</v>
+      </c>
+      <c r="AH81">
+        <v>7.6</v>
+      </c>
+      <c r="AI81">
         <v>1.07</v>
-      </c>
-      <c r="X81">
-        <v>1.04</v>
-      </c>
-      <c r="Y81">
-        <v>13</v>
-      </c>
-      <c r="Z81">
-        <v>1.18</v>
-      </c>
-      <c r="AA81">
-        <v>4</v>
-      </c>
-      <c r="AB81">
-        <v>1.72</v>
-      </c>
-      <c r="AC81">
-        <v>2.01</v>
-      </c>
-      <c r="AD81">
-        <v>2.83</v>
-      </c>
-      <c r="AE81">
-        <v>1.38</v>
-      </c>
-      <c r="AF81">
-        <v>1.73</v>
-      </c>
-      <c r="AG81">
-        <v>2.1</v>
-      </c>
-      <c r="AH81">
-        <v>5</v>
-      </c>
-      <c r="AI81">
-        <v>1.15</v>
       </c>
       <c r="AJ81" t="s">
         <v>303</v>
@@ -10812,7 +10812,7 @@
         <v>64</v>
       </c>
       <c r="C83" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="D83" t="s">
         <v>94</v>
@@ -10839,76 +10839,76 @@
         <v>301</v>
       </c>
       <c r="L83">
-        <v>1.87</v>
+        <v>2.63</v>
       </c>
       <c r="M83">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="N83">
-        <v>3.46</v>
+        <v>2.4</v>
       </c>
       <c r="O83">
-        <v>1.57</v>
+        <v>2.05</v>
       </c>
       <c r="P83">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Q83">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="R83">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S83">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T83">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U83">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V83">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W83">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X83">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y83">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z83">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AA83">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB83">
+        <v>1.5</v>
+      </c>
+      <c r="AC83">
+        <v>2.4</v>
+      </c>
+      <c r="AD83">
+        <v>2.2</v>
+      </c>
+      <c r="AE83">
         <v>1.61</v>
       </c>
-      <c r="AC83">
-        <v>2.25</v>
-      </c>
-      <c r="AD83">
-        <v>0</v>
-      </c>
-      <c r="AE83">
-        <v>0</v>
-      </c>
       <c r="AF83">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG83">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH83">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AI83">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AJ83" t="s">
         <v>303</v>
@@ -10928,7 +10928,7 @@
         <v>64</v>
       </c>
       <c r="C84" t="s">
-        <v>93</v>
+        <v>70</v>
       </c>
       <c r="D84" t="s">
         <v>94</v>
@@ -10955,76 +10955,76 @@
         <v>301</v>
       </c>
       <c r="L84">
-        <v>2.11</v>
+        <v>1.87</v>
       </c>
       <c r="M84">
-        <v>3.12</v>
+        <v>3.6</v>
       </c>
       <c r="N84">
-        <v>3.08</v>
+        <v>3.46</v>
       </c>
       <c r="O84">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="P84">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="Q84">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="R84">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S84">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T84">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U84">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="V84">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="W84">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X84">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y84">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Z84">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AA84">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AB84">
-        <v>1.44</v>
+        <v>1.61</v>
       </c>
       <c r="AC84">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="AD84">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE84">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF84">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AG84">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AH84">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AI84">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AJ84" t="s">
         <v>303</v>
@@ -11044,7 +11044,7 @@
         <v>64</v>
       </c>
       <c r="C85" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D85" t="s">
         <v>94</v>
@@ -11071,76 +11071,76 @@
         <v>301</v>
       </c>
       <c r="L85">
-        <v>1.45</v>
+        <v>3.14</v>
       </c>
       <c r="M85">
-        <v>3.8</v>
+        <v>3.12</v>
       </c>
       <c r="N85">
+        <v>2.5</v>
+      </c>
+      <c r="O85">
+        <v>2.3</v>
+      </c>
+      <c r="P85">
         <v>6</v>
       </c>
-      <c r="O85">
-        <v>1.36</v>
-      </c>
-      <c r="P85">
-        <v>14</v>
-      </c>
       <c r="Q85">
-        <v>3.1</v>
+        <v>1.91</v>
       </c>
       <c r="R85">
+        <v>1.6</v>
+      </c>
+      <c r="S85">
+        <v>2.25</v>
+      </c>
+      <c r="T85">
+        <v>3.6</v>
+      </c>
+      <c r="U85">
         <v>1.25</v>
       </c>
-      <c r="S85">
-        <v>3.75</v>
-      </c>
-      <c r="T85">
-        <v>2.1</v>
-      </c>
-      <c r="U85">
-        <v>1.67</v>
-      </c>
       <c r="V85">
-        <v>4.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W85">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="X85">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="Y85">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="Z85">
-        <v>1.17</v>
+        <v>1.53</v>
       </c>
       <c r="AA85">
-        <v>5</v>
+        <v>2.45</v>
       </c>
       <c r="AB85">
-        <v>1.5</v>
+        <v>2.65</v>
       </c>
       <c r="AC85">
-        <v>2.4</v>
+        <v>1.48</v>
       </c>
       <c r="AD85">
-        <v>2.15</v>
+        <v>4.9</v>
       </c>
       <c r="AE85">
-        <v>1.61</v>
+        <v>1.15</v>
       </c>
       <c r="AF85">
-        <v>1.57</v>
+        <v>2.05</v>
       </c>
       <c r="AG85">
-        <v>2.25</v>
+        <v>1.68</v>
       </c>
       <c r="AH85">
-        <v>3.8</v>
+        <v>11.5</v>
       </c>
       <c r="AI85">
-        <v>1.25</v>
+        <v>1.04</v>
       </c>
       <c r="AJ85" t="s">
         <v>303</v>
@@ -11187,22 +11187,22 @@
         <v>301</v>
       </c>
       <c r="L86">
-        <v>2.63</v>
+        <v>1.45</v>
       </c>
       <c r="M86">
+        <v>3.8</v>
+      </c>
+      <c r="N86">
+        <v>6</v>
+      </c>
+      <c r="O86">
+        <v>1.36</v>
+      </c>
+      <c r="P86">
+        <v>14</v>
+      </c>
+      <c r="Q86">
         <v>3.1</v>
-      </c>
-      <c r="N86">
-        <v>2.4</v>
-      </c>
-      <c r="O86">
-        <v>2.05</v>
-      </c>
-      <c r="P86">
-        <v>11.5</v>
-      </c>
-      <c r="Q86">
-        <v>1.8</v>
       </c>
       <c r="R86">
         <v>1.25</v>
@@ -11211,22 +11211,22 @@
         <v>3.75</v>
       </c>
       <c r="T86">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="U86">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="V86">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="W86">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X86">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y86">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="Z86">
         <v>1.17</v>
@@ -11241,16 +11241,16 @@
         <v>2.4</v>
       </c>
       <c r="AD86">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AE86">
         <v>1.61</v>
       </c>
       <c r="AF86">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AG86">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="AH86">
         <v>3.8</v>
@@ -11276,7 +11276,7 @@
         <v>64</v>
       </c>
       <c r="C87" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="D87" t="s">
         <v>94</v>
@@ -11303,76 +11303,76 @@
         <v>301</v>
       </c>
       <c r="L87">
-        <v>3.14</v>
+        <v>2.98</v>
       </c>
       <c r="M87">
-        <v>3.12</v>
+        <v>3.07</v>
       </c>
       <c r="N87">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="O87">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="P87">
-        <v>6</v>
+        <v>11.5</v>
       </c>
       <c r="Q87">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="R87">
-        <v>1.6</v>
+        <v>1.25</v>
       </c>
       <c r="S87">
+        <v>3.75</v>
+      </c>
+      <c r="T87">
         <v>2.25</v>
       </c>
-      <c r="T87">
-        <v>3.6</v>
-      </c>
       <c r="U87">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="V87">
-        <v>8.699999999999999</v>
+        <v>5.5</v>
       </c>
       <c r="W87">
+        <v>1.14</v>
+      </c>
+      <c r="X87">
         <v>1.01</v>
       </c>
-      <c r="X87">
-        <v>1.11</v>
-      </c>
       <c r="Y87">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="Z87">
+        <v>1.18</v>
+      </c>
+      <c r="AA87">
+        <v>4.75</v>
+      </c>
+      <c r="AB87">
         <v>1.53</v>
       </c>
-      <c r="AA87">
-        <v>2.45</v>
-      </c>
-      <c r="AB87">
-        <v>2.65</v>
-      </c>
       <c r="AC87">
-        <v>1.48</v>
+        <v>2.35</v>
       </c>
       <c r="AD87">
-        <v>4.9</v>
+        <v>2.25</v>
       </c>
       <c r="AE87">
-        <v>1.15</v>
+        <v>1.57</v>
       </c>
       <c r="AF87">
-        <v>2.05</v>
+        <v>1.44</v>
       </c>
       <c r="AG87">
-        <v>1.68</v>
+        <v>2.63</v>
       </c>
       <c r="AH87">
-        <v>11.5</v>
+        <v>4</v>
       </c>
       <c r="AI87">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="AJ87" t="s">
         <v>303</v>
@@ -11392,7 +11392,7 @@
         <v>64</v>
       </c>
       <c r="C88" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D88" t="s">
         <v>94</v>
@@ -11419,76 +11419,76 @@
         <v>301</v>
       </c>
       <c r="L88">
-        <v>1.3</v>
+        <v>2.47</v>
       </c>
       <c r="M88">
-        <v>4.75</v>
+        <v>3.07</v>
       </c>
       <c r="N88">
-        <v>6.4</v>
+        <v>2.57</v>
       </c>
       <c r="O88">
-        <v>1.28</v>
+        <v>2.05</v>
       </c>
       <c r="P88">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="Q88">
-        <v>3.35</v>
+        <v>1.83</v>
       </c>
       <c r="R88">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="S88">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="T88">
-        <v>2.22</v>
+        <v>2.5</v>
       </c>
       <c r="U88">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="V88">
-        <v>4.3</v>
+        <v>6.5</v>
       </c>
       <c r="W88">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="X88">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y88">
-        <v>16.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Z88">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="AA88">
-        <v>5.5</v>
+        <v>3.74</v>
       </c>
       <c r="AB88">
-        <v>1.42</v>
+        <v>1.8</v>
       </c>
       <c r="AC88">
-        <v>2.5</v>
+        <v>1.91</v>
       </c>
       <c r="AD88">
-        <v>2.2</v>
+        <v>2.74</v>
       </c>
       <c r="AE88">
-        <v>1.6</v>
+        <v>1.37</v>
       </c>
       <c r="AF88">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AG88">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AH88">
-        <v>3.58</v>
+        <v>4.95</v>
       </c>
       <c r="AI88">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="AJ88" t="s">
         <v>303</v>
@@ -11508,7 +11508,7 @@
         <v>64</v>
       </c>
       <c r="C89" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D89" t="s">
         <v>94</v>
@@ -11535,76 +11535,76 @@
         <v>301</v>
       </c>
       <c r="L89">
-        <v>2.98</v>
+        <v>1.3</v>
       </c>
       <c r="M89">
-        <v>3.07</v>
+        <v>4.75</v>
       </c>
       <c r="N89">
-        <v>2.18</v>
+        <v>6.4</v>
       </c>
       <c r="O89">
+        <v>1.28</v>
+      </c>
+      <c r="P89">
+        <v>27</v>
+      </c>
+      <c r="Q89">
+        <v>3.35</v>
+      </c>
+      <c r="R89">
+        <v>1.22</v>
+      </c>
+      <c r="S89">
+        <v>4</v>
+      </c>
+      <c r="T89">
+        <v>2.22</v>
+      </c>
+      <c r="U89">
+        <v>1.75</v>
+      </c>
+      <c r="V89">
+        <v>4.3</v>
+      </c>
+      <c r="W89">
+        <v>1.2</v>
+      </c>
+      <c r="X89">
+        <v>1.02</v>
+      </c>
+      <c r="Y89">
+        <v>16.5</v>
+      </c>
+      <c r="Z89">
+        <v>1.15</v>
+      </c>
+      <c r="AA89">
+        <v>5.5</v>
+      </c>
+      <c r="AB89">
+        <v>1.42</v>
+      </c>
+      <c r="AC89">
+        <v>2.5</v>
+      </c>
+      <c r="AD89">
         <v>2.2</v>
       </c>
-      <c r="P89">
-        <v>11.5</v>
-      </c>
-      <c r="Q89">
-        <v>1.73</v>
-      </c>
-      <c r="R89">
-        <v>1.25</v>
-      </c>
-      <c r="S89">
-        <v>3.75</v>
-      </c>
-      <c r="T89">
-        <v>2.25</v>
-      </c>
-      <c r="U89">
-        <v>1.57</v>
-      </c>
-      <c r="V89">
-        <v>5.5</v>
-      </c>
-      <c r="W89">
-        <v>1.14</v>
-      </c>
-      <c r="X89">
-        <v>1.01</v>
-      </c>
-      <c r="Y89">
-        <v>17</v>
-      </c>
-      <c r="Z89">
-        <v>1.18</v>
-      </c>
-      <c r="AA89">
-        <v>4.75</v>
-      </c>
-      <c r="AB89">
-        <v>1.53</v>
-      </c>
-      <c r="AC89">
-        <v>2.35</v>
-      </c>
-      <c r="AD89">
-        <v>2.25</v>
-      </c>
       <c r="AE89">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AF89">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AG89">
-        <v>2.63</v>
+        <v>2</v>
       </c>
       <c r="AH89">
-        <v>4</v>
+        <v>3.58</v>
       </c>
       <c r="AI89">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AJ89" t="s">
         <v>303</v>
@@ -11651,76 +11651,76 @@
         <v>301</v>
       </c>
       <c r="L90">
-        <v>2.47</v>
+        <v>2.11</v>
       </c>
       <c r="M90">
-        <v>3.07</v>
+        <v>3.12</v>
       </c>
       <c r="N90">
-        <v>2.57</v>
+        <v>3.08</v>
       </c>
       <c r="O90">
+        <v>1.67</v>
+      </c>
+      <c r="P90">
+        <v>12.5</v>
+      </c>
+      <c r="Q90">
+        <v>2.2</v>
+      </c>
+      <c r="R90">
+        <v>1.22</v>
+      </c>
+      <c r="S90">
+        <v>4</v>
+      </c>
+      <c r="T90">
+        <v>2.1</v>
+      </c>
+      <c r="U90">
+        <v>1.67</v>
+      </c>
+      <c r="V90">
+        <v>4.5</v>
+      </c>
+      <c r="W90">
+        <v>1.18</v>
+      </c>
+      <c r="X90">
+        <v>1.01</v>
+      </c>
+      <c r="Y90">
+        <v>17</v>
+      </c>
+      <c r="Z90">
+        <v>1.17</v>
+      </c>
+      <c r="AA90">
+        <v>5</v>
+      </c>
+      <c r="AB90">
+        <v>1.44</v>
+      </c>
+      <c r="AC90">
+        <v>2.6</v>
+      </c>
+      <c r="AD90">
         <v>2.05</v>
       </c>
-      <c r="P90">
-        <v>10</v>
-      </c>
-      <c r="Q90">
-        <v>1.83</v>
-      </c>
-      <c r="R90">
-        <v>1.33</v>
-      </c>
-      <c r="S90">
-        <v>3.25</v>
-      </c>
-      <c r="T90">
-        <v>2.5</v>
-      </c>
-      <c r="U90">
-        <v>1.5</v>
-      </c>
-      <c r="V90">
-        <v>6.5</v>
-      </c>
-      <c r="W90">
-        <v>1.11</v>
-      </c>
-      <c r="X90">
-        <v>1</v>
-      </c>
-      <c r="Y90">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="Z90">
-        <v>1.21</v>
-      </c>
-      <c r="AA90">
-        <v>3.74</v>
-      </c>
-      <c r="AB90">
-        <v>1.8</v>
-      </c>
-      <c r="AC90">
-        <v>1.91</v>
-      </c>
-      <c r="AD90">
-        <v>2.74</v>
-      </c>
       <c r="AE90">
-        <v>1.37</v>
+        <v>1.7</v>
       </c>
       <c r="AF90">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AG90">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="AH90">
-        <v>4.95</v>
+        <v>3.65</v>
       </c>
       <c r="AI90">
-        <v>1.11</v>
+        <v>1.28</v>
       </c>
       <c r="AJ90" t="s">
         <v>303</v>
@@ -11740,7 +11740,7 @@
         <v>65</v>
       </c>
       <c r="C91" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D91" t="s">
         <v>94</v>
@@ -11767,64 +11767,64 @@
         <v>301</v>
       </c>
       <c r="L91">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="M91">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="N91">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="O91">
-        <v>1.83</v>
+        <v>2.65</v>
       </c>
       <c r="P91">
         <v>6.5</v>
       </c>
       <c r="Q91">
-        <v>2.38</v>
+        <v>1.75</v>
       </c>
       <c r="R91">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="S91">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="T91">
-        <v>3.48</v>
+        <v>3.2</v>
       </c>
       <c r="U91">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="V91">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="W91">
         <v>1.05</v>
       </c>
       <c r="X91">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Y91">
         <v>6.5</v>
       </c>
       <c r="Z91">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AA91">
-        <v>2.49</v>
+        <v>2.65</v>
       </c>
       <c r="AB91">
-        <v>2.52</v>
+        <v>2.4</v>
       </c>
       <c r="AC91">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AD91">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="AE91">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AF91">
         <v>2.05</v>
@@ -11833,10 +11833,10 @@
         <v>1.7</v>
       </c>
       <c r="AH91">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="AI91">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AJ91" t="s">
         <v>303</v>
@@ -11856,7 +11856,7 @@
         <v>65</v>
       </c>
       <c r="C92" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D92" t="s">
         <v>94</v>
@@ -11883,76 +11883,76 @@
         <v>301</v>
       </c>
       <c r="L92">
-        <v>2.43</v>
+        <v>1.43</v>
       </c>
       <c r="M92">
-        <v>3.34</v>
+        <v>4.4</v>
       </c>
       <c r="N92">
-        <v>2.53</v>
+        <v>6.5</v>
       </c>
       <c r="O92">
-        <v>1.83</v>
+        <v>1.33</v>
       </c>
       <c r="P92">
-        <v>0</v>
+        <v>14.75</v>
       </c>
       <c r="Q92">
+        <v>3.5</v>
+      </c>
+      <c r="R92">
+        <v>1.3</v>
+      </c>
+      <c r="S92">
+        <v>3.1</v>
+      </c>
+      <c r="T92">
+        <v>2.4</v>
+      </c>
+      <c r="U92">
+        <v>1.5</v>
+      </c>
+      <c r="V92">
+        <v>5.5</v>
+      </c>
+      <c r="W92">
+        <v>1.12</v>
+      </c>
+      <c r="X92">
+        <v>1.01</v>
+      </c>
+      <c r="Y92">
+        <v>11</v>
+      </c>
+      <c r="Z92">
+        <v>1.15</v>
+      </c>
+      <c r="AA92">
+        <v>4</v>
+      </c>
+      <c r="AB92">
+        <v>1.67</v>
+      </c>
+      <c r="AC92">
         <v>2.1</v>
       </c>
-      <c r="R92">
-        <v>1.36</v>
-      </c>
-      <c r="S92">
-        <v>2.95</v>
-      </c>
-      <c r="T92">
-        <v>2.8</v>
-      </c>
-      <c r="U92">
-        <v>1.4</v>
-      </c>
-      <c r="V92">
-        <v>7.3</v>
-      </c>
-      <c r="W92">
-        <v>1.08</v>
-      </c>
-      <c r="X92">
-        <v>1.02</v>
-      </c>
-      <c r="Y92">
-        <v>10</v>
-      </c>
-      <c r="Z92">
-        <v>1.23</v>
-      </c>
-      <c r="AA92">
-        <v>3.4</v>
-      </c>
-      <c r="AB92">
-        <v>1.92</v>
-      </c>
-      <c r="AC92">
-        <v>1.86</v>
-      </c>
       <c r="AD92">
-        <v>3.25</v>
+        <v>2.59</v>
       </c>
       <c r="AE92">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="AF92">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AG92">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AH92">
-        <v>5.8</v>
+        <v>4.85</v>
       </c>
       <c r="AI92">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AJ92" t="s">
         <v>303</v>
@@ -11972,7 +11972,7 @@
         <v>65</v>
       </c>
       <c r="C93" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D93" t="s">
         <v>94</v>
@@ -11999,76 +11999,76 @@
         <v>301</v>
       </c>
       <c r="L93">
-        <v>1.43</v>
+        <v>2.43</v>
       </c>
       <c r="M93">
-        <v>4.4</v>
+        <v>3.34</v>
       </c>
       <c r="N93">
-        <v>6.5</v>
+        <v>2.53</v>
       </c>
       <c r="O93">
-        <v>1.33</v>
+        <v>1.83</v>
       </c>
       <c r="P93">
-        <v>14.75</v>
+        <v>0</v>
       </c>
       <c r="Q93">
-        <v>3.5</v>
+        <v>2.1</v>
       </c>
       <c r="R93">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="S93">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="T93">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="U93">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="V93">
-        <v>5.5</v>
+        <v>7.3</v>
       </c>
       <c r="W93">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X93">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y93">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Z93">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="AA93">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="AB93">
-        <v>1.67</v>
+        <v>1.92</v>
       </c>
       <c r="AC93">
-        <v>2.1</v>
+        <v>1.86</v>
       </c>
       <c r="AD93">
-        <v>2.59</v>
+        <v>3.25</v>
       </c>
       <c r="AE93">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AF93">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AG93">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AH93">
-        <v>4.85</v>
+        <v>5.8</v>
       </c>
       <c r="AI93">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AJ93" t="s">
         <v>303</v>
@@ -12088,7 +12088,7 @@
         <v>65</v>
       </c>
       <c r="C94" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D94" t="s">
         <v>94</v>
@@ -12115,64 +12115,64 @@
         <v>301</v>
       </c>
       <c r="L94">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="M94">
+        <v>3.13</v>
+      </c>
+      <c r="N94">
         <v>3.1</v>
       </c>
-      <c r="N94">
-        <v>2</v>
-      </c>
       <c r="O94">
-        <v>2.65</v>
+        <v>1.83</v>
       </c>
       <c r="P94">
         <v>6.5</v>
       </c>
       <c r="Q94">
-        <v>1.75</v>
+        <v>2.38</v>
       </c>
       <c r="R94">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="S94">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="T94">
-        <v>3.2</v>
+        <v>3.48</v>
       </c>
       <c r="U94">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="V94">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="W94">
         <v>1.05</v>
       </c>
       <c r="X94">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Y94">
         <v>6.5</v>
       </c>
       <c r="Z94">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AA94">
-        <v>2.65</v>
+        <v>2.49</v>
       </c>
       <c r="AB94">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="AC94">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AD94">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AE94">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AF94">
         <v>2.05</v>
@@ -12181,10 +12181,10 @@
         <v>1.7</v>
       </c>
       <c r="AH94">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="AI94">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AJ94" t="s">
         <v>303</v>
@@ -12231,22 +12231,22 @@
         <v>301</v>
       </c>
       <c r="L95">
-        <v>1.56</v>
+        <v>2.63</v>
       </c>
       <c r="M95">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="N95">
-        <v>4.9</v>
+        <v>2.4</v>
       </c>
       <c r="O95">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="P95">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Q95">
-        <v>2.88</v>
+        <v>1.8</v>
       </c>
       <c r="R95">
         <v>1.22</v>
@@ -12267,10 +12267,10 @@
         <v>1.18</v>
       </c>
       <c r="X95">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y95">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z95">
         <v>1.15</v>
@@ -12279,25 +12279,25 @@
         <v>5.25</v>
       </c>
       <c r="AB95">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AC95">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="AD95">
         <v>2.1</v>
       </c>
       <c r="AE95">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AF95">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AG95">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="AH95">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AI95">
         <v>1.28</v>
@@ -12347,76 +12347,76 @@
         <v>301</v>
       </c>
       <c r="L96">
-        <v>2.15</v>
+        <v>1.53</v>
       </c>
       <c r="M96">
+        <v>3.79</v>
+      </c>
+      <c r="N96">
+        <v>4.9</v>
+      </c>
+      <c r="O96">
+        <v>1.43</v>
+      </c>
+      <c r="P96">
+        <v>10.5</v>
+      </c>
+      <c r="Q96">
         <v>3.2</v>
       </c>
-      <c r="N96">
-        <v>2.93</v>
-      </c>
-      <c r="O96">
-        <v>1.67</v>
-      </c>
-      <c r="P96">
-        <v>11.5</v>
-      </c>
-      <c r="Q96">
-        <v>2.2</v>
-      </c>
       <c r="R96">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S96">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="T96">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="U96">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="V96">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="W96">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X96">
         <v>1.04</v>
       </c>
       <c r="Y96">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Z96">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AA96">
-        <v>4.33</v>
+        <v>3.7</v>
       </c>
       <c r="AB96">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AC96">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AD96">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="AE96">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="AF96">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="AG96">
-        <v>2.38</v>
+        <v>1.83</v>
       </c>
       <c r="AH96">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AI96">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AJ96" t="s">
         <v>303</v>
@@ -12463,76 +12463,76 @@
         <v>301</v>
       </c>
       <c r="L97">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="M97">
-        <v>3.79</v>
+        <v>3.65</v>
       </c>
       <c r="N97">
         <v>4.9</v>
       </c>
       <c r="O97">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="P97">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="Q97">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="R97">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="S97">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="T97">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="U97">
-        <v>1.49</v>
+        <v>1.67</v>
       </c>
       <c r="V97">
-        <v>5.75</v>
+        <v>4.5</v>
       </c>
       <c r="W97">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="X97">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y97">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="Z97">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="AA97">
-        <v>3.7</v>
+        <v>5.25</v>
       </c>
       <c r="AB97">
-        <v>1.7</v>
+        <v>1.45</v>
       </c>
       <c r="AC97">
-        <v>2</v>
+        <v>2.55</v>
       </c>
       <c r="AD97">
-        <v>2.75</v>
+        <v>2.1</v>
       </c>
       <c r="AE97">
-        <v>1.39</v>
+        <v>1.67</v>
       </c>
       <c r="AF97">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="AG97">
-        <v>1.83</v>
+        <v>2.5</v>
       </c>
       <c r="AH97">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="AI97">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="AJ97" t="s">
         <v>303</v>
@@ -12579,76 +12579,76 @@
         <v>301</v>
       </c>
       <c r="L98">
-        <v>2.63</v>
+        <v>2.15</v>
       </c>
       <c r="M98">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N98">
-        <v>2.4</v>
+        <v>2.93</v>
       </c>
       <c r="O98">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="P98">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="Q98">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="R98">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="S98">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="T98">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="U98">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="V98">
+        <v>6</v>
+      </c>
+      <c r="W98">
+        <v>1.13</v>
+      </c>
+      <c r="X98">
+        <v>1.04</v>
+      </c>
+      <c r="Y98">
+        <v>10</v>
+      </c>
+      <c r="Z98">
+        <v>1.2</v>
+      </c>
+      <c r="AA98">
+        <v>4.33</v>
+      </c>
+      <c r="AB98">
+        <v>1.62</v>
+      </c>
+      <c r="AC98">
+        <v>2.15</v>
+      </c>
+      <c r="AD98">
+        <v>2.55</v>
+      </c>
+      <c r="AE98">
+        <v>1.5</v>
+      </c>
+      <c r="AF98">
+        <v>1.53</v>
+      </c>
+      <c r="AG98">
+        <v>2.38</v>
+      </c>
+      <c r="AH98">
         <v>4.5</v>
       </c>
-      <c r="W98">
-        <v>1.18</v>
-      </c>
-      <c r="X98">
-        <v>1.01</v>
-      </c>
-      <c r="Y98">
-        <v>17</v>
-      </c>
-      <c r="Z98">
-        <v>1.15</v>
-      </c>
-      <c r="AA98">
-        <v>5.25</v>
-      </c>
-      <c r="AB98">
-        <v>1.4</v>
-      </c>
-      <c r="AC98">
-        <v>2.75</v>
-      </c>
-      <c r="AD98">
-        <v>2.1</v>
-      </c>
-      <c r="AE98">
-        <v>1.65</v>
-      </c>
-      <c r="AF98">
-        <v>1.4</v>
-      </c>
-      <c r="AG98">
-        <v>2.75</v>
-      </c>
-      <c r="AH98">
-        <v>3.5</v>
-      </c>
       <c r="AI98">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AJ98" t="s">
         <v>303</v>
@@ -12900,7 +12900,7 @@
         <v>68</v>
       </c>
       <c r="C101" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D101" t="s">
         <v>94</v>

--- a/jogos_2025-07-19.xlsx
+++ b/jogos_2025-07-19.xlsx
@@ -232,15 +232,15 @@
     <t>Australia New South Wales NPL</t>
   </si>
   <si>
+    <t>South Korea K League 2</t>
+  </si>
+  <si>
     <t>South Korea K League 1</t>
   </si>
   <si>
     <t>Japan J1 League</t>
   </si>
   <si>
-    <t>South Korea K League 2</t>
-  </si>
-  <si>
     <t>China China League One</t>
   </si>
   <si>
@@ -250,42 +250,42 @@
     <t>Norway Eliteserien</t>
   </si>
   <si>
+    <t>Kazakhstan Kazakhstan Premier League</t>
+  </si>
+  <si>
     <t>Sweden Superettan</t>
   </si>
   <si>
     <t>Sweden Allsvenskan</t>
   </si>
   <si>
-    <t>Kazakhstan Kazakhstan Premier League</t>
+    <t>Finland Veikkausliiga</t>
   </si>
   <si>
     <t>Iceland Úrvalsdeild</t>
   </si>
   <si>
-    <t>Finland Veikkausliiga</t>
-  </si>
-  <si>
     <t>Estonia Meistriliiga</t>
   </si>
   <si>
+    <t>Chile Primera División</t>
+  </si>
+  <si>
     <t>Chile Primera B</t>
   </si>
   <si>
-    <t>Chile Primera División</t>
-  </si>
-  <si>
     <t>Argentina Primera División</t>
   </si>
   <si>
     <t>Argentina Prim B Nacional</t>
   </si>
   <si>
+    <t>Brazil Serie A</t>
+  </si>
+  <si>
     <t>Brazil Serie B</t>
   </si>
   <si>
-    <t>Brazil Serie A</t>
-  </si>
-  <si>
     <t>USA USL Championship</t>
   </si>
   <si>
@@ -316,45 +316,45 @@
     <t>Sutherland Sharks</t>
   </si>
   <si>
+    <t>Jeonnam Dragons</t>
+  </si>
+  <si>
     <t>Jeju United</t>
   </si>
   <si>
+    <t>Hwaseong</t>
+  </si>
+  <si>
+    <t>Gimpo Citizen</t>
+  </si>
+  <si>
+    <t>Gangwon</t>
+  </si>
+  <si>
     <t>Pohang Steelers</t>
   </si>
   <si>
+    <t>Shonan Bellmare</t>
+  </si>
+  <si>
+    <t>Yanbian Longding</t>
+  </si>
+  <si>
+    <t>Seoul E-Land</t>
+  </si>
+  <si>
     <t>Tokyo</t>
   </si>
   <si>
-    <t>Gangwon</t>
-  </si>
-  <si>
-    <t>Jeonnam Dragons</t>
-  </si>
-  <si>
-    <t>Shonan Bellmare</t>
-  </si>
-  <si>
-    <t>Yanbian Longding</t>
-  </si>
-  <si>
-    <t>Gimpo Citizen</t>
-  </si>
-  <si>
-    <t>Hwaseong</t>
-  </si>
-  <si>
-    <t>Seoul E-Land</t>
+    <t>Suzhou Dongwu</t>
+  </si>
+  <si>
+    <t>Shenyang Urban</t>
   </si>
   <si>
     <t>Dalian Zhixing</t>
   </si>
   <si>
-    <t>Shenyang Urban</t>
-  </si>
-  <si>
-    <t>Suzhou Dongwu</t>
-  </si>
-  <si>
     <t>Hebei Kungfu</t>
   </si>
   <si>
@@ -364,42 +364,42 @@
     <t>Beijing Guoan</t>
   </si>
   <si>
+    <t>KFUM</t>
+  </si>
+  <si>
     <t>Henan Jianye</t>
   </si>
   <si>
-    <t>KFUM</t>
+    <t>Yelimay Semey</t>
   </si>
   <si>
     <t>Oddevold</t>
   </si>
   <si>
+    <t>Kairat</t>
+  </si>
+  <si>
+    <t>Öster</t>
+  </si>
+  <si>
+    <t>Umeå</t>
+  </si>
+  <si>
+    <t>Östersunds FK</t>
+  </si>
+  <si>
     <t>Djurgården</t>
   </si>
   <si>
-    <t>Umeå</t>
-  </si>
-  <si>
-    <t>Yelimay Semey</t>
-  </si>
-  <si>
-    <t>Öster</t>
-  </si>
-  <si>
-    <t>Östersunds FK</t>
-  </si>
-  <si>
-    <t>Kairat</t>
-  </si>
-  <si>
     <t>Molde</t>
   </si>
   <si>
+    <t>VPS</t>
+  </si>
+  <si>
     <t>Breidablik</t>
   </si>
   <si>
-    <t>VPS</t>
-  </si>
-  <si>
     <t>Okzhetpes</t>
   </si>
   <si>
@@ -412,18 +412,18 @@
     <t>Harju Jalgpallikool</t>
   </si>
   <si>
+    <t>Tallinna FC Levadia</t>
+  </si>
+  <si>
     <t>Viking</t>
   </si>
   <si>
-    <t>Tallinna FC Levadia</t>
+    <t>Unión Española</t>
   </si>
   <si>
     <t>Cobreloa</t>
   </si>
   <si>
-    <t>Unión Española</t>
-  </si>
-  <si>
     <t>San Lorenzo</t>
   </si>
   <si>
@@ -433,106 +433,109 @@
     <t>Club Atlético Mitre</t>
   </si>
   <si>
+    <t>Fortaleza</t>
+  </si>
+  <si>
+    <t>Deportes Santa Cruz</t>
+  </si>
+  <si>
+    <t>Colo-Colo</t>
+  </si>
+  <si>
     <t>Goiás</t>
   </si>
   <si>
-    <t>Fortaleza</t>
-  </si>
-  <si>
-    <t>Deportes Santa Cruz</t>
-  </si>
-  <si>
-    <t>Colo-Colo</t>
-  </si>
-  <si>
     <t>Lanús</t>
   </si>
   <si>
+    <t>All Boys</t>
+  </si>
+  <si>
+    <t>Chaco For Ever</t>
+  </si>
+  <si>
+    <t>Rhode Island</t>
+  </si>
+  <si>
+    <t>ABC</t>
+  </si>
+  <si>
+    <t>Ituano</t>
+  </si>
+  <si>
+    <t>Deportivo Maipú</t>
+  </si>
+  <si>
+    <t>Colegiales</t>
+  </si>
+  <si>
+    <t>York9 FC</t>
+  </si>
+  <si>
+    <t>Arsenal de Sarandí</t>
+  </si>
+  <si>
+    <t>Colón</t>
+  </si>
+  <si>
+    <t>Estudiantes Río Cuarto</t>
+  </si>
+  <si>
     <t>Tristán Suárez</t>
   </si>
   <si>
-    <t>Deportivo Maipú</t>
-  </si>
-  <si>
-    <t>Rhode Island</t>
-  </si>
-  <si>
-    <t>Arsenal de Sarandí</t>
-  </si>
-  <si>
-    <t>Colegiales</t>
+    <t>Atlanta</t>
+  </si>
+  <si>
+    <t>Estudiantes Caseros</t>
+  </si>
+  <si>
+    <t>Gimnasia y Tiro</t>
   </si>
   <si>
     <t>Temperley</t>
   </si>
   <si>
-    <t>Colón</t>
-  </si>
-  <si>
-    <t>ABC</t>
-  </si>
-  <si>
-    <t>Estudiantes Río Cuarto</t>
-  </si>
-  <si>
-    <t>York9 FC</t>
+    <t>Alvarado</t>
+  </si>
+  <si>
+    <t>Defensores Unidos</t>
   </si>
   <si>
     <t>Deportivo Madryn</t>
   </si>
   <si>
-    <t>Defensores Unidos</t>
-  </si>
-  <si>
-    <t>Chaco For Ever</t>
-  </si>
-  <si>
     <t>Deportivo Morón</t>
   </si>
   <si>
-    <t>Ituano</t>
-  </si>
-  <si>
-    <t>Alvarado</t>
-  </si>
-  <si>
-    <t>Gimnasia y Tiro</t>
-  </si>
-  <si>
-    <t>Estudiantes Caseros</t>
-  </si>
-  <si>
-    <t>All Boys</t>
-  </si>
-  <si>
-    <t>Atlanta</t>
-  </si>
-  <si>
     <t>Vasco da Gama</t>
   </si>
   <si>
+    <t>Avaí</t>
+  </si>
+  <si>
     <t>Coritiba</t>
   </si>
   <si>
+    <t>Mirassol</t>
+  </si>
+  <si>
     <t>Coquimbo Unido</t>
   </si>
   <si>
-    <t>Avaí</t>
-  </si>
-  <si>
-    <t>Mirassol</t>
-  </si>
-  <si>
     <t>Platense</t>
   </si>
   <si>
     <t>Godoy Cruz</t>
   </si>
   <si>
+    <t>Ponte Preta</t>
+  </si>
+  <si>
     <t>Londrina</t>
   </si>
   <si>
-    <t>Ponte Preta</t>
+    <t>Crown Legacy</t>
   </si>
   <si>
     <t>Loudoun United</t>
@@ -541,63 +544,60 @@
     <t>Concepción</t>
   </si>
   <si>
-    <t>Crown Legacy</t>
-  </si>
-  <si>
     <t>Chattanooga FC</t>
   </si>
   <si>
+    <t>Columbus Crew</t>
+  </si>
+  <si>
+    <t>Carolina Core</t>
+  </si>
+  <si>
+    <t>Atlanta United FC</t>
+  </si>
+  <si>
+    <t>New York RB</t>
+  </si>
+  <si>
     <t>Montreal Impact</t>
   </si>
   <si>
+    <t>Volta Redonda</t>
+  </si>
+  <si>
+    <t>Charleston Battery</t>
+  </si>
+  <si>
     <t>New England Revolution</t>
   </si>
   <si>
-    <t>New York RB</t>
-  </si>
-  <si>
-    <t>Volta Redonda</t>
-  </si>
-  <si>
-    <t>Columbus Crew</t>
-  </si>
-  <si>
-    <t>Atlanta United FC</t>
-  </si>
-  <si>
-    <t>Carolina Core</t>
-  </si>
-  <si>
-    <t>Charleston Battery</t>
-  </si>
-  <si>
     <t>São Paulo</t>
   </si>
   <si>
+    <t>Instituto</t>
+  </si>
+  <si>
+    <t>Birmingham Legion</t>
+  </si>
+  <si>
     <t>Louisville City</t>
   </si>
   <si>
-    <t>Instituto</t>
-  </si>
-  <si>
-    <t>Birmingham Legion</t>
+    <t>FC Dallas</t>
+  </si>
+  <si>
+    <t>Nashville SC</t>
+  </si>
+  <si>
+    <t>Sporting KC</t>
+  </si>
+  <si>
+    <t>Seattle Sounders</t>
   </si>
   <si>
     <t>Houston Dynamo</t>
   </si>
   <si>
-    <t>Nashville SC</t>
-  </si>
-  <si>
-    <t>Sporting KC</t>
-  </si>
-  <si>
-    <t>Seattle Sounders</t>
-  </si>
-  <si>
-    <t>FC Dallas</t>
-  </si>
-  <si>
     <t>Real Salt Lake</t>
   </si>
   <si>
@@ -607,12 +607,12 @@
     <t>Los Angeles FC</t>
   </si>
   <si>
+    <t>San Diego</t>
+  </si>
+  <si>
     <t>Portland Timbers</t>
   </si>
   <si>
-    <t>San Diego</t>
-  </si>
-  <si>
     <t>Minnesota United II</t>
   </si>
   <si>
@@ -628,45 +628,45 @@
     <t>Blacktown City</t>
   </si>
   <si>
+    <t>Suwon Bluewings</t>
+  </si>
+  <si>
     <t>Anyang</t>
   </si>
   <si>
+    <t>Busan I'Park</t>
+  </si>
+  <si>
+    <t>Ansan Greeners</t>
+  </si>
+  <si>
+    <t>Daejeon Citizen</t>
+  </si>
+  <si>
     <t>Jeonbuk Motors</t>
   </si>
   <si>
+    <t>Cerezo Osaka</t>
+  </si>
+  <si>
+    <t>Qingdao Red Lions</t>
+  </si>
+  <si>
+    <t>Seongnam</t>
+  </si>
+  <si>
     <t>Urawa Reds</t>
   </si>
   <si>
-    <t>Daejeon Citizen</t>
-  </si>
-  <si>
-    <t>Suwon Bluewings</t>
-  </si>
-  <si>
-    <t>Cerezo Osaka</t>
-  </si>
-  <si>
-    <t>Qingdao Red Lions</t>
-  </si>
-  <si>
-    <t>Ansan Greeners</t>
-  </si>
-  <si>
-    <t>Busan I'Park</t>
-  </si>
-  <si>
-    <t>Seongnam</t>
+    <t>Dongguan United</t>
+  </si>
+  <si>
+    <t>Chongqing Tongliang Long</t>
   </si>
   <si>
     <t>Shandong Luneng</t>
   </si>
   <si>
-    <t>Chongqing Tongliang Long</t>
-  </si>
-  <si>
-    <t>Dongguan United</t>
-  </si>
-  <si>
     <t>Nantong Zhiyun</t>
   </si>
   <si>
@@ -676,42 +676,42 @@
     <t>Shanghai Shenhua</t>
   </si>
   <si>
+    <t>Brann</t>
+  </si>
+  <si>
     <t>Meizhou Hakka</t>
   </si>
   <si>
-    <t>Brann</t>
+    <t>Zhenys</t>
   </si>
   <si>
     <t>Örgryte</t>
   </si>
   <si>
+    <t>Kaisar</t>
+  </si>
+  <si>
+    <t>Malmö FF</t>
+  </si>
+  <si>
+    <t>Örebro</t>
+  </si>
+  <si>
+    <t>Falkenberg</t>
+  </si>
+  <si>
     <t>Elfsborg</t>
   </si>
   <si>
-    <t>Örebro</t>
-  </si>
-  <si>
-    <t>Zhenys</t>
-  </si>
-  <si>
-    <t>Malmö FF</t>
-  </si>
-  <si>
-    <t>Falkenberg</t>
-  </si>
-  <si>
-    <t>Kaisar</t>
-  </si>
-  <si>
     <t>Strømsgodset</t>
   </si>
   <si>
+    <t>KuPS</t>
+  </si>
+  <si>
     <t>Vestri</t>
   </si>
   <si>
-    <t>KuPS</t>
-  </si>
-  <si>
     <t>Ulytau</t>
   </si>
   <si>
@@ -724,12 +724,12 @@
     <t>FK Bodo - Glimt</t>
   </si>
   <si>
+    <t>Unión La Calera</t>
+  </si>
+  <si>
     <t>San Marcos</t>
   </si>
   <si>
-    <t>Unión La Calera</t>
-  </si>
-  <si>
     <t>Gimnasia La Plata</t>
   </si>
   <si>
@@ -739,106 +739,109 @@
     <t>Central Norte</t>
   </si>
   <si>
+    <t>Bahia</t>
+  </si>
+  <si>
+    <t>Recoleta</t>
+  </si>
+  <si>
+    <t>La Serena</t>
+  </si>
+  <si>
     <t>Cuiabá</t>
   </si>
   <si>
-    <t>Bahia</t>
-  </si>
-  <si>
-    <t>Recoleta</t>
-  </si>
-  <si>
-    <t>La Serena</t>
-  </si>
-  <si>
     <t>Rosario Central</t>
   </si>
   <si>
+    <t>Almagro</t>
+  </si>
+  <si>
+    <t>Almirante Brown</t>
+  </si>
+  <si>
+    <t>Hartford Athletic</t>
+  </si>
+  <si>
+    <t>Maringá</t>
+  </si>
+  <si>
+    <t>Botafogo PB</t>
+  </si>
+  <si>
+    <t>Club Atlético Güemes</t>
+  </si>
+  <si>
+    <t>Quilmes</t>
+  </si>
+  <si>
+    <t>Vancouver FC</t>
+  </si>
+  <si>
+    <t>San Miguel</t>
+  </si>
+  <si>
+    <t>Gimnasia Mendoza</t>
+  </si>
+  <si>
+    <t>Nueva Chicago</t>
+  </si>
+  <si>
     <t>Los Andes</t>
   </si>
   <si>
-    <t>Club Atlético Güemes</t>
-  </si>
-  <si>
-    <t>Hartford Athletic</t>
-  </si>
-  <si>
-    <t>San Miguel</t>
-  </si>
-  <si>
-    <t>Quilmes</t>
+    <t>Racing Córdoba</t>
+  </si>
+  <si>
+    <t>San Telmo</t>
+  </si>
+  <si>
+    <t>San Martín Tucumán</t>
   </si>
   <si>
     <t>Gimnasia Jujuy</t>
   </si>
   <si>
-    <t>Gimnasia Mendoza</t>
-  </si>
-  <si>
-    <t>Maringá</t>
-  </si>
-  <si>
-    <t>Nueva Chicago</t>
-  </si>
-  <si>
-    <t>Vancouver FC</t>
+    <t>Ferro Carril Oeste</t>
+  </si>
+  <si>
+    <t>Agropecuario</t>
   </si>
   <si>
     <t>Patronato</t>
   </si>
   <si>
-    <t>Agropecuario</t>
-  </si>
-  <si>
-    <t>Almirante Brown</t>
-  </si>
-  <si>
     <t>Chacarita Juniors</t>
   </si>
   <si>
-    <t>Botafogo PB</t>
-  </si>
-  <si>
-    <t>Ferro Carril Oeste</t>
-  </si>
-  <si>
-    <t>San Martín Tucumán</t>
-  </si>
-  <si>
-    <t>San Telmo</t>
-  </si>
-  <si>
-    <t>Almagro</t>
-  </si>
-  <si>
-    <t>Racing Córdoba</t>
-  </si>
-  <si>
     <t>Grêmio</t>
   </si>
   <si>
+    <t>Vila Nova</t>
+  </si>
+  <si>
     <t>Paysandu</t>
   </si>
   <si>
+    <t>Santos</t>
+  </si>
+  <si>
     <t>Deportes Iquique</t>
   </si>
   <si>
-    <t>Vila Nova</t>
-  </si>
-  <si>
-    <t>Santos</t>
-  </si>
-  <si>
     <t>Vélez Sarsfield</t>
   </si>
   <si>
     <t>Sarmiento</t>
   </si>
   <si>
+    <t>Floresta</t>
+  </si>
+  <si>
     <t>Itabaiana</t>
   </si>
   <si>
-    <t>Floresta</t>
+    <t>Philadelphia Union II</t>
   </si>
   <si>
     <t>Oakland Roots</t>
@@ -847,63 +850,60 @@
     <t>Antofagasta</t>
   </si>
   <si>
-    <t>Philadelphia Union II</t>
-  </si>
-  <si>
     <t>Inter Miami II</t>
   </si>
   <si>
+    <t>DC United</t>
+  </si>
+  <si>
+    <t>Atlanta United II</t>
+  </si>
+  <si>
+    <t>Charlotte</t>
+  </si>
+  <si>
+    <t>Inter Miami</t>
+  </si>
+  <si>
     <t>Chicago Fire</t>
   </si>
   <si>
+    <t>Atlético PR</t>
+  </si>
+  <si>
+    <t>Miami FC II</t>
+  </si>
+  <si>
     <t>Orlando City</t>
   </si>
   <si>
-    <t>Inter Miami</t>
-  </si>
-  <si>
-    <t>Atlético PR</t>
-  </si>
-  <si>
-    <t>DC United</t>
-  </si>
-  <si>
-    <t>Charlotte</t>
-  </si>
-  <si>
-    <t>Atlanta United II</t>
-  </si>
-  <si>
-    <t>Miami FC II</t>
-  </si>
-  <si>
     <t>Corinthians</t>
   </si>
   <si>
+    <t>River Plate</t>
+  </si>
+  <si>
+    <t>Colorado Springs</t>
+  </si>
+  <si>
     <t>Tulsa Roughnecks</t>
   </si>
   <si>
-    <t>River Plate</t>
-  </si>
-  <si>
-    <t>Colorado Springs</t>
+    <t>St. Louis City</t>
+  </si>
+  <si>
+    <t>Toronto</t>
+  </si>
+  <si>
+    <t>New York City</t>
+  </si>
+  <si>
+    <t>SJ Earthquakes</t>
   </si>
   <si>
     <t>Philadelphia Union</t>
   </si>
   <si>
-    <t>Toronto</t>
-  </si>
-  <si>
-    <t>New York City</t>
-  </si>
-  <si>
-    <t>SJ Earthquakes</t>
-  </si>
-  <si>
-    <t>St. Louis City</t>
-  </si>
-  <si>
     <t>FC Cincinnati</t>
   </si>
   <si>
@@ -913,10 +913,10 @@
     <t>LA Galaxy</t>
   </si>
   <si>
+    <t>Vancouver Whitecaps</t>
+  </si>
+  <si>
     <t>Minnesota United</t>
-  </si>
-  <si>
-    <t>Vancouver Whitecaps</t>
   </si>
   <si>
     <t>incomplete</t>
@@ -1559,13 +1559,13 @@
         <v>301</v>
       </c>
       <c r="L3">
-        <v>2.02</v>
+        <v>3.3</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="N3">
-        <v>2.75</v>
+        <v>1.91</v>
       </c>
       <c r="O3">
         <v>2</v>
@@ -1577,58 +1577,58 @@
         <v>1.8</v>
       </c>
       <c r="R3">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="S3">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="T3">
-        <v>2.25</v>
+        <v>2.01</v>
       </c>
       <c r="U3">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="V3">
-        <v>5.05</v>
+        <v>4.2</v>
       </c>
       <c r="W3">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X3">
         <v>1.02</v>
       </c>
       <c r="Y3">
-        <v>13.4</v>
+        <v>16.5</v>
       </c>
       <c r="Z3">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AA3">
-        <v>4.9</v>
+        <v>5.75</v>
       </c>
       <c r="AB3">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AC3">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="AD3">
-        <v>2.28</v>
+        <v>1.94</v>
       </c>
       <c r="AE3">
-        <v>1.52</v>
+        <v>1.75</v>
       </c>
       <c r="AF3">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="AG3">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="AH3">
-        <v>3.92</v>
+        <v>3.08</v>
       </c>
       <c r="AI3">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AJ3" t="s">
         <v>303</v>
@@ -1693,40 +1693,40 @@
         <v>2.25</v>
       </c>
       <c r="R4">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S4">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="T4">
         <v>2.46</v>
       </c>
       <c r="U4">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="V4">
-        <v>5.75</v>
+        <v>5.7</v>
       </c>
       <c r="W4">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X4">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Z4">
         <v>1.17</v>
       </c>
       <c r="AA4">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="AB4">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AC4">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AD4">
         <v>2.62</v>
@@ -1735,16 +1735,16 @@
         <v>1.42</v>
       </c>
       <c r="AF4">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AG4">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="AH4">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="AI4">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AJ4" t="s">
         <v>303</v>
@@ -1791,13 +1791,13 @@
         <v>301</v>
       </c>
       <c r="L5">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="M5">
-        <v>4</v>
+        <v>3.79</v>
       </c>
       <c r="N5">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="O5">
         <v>2.3</v>
@@ -1839,10 +1839,10 @@
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="AC5">
-        <v>2.07</v>
+        <v>2.35</v>
       </c>
       <c r="AD5">
         <v>0</v>
@@ -1907,13 +1907,13 @@
         <v>301</v>
       </c>
       <c r="L6">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="M6">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="N6">
-        <v>1.46</v>
+        <v>1.66</v>
       </c>
       <c r="O6">
         <v>1.33</v>
@@ -1928,7 +1928,7 @@
         <v>1.28</v>
       </c>
       <c r="S6">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="T6">
         <v>2.46</v>
@@ -1937,46 +1937,46 @@
         <v>1.46</v>
       </c>
       <c r="V6">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="W6">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X6">
         <v>1.03</v>
       </c>
       <c r="Y6">
-        <v>12.4</v>
+        <v>12.3</v>
       </c>
       <c r="Z6">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AA6">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="AB6">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AC6">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="AD6">
-        <v>2.66</v>
+        <v>2.59</v>
       </c>
       <c r="AE6">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AF6">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="AG6">
-        <v>2.11</v>
+        <v>1.93</v>
       </c>
       <c r="AH6">
-        <v>4.9</v>
+        <v>4.85</v>
       </c>
       <c r="AI6">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AJ6" t="s">
         <v>303</v>
@@ -2023,76 +2023,76 @@
         <v>301</v>
       </c>
       <c r="L7">
-        <v>2.32</v>
+        <v>3.74</v>
       </c>
       <c r="M7">
-        <v>3.03</v>
+        <v>3.5</v>
       </c>
       <c r="N7">
-        <v>2.79</v>
+        <v>1.77</v>
       </c>
       <c r="O7">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="P7">
-        <v>8</v>
+        <v>13.75</v>
       </c>
       <c r="Q7">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="R7">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="S7">
-        <v>2.65</v>
+        <v>3.3</v>
       </c>
       <c r="T7">
-        <v>2.88</v>
+        <v>2.45</v>
       </c>
       <c r="U7">
+        <v>1.5</v>
+      </c>
+      <c r="V7">
+        <v>6</v>
+      </c>
+      <c r="W7">
+        <v>1.12</v>
+      </c>
+      <c r="X7">
+        <v>1.01</v>
+      </c>
+      <c r="Y7">
+        <v>11</v>
+      </c>
+      <c r="Z7">
+        <v>1.16</v>
+      </c>
+      <c r="AA7">
+        <v>4.05</v>
+      </c>
+      <c r="AB7">
+        <v>1.65</v>
+      </c>
+      <c r="AC7">
+        <v>2</v>
+      </c>
+      <c r="AD7">
+        <v>2.69</v>
+      </c>
+      <c r="AE7">
         <v>1.36</v>
       </c>
-      <c r="V7">
-        <v>7</v>
-      </c>
-      <c r="W7">
-        <v>1.08</v>
-      </c>
-      <c r="X7">
-        <v>1.07</v>
-      </c>
-      <c r="Y7">
-        <v>8</v>
-      </c>
-      <c r="Z7">
-        <v>1.38</v>
-      </c>
-      <c r="AA7">
-        <v>3</v>
-      </c>
-      <c r="AB7">
-        <v>2.1</v>
-      </c>
-      <c r="AC7">
-        <v>1.65</v>
-      </c>
-      <c r="AD7">
-        <v>3.8</v>
-      </c>
-      <c r="AE7">
-        <v>1.25</v>
-      </c>
       <c r="AF7">
-        <v>1.77</v>
+        <v>1.62</v>
       </c>
       <c r="AG7">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="AH7">
-        <v>7.5</v>
+        <v>5.15</v>
       </c>
       <c r="AI7">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AJ7" t="s">
         <v>303</v>
@@ -2112,7 +2112,7 @@
         <v>43</v>
       </c>
       <c r="C8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D8" t="s">
         <v>94</v>
@@ -2139,76 +2139,76 @@
         <v>301</v>
       </c>
       <c r="L8">
-        <v>2.85</v>
+        <v>2.32</v>
       </c>
       <c r="M8">
+        <v>3.03</v>
+      </c>
+      <c r="N8">
+        <v>2.79</v>
+      </c>
+      <c r="O8">
+        <v>1.91</v>
+      </c>
+      <c r="P8">
+        <v>8</v>
+      </c>
+      <c r="Q8">
+        <v>2.25</v>
+      </c>
+      <c r="R8">
+        <v>1.42</v>
+      </c>
+      <c r="S8">
+        <v>2.65</v>
+      </c>
+      <c r="T8">
+        <v>2.88</v>
+      </c>
+      <c r="U8">
+        <v>1.36</v>
+      </c>
+      <c r="V8">
+        <v>7</v>
+      </c>
+      <c r="W8">
+        <v>1.08</v>
+      </c>
+      <c r="X8">
+        <v>1.07</v>
+      </c>
+      <c r="Y8">
+        <v>8</v>
+      </c>
+      <c r="Z8">
+        <v>1.38</v>
+      </c>
+      <c r="AA8">
         <v>3</v>
       </c>
-      <c r="N8">
-        <v>2.3</v>
-      </c>
-      <c r="O8">
-        <v>2.25</v>
-      </c>
-      <c r="P8">
-        <v>7</v>
-      </c>
-      <c r="Q8">
-        <v>1.95</v>
-      </c>
-      <c r="R8">
-        <v>1.48</v>
-      </c>
-      <c r="S8">
-        <v>2.45</v>
-      </c>
-      <c r="T8">
-        <v>3.2</v>
-      </c>
-      <c r="U8">
-        <v>1.3</v>
-      </c>
-      <c r="V8">
+      <c r="AB8">
+        <v>2.1</v>
+      </c>
+      <c r="AC8">
+        <v>1.65</v>
+      </c>
+      <c r="AD8">
+        <v>3.8</v>
+      </c>
+      <c r="AE8">
+        <v>1.25</v>
+      </c>
+      <c r="AF8">
+        <v>1.77</v>
+      </c>
+      <c r="AG8">
+        <v>1.9</v>
+      </c>
+      <c r="AH8">
         <v>7.5</v>
       </c>
-      <c r="W8">
-        <v>1.07</v>
-      </c>
-      <c r="X8">
-        <v>1.09</v>
-      </c>
-      <c r="Y8">
-        <v>7</v>
-      </c>
-      <c r="Z8">
-        <v>1.42</v>
-      </c>
-      <c r="AA8">
-        <v>2.8</v>
-      </c>
-      <c r="AB8">
-        <v>1.91</v>
-      </c>
-      <c r="AC8">
-        <v>1.79</v>
-      </c>
-      <c r="AD8">
-        <v>4.2</v>
-      </c>
-      <c r="AE8">
-        <v>1.22</v>
-      </c>
-      <c r="AF8">
-        <v>1.85</v>
-      </c>
-      <c r="AG8">
-        <v>1.8</v>
-      </c>
-      <c r="AH8">
-        <v>8.5</v>
-      </c>
       <c r="AI8">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AJ8" t="s">
         <v>303</v>
@@ -2228,7 +2228,7 @@
         <v>43</v>
       </c>
       <c r="C9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D9" t="s">
         <v>94</v>
@@ -2255,76 +2255,76 @@
         <v>301</v>
       </c>
       <c r="L9">
-        <v>2.4</v>
+        <v>3.41</v>
       </c>
       <c r="M9">
-        <v>3.26</v>
+        <v>3.32</v>
       </c>
       <c r="N9">
+        <v>1.9</v>
+      </c>
+      <c r="O9">
+        <v>2.42</v>
+      </c>
+      <c r="P9">
+        <v>7.1</v>
+      </c>
+      <c r="Q9">
+        <v>1.78</v>
+      </c>
+      <c r="R9">
+        <v>1.44</v>
+      </c>
+      <c r="S9">
+        <v>2.62</v>
+      </c>
+      <c r="T9">
+        <v>3.25</v>
+      </c>
+      <c r="U9">
+        <v>1.3</v>
+      </c>
+      <c r="V9">
+        <v>10</v>
+      </c>
+      <c r="W9">
+        <v>1.05</v>
+      </c>
+      <c r="X9">
+        <v>1.04</v>
+      </c>
+      <c r="Y9">
+        <v>7.1</v>
+      </c>
+      <c r="Z9">
+        <v>1.41</v>
+      </c>
+      <c r="AA9">
         <v>2.52</v>
       </c>
-      <c r="O9">
+      <c r="AB9">
+        <v>2.2</v>
+      </c>
+      <c r="AC9">
+        <v>1.53</v>
+      </c>
+      <c r="AD9">
+        <v>4.3</v>
+      </c>
+      <c r="AE9">
+        <v>1.15</v>
+      </c>
+      <c r="AF9">
         <v>2.05</v>
       </c>
-      <c r="P9">
-        <v>8.5</v>
-      </c>
-      <c r="Q9">
-        <v>2.05</v>
-      </c>
-      <c r="R9">
-        <v>1.4</v>
-      </c>
-      <c r="S9">
-        <v>2.75</v>
-      </c>
-      <c r="T9">
-        <v>2.8</v>
-      </c>
-      <c r="U9">
-        <v>1.38</v>
-      </c>
-      <c r="V9">
-        <v>7</v>
-      </c>
-      <c r="W9">
-        <v>1.08</v>
-      </c>
-      <c r="X9">
-        <v>1.06</v>
-      </c>
-      <c r="Y9">
-        <v>8.5</v>
-      </c>
-      <c r="Z9">
-        <v>1.3</v>
-      </c>
-      <c r="AA9">
-        <v>3.35</v>
-      </c>
-      <c r="AB9">
-        <v>1.87</v>
-      </c>
-      <c r="AC9">
-        <v>1.83</v>
-      </c>
-      <c r="AD9">
-        <v>3.4</v>
-      </c>
-      <c r="AE9">
-        <v>1.3</v>
-      </c>
-      <c r="AF9">
-        <v>1.7</v>
-      </c>
       <c r="AG9">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="AH9">
-        <v>6.5</v>
+        <v>8.4</v>
       </c>
       <c r="AI9">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="AJ9" t="s">
         <v>303</v>
@@ -2371,76 +2371,76 @@
         <v>301</v>
       </c>
       <c r="L10">
-        <v>2.29</v>
+        <v>1.74</v>
       </c>
       <c r="M10">
-        <v>3.12</v>
+        <v>3.28</v>
       </c>
       <c r="N10">
-        <v>2.75</v>
+        <v>4.2</v>
       </c>
       <c r="O10">
-        <v>2</v>
+        <v>1.53</v>
       </c>
       <c r="P10">
-        <v>8</v>
+        <v>6.75</v>
       </c>
       <c r="Q10">
-        <v>2.1</v>
+        <v>3.18</v>
       </c>
       <c r="R10">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="S10">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="T10">
-        <v>2.88</v>
+        <v>3.34</v>
       </c>
       <c r="U10">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="V10">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W10">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X10">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y10">
         <v>8</v>
       </c>
       <c r="Z10">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AA10">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="AB10">
-        <v>1.93</v>
+        <v>2.3</v>
       </c>
       <c r="AC10">
-        <v>1.77</v>
+        <v>1.5</v>
       </c>
       <c r="AD10">
-        <v>3.45</v>
+        <v>4.8</v>
       </c>
       <c r="AE10">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AF10">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="AG10">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AH10">
-        <v>6.5</v>
+        <v>9</v>
       </c>
       <c r="AI10">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="AJ10" t="s">
         <v>303</v>
@@ -2460,7 +2460,7 @@
         <v>43</v>
       </c>
       <c r="C11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D11" t="s">
         <v>94</v>
@@ -2487,73 +2487,73 @@
         <v>301</v>
       </c>
       <c r="L11">
-        <v>3.74</v>
+        <v>2.29</v>
       </c>
       <c r="M11">
-        <v>3.5</v>
+        <v>3.12</v>
       </c>
       <c r="N11">
+        <v>2.75</v>
+      </c>
+      <c r="O11">
+        <v>2</v>
+      </c>
+      <c r="P11">
+        <v>8</v>
+      </c>
+      <c r="Q11">
+        <v>2.1</v>
+      </c>
+      <c r="R11">
+        <v>1.42</v>
+      </c>
+      <c r="S11">
+        <v>2.65</v>
+      </c>
+      <c r="T11">
+        <v>2.88</v>
+      </c>
+      <c r="U11">
+        <v>1.36</v>
+      </c>
+      <c r="V11">
+        <v>7</v>
+      </c>
+      <c r="W11">
+        <v>1.08</v>
+      </c>
+      <c r="X11">
+        <v>1.07</v>
+      </c>
+      <c r="Y11">
+        <v>8</v>
+      </c>
+      <c r="Z11">
+        <v>1.33</v>
+      </c>
+      <c r="AA11">
+        <v>3.25</v>
+      </c>
+      <c r="AB11">
+        <v>1.93</v>
+      </c>
+      <c r="AC11">
         <v>1.77</v>
       </c>
-      <c r="O11">
-        <v>2.25</v>
-      </c>
-      <c r="P11">
-        <v>13.75</v>
-      </c>
-      <c r="Q11">
-        <v>1.67</v>
-      </c>
-      <c r="R11">
+      <c r="AD11">
+        <v>3.45</v>
+      </c>
+      <c r="AE11">
         <v>1.3</v>
       </c>
-      <c r="S11">
-        <v>3.3</v>
-      </c>
-      <c r="T11">
-        <v>2.45</v>
-      </c>
-      <c r="U11">
-        <v>1.5</v>
-      </c>
-      <c r="V11">
-        <v>6</v>
-      </c>
-      <c r="W11">
-        <v>1.12</v>
-      </c>
-      <c r="X11">
-        <v>1.01</v>
-      </c>
-      <c r="Y11">
-        <v>11</v>
-      </c>
-      <c r="Z11">
-        <v>1.16</v>
-      </c>
-      <c r="AA11">
-        <v>4.05</v>
-      </c>
-      <c r="AB11">
-        <v>1.65</v>
-      </c>
-      <c r="AC11">
+      <c r="AF11">
+        <v>1.7</v>
+      </c>
+      <c r="AG11">
         <v>2</v>
       </c>
-      <c r="AD11">
-        <v>2.69</v>
-      </c>
-      <c r="AE11">
-        <v>1.36</v>
-      </c>
-      <c r="AF11">
-        <v>1.62</v>
-      </c>
-      <c r="AG11">
-        <v>2.2</v>
-      </c>
       <c r="AH11">
-        <v>5.15</v>
+        <v>6.5</v>
       </c>
       <c r="AI11">
         <v>1.1</v>
@@ -2603,76 +2603,76 @@
         <v>301</v>
       </c>
       <c r="L12">
-        <v>2.74</v>
+        <v>2.85</v>
       </c>
       <c r="M12">
-        <v>3.41</v>
+        <v>3</v>
       </c>
       <c r="N12">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="O12">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="P12">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="Q12">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="R12">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="S12">
-        <v>3</v>
+        <v>2.45</v>
       </c>
       <c r="T12">
-        <v>2.45</v>
+        <v>3.2</v>
       </c>
       <c r="U12">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="V12">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="W12">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X12">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="Y12">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="Z12">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="AA12">
-        <v>3.95</v>
+        <v>2.8</v>
       </c>
       <c r="AB12">
-        <v>1.69</v>
+        <v>1.91</v>
       </c>
       <c r="AC12">
-        <v>2.04</v>
+        <v>1.79</v>
       </c>
       <c r="AD12">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="AE12">
-        <v>1.42</v>
+        <v>1.22</v>
       </c>
       <c r="AF12">
-        <v>1.55</v>
+        <v>1.85</v>
       </c>
       <c r="AG12">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AH12">
-        <v>5</v>
+        <v>8.5</v>
       </c>
       <c r="AI12">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="AJ12" t="s">
         <v>303</v>
@@ -2692,7 +2692,7 @@
         <v>43</v>
       </c>
       <c r="C13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D13" t="s">
         <v>94</v>
@@ -2719,76 +2719,76 @@
         <v>301</v>
       </c>
       <c r="L13">
-        <v>1.66</v>
+        <v>2.74</v>
       </c>
       <c r="M13">
-        <v>3.55</v>
+        <v>3.41</v>
       </c>
       <c r="N13">
-        <v>5.4</v>
+        <v>2.16</v>
       </c>
       <c r="O13">
-        <v>1.38</v>
+        <v>2.1</v>
       </c>
       <c r="P13">
-        <v>8.9</v>
+        <v>9.5</v>
       </c>
       <c r="Q13">
-        <v>3.58</v>
+        <v>1.9</v>
       </c>
       <c r="R13">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="S13">
-        <v>2.52</v>
+        <v>3</v>
       </c>
       <c r="T13">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="U13">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="V13">
-        <v>7.3</v>
+        <v>6</v>
       </c>
       <c r="W13">
+        <v>1.12</v>
+      </c>
+      <c r="X13">
         <v>1.05</v>
       </c>
-      <c r="X13">
-        <v>1.03</v>
-      </c>
       <c r="Y13">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="Z13">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AA13">
-        <v>2.83</v>
+        <v>3.95</v>
       </c>
       <c r="AB13">
-        <v>2.08</v>
+        <v>1.69</v>
       </c>
       <c r="AC13">
-        <v>1.65</v>
+        <v>2.04</v>
       </c>
       <c r="AD13">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="AE13">
-        <v>1.21</v>
+        <v>1.42</v>
       </c>
       <c r="AF13">
-        <v>2</v>
+        <v>1.55</v>
       </c>
       <c r="AG13">
-        <v>1.7</v>
+        <v>2.25</v>
       </c>
       <c r="AH13">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="AI13">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AJ13" t="s">
         <v>303</v>
@@ -2808,7 +2808,7 @@
         <v>43</v>
       </c>
       <c r="C14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D14" t="s">
         <v>94</v>
@@ -2835,76 +2835,76 @@
         <v>301</v>
       </c>
       <c r="L14">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="M14">
-        <v>3.28</v>
+        <v>3.55</v>
       </c>
       <c r="N14">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="O14">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="P14">
-        <v>6.75</v>
+        <v>8.9</v>
       </c>
       <c r="Q14">
-        <v>3.18</v>
+        <v>3.58</v>
       </c>
       <c r="R14">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="S14">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="T14">
-        <v>3.34</v>
+        <v>2.75</v>
       </c>
       <c r="U14">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="V14">
-        <v>8.199999999999999</v>
+        <v>7.3</v>
       </c>
       <c r="W14">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X14">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y14">
         <v>8</v>
       </c>
       <c r="Z14">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="AA14">
-        <v>2.75</v>
+        <v>2.83</v>
       </c>
       <c r="AB14">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="AC14">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AD14">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="AE14">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AF14">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AG14">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AH14">
-        <v>9</v>
+        <v>5.3</v>
       </c>
       <c r="AI14">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AJ14" t="s">
         <v>303</v>
@@ -2924,7 +2924,7 @@
         <v>43</v>
       </c>
       <c r="C15" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D15" t="s">
         <v>94</v>
@@ -2951,76 +2951,76 @@
         <v>301</v>
       </c>
       <c r="L15">
-        <v>3.41</v>
+        <v>1.83</v>
       </c>
       <c r="M15">
-        <v>3.32</v>
+        <v>3.11</v>
       </c>
       <c r="N15">
-        <v>1.9</v>
+        <v>3.97</v>
       </c>
       <c r="O15">
-        <v>2.42</v>
+        <v>1.67</v>
       </c>
       <c r="P15">
-        <v>7.1</v>
+        <v>12</v>
       </c>
       <c r="Q15">
-        <v>1.78</v>
+        <v>2.31</v>
       </c>
       <c r="R15">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="S15">
-        <v>2.62</v>
+        <v>3.01</v>
       </c>
       <c r="T15">
-        <v>3.25</v>
+        <v>2.84</v>
       </c>
       <c r="U15">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="V15">
-        <v>10</v>
+        <v>6.5</v>
       </c>
       <c r="W15">
         <v>1.05</v>
       </c>
       <c r="X15">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>7.1</v>
+        <v>11</v>
       </c>
       <c r="Z15">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="AA15">
-        <v>2.52</v>
+        <v>3.6</v>
       </c>
       <c r="AB15">
-        <v>2.2</v>
+        <v>1.87</v>
       </c>
       <c r="AC15">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="AD15">
-        <v>4.3</v>
+        <v>3.2</v>
       </c>
       <c r="AE15">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AF15">
-        <v>2.05</v>
+        <v>1.67</v>
       </c>
       <c r="AG15">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="AH15">
-        <v>8.4</v>
+        <v>6.5</v>
       </c>
       <c r="AI15">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AJ15" t="s">
         <v>303</v>
@@ -3067,52 +3067,52 @@
         <v>301</v>
       </c>
       <c r="L16">
-        <v>1.83</v>
+        <v>2.4</v>
       </c>
       <c r="M16">
-        <v>3.11</v>
+        <v>3.26</v>
       </c>
       <c r="N16">
-        <v>3.97</v>
+        <v>2.52</v>
       </c>
       <c r="O16">
-        <v>1.67</v>
+        <v>2.05</v>
       </c>
       <c r="P16">
-        <v>12</v>
+        <v>8.5</v>
       </c>
       <c r="Q16">
-        <v>2.31</v>
+        <v>2.05</v>
       </c>
       <c r="R16">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="S16">
-        <v>3.01</v>
+        <v>2.75</v>
       </c>
       <c r="T16">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="U16">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="V16">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="W16">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X16">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y16">
-        <v>11</v>
+        <v>8.5</v>
       </c>
       <c r="Z16">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AA16">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="AB16">
         <v>1.87</v>
@@ -3121,22 +3121,22 @@
         <v>1.83</v>
       </c>
       <c r="AD16">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AE16">
         <v>1.3</v>
       </c>
       <c r="AF16">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AG16">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH16">
         <v>6.5</v>
       </c>
       <c r="AI16">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AJ16" t="s">
         <v>303</v>
@@ -3156,7 +3156,7 @@
         <v>44</v>
       </c>
       <c r="C17" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D17" t="s">
         <v>94</v>
@@ -3183,76 +3183,76 @@
         <v>301</v>
       </c>
       <c r="L17">
-        <v>3.1</v>
+        <v>1.48</v>
       </c>
       <c r="M17">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="N17">
-        <v>2.09</v>
+        <v>5.85</v>
       </c>
       <c r="O17">
-        <v>2.4</v>
+        <v>1.53</v>
       </c>
       <c r="P17">
-        <v>18.75</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q17">
-        <v>1.57</v>
+        <v>2.88</v>
       </c>
       <c r="R17">
+        <v>1.39</v>
+      </c>
+      <c r="S17">
+        <v>2.5</v>
+      </c>
+      <c r="T17">
+        <v>3</v>
+      </c>
+      <c r="U17">
+        <v>1.32</v>
+      </c>
+      <c r="V17">
+        <v>7.9</v>
+      </c>
+      <c r="W17">
+        <v>1.05</v>
+      </c>
+      <c r="X17">
+        <v>1</v>
+      </c>
+      <c r="Y17">
+        <v>9</v>
+      </c>
+      <c r="Z17">
+        <v>1.33</v>
+      </c>
+      <c r="AA17">
+        <v>3.04</v>
+      </c>
+      <c r="AB17">
+        <v>2</v>
+      </c>
+      <c r="AC17">
+        <v>1.73</v>
+      </c>
+      <c r="AD17">
+        <v>3.58</v>
+      </c>
+      <c r="AE17">
         <v>1.25</v>
       </c>
-      <c r="S17">
-        <v>3.75</v>
-      </c>
-      <c r="T17">
-        <v>2.25</v>
-      </c>
-      <c r="U17">
-        <v>1.57</v>
-      </c>
-      <c r="V17">
-        <v>5.5</v>
-      </c>
-      <c r="W17">
-        <v>1.14</v>
-      </c>
-      <c r="X17">
-        <v>1.01</v>
-      </c>
-      <c r="Y17">
-        <v>13</v>
-      </c>
-      <c r="Z17">
-        <v>1.1</v>
-      </c>
-      <c r="AA17">
-        <v>5</v>
-      </c>
-      <c r="AB17">
-        <v>1.53</v>
-      </c>
-      <c r="AC17">
-        <v>2.25</v>
-      </c>
-      <c r="AD17">
-        <v>2.35</v>
-      </c>
-      <c r="AE17">
-        <v>1.57</v>
-      </c>
       <c r="AF17">
-        <v>1.53</v>
+        <v>1.97</v>
       </c>
       <c r="AG17">
-        <v>2.38</v>
+        <v>1.72</v>
       </c>
       <c r="AH17">
-        <v>4.05</v>
+        <v>7.4</v>
       </c>
       <c r="AI17">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AJ17" t="s">
         <v>303</v>
@@ -3388,7 +3388,7 @@
         <v>44</v>
       </c>
       <c r="C19" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D19" t="s">
         <v>94</v>
@@ -3415,76 +3415,76 @@
         <v>301</v>
       </c>
       <c r="L19">
-        <v>1.48</v>
+        <v>3.1</v>
       </c>
       <c r="M19">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="N19">
-        <v>5.85</v>
+        <v>2.09</v>
       </c>
       <c r="O19">
+        <v>2.4</v>
+      </c>
+      <c r="P19">
+        <v>18.75</v>
+      </c>
+      <c r="Q19">
+        <v>1.57</v>
+      </c>
+      <c r="R19">
+        <v>1.25</v>
+      </c>
+      <c r="S19">
+        <v>3.75</v>
+      </c>
+      <c r="T19">
+        <v>2.25</v>
+      </c>
+      <c r="U19">
+        <v>1.57</v>
+      </c>
+      <c r="V19">
+        <v>5.5</v>
+      </c>
+      <c r="W19">
+        <v>1.14</v>
+      </c>
+      <c r="X19">
+        <v>1.01</v>
+      </c>
+      <c r="Y19">
+        <v>13</v>
+      </c>
+      <c r="Z19">
+        <v>1.1</v>
+      </c>
+      <c r="AA19">
+        <v>5</v>
+      </c>
+      <c r="AB19">
         <v>1.53</v>
       </c>
-      <c r="P19">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="Q19">
-        <v>2.88</v>
-      </c>
-      <c r="R19">
-        <v>1.39</v>
-      </c>
-      <c r="S19">
-        <v>2.5</v>
-      </c>
-      <c r="T19">
-        <v>3</v>
-      </c>
-      <c r="U19">
-        <v>1.32</v>
-      </c>
-      <c r="V19">
-        <v>7.9</v>
-      </c>
-      <c r="W19">
-        <v>1.05</v>
-      </c>
-      <c r="X19">
-        <v>1</v>
-      </c>
-      <c r="Y19">
-        <v>9</v>
-      </c>
-      <c r="Z19">
-        <v>1.33</v>
-      </c>
-      <c r="AA19">
-        <v>3.04</v>
-      </c>
-      <c r="AB19">
-        <v>2</v>
-      </c>
       <c r="AC19">
-        <v>1.73</v>
+        <v>2.25</v>
       </c>
       <c r="AD19">
-        <v>3.58</v>
+        <v>2.35</v>
       </c>
       <c r="AE19">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="AF19">
-        <v>1.97</v>
+        <v>1.53</v>
       </c>
       <c r="AG19">
-        <v>1.72</v>
+        <v>2.38</v>
       </c>
       <c r="AH19">
-        <v>7.4</v>
+        <v>4.05</v>
       </c>
       <c r="AI19">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="AJ19" t="s">
         <v>303</v>
@@ -3852,7 +3852,7 @@
         <v>47</v>
       </c>
       <c r="C23" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D23" t="s">
         <v>94</v>
@@ -3879,76 +3879,76 @@
         <v>301</v>
       </c>
       <c r="L23">
-        <v>1.45</v>
+        <v>2.88</v>
       </c>
       <c r="M23">
-        <v>4.8</v>
+        <v>3.11</v>
       </c>
       <c r="N23">
-        <v>5.8</v>
+        <v>2.22</v>
       </c>
       <c r="O23">
+        <v>2.15</v>
+      </c>
+      <c r="P23">
+        <v>8.5</v>
+      </c>
+      <c r="Q23">
+        <v>1.93</v>
+      </c>
+      <c r="R23">
+        <v>1.4</v>
+      </c>
+      <c r="S23">
+        <v>2.7</v>
+      </c>
+      <c r="T23">
+        <v>2.8</v>
+      </c>
+      <c r="U23">
+        <v>1.38</v>
+      </c>
+      <c r="V23">
+        <v>7.3</v>
+      </c>
+      <c r="W23">
+        <v>1.03</v>
+      </c>
+      <c r="X23">
+        <v>1.06</v>
+      </c>
+      <c r="Y23">
+        <v>8.5</v>
+      </c>
+      <c r="Z23">
+        <v>1.3</v>
+      </c>
+      <c r="AA23">
+        <v>3.45</v>
+      </c>
+      <c r="AB23">
+        <v>1.89</v>
+      </c>
+      <c r="AC23">
+        <v>1.81</v>
+      </c>
+      <c r="AD23">
+        <v>3.2</v>
+      </c>
+      <c r="AE23">
         <v>1.33</v>
       </c>
-      <c r="P23">
-        <v>22</v>
-      </c>
-      <c r="Q23">
-        <v>3.25</v>
-      </c>
-      <c r="R23">
-        <v>1.22</v>
-      </c>
-      <c r="S23">
-        <v>4</v>
-      </c>
-      <c r="T23">
-        <v>2.1</v>
-      </c>
-      <c r="U23">
-        <v>1.67</v>
-      </c>
-      <c r="V23">
-        <v>4.5</v>
-      </c>
-      <c r="W23">
-        <v>1.18</v>
-      </c>
-      <c r="X23">
-        <v>1.01</v>
-      </c>
-      <c r="Y23">
-        <v>17</v>
-      </c>
-      <c r="Z23">
-        <v>1.08</v>
-      </c>
-      <c r="AA23">
-        <v>5.55</v>
-      </c>
-      <c r="AB23">
-        <v>1.48</v>
-      </c>
-      <c r="AC23">
-        <v>2.6</v>
-      </c>
-      <c r="AD23">
-        <v>2.1</v>
-      </c>
-      <c r="AE23">
-        <v>1.6</v>
-      </c>
       <c r="AF23">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG23">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AH23">
-        <v>3.44</v>
+        <v>6.25</v>
       </c>
       <c r="AI23">
-        <v>1.23</v>
+        <v>1.11</v>
       </c>
       <c r="AJ23" t="s">
         <v>303</v>
@@ -3968,7 +3968,7 @@
         <v>47</v>
       </c>
       <c r="C24" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D24" t="s">
         <v>94</v>
@@ -3995,76 +3995,76 @@
         <v>301</v>
       </c>
       <c r="L24">
-        <v>2.88</v>
+        <v>1.45</v>
       </c>
       <c r="M24">
-        <v>3.11</v>
+        <v>4.8</v>
       </c>
       <c r="N24">
-        <v>2.22</v>
+        <v>5.8</v>
       </c>
       <c r="O24">
-        <v>2.15</v>
+        <v>1.33</v>
       </c>
       <c r="P24">
-        <v>8.5</v>
+        <v>22</v>
       </c>
       <c r="Q24">
-        <v>1.93</v>
+        <v>3.25</v>
       </c>
       <c r="R24">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="S24">
-        <v>2.7</v>
+        <v>4</v>
       </c>
       <c r="T24">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="U24">
-        <v>1.38</v>
+        <v>1.67</v>
       </c>
       <c r="V24">
-        <v>7.3</v>
+        <v>4.5</v>
       </c>
       <c r="W24">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="X24">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>8.5</v>
+        <v>17</v>
       </c>
       <c r="Z24">
-        <v>1.3</v>
+        <v>1.08</v>
       </c>
       <c r="AA24">
-        <v>3.45</v>
+        <v>5.55</v>
       </c>
       <c r="AB24">
-        <v>1.89</v>
+        <v>1.48</v>
       </c>
       <c r="AC24">
-        <v>1.81</v>
+        <v>2.6</v>
       </c>
       <c r="AD24">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="AE24">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="AF24">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG24">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AH24">
-        <v>6.25</v>
+        <v>3.44</v>
       </c>
       <c r="AI24">
-        <v>1.11</v>
+        <v>1.23</v>
       </c>
       <c r="AJ24" t="s">
         <v>303</v>
@@ -4111,76 +4111,76 @@
         <v>301</v>
       </c>
       <c r="L25">
-        <v>2.57</v>
+        <v>1.8</v>
       </c>
       <c r="M25">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="N25">
-        <v>2.34</v>
+        <v>4.3</v>
       </c>
       <c r="O25">
-        <v>2.05</v>
+        <v>1.61</v>
       </c>
       <c r="P25">
-        <v>10</v>
+        <v>6.7</v>
       </c>
       <c r="Q25">
-        <v>1.8</v>
+        <v>2.89</v>
       </c>
       <c r="R25">
+        <v>1.49</v>
+      </c>
+      <c r="S25">
+        <v>2.4</v>
+      </c>
+      <c r="T25">
+        <v>3.14</v>
+      </c>
+      <c r="U25">
         <v>1.3</v>
       </c>
-      <c r="S25">
-        <v>3.4</v>
-      </c>
-      <c r="T25">
-        <v>2.5</v>
-      </c>
-      <c r="U25">
-        <v>1.5</v>
-      </c>
       <c r="V25">
-        <v>6</v>
+        <v>7.7</v>
       </c>
       <c r="W25">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="X25">
+        <v>1.04</v>
+      </c>
+      <c r="Y25">
+        <v>6.75</v>
+      </c>
+      <c r="Z25">
+        <v>1.35</v>
+      </c>
+      <c r="AA25">
+        <v>2.8</v>
+      </c>
+      <c r="AB25">
+        <v>2.2</v>
+      </c>
+      <c r="AC25">
+        <v>1.62</v>
+      </c>
+      <c r="AD25">
+        <v>3.74</v>
+      </c>
+      <c r="AE25">
+        <v>1.22</v>
+      </c>
+      <c r="AF25">
+        <v>2</v>
+      </c>
+      <c r="AG25">
+        <v>1.7</v>
+      </c>
+      <c r="AH25">
+        <v>7.2</v>
+      </c>
+      <c r="AI25">
         <v>1.05</v>
-      </c>
-      <c r="Y25">
-        <v>10</v>
-      </c>
-      <c r="Z25">
-        <v>1.22</v>
-      </c>
-      <c r="AA25">
-        <v>4.33</v>
-      </c>
-      <c r="AB25">
-        <v>1.6</v>
-      </c>
-      <c r="AC25">
-        <v>2.1</v>
-      </c>
-      <c r="AD25">
-        <v>2.26</v>
-      </c>
-      <c r="AE25">
-        <v>1.51</v>
-      </c>
-      <c r="AF25">
-        <v>1.57</v>
-      </c>
-      <c r="AG25">
-        <v>2.25</v>
-      </c>
-      <c r="AH25">
-        <v>4.75</v>
-      </c>
-      <c r="AI25">
-        <v>1.2</v>
       </c>
       <c r="AJ25" t="s">
         <v>303</v>
@@ -4227,76 +4227,76 @@
         <v>301</v>
       </c>
       <c r="L26">
-        <v>2.09</v>
+        <v>2.57</v>
       </c>
       <c r="M26">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="N26">
-        <v>2.98</v>
+        <v>2.34</v>
       </c>
       <c r="O26">
-        <v>1.67</v>
+        <v>2.05</v>
       </c>
       <c r="P26">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Q26">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="R26">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S26">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="T26">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="U26">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="V26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W26">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X26">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y26">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Z26">
         <v>1.22</v>
       </c>
       <c r="AA26">
-        <v>3.64</v>
+        <v>4.33</v>
       </c>
       <c r="AB26">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="AC26">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AD26">
-        <v>2.88</v>
+        <v>2.26</v>
       </c>
       <c r="AE26">
-        <v>1.34</v>
+        <v>1.51</v>
       </c>
       <c r="AF26">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AG26">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AH26">
-        <v>5.3</v>
+        <v>4.75</v>
       </c>
       <c r="AI26">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="AJ26" t="s">
         <v>303</v>
@@ -4343,76 +4343,76 @@
         <v>301</v>
       </c>
       <c r="L27">
-        <v>2.73</v>
+        <v>1.22</v>
       </c>
       <c r="M27">
-        <v>3.29</v>
+        <v>4.9</v>
       </c>
       <c r="N27">
-        <v>2.23</v>
+        <v>12</v>
       </c>
       <c r="O27">
-        <v>2.2</v>
+        <v>1.23</v>
       </c>
       <c r="P27">
-        <v>10</v>
+        <v>7.9</v>
       </c>
       <c r="Q27">
-        <v>1.73</v>
+        <v>5.65</v>
       </c>
       <c r="R27">
+        <v>1.39</v>
+      </c>
+      <c r="S27">
+        <v>3</v>
+      </c>
+      <c r="T27">
+        <v>2.6</v>
+      </c>
+      <c r="U27">
+        <v>1.41</v>
+      </c>
+      <c r="V27">
+        <v>6.05</v>
+      </c>
+      <c r="W27">
+        <v>1.06</v>
+      </c>
+      <c r="X27">
+        <v>1.02</v>
+      </c>
+      <c r="Y27">
+        <v>8.4</v>
+      </c>
+      <c r="Z27">
+        <v>1.24</v>
+      </c>
+      <c r="AA27">
+        <v>3.55</v>
+      </c>
+      <c r="AB27">
+        <v>1.8</v>
+      </c>
+      <c r="AC27">
+        <v>1.93</v>
+      </c>
+      <c r="AD27">
+        <v>2.83</v>
+      </c>
+      <c r="AE27">
         <v>1.33</v>
       </c>
-      <c r="S27">
-        <v>3.25</v>
-      </c>
-      <c r="T27">
-        <v>2.5</v>
-      </c>
-      <c r="U27">
-        <v>1.5</v>
-      </c>
-      <c r="V27">
-        <v>6</v>
-      </c>
-      <c r="W27">
-        <v>1.13</v>
-      </c>
-      <c r="X27">
-        <v>1.05</v>
-      </c>
-      <c r="Y27">
-        <v>10</v>
-      </c>
-      <c r="Z27">
-        <v>1.25</v>
-      </c>
-      <c r="AA27">
-        <v>4</v>
-      </c>
-      <c r="AB27">
-        <v>1.67</v>
-      </c>
-      <c r="AC27">
-        <v>2</v>
-      </c>
-      <c r="AD27">
-        <v>2.8</v>
-      </c>
-      <c r="AE27">
-        <v>1.44</v>
-      </c>
       <c r="AF27">
-        <v>1.57</v>
+        <v>2.51</v>
       </c>
       <c r="AG27">
-        <v>2.25</v>
+        <v>1.48</v>
       </c>
       <c r="AH27">
-        <v>5.25</v>
+        <v>5.15</v>
       </c>
       <c r="AI27">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AJ27" t="s">
         <v>303</v>
@@ -4459,76 +4459,76 @@
         <v>301</v>
       </c>
       <c r="L28">
-        <v>1.8</v>
+        <v>5.9</v>
       </c>
       <c r="M28">
-        <v>3.15</v>
+        <v>4.2</v>
       </c>
       <c r="N28">
-        <v>4.3</v>
+        <v>1.4</v>
       </c>
       <c r="O28">
-        <v>1.61</v>
+        <v>3.35</v>
       </c>
       <c r="P28">
-        <v>6.7</v>
+        <v>11</v>
       </c>
       <c r="Q28">
-        <v>2.89</v>
+        <v>1.4</v>
       </c>
       <c r="R28">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="S28">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="T28">
-        <v>3.14</v>
+        <v>2.38</v>
       </c>
       <c r="U28">
-        <v>1.31</v>
+        <v>1.53</v>
       </c>
       <c r="V28">
-        <v>7.7</v>
+        <v>5.75</v>
       </c>
       <c r="W28">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X28">
         <v>1.04</v>
       </c>
       <c r="Y28">
-        <v>6.75</v>
+        <v>11</v>
       </c>
       <c r="Z28">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AA28">
-        <v>2.8</v>
+        <v>4.33</v>
       </c>
       <c r="AB28">
-        <v>2.22</v>
+        <v>1.65</v>
       </c>
       <c r="AC28">
-        <v>1.63</v>
+        <v>2.1</v>
       </c>
       <c r="AD28">
-        <v>3.74</v>
+        <v>2.65</v>
       </c>
       <c r="AE28">
-        <v>1.19</v>
+        <v>1.48</v>
       </c>
       <c r="AF28">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="AG28">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="AH28">
-        <v>7.2</v>
+        <v>5</v>
       </c>
       <c r="AI28">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="AJ28" t="s">
         <v>303</v>
@@ -4575,76 +4575,76 @@
         <v>301</v>
       </c>
       <c r="L29">
-        <v>5.9</v>
+        <v>2.73</v>
       </c>
       <c r="M29">
-        <v>4.2</v>
+        <v>3.29</v>
       </c>
       <c r="N29">
-        <v>1.4</v>
+        <v>2.23</v>
       </c>
       <c r="O29">
-        <v>3.35</v>
+        <v>2.2</v>
       </c>
       <c r="P29">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q29">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="R29">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S29">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T29">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="U29">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="V29">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="W29">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X29">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y29">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Z29">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AA29">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="AB29">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AC29">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AD29">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="AE29">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AF29">
-        <v>1.77</v>
+        <v>1.57</v>
       </c>
       <c r="AG29">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="AH29">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="AI29">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AJ29" t="s">
         <v>303</v>
@@ -4664,7 +4664,7 @@
         <v>48</v>
       </c>
       <c r="C30" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D30" t="s">
         <v>94</v>
@@ -4807,76 +4807,76 @@
         <v>301</v>
       </c>
       <c r="L31">
-        <v>1.22</v>
+        <v>2.09</v>
       </c>
       <c r="M31">
-        <v>4.8</v>
+        <v>3.25</v>
       </c>
       <c r="N31">
-        <v>12</v>
+        <v>2.98</v>
       </c>
       <c r="O31">
-        <v>1.23</v>
+        <v>1.67</v>
       </c>
       <c r="P31">
-        <v>7.9</v>
+        <v>10.5</v>
       </c>
       <c r="Q31">
-        <v>5.65</v>
+        <v>2.3</v>
       </c>
       <c r="R31">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="S31">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="T31">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="U31">
         <v>1.44</v>
       </c>
       <c r="V31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W31">
+        <v>1.1</v>
+      </c>
+      <c r="X31">
+        <v>1.01</v>
+      </c>
+      <c r="Y31">
+        <v>11</v>
+      </c>
+      <c r="Z31">
+        <v>1.22</v>
+      </c>
+      <c r="AA31">
+        <v>3.64</v>
+      </c>
+      <c r="AB31">
+        <v>1.77</v>
+      </c>
+      <c r="AC31">
+        <v>1.93</v>
+      </c>
+      <c r="AD31">
+        <v>2.88</v>
+      </c>
+      <c r="AE31">
+        <v>1.34</v>
+      </c>
+      <c r="AF31">
+        <v>1.67</v>
+      </c>
+      <c r="AG31">
+        <v>2.1</v>
+      </c>
+      <c r="AH31">
+        <v>5.3</v>
+      </c>
+      <c r="AI31">
         <v>1.09</v>
-      </c>
-      <c r="X31">
-        <v>1.02</v>
-      </c>
-      <c r="Y31">
-        <v>10</v>
-      </c>
-      <c r="Z31">
-        <v>1.24</v>
-      </c>
-      <c r="AA31">
-        <v>3.6</v>
-      </c>
-      <c r="AB31">
-        <v>1.93</v>
-      </c>
-      <c r="AC31">
-        <v>1.83</v>
-      </c>
-      <c r="AD31">
-        <v>2.83</v>
-      </c>
-      <c r="AE31">
-        <v>1.33</v>
-      </c>
-      <c r="AF31">
-        <v>2.5</v>
-      </c>
-      <c r="AG31">
-        <v>1.44</v>
-      </c>
-      <c r="AH31">
-        <v>5.5</v>
-      </c>
-      <c r="AI31">
-        <v>1.11</v>
       </c>
       <c r="AJ31" t="s">
         <v>303</v>
@@ -5039,64 +5039,64 @@
         <v>301</v>
       </c>
       <c r="L33">
-        <v>1.34</v>
+        <v>2.95</v>
       </c>
       <c r="M33">
-        <v>5</v>
+        <v>3.46</v>
       </c>
       <c r="N33">
-        <v>6.5</v>
+        <v>2.33</v>
       </c>
       <c r="O33">
-        <v>1.37</v>
+        <v>2.3</v>
       </c>
       <c r="P33">
-        <v>19.25</v>
+        <v>13.75</v>
       </c>
       <c r="Q33">
-        <v>3.1</v>
+        <v>1.67</v>
       </c>
       <c r="R33">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S33">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="T33">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="U33">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="V33">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="W33">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="X33">
         <v>1.02</v>
       </c>
       <c r="Y33">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="Z33">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AA33">
-        <v>5</v>
+        <v>3.92</v>
       </c>
       <c r="AB33">
-        <v>1.46</v>
+        <v>1.74</v>
       </c>
       <c r="AC33">
-        <v>2.62</v>
+        <v>1.98</v>
       </c>
       <c r="AD33">
-        <v>2.15</v>
+        <v>2.78</v>
       </c>
       <c r="AE33">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="AF33">
         <v>1.62</v>
@@ -5105,10 +5105,10 @@
         <v>2.2</v>
       </c>
       <c r="AH33">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="AI33">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AJ33" t="s">
         <v>303</v>
@@ -5155,40 +5155,40 @@
         <v>301</v>
       </c>
       <c r="L34">
-        <v>2.95</v>
+        <v>1.3</v>
       </c>
       <c r="M34">
-        <v>3.46</v>
+        <v>5</v>
       </c>
       <c r="N34">
-        <v>2.33</v>
+        <v>6</v>
       </c>
       <c r="O34">
-        <v>2.3</v>
+        <v>1.37</v>
       </c>
       <c r="P34">
-        <v>13.75</v>
+        <v>19.25</v>
       </c>
       <c r="Q34">
-        <v>1.67</v>
+        <v>3.1</v>
       </c>
       <c r="R34">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S34">
-        <v>3.04</v>
+        <v>3.6</v>
       </c>
       <c r="T34">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="U34">
-        <v>1.48</v>
+        <v>1.7</v>
       </c>
       <c r="V34">
-        <v>5.75</v>
+        <v>4.2</v>
       </c>
       <c r="W34">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="X34">
         <v>1.02</v>
@@ -5197,22 +5197,22 @@
         <v>10</v>
       </c>
       <c r="Z34">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AA34">
-        <v>3.75</v>
+        <v>5.32</v>
       </c>
       <c r="AB34">
-        <v>1.71</v>
+        <v>1.46</v>
       </c>
       <c r="AC34">
-        <v>2.11</v>
+        <v>2.47</v>
       </c>
       <c r="AD34">
-        <v>2.75</v>
+        <v>2.17</v>
       </c>
       <c r="AE34">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="AF34">
         <v>1.62</v>
@@ -5221,10 +5221,10 @@
         <v>2.2</v>
       </c>
       <c r="AH34">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="AI34">
-        <v>1.13</v>
+        <v>1.26</v>
       </c>
       <c r="AJ34" t="s">
         <v>303</v>
@@ -5244,7 +5244,7 @@
         <v>50</v>
       </c>
       <c r="C35" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D35" t="s">
         <v>94</v>
@@ -5292,22 +5292,22 @@
         <v>1.44</v>
       </c>
       <c r="S35">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="T35">
-        <v>2.93</v>
+        <v>2.88</v>
       </c>
       <c r="U35">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="V35">
-        <v>8.1</v>
+        <v>7</v>
       </c>
       <c r="W35">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X35">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y35">
         <v>9</v>
@@ -5316,28 +5316,28 @@
         <v>1.27</v>
       </c>
       <c r="AA35">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="AB35">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AC35">
         <v>1.73</v>
       </c>
       <c r="AD35">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="AE35">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AF35">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AG35">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AH35">
-        <v>6.95</v>
+        <v>6</v>
       </c>
       <c r="AI35">
         <v>1.04</v>
@@ -5360,7 +5360,7 @@
         <v>50</v>
       </c>
       <c r="C36" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D36" t="s">
         <v>94</v>
@@ -5476,7 +5476,7 @@
         <v>51</v>
       </c>
       <c r="C37" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D37" t="s">
         <v>94</v>
@@ -5601,7 +5601,7 @@
         <v>131</v>
       </c>
       <c r="F38" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -5708,7 +5708,7 @@
         <v>52</v>
       </c>
       <c r="C39" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="D39" t="s">
         <v>94</v>
@@ -5717,7 +5717,7 @@
         <v>132</v>
       </c>
       <c r="F39" t="s">
-        <v>235</v>
+        <v>131</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -5735,76 +5735,76 @@
         <v>301</v>
       </c>
       <c r="L39">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="M39">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="N39">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O39">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P39">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Q39">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="R39">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S39">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="T39">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U39">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V39">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="W39">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X39">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y39">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="Z39">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AA39">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AB39">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AC39">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="AD39">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AE39">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF39">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AG39">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AH39">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AI39">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AJ39" t="s">
         <v>303</v>
@@ -5824,7 +5824,7 @@
         <v>52</v>
       </c>
       <c r="C40" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="D40" t="s">
         <v>94</v>
@@ -5833,7 +5833,7 @@
         <v>133</v>
       </c>
       <c r="F40" t="s">
-        <v>131</v>
+        <v>235</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -5851,76 +5851,76 @@
         <v>301</v>
       </c>
       <c r="L40">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="M40">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="T40">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U40">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V40">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="W40">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X40">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y40">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Z40">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AA40">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AB40">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AC40">
+        <v>2.45</v>
+      </c>
+      <c r="AD40">
+        <v>2.08</v>
+      </c>
+      <c r="AE40">
+        <v>1.66</v>
+      </c>
+      <c r="AF40">
+        <v>1.42</v>
+      </c>
+      <c r="AG40">
         <v>2.62</v>
       </c>
-      <c r="AD40">
-        <v>0</v>
-      </c>
-      <c r="AE40">
-        <v>0</v>
-      </c>
-      <c r="AF40">
-        <v>0</v>
-      </c>
-      <c r="AG40">
-        <v>0</v>
-      </c>
       <c r="AH40">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AI40">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AJ40" t="s">
         <v>303</v>
@@ -5967,76 +5967,76 @@
         <v>301</v>
       </c>
       <c r="L41">
-        <v>2.05</v>
+        <v>2.53</v>
       </c>
       <c r="M41">
-        <v>3.14</v>
+        <v>3.21</v>
       </c>
       <c r="N41">
-        <v>3.19</v>
+        <v>2.85</v>
       </c>
       <c r="O41">
+        <v>1.83</v>
+      </c>
+      <c r="P41">
+        <v>7.4</v>
+      </c>
+      <c r="Q41">
+        <v>2.2</v>
+      </c>
+      <c r="R41">
+        <v>1.44</v>
+      </c>
+      <c r="S41">
+        <v>2.63</v>
+      </c>
+      <c r="T41">
+        <v>3.25</v>
+      </c>
+      <c r="U41">
+        <v>1.33</v>
+      </c>
+      <c r="V41">
+        <v>9</v>
+      </c>
+      <c r="W41">
+        <v>1.07</v>
+      </c>
+      <c r="X41">
+        <v>1.03</v>
+      </c>
+      <c r="Y41">
+        <v>7.4</v>
+      </c>
+      <c r="Z41">
+        <v>1.33</v>
+      </c>
+      <c r="AA41">
+        <v>2.84</v>
+      </c>
+      <c r="AB41">
+        <v>2.15</v>
+      </c>
+      <c r="AC41">
         <v>1.67</v>
       </c>
-      <c r="P41">
-        <v>8.4</v>
-      </c>
-      <c r="Q41">
-        <v>2.5</v>
-      </c>
-      <c r="R41">
-        <v>1.37</v>
-      </c>
-      <c r="S41">
-        <v>2.8</v>
-      </c>
-      <c r="T41">
-        <v>2.75</v>
-      </c>
-      <c r="U41">
-        <v>1.38</v>
-      </c>
-      <c r="V41">
-        <v>7</v>
-      </c>
-      <c r="W41">
-        <v>1.06</v>
-      </c>
-      <c r="X41">
-        <v>1.02</v>
-      </c>
-      <c r="Y41">
-        <v>8.1</v>
-      </c>
-      <c r="Z41">
-        <v>1.3</v>
-      </c>
-      <c r="AA41">
-        <v>3.15</v>
-      </c>
-      <c r="AB41">
-        <v>1.94</v>
-      </c>
-      <c r="AC41">
-        <v>1.76</v>
-      </c>
       <c r="AD41">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="AE41">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AF41">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AG41">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AH41">
-        <v>6.45</v>
+        <v>7.1</v>
       </c>
       <c r="AI41">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="AJ41" t="s">
         <v>303</v>
@@ -6083,76 +6083,76 @@
         <v>301</v>
       </c>
       <c r="L42">
-        <v>2.53</v>
+        <v>2.03</v>
       </c>
       <c r="M42">
-        <v>3.21</v>
+        <v>3.31</v>
       </c>
       <c r="N42">
-        <v>2.85</v>
+        <v>3.19</v>
       </c>
       <c r="O42">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="P42">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="Q42">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="R42">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="S42">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="T42">
-        <v>3.25</v>
+        <v>2.62</v>
       </c>
       <c r="U42">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="V42">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W42">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X42">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y42">
-        <v>7.4</v>
+        <v>9.1</v>
       </c>
       <c r="Z42">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AA42">
-        <v>2.84</v>
+        <v>3.15</v>
       </c>
       <c r="AB42">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="AC42">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="AD42">
-        <v>3.6</v>
+        <v>2.97</v>
       </c>
       <c r="AE42">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AF42">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AG42">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AH42">
-        <v>7.1</v>
+        <v>5.5</v>
       </c>
       <c r="AI42">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AJ42" t="s">
         <v>303</v>
@@ -6547,76 +6547,76 @@
         <v>301</v>
       </c>
       <c r="L46">
-        <v>1.91</v>
+        <v>2.4</v>
       </c>
       <c r="M46">
-        <v>3.15</v>
+        <v>2.96</v>
       </c>
       <c r="N46">
-        <v>4.18</v>
+        <v>2.75</v>
       </c>
       <c r="O46">
-        <v>1.57</v>
+        <v>1.95</v>
       </c>
       <c r="P46">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q46">
-        <v>3.1</v>
+        <v>2.15</v>
       </c>
       <c r="R46">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="S46">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="T46">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="U46">
         <v>1.29</v>
       </c>
       <c r="V46">
-        <v>11</v>
+        <v>8.5</v>
       </c>
       <c r="W46">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X46">
         <v>1.08</v>
       </c>
       <c r="Y46">
-        <v>6.64</v>
+        <v>7.1</v>
       </c>
       <c r="Z46">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="AA46">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="AB46">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="AC46">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="AD46">
-        <v>4.75</v>
+        <v>4.2</v>
       </c>
       <c r="AE46">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AF46">
-        <v>2.2</v>
+        <v>1.92</v>
       </c>
       <c r="AG46">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AH46">
-        <v>10</v>
+        <v>8.1</v>
       </c>
       <c r="AI46">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="AJ46" t="s">
         <v>303</v>
@@ -6636,7 +6636,7 @@
         <v>56</v>
       </c>
       <c r="C47" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D47" t="s">
         <v>94</v>
@@ -6663,76 +6663,76 @@
         <v>301</v>
       </c>
       <c r="L47">
-        <v>2.4</v>
+        <v>2.09</v>
       </c>
       <c r="M47">
-        <v>2.96</v>
+        <v>3.16</v>
       </c>
       <c r="N47">
-        <v>2.75</v>
+        <v>3.35</v>
       </c>
       <c r="O47">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="P47">
+        <v>7.2</v>
+      </c>
+      <c r="Q47">
+        <v>2.2</v>
+      </c>
+      <c r="R47">
+        <v>1.44</v>
+      </c>
+      <c r="S47">
+        <v>2.6</v>
+      </c>
+      <c r="T47">
+        <v>3.04</v>
+      </c>
+      <c r="U47">
+        <v>1.33</v>
+      </c>
+      <c r="V47">
+        <v>8</v>
+      </c>
+      <c r="W47">
+        <v>1.05</v>
+      </c>
+      <c r="X47">
+        <v>1.05</v>
+      </c>
+      <c r="Y47">
+        <v>8</v>
+      </c>
+      <c r="Z47">
+        <v>1.33</v>
+      </c>
+      <c r="AA47">
+        <v>2.83</v>
+      </c>
+      <c r="AB47">
+        <v>2.1</v>
+      </c>
+      <c r="AC47">
+        <v>1.66</v>
+      </c>
+      <c r="AD47">
+        <v>3.6</v>
+      </c>
+      <c r="AE47">
+        <v>1.22</v>
+      </c>
+      <c r="AF47">
+        <v>1.71</v>
+      </c>
+      <c r="AG47">
+        <v>1.82</v>
+      </c>
+      <c r="AH47">
         <v>7</v>
       </c>
-      <c r="Q47">
-        <v>2.15</v>
-      </c>
-      <c r="R47">
-        <v>1.46</v>
-      </c>
-      <c r="S47">
-        <v>2.4</v>
-      </c>
-      <c r="T47">
-        <v>3.2</v>
-      </c>
-      <c r="U47">
-        <v>1.29</v>
-      </c>
-      <c r="V47">
-        <v>8.5</v>
-      </c>
-      <c r="W47">
-        <v>1.06</v>
-      </c>
-      <c r="X47">
-        <v>1.08</v>
-      </c>
-      <c r="Y47">
-        <v>7.1</v>
-      </c>
-      <c r="Z47">
-        <v>1.42</v>
-      </c>
-      <c r="AA47">
-        <v>2.7</v>
-      </c>
-      <c r="AB47">
-        <v>2.25</v>
-      </c>
-      <c r="AC47">
-        <v>1.58</v>
-      </c>
-      <c r="AD47">
-        <v>4.2</v>
-      </c>
-      <c r="AE47">
-        <v>1.19</v>
-      </c>
-      <c r="AF47">
-        <v>1.92</v>
-      </c>
-      <c r="AG47">
-        <v>1.85</v>
-      </c>
-      <c r="AH47">
-        <v>8.1</v>
-      </c>
       <c r="AI47">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AJ47" t="s">
         <v>303</v>
@@ -6779,76 +6779,76 @@
         <v>301</v>
       </c>
       <c r="L48">
-        <v>2.67</v>
+        <v>1.34</v>
       </c>
       <c r="M48">
-        <v>3</v>
+        <v>4.96</v>
       </c>
       <c r="N48">
-        <v>2.43</v>
+        <v>8.35</v>
       </c>
       <c r="O48">
-        <v>1.91</v>
+        <v>1.25</v>
       </c>
       <c r="P48">
-        <v>7.2</v>
+        <v>15.25</v>
       </c>
       <c r="Q48">
-        <v>2.2</v>
+        <v>4.33</v>
       </c>
       <c r="R48">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="S48">
-        <v>2.58</v>
+        <v>3.4</v>
       </c>
       <c r="T48">
-        <v>2.97</v>
+        <v>2.5</v>
       </c>
       <c r="U48">
-        <v>1.32</v>
+        <v>1.5</v>
       </c>
       <c r="V48">
-        <v>7.8</v>
+        <v>6</v>
       </c>
       <c r="W48">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="X48">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="Z48">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AA48">
-        <v>2.83</v>
+        <v>4</v>
       </c>
       <c r="AB48">
-        <v>2.2</v>
+        <v>1.73</v>
       </c>
       <c r="AC48">
-        <v>1.62</v>
+        <v>2.08</v>
       </c>
       <c r="AD48">
-        <v>3.6</v>
+        <v>2.75</v>
       </c>
       <c r="AE48">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AF48">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AG48">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AH48">
-        <v>7</v>
+        <v>5.3</v>
       </c>
       <c r="AI48">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AJ48" t="s">
         <v>303</v>
@@ -6868,7 +6868,7 @@
         <v>56</v>
       </c>
       <c r="C49" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D49" t="s">
         <v>94</v>
@@ -6895,76 +6895,76 @@
         <v>301</v>
       </c>
       <c r="L49">
-        <v>1.34</v>
+        <v>1.91</v>
       </c>
       <c r="M49">
-        <v>4.96</v>
+        <v>3.15</v>
       </c>
       <c r="N49">
-        <v>8.35</v>
+        <v>4.18</v>
       </c>
       <c r="O49">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="P49">
-        <v>15.25</v>
+        <v>6</v>
       </c>
       <c r="Q49">
-        <v>4.33</v>
+        <v>3.1</v>
       </c>
       <c r="R49">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="S49">
-        <v>3.4</v>
+        <v>2.42</v>
       </c>
       <c r="T49">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="U49">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="V49">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="W49">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="X49">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="Y49">
-        <v>11</v>
+        <v>6.64</v>
       </c>
       <c r="Z49">
-        <v>1.17</v>
+        <v>1.47</v>
       </c>
       <c r="AA49">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="AB49">
-        <v>1.73</v>
+        <v>2.6</v>
       </c>
       <c r="AC49">
-        <v>2.08</v>
+        <v>1.49</v>
       </c>
       <c r="AD49">
-        <v>2.75</v>
+        <v>4.75</v>
       </c>
       <c r="AE49">
-        <v>1.35</v>
+        <v>1.16</v>
       </c>
       <c r="AF49">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AG49">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AH49">
-        <v>5.3</v>
+        <v>10</v>
       </c>
       <c r="AI49">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AJ49" t="s">
         <v>303</v>
@@ -7240,7 +7240,7 @@
         <v>0</v>
       </c>
       <c r="K52" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L52">
         <v>0</v>
@@ -7359,13 +7359,13 @@
         <v>301</v>
       </c>
       <c r="L53">
-        <v>1.76</v>
+        <v>1.57</v>
       </c>
       <c r="M53">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="N53">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
       <c r="O53">
         <v>1.53</v>
@@ -7377,19 +7377,19 @@
         <v>2.75</v>
       </c>
       <c r="R53">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S53">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="T53">
         <v>2.6</v>
       </c>
       <c r="U53">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="V53">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="W53">
         <v>1.11</v>
@@ -7401,34 +7401,34 @@
         <v>9.1</v>
       </c>
       <c r="Z53">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AA53">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AB53">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AC53">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="AD53">
-        <v>3.01</v>
+        <v>2.9</v>
       </c>
       <c r="AE53">
         <v>1.32</v>
       </c>
       <c r="AF53">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AG53">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="AH53">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AI53">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AJ53" t="s">
         <v>303</v>
@@ -7448,7 +7448,7 @@
         <v>58</v>
       </c>
       <c r="C54" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D54" t="s">
         <v>94</v>
@@ -7475,76 +7475,76 @@
         <v>301</v>
       </c>
       <c r="L54">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M54">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N54">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O54">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="P54">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q54">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R54">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S54">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T54">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U54">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V54">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W54">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X54">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y54">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Z54">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AA54">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AB54">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AC54">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD54">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AE54">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF54">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG54">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH54">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AI54">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AJ54" t="s">
         <v>303</v>
@@ -7564,7 +7564,7 @@
         <v>58</v>
       </c>
       <c r="C55" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D55" t="s">
         <v>94</v>
@@ -7591,76 +7591,76 @@
         <v>301</v>
       </c>
       <c r="L55">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M55">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N55">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O55">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="P55">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="Q55">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R55">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S55">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="T55">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U55">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V55">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W55">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X55">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y55">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Z55">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA55">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AB55">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC55">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AD55">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AE55">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF55">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG55">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH55">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AI55">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AJ55" t="s">
         <v>303</v>
@@ -7912,7 +7912,7 @@
         <v>58</v>
       </c>
       <c r="C58" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D58" t="s">
         <v>94</v>
@@ -7939,76 +7939,76 @@
         <v>301</v>
       </c>
       <c r="L58">
-        <v>2.2</v>
+        <v>1.79</v>
       </c>
       <c r="M58">
-        <v>2.95</v>
+        <v>3.45</v>
       </c>
       <c r="N58">
-        <v>3.2</v>
+        <v>3.95</v>
       </c>
       <c r="O58">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="P58">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q58">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="R58">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="S58">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="T58">
-        <v>3.2</v>
+        <v>2.63</v>
       </c>
       <c r="U58">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="V58">
-        <v>8.199999999999999</v>
+        <v>6</v>
       </c>
       <c r="W58">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="X58">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Y58">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Z58">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AA58">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AB58">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="AC58">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AD58">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AE58">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF58">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AG58">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AH58">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AI58">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AJ58" t="s">
         <v>303</v>
@@ -8144,7 +8144,7 @@
         <v>58</v>
       </c>
       <c r="C60" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D60" t="s">
         <v>94</v>
@@ -8171,40 +8171,40 @@
         <v>301</v>
       </c>
       <c r="L60">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M60">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N60">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O60">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="P60">
         <v>0</v>
       </c>
       <c r="Q60">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R60">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S60">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T60">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U60">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V60">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W60">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X60">
         <v>0</v>
@@ -8219,10 +8219,10 @@
         <v>0</v>
       </c>
       <c r="AB60">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC60">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD60">
         <v>0</v>
@@ -8231,10 +8231,10 @@
         <v>0</v>
       </c>
       <c r="AF60">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG60">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH60">
         <v>0</v>
@@ -8516,7 +8516,7 @@
         <v>0</v>
       </c>
       <c r="K63" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L63">
         <v>0</v>
@@ -8724,7 +8724,7 @@
         <v>58</v>
       </c>
       <c r="C65" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D65" t="s">
         <v>94</v>
@@ -8751,76 +8751,76 @@
         <v>301</v>
       </c>
       <c r="L65">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M65">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N65">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O65">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="P65">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="Q65">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="R65">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="S65">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="T65">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="U65">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V65">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="W65">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X65">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y65">
-        <v>6.35</v>
+        <v>0</v>
       </c>
       <c r="Z65">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AA65">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AB65">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AC65">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AD65">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AE65">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF65">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG65">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AH65">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AI65">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AJ65" t="s">
         <v>303</v>
@@ -9096,7 +9096,7 @@
         <v>0</v>
       </c>
       <c r="K68" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L68">
         <v>0</v>
@@ -9328,7 +9328,7 @@
         <v>0</v>
       </c>
       <c r="K70" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L70">
         <v>0</v>
@@ -9420,7 +9420,7 @@
         <v>59</v>
       </c>
       <c r="C71" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D71" t="s">
         <v>94</v>
@@ -9536,7 +9536,7 @@
         <v>60</v>
       </c>
       <c r="C72" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D72" t="s">
         <v>94</v>
@@ -9563,76 +9563,76 @@
         <v>301</v>
       </c>
       <c r="L72">
+        <v>2.11</v>
+      </c>
+      <c r="M72">
+        <v>2.88</v>
+      </c>
+      <c r="N72">
+        <v>3.5</v>
+      </c>
+      <c r="O72">
+        <v>1.9</v>
+      </c>
+      <c r="P72">
+        <v>5.75</v>
+      </c>
+      <c r="Q72">
+        <v>2.37</v>
+      </c>
+      <c r="R72">
         <v>1.6</v>
       </c>
-      <c r="M72">
-        <v>3.54</v>
-      </c>
-      <c r="N72">
+      <c r="S72">
+        <v>2.2</v>
+      </c>
+      <c r="T72">
+        <v>3.66</v>
+      </c>
+      <c r="U72">
+        <v>1.22</v>
+      </c>
+      <c r="V72">
+        <v>11.5</v>
+      </c>
+      <c r="W72">
+        <v>1.02</v>
+      </c>
+      <c r="X72">
+        <v>1.11</v>
+      </c>
+      <c r="Y72">
+        <v>6</v>
+      </c>
+      <c r="Z72">
+        <v>1.57</v>
+      </c>
+      <c r="AA72">
+        <v>2.4</v>
+      </c>
+      <c r="AB72">
+        <v>2.62</v>
+      </c>
+      <c r="AC72">
+        <v>1.42</v>
+      </c>
+      <c r="AD72">
         <v>5</v>
-      </c>
-      <c r="O72">
-        <v>1.5</v>
-      </c>
-      <c r="P72">
-        <v>6.5</v>
-      </c>
-      <c r="Q72">
-        <v>3.3</v>
-      </c>
-      <c r="R72">
-        <v>1.47</v>
-      </c>
-      <c r="S72">
-        <v>2.52</v>
-      </c>
-      <c r="T72">
-        <v>3.3</v>
-      </c>
-      <c r="U72">
-        <v>1.28</v>
-      </c>
-      <c r="V72">
-        <v>9</v>
-      </c>
-      <c r="W72">
-        <v>1.06</v>
-      </c>
-      <c r="X72">
-        <v>1.04</v>
-      </c>
-      <c r="Y72">
-        <v>6.5</v>
-      </c>
-      <c r="Z72">
-        <v>1.41</v>
-      </c>
-      <c r="AA72">
-        <v>2.5</v>
-      </c>
-      <c r="AB72">
-        <v>2.45</v>
-      </c>
-      <c r="AC72">
-        <v>1.53</v>
-      </c>
-      <c r="AD72">
-        <v>4.5</v>
       </c>
       <c r="AE72">
         <v>1.14</v>
       </c>
       <c r="AF72">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AG72">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AH72">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="AI72">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AJ72" t="s">
         <v>303</v>
@@ -9652,7 +9652,7 @@
         <v>60</v>
       </c>
       <c r="C73" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D73" t="s">
         <v>94</v>
@@ -9679,76 +9679,76 @@
         <v>301</v>
       </c>
       <c r="L73">
+        <v>1.6</v>
+      </c>
+      <c r="M73">
+        <v>3.54</v>
+      </c>
+      <c r="N73">
+        <v>5</v>
+      </c>
+      <c r="O73">
+        <v>1.5</v>
+      </c>
+      <c r="P73">
+        <v>6.5</v>
+      </c>
+      <c r="Q73">
+        <v>3.3</v>
+      </c>
+      <c r="R73">
         <v>1.47</v>
       </c>
-      <c r="M73">
-        <v>4.25</v>
-      </c>
-      <c r="N73">
-        <v>6.55</v>
-      </c>
-      <c r="O73">
-        <v>1.36</v>
-      </c>
-      <c r="P73">
-        <v>12</v>
-      </c>
-      <c r="Q73">
-        <v>3.5</v>
-      </c>
-      <c r="R73">
-        <v>1.36</v>
-      </c>
       <c r="S73">
-        <v>3</v>
+        <v>2.52</v>
       </c>
       <c r="T73">
-        <v>2.63</v>
+        <v>3.3</v>
       </c>
       <c r="U73">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="V73">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W73">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X73">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y73">
-        <v>11</v>
+        <v>6.5</v>
       </c>
       <c r="Z73">
-        <v>1.22</v>
+        <v>1.41</v>
       </c>
       <c r="AA73">
-        <v>3.52</v>
+        <v>2.5</v>
       </c>
       <c r="AB73">
-        <v>1.85</v>
+        <v>2.45</v>
       </c>
       <c r="AC73">
-        <v>1.95</v>
+        <v>1.53</v>
       </c>
       <c r="AD73">
-        <v>2.98</v>
+        <v>4.5</v>
       </c>
       <c r="AE73">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AF73">
-        <v>1.91</v>
+        <v>2.38</v>
       </c>
       <c r="AG73">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AH73">
-        <v>5.8</v>
+        <v>9.5</v>
       </c>
       <c r="AI73">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AJ73" t="s">
         <v>303</v>
@@ -9795,76 +9795,76 @@
         <v>301</v>
       </c>
       <c r="L74">
-        <v>2.11</v>
+        <v>2.5</v>
       </c>
       <c r="M74">
-        <v>2.88</v>
+        <v>3.01</v>
       </c>
       <c r="N74">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="O74">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="P74">
-        <v>5.75</v>
+        <v>6.75</v>
       </c>
       <c r="Q74">
-        <v>2.37</v>
+        <v>2.2</v>
       </c>
       <c r="R74">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="S74">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="T74">
-        <v>3.66</v>
+        <v>3.3</v>
       </c>
       <c r="U74">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="V74">
-        <v>11.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W74">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X74">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Y74">
-        <v>6</v>
+        <v>7.15</v>
       </c>
       <c r="Z74">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AA74">
+        <v>2.63</v>
+      </c>
+      <c r="AB74">
         <v>2.4</v>
       </c>
-      <c r="AB74">
-        <v>2.62</v>
-      </c>
       <c r="AC74">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="AD74">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="AE74">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AF74">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AG74">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="AH74">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="AI74">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AJ74" t="s">
         <v>303</v>
@@ -9884,7 +9884,7 @@
         <v>60</v>
       </c>
       <c r="C75" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D75" t="s">
         <v>94</v>
@@ -9911,76 +9911,76 @@
         <v>301</v>
       </c>
       <c r="L75">
-        <v>2.5</v>
+        <v>1.47</v>
       </c>
       <c r="M75">
-        <v>3.01</v>
+        <v>4.25</v>
       </c>
       <c r="N75">
+        <v>6.55</v>
+      </c>
+      <c r="O75">
+        <v>1.36</v>
+      </c>
+      <c r="P75">
+        <v>12</v>
+      </c>
+      <c r="Q75">
+        <v>3.5</v>
+      </c>
+      <c r="R75">
+        <v>1.36</v>
+      </c>
+      <c r="S75">
         <v>3</v>
       </c>
-      <c r="O75">
+      <c r="T75">
+        <v>2.63</v>
+      </c>
+      <c r="U75">
+        <v>1.44</v>
+      </c>
+      <c r="V75">
+        <v>7</v>
+      </c>
+      <c r="W75">
+        <v>1.1</v>
+      </c>
+      <c r="X75">
+        <v>1.01</v>
+      </c>
+      <c r="Y75">
+        <v>11</v>
+      </c>
+      <c r="Z75">
+        <v>1.22</v>
+      </c>
+      <c r="AA75">
+        <v>3.52</v>
+      </c>
+      <c r="AB75">
+        <v>1.85</v>
+      </c>
+      <c r="AC75">
         <v>1.95</v>
       </c>
-      <c r="P75">
-        <v>6.75</v>
-      </c>
-      <c r="Q75">
-        <v>2.2</v>
-      </c>
-      <c r="R75">
-        <v>1.53</v>
-      </c>
-      <c r="S75">
-        <v>2.32</v>
-      </c>
-      <c r="T75">
-        <v>3.3</v>
-      </c>
-      <c r="U75">
-        <v>1.27</v>
-      </c>
-      <c r="V75">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="W75">
-        <v>1.03</v>
-      </c>
-      <c r="X75">
-        <v>1.1</v>
-      </c>
-      <c r="Y75">
-        <v>7.15</v>
-      </c>
-      <c r="Z75">
-        <v>1.44</v>
-      </c>
-      <c r="AA75">
-        <v>2.63</v>
-      </c>
-      <c r="AB75">
-        <v>2.4</v>
-      </c>
-      <c r="AC75">
-        <v>1.53</v>
-      </c>
       <c r="AD75">
-        <v>4.75</v>
+        <v>2.98</v>
       </c>
       <c r="AE75">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AF75">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AG75">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AH75">
-        <v>9.5</v>
+        <v>5.8</v>
       </c>
       <c r="AI75">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AJ75" t="s">
         <v>303</v>
@@ -10259,76 +10259,76 @@
         <v>301</v>
       </c>
       <c r="L78">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="M78">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="N78">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="O78">
         <v>1.49</v>
       </c>
       <c r="P78">
-        <v>8.75</v>
+        <v>6.5</v>
       </c>
       <c r="Q78">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="R78">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="S78">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="T78">
-        <v>2.84</v>
+        <v>3.3</v>
       </c>
       <c r="U78">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="V78">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W78">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X78">
+        <v>1.05</v>
+      </c>
+      <c r="Y78">
+        <v>6.75</v>
+      </c>
+      <c r="Z78">
+        <v>1.42</v>
+      </c>
+      <c r="AA78">
+        <v>2.5</v>
+      </c>
+      <c r="AB78">
+        <v>2.4</v>
+      </c>
+      <c r="AC78">
+        <v>1.52</v>
+      </c>
+      <c r="AD78">
+        <v>4.35</v>
+      </c>
+      <c r="AE78">
+        <v>1.14</v>
+      </c>
+      <c r="AF78">
+        <v>2.4</v>
+      </c>
+      <c r="AG78">
+        <v>1.5</v>
+      </c>
+      <c r="AH78">
+        <v>8.5</v>
+      </c>
+      <c r="AI78">
         <v>1.01</v>
-      </c>
-      <c r="Y78">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="Z78">
-        <v>1.28</v>
-      </c>
-      <c r="AA78">
-        <v>3.2</v>
-      </c>
-      <c r="AB78">
-        <v>1.91</v>
-      </c>
-      <c r="AC78">
-        <v>1.73</v>
-      </c>
-      <c r="AD78">
-        <v>3.35</v>
-      </c>
-      <c r="AE78">
-        <v>1.25</v>
-      </c>
-      <c r="AF78">
-        <v>2</v>
-      </c>
-      <c r="AG78">
-        <v>1.73</v>
-      </c>
-      <c r="AH78">
-        <v>6.25</v>
-      </c>
-      <c r="AI78">
-        <v>1.08</v>
       </c>
       <c r="AJ78" t="s">
         <v>303</v>
@@ -10375,10 +10375,10 @@
         <v>301</v>
       </c>
       <c r="L79">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="M79">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="N79">
         <v>5.6</v>
@@ -10387,64 +10387,64 @@
         <v>1.49</v>
       </c>
       <c r="P79">
-        <v>6.5</v>
+        <v>8.75</v>
       </c>
       <c r="Q79">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="R79">
-        <v>1.49</v>
+        <v>1.39</v>
       </c>
       <c r="S79">
-        <v>2.38</v>
+        <v>2.68</v>
       </c>
       <c r="T79">
-        <v>3.3</v>
+        <v>2.84</v>
       </c>
       <c r="U79">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="V79">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W79">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X79">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y79">
-        <v>6.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Z79">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="AA79">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="AB79">
-        <v>2.3</v>
+        <v>1.96</v>
       </c>
       <c r="AC79">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AD79">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="AE79">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AF79">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AG79">
-        <v>1.5</v>
+        <v>1.69</v>
       </c>
       <c r="AH79">
-        <v>8.5</v>
+        <v>6.3</v>
       </c>
       <c r="AI79">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AJ79" t="s">
         <v>303</v>
@@ -10464,7 +10464,7 @@
         <v>63</v>
       </c>
       <c r="C80" t="s">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="D80" t="s">
         <v>94</v>
@@ -10491,76 +10491,76 @@
         <v>301</v>
       </c>
       <c r="L80">
-        <v>1.75</v>
+        <v>2.75</v>
       </c>
       <c r="M80">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="N80">
-        <v>3.45</v>
+        <v>2.05</v>
       </c>
       <c r="O80">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="P80">
         <v>0</v>
       </c>
       <c r="Q80">
-        <v>2.75</v>
+        <v>1.67</v>
       </c>
       <c r="R80">
         <v>1.25</v>
       </c>
       <c r="S80">
+        <v>3.6</v>
+      </c>
+      <c r="T80">
+        <v>2.1</v>
+      </c>
+      <c r="U80">
+        <v>1.65</v>
+      </c>
+      <c r="V80">
+        <v>4.5</v>
+      </c>
+      <c r="W80">
+        <v>1.17</v>
+      </c>
+      <c r="X80">
+        <v>0</v>
+      </c>
+      <c r="Y80">
+        <v>0</v>
+      </c>
+      <c r="Z80">
+        <v>1.13</v>
+      </c>
+      <c r="AA80">
+        <v>5.25</v>
+      </c>
+      <c r="AB80">
+        <v>1.48</v>
+      </c>
+      <c r="AC80">
+        <v>2.48</v>
+      </c>
+      <c r="AD80">
+        <v>2.11</v>
+      </c>
+      <c r="AE80">
+        <v>1.64</v>
+      </c>
+      <c r="AF80">
+        <v>1.48</v>
+      </c>
+      <c r="AG80">
+        <v>2.48</v>
+      </c>
+      <c r="AH80">
         <v>3.55</v>
       </c>
-      <c r="T80">
-        <v>2.45</v>
-      </c>
-      <c r="U80">
-        <v>1.5</v>
-      </c>
-      <c r="V80">
-        <v>5.5</v>
-      </c>
-      <c r="W80">
-        <v>1.11</v>
-      </c>
-      <c r="X80">
-        <v>1.04</v>
-      </c>
-      <c r="Y80">
-        <v>13</v>
-      </c>
-      <c r="Z80">
-        <v>1.2</v>
-      </c>
-      <c r="AA80">
-        <v>4.2</v>
-      </c>
-      <c r="AB80">
-        <v>1.74</v>
-      </c>
-      <c r="AC80">
-        <v>1.97</v>
-      </c>
-      <c r="AD80">
-        <v>2.83</v>
-      </c>
-      <c r="AE80">
-        <v>1.4</v>
-      </c>
-      <c r="AF80">
-        <v>1.65</v>
-      </c>
-      <c r="AG80">
-        <v>2.08</v>
-      </c>
-      <c r="AH80">
-        <v>5</v>
-      </c>
       <c r="AI80">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AJ80" t="s">
         <v>303</v>
@@ -10580,7 +10580,7 @@
         <v>63</v>
       </c>
       <c r="C81" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="D81" t="s">
         <v>94</v>
@@ -10607,76 +10607,76 @@
         <v>301</v>
       </c>
       <c r="L81">
-        <v>2.14</v>
+        <v>1.49</v>
       </c>
       <c r="M81">
-        <v>3.14</v>
+        <v>4.3</v>
       </c>
       <c r="N81">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="O81">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="P81">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q81">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="R81">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="S81">
-        <v>2.85</v>
+        <v>3.3</v>
       </c>
       <c r="T81">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="U81">
+        <v>1.55</v>
+      </c>
+      <c r="V81">
+        <v>5.25</v>
+      </c>
+      <c r="W81">
+        <v>1.13</v>
+      </c>
+      <c r="X81">
+        <v>1.04</v>
+      </c>
+      <c r="Y81">
+        <v>13</v>
+      </c>
+      <c r="Z81">
+        <v>1.18</v>
+      </c>
+      <c r="AA81">
+        <v>4.2</v>
+      </c>
+      <c r="AB81">
+        <v>1.67</v>
+      </c>
+      <c r="AC81">
+        <v>2.09</v>
+      </c>
+      <c r="AD81">
+        <v>2.74</v>
+      </c>
+      <c r="AE81">
         <v>1.4</v>
       </c>
-      <c r="V81">
-        <v>7</v>
-      </c>
-      <c r="W81">
-        <v>1.06</v>
-      </c>
-      <c r="X81">
-        <v>1.05</v>
-      </c>
-      <c r="Y81">
-        <v>8</v>
-      </c>
-      <c r="Z81">
-        <v>1.33</v>
-      </c>
-      <c r="AA81">
-        <v>3.42</v>
-      </c>
-      <c r="AB81">
-        <v>1.92</v>
-      </c>
-      <c r="AC81">
-        <v>1.78</v>
-      </c>
-      <c r="AD81">
-        <v>3.08</v>
-      </c>
-      <c r="AE81">
-        <v>1.25</v>
-      </c>
       <c r="AF81">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AG81">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="AH81">
-        <v>6.1</v>
+        <v>5</v>
       </c>
       <c r="AI81">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="AJ81" t="s">
         <v>303</v>
@@ -10696,7 +10696,7 @@
         <v>63</v>
       </c>
       <c r="C82" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="D82" t="s">
         <v>94</v>
@@ -10723,76 +10723,76 @@
         <v>301</v>
       </c>
       <c r="L82">
-        <v>2.75</v>
+        <v>2.22</v>
       </c>
       <c r="M82">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="N82">
-        <v>2.05</v>
+        <v>3.2</v>
       </c>
       <c r="O82">
-        <v>2.2</v>
+        <v>1.62</v>
       </c>
       <c r="P82">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q82">
-        <v>1.67</v>
+        <v>2.63</v>
       </c>
       <c r="R82">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="S82">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="T82">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="U82">
-        <v>1.65</v>
+        <v>1.37</v>
       </c>
       <c r="V82">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="W82">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="X82">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y82">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Z82">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="AA82">
-        <v>5.25</v>
+        <v>3.08</v>
       </c>
       <c r="AB82">
-        <v>1.48</v>
+        <v>2</v>
       </c>
       <c r="AC82">
-        <v>2.48</v>
+        <v>1.75</v>
       </c>
       <c r="AD82">
-        <v>2.11</v>
+        <v>3.42</v>
       </c>
       <c r="AE82">
-        <v>1.64</v>
+        <v>1.29</v>
       </c>
       <c r="AF82">
-        <v>1.48</v>
+        <v>1.76</v>
       </c>
       <c r="AG82">
-        <v>2.48</v>
+        <v>1.91</v>
       </c>
       <c r="AH82">
-        <v>3.55</v>
+        <v>6.9</v>
       </c>
       <c r="AI82">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="AJ82" t="s">
         <v>303</v>
@@ -10955,22 +10955,22 @@
         <v>301</v>
       </c>
       <c r="L84">
-        <v>2.63</v>
+        <v>1.45</v>
       </c>
       <c r="M84">
+        <v>3.8</v>
+      </c>
+      <c r="N84">
+        <v>6</v>
+      </c>
+      <c r="O84">
+        <v>1.36</v>
+      </c>
+      <c r="P84">
+        <v>14</v>
+      </c>
+      <c r="Q84">
         <v>3.1</v>
-      </c>
-      <c r="N84">
-        <v>2.4</v>
-      </c>
-      <c r="O84">
-        <v>2.05</v>
-      </c>
-      <c r="P84">
-        <v>11.5</v>
-      </c>
-      <c r="Q84">
-        <v>1.8</v>
       </c>
       <c r="R84">
         <v>1.25</v>
@@ -10979,22 +10979,22 @@
         <v>3.75</v>
       </c>
       <c r="T84">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="U84">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="V84">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="W84">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X84">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y84">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="Z84">
         <v>1.17</v>
@@ -11009,16 +11009,16 @@
         <v>2.4</v>
       </c>
       <c r="AD84">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AE84">
         <v>1.61</v>
       </c>
       <c r="AF84">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AG84">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="AH84">
         <v>3.8</v>
@@ -11044,7 +11044,7 @@
         <v>64</v>
       </c>
       <c r="C85" t="s">
-        <v>93</v>
+        <v>70</v>
       </c>
       <c r="D85" t="s">
         <v>94</v>
@@ -11071,76 +11071,76 @@
         <v>301</v>
       </c>
       <c r="L85">
-        <v>2.47</v>
+        <v>1.91</v>
       </c>
       <c r="M85">
-        <v>3.07</v>
+        <v>3.6</v>
       </c>
       <c r="N85">
-        <v>2.57</v>
+        <v>3.35</v>
       </c>
       <c r="O85">
-        <v>2.05</v>
+        <v>1.57</v>
       </c>
       <c r="P85">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q85">
-        <v>1.83</v>
+        <v>2.5</v>
       </c>
       <c r="R85">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="S85">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T85">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="U85">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="V85">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="W85">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X85">
         <v>1</v>
       </c>
       <c r="Y85">
-        <v>9.300000000000001</v>
+        <v>12</v>
       </c>
       <c r="Z85">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AA85">
-        <v>3.74</v>
+        <v>4.25</v>
       </c>
       <c r="AB85">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AC85">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="AD85">
-        <v>2.74</v>
+        <v>2.38</v>
       </c>
       <c r="AE85">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="AF85">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AG85">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AH85">
-        <v>4.95</v>
+        <v>4</v>
       </c>
       <c r="AI85">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AJ85" t="s">
         <v>303</v>
@@ -11187,40 +11187,40 @@
         <v>301</v>
       </c>
       <c r="L86">
-        <v>2.98</v>
+        <v>2.11</v>
       </c>
       <c r="M86">
-        <v>3.07</v>
+        <v>3.12</v>
       </c>
       <c r="N86">
-        <v>2.18</v>
+        <v>3.08</v>
       </c>
       <c r="O86">
+        <v>1.67</v>
+      </c>
+      <c r="P86">
+        <v>12.5</v>
+      </c>
+      <c r="Q86">
         <v>2.2</v>
       </c>
-      <c r="P86">
-        <v>11.5</v>
-      </c>
-      <c r="Q86">
-        <v>1.73</v>
-      </c>
       <c r="R86">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="S86">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="T86">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="U86">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="V86">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="W86">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X86">
         <v>1.01</v>
@@ -11229,34 +11229,34 @@
         <v>17</v>
       </c>
       <c r="Z86">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AA86">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="AB86">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AC86">
-        <v>2.35</v>
+        <v>2.6</v>
       </c>
       <c r="AD86">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AE86">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AF86">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AG86">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="AH86">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="AI86">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AJ86" t="s">
         <v>303</v>
@@ -11276,7 +11276,7 @@
         <v>64</v>
       </c>
       <c r="C87" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="D87" t="s">
         <v>94</v>
@@ -11303,76 +11303,76 @@
         <v>301</v>
       </c>
       <c r="L87">
-        <v>3.14</v>
+        <v>2.98</v>
       </c>
       <c r="M87">
-        <v>3.12</v>
+        <v>3.07</v>
       </c>
       <c r="N87">
-        <v>2.45</v>
+        <v>2.18</v>
       </c>
       <c r="O87">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="P87">
-        <v>6</v>
+        <v>11.5</v>
       </c>
       <c r="Q87">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="R87">
+        <v>1.25</v>
+      </c>
+      <c r="S87">
+        <v>3.75</v>
+      </c>
+      <c r="T87">
+        <v>2.25</v>
+      </c>
+      <c r="U87">
         <v>1.57</v>
       </c>
-      <c r="S87">
-        <v>2.3</v>
-      </c>
-      <c r="T87">
-        <v>3.4</v>
-      </c>
-      <c r="U87">
-        <v>1.25</v>
-      </c>
       <c r="V87">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="W87">
+        <v>1.14</v>
+      </c>
+      <c r="X87">
         <v>1.01</v>
       </c>
-      <c r="X87">
-        <v>1.12</v>
-      </c>
       <c r="Y87">
-        <v>6.05</v>
+        <v>17</v>
       </c>
       <c r="Z87">
+        <v>1.18</v>
+      </c>
+      <c r="AA87">
+        <v>4.75</v>
+      </c>
+      <c r="AB87">
         <v>1.53</v>
       </c>
-      <c r="AA87">
-        <v>2.45</v>
-      </c>
-      <c r="AB87">
-        <v>2.6</v>
-      </c>
       <c r="AC87">
-        <v>1.46</v>
+        <v>2.35</v>
       </c>
       <c r="AD87">
-        <v>5.2</v>
+        <v>2.25</v>
       </c>
       <c r="AE87">
-        <v>1.1</v>
+        <v>1.57</v>
       </c>
       <c r="AF87">
-        <v>2.05</v>
+        <v>1.44</v>
       </c>
       <c r="AG87">
-        <v>1.7</v>
+        <v>2.63</v>
       </c>
       <c r="AH87">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="AI87">
-        <v>1.02</v>
+        <v>1.22</v>
       </c>
       <c r="AJ87" t="s">
         <v>303</v>
@@ -11419,22 +11419,22 @@
         <v>301</v>
       </c>
       <c r="L88">
-        <v>1.45</v>
+        <v>2.63</v>
       </c>
       <c r="M88">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="N88">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="O88">
-        <v>1.36</v>
+        <v>2.05</v>
       </c>
       <c r="P88">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="Q88">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="R88">
         <v>1.25</v>
@@ -11443,22 +11443,22 @@
         <v>3.75</v>
       </c>
       <c r="T88">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="U88">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="V88">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="W88">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X88">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y88">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="Z88">
         <v>1.17</v>
@@ -11473,16 +11473,16 @@
         <v>2.4</v>
       </c>
       <c r="AD88">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AE88">
         <v>1.61</v>
       </c>
       <c r="AF88">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AG88">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="AH88">
         <v>3.8</v>
@@ -11508,7 +11508,7 @@
         <v>64</v>
       </c>
       <c r="C89" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D89" t="s">
         <v>94</v>
@@ -11535,76 +11535,76 @@
         <v>301</v>
       </c>
       <c r="L89">
-        <v>2.11</v>
+        <v>3.14</v>
       </c>
       <c r="M89">
         <v>3.12</v>
       </c>
       <c r="N89">
-        <v>3.08</v>
+        <v>2.45</v>
       </c>
       <c r="O89">
-        <v>1.67</v>
+        <v>2.3</v>
       </c>
       <c r="P89">
-        <v>12.5</v>
+        <v>6</v>
       </c>
       <c r="Q89">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="R89">
-        <v>1.22</v>
+        <v>1.57</v>
       </c>
       <c r="S89">
-        <v>4</v>
+        <v>2.3</v>
       </c>
       <c r="T89">
-        <v>2.1</v>
+        <v>3.4</v>
       </c>
       <c r="U89">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="V89">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="W89">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="X89">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="Y89">
-        <v>17</v>
+        <v>6.05</v>
       </c>
       <c r="Z89">
-        <v>1.17</v>
+        <v>1.53</v>
       </c>
       <c r="AA89">
-        <v>5</v>
+        <v>2.45</v>
       </c>
       <c r="AB89">
-        <v>1.44</v>
+        <v>2.6</v>
       </c>
       <c r="AC89">
-        <v>2.6</v>
+        <v>1.46</v>
       </c>
       <c r="AD89">
+        <v>5.2</v>
+      </c>
+      <c r="AE89">
+        <v>1.1</v>
+      </c>
+      <c r="AF89">
         <v>2.05</v>
       </c>
-      <c r="AE89">
+      <c r="AG89">
         <v>1.7</v>
       </c>
-      <c r="AF89">
-        <v>1.4</v>
-      </c>
-      <c r="AG89">
-        <v>2.75</v>
-      </c>
       <c r="AH89">
-        <v>3.65</v>
+        <v>10</v>
       </c>
       <c r="AI89">
-        <v>1.28</v>
+        <v>1.02</v>
       </c>
       <c r="AJ89" t="s">
         <v>303</v>
@@ -11624,7 +11624,7 @@
         <v>64</v>
       </c>
       <c r="C90" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="D90" t="s">
         <v>94</v>
@@ -11651,76 +11651,76 @@
         <v>301</v>
       </c>
       <c r="L90">
-        <v>1.91</v>
+        <v>1.2</v>
       </c>
       <c r="M90">
-        <v>3.6</v>
+        <v>5.2</v>
       </c>
       <c r="N90">
+        <v>6.6</v>
+      </c>
+      <c r="O90">
+        <v>1.28</v>
+      </c>
+      <c r="P90">
+        <v>27</v>
+      </c>
+      <c r="Q90">
         <v>3.35</v>
       </c>
-      <c r="O90">
-        <v>1.57</v>
-      </c>
-      <c r="P90">
-        <v>0</v>
-      </c>
-      <c r="Q90">
-        <v>2.5</v>
-      </c>
       <c r="R90">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="S90">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="T90">
-        <v>2.33</v>
+        <v>1.96</v>
       </c>
       <c r="U90">
-        <v>1.52</v>
+        <v>1.75</v>
       </c>
       <c r="V90">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="W90">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="X90">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y90">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="Z90">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AA90">
-        <v>4.25</v>
+        <v>5.5</v>
       </c>
       <c r="AB90">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="AC90">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="AD90">
-        <v>2.38</v>
+        <v>2.04</v>
       </c>
       <c r="AE90">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AF90">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AG90">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AH90">
-        <v>4</v>
+        <v>3.14</v>
       </c>
       <c r="AI90">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AJ90" t="s">
         <v>303</v>
@@ -11740,7 +11740,7 @@
         <v>64</v>
       </c>
       <c r="C91" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D91" t="s">
         <v>94</v>
@@ -11767,76 +11767,76 @@
         <v>301</v>
       </c>
       <c r="L91">
-        <v>1.24</v>
+        <v>2.47</v>
       </c>
       <c r="M91">
-        <v>7</v>
+        <v>3.07</v>
       </c>
       <c r="N91">
-        <v>6.6</v>
+        <v>2.57</v>
       </c>
       <c r="O91">
-        <v>1.28</v>
+        <v>2.05</v>
       </c>
       <c r="P91">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="Q91">
-        <v>3.35</v>
+        <v>1.83</v>
       </c>
       <c r="R91">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="S91">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="T91">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="U91">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="V91">
-        <v>4.3</v>
+        <v>6.5</v>
       </c>
       <c r="W91">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="X91">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y91">
-        <v>19</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Z91">
-        <v>1.1</v>
+        <v>1.21</v>
       </c>
       <c r="AA91">
-        <v>5.7</v>
+        <v>3.74</v>
       </c>
       <c r="AB91">
-        <v>1.42</v>
+        <v>1.8</v>
       </c>
       <c r="AC91">
-        <v>2.6</v>
+        <v>1.91</v>
       </c>
       <c r="AD91">
-        <v>2.1</v>
+        <v>2.74</v>
       </c>
       <c r="AE91">
-        <v>1.66</v>
+        <v>1.37</v>
       </c>
       <c r="AF91">
-        <v>1.88</v>
+        <v>1.57</v>
       </c>
       <c r="AG91">
-        <v>1.87</v>
+        <v>2.25</v>
       </c>
       <c r="AH91">
-        <v>3.5</v>
+        <v>4.95</v>
       </c>
       <c r="AI91">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AJ91" t="s">
         <v>303</v>
@@ -11856,7 +11856,7 @@
         <v>65</v>
       </c>
       <c r="C92" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D92" t="s">
         <v>94</v>
@@ -11972,7 +11972,7 @@
         <v>65</v>
       </c>
       <c r="C93" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D93" t="s">
         <v>94</v>
@@ -11999,76 +11999,76 @@
         <v>301</v>
       </c>
       <c r="L93">
-        <v>1.61</v>
+        <v>4</v>
       </c>
       <c r="M93">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="N93">
-        <v>4.6</v>
+        <v>2</v>
       </c>
       <c r="O93">
-        <v>1.33</v>
+        <v>2.65</v>
       </c>
       <c r="P93">
-        <v>14.75</v>
+        <v>6.5</v>
       </c>
       <c r="Q93">
-        <v>3.5</v>
+        <v>1.75</v>
       </c>
       <c r="R93">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="S93">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="T93">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="U93">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="V93">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="W93">
+        <v>1.05</v>
+      </c>
+      <c r="X93">
         <v>1.1</v>
       </c>
-      <c r="X93">
-        <v>1.02</v>
-      </c>
       <c r="Y93">
-        <v>10</v>
+        <v>6.5</v>
       </c>
       <c r="Z93">
-        <v>1.21</v>
+        <v>1.48</v>
       </c>
       <c r="AA93">
-        <v>3.9</v>
+        <v>2.65</v>
       </c>
       <c r="AB93">
-        <v>1.82</v>
+        <v>2.4</v>
       </c>
       <c r="AC93">
-        <v>1.94</v>
+        <v>1.55</v>
       </c>
       <c r="AD93">
-        <v>2.97</v>
+        <v>4.5</v>
       </c>
       <c r="AE93">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="AF93">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AG93">
-        <v>1.93</v>
+        <v>1.7</v>
       </c>
       <c r="AH93">
-        <v>5.4</v>
+        <v>9</v>
       </c>
       <c r="AI93">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AJ93" t="s">
         <v>303</v>
@@ -12088,7 +12088,7 @@
         <v>65</v>
       </c>
       <c r="C94" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="D94" t="s">
         <v>94</v>
@@ -12115,76 +12115,76 @@
         <v>301</v>
       </c>
       <c r="L94">
-        <v>4</v>
+        <v>2.53</v>
       </c>
       <c r="M94">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="N94">
+        <v>2.53</v>
+      </c>
+      <c r="O94">
+        <v>1.83</v>
+      </c>
+      <c r="P94">
+        <v>0</v>
+      </c>
+      <c r="Q94">
+        <v>2.1</v>
+      </c>
+      <c r="R94">
+        <v>1.36</v>
+      </c>
+      <c r="S94">
+        <v>2.95</v>
+      </c>
+      <c r="T94">
+        <v>2.8</v>
+      </c>
+      <c r="U94">
+        <v>1.37</v>
+      </c>
+      <c r="V94">
+        <v>7.2</v>
+      </c>
+      <c r="W94">
+        <v>1.08</v>
+      </c>
+      <c r="X94">
+        <v>1.02</v>
+      </c>
+      <c r="Y94">
+        <v>10</v>
+      </c>
+      <c r="Z94">
+        <v>1.24</v>
+      </c>
+      <c r="AA94">
+        <v>3.42</v>
+      </c>
+      <c r="AB94">
+        <v>1.92</v>
+      </c>
+      <c r="AC94">
+        <v>1.85</v>
+      </c>
+      <c r="AD94">
+        <v>3.24</v>
+      </c>
+      <c r="AE94">
+        <v>1.32</v>
+      </c>
+      <c r="AF94">
+        <v>1.73</v>
+      </c>
+      <c r="AG94">
         <v>2</v>
       </c>
-      <c r="O94">
-        <v>2.65</v>
-      </c>
-      <c r="P94">
-        <v>6.5</v>
-      </c>
-      <c r="Q94">
-        <v>1.75</v>
-      </c>
-      <c r="R94">
-        <v>1.5</v>
-      </c>
-      <c r="S94">
-        <v>2.4</v>
-      </c>
-      <c r="T94">
-        <v>3.2</v>
-      </c>
-      <c r="U94">
-        <v>1.3</v>
-      </c>
-      <c r="V94">
-        <v>8</v>
-      </c>
-      <c r="W94">
-        <v>1.05</v>
-      </c>
-      <c r="X94">
-        <v>1.1</v>
-      </c>
-      <c r="Y94">
-        <v>6.5</v>
-      </c>
-      <c r="Z94">
-        <v>1.48</v>
-      </c>
-      <c r="AA94">
-        <v>2.65</v>
-      </c>
-      <c r="AB94">
-        <v>2.4</v>
-      </c>
-      <c r="AC94">
-        <v>1.55</v>
-      </c>
-      <c r="AD94">
-        <v>4.5</v>
-      </c>
-      <c r="AE94">
-        <v>1.2</v>
-      </c>
-      <c r="AF94">
-        <v>2.05</v>
-      </c>
-      <c r="AG94">
-        <v>1.7</v>
-      </c>
       <c r="AH94">
-        <v>9</v>
+        <v>5.8</v>
       </c>
       <c r="AI94">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AJ94" t="s">
         <v>303</v>
@@ -12231,37 +12231,37 @@
         <v>301</v>
       </c>
       <c r="L95">
-        <v>2.5</v>
+        <v>1.85</v>
       </c>
       <c r="M95">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N95">
-        <v>2.5</v>
+        <v>3.9</v>
       </c>
       <c r="O95">
-        <v>1.83</v>
+        <v>1.33</v>
       </c>
       <c r="P95">
-        <v>0</v>
+        <v>14.75</v>
       </c>
       <c r="Q95">
-        <v>2.1</v>
+        <v>3.5</v>
       </c>
       <c r="R95">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="S95">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="T95">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="U95">
         <v>1.42</v>
       </c>
       <c r="V95">
-        <v>7.2</v>
+        <v>5.5</v>
       </c>
       <c r="W95">
         <v>1.03</v>
@@ -12273,34 +12273,34 @@
         <v>10</v>
       </c>
       <c r="Z95">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AA95">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="AB95">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC95">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AD95">
-        <v>3.24</v>
+        <v>3.14</v>
       </c>
       <c r="AE95">
         <v>1.32</v>
       </c>
       <c r="AF95">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AG95">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AH95">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="AI95">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AJ95" t="s">
         <v>303</v>
@@ -12347,22 +12347,22 @@
         <v>301</v>
       </c>
       <c r="L96">
-        <v>2.34</v>
+        <v>2.15</v>
       </c>
       <c r="M96">
-        <v>3.07</v>
+        <v>3.2</v>
       </c>
       <c r="N96">
-        <v>2.73</v>
+        <v>2.93</v>
       </c>
       <c r="O96">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="P96">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="Q96">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="R96">
         <v>1.3</v>
@@ -12371,10 +12371,10 @@
         <v>3.4</v>
       </c>
       <c r="T96">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="U96">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="V96">
         <v>6</v>
@@ -12383,40 +12383,40 @@
         <v>1.13</v>
       </c>
       <c r="X96">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y96">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="Z96">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AA96">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="AB96">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AC96">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AD96">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="AE96">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AF96">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG96">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AH96">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AI96">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AJ96" t="s">
         <v>303</v>
@@ -12811,22 +12811,22 @@
         <v>301</v>
       </c>
       <c r="L100">
-        <v>2.15</v>
+        <v>2.34</v>
       </c>
       <c r="M100">
-        <v>3.2</v>
+        <v>3.07</v>
       </c>
       <c r="N100">
-        <v>2.93</v>
+        <v>2.73</v>
       </c>
       <c r="O100">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="P100">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="Q100">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="R100">
         <v>1.3</v>
@@ -12835,10 +12835,10 @@
         <v>3.4</v>
       </c>
       <c r="T100">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="U100">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="V100">
         <v>6</v>
@@ -12847,40 +12847,40 @@
         <v>1.13</v>
       </c>
       <c r="X100">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y100">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="Z100">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AA100">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="AB100">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AC100">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AD100">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="AE100">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AF100">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG100">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AH100">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AI100">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AJ100" t="s">
         <v>303</v>
@@ -13043,13 +13043,13 @@
         <v>301</v>
       </c>
       <c r="L102">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="M102">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="N102">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="O102">
         <v>1.44</v>
@@ -13064,16 +13064,16 @@
         <v>1.33</v>
       </c>
       <c r="S102">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="T102">
-        <v>2.83</v>
+        <v>2.63</v>
       </c>
       <c r="U102">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="V102">
-        <v>6.8</v>
+        <v>7.1</v>
       </c>
       <c r="W102">
         <v>1.1</v>
@@ -13091,22 +13091,22 @@
         <v>3.5</v>
       </c>
       <c r="AB102">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AC102">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AD102">
         <v>3.3</v>
       </c>
       <c r="AE102">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AF102">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AG102">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AH102">
         <v>6</v>
@@ -13275,76 +13275,76 @@
         <v>301</v>
       </c>
       <c r="L104">
-        <v>2.4</v>
+        <v>1.79</v>
       </c>
       <c r="M104">
-        <v>3.1</v>
+        <v>3.32</v>
       </c>
       <c r="N104">
-        <v>2.63</v>
+        <v>3.87</v>
       </c>
       <c r="O104">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="P104">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="Q104">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="R104">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S104">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="T104">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U104">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="V104">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="W104">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X104">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y104">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Z104">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AA104">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AB104">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AC104">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="AD104">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AE104">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AF104">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AG104">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AH104">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AI104">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AJ104" t="s">
         <v>303</v>
@@ -13391,76 +13391,76 @@
         <v>301</v>
       </c>
       <c r="L105">
-        <v>1.79</v>
+        <v>2.4</v>
       </c>
       <c r="M105">
-        <v>3.32</v>
+        <v>3.1</v>
       </c>
       <c r="N105">
-        <v>3.87</v>
+        <v>2.63</v>
       </c>
       <c r="O105">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="P105">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Q105">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R105">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S105">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T105">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U105">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V105">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="W105">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X105">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y105">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z105">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AA105">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB105">
+        <v>1.45</v>
+      </c>
+      <c r="AC105">
+        <v>2.55</v>
+      </c>
+      <c r="AD105">
+        <v>2.15</v>
+      </c>
+      <c r="AE105">
+        <v>1.65</v>
+      </c>
+      <c r="AF105">
         <v>1.4</v>
       </c>
-      <c r="AC105">
+      <c r="AG105">
         <v>2.75</v>
       </c>
-      <c r="AD105">
-        <v>1.95</v>
-      </c>
-      <c r="AE105">
-        <v>1.75</v>
-      </c>
-      <c r="AF105">
-        <v>0</v>
-      </c>
-      <c r="AG105">
-        <v>0</v>
-      </c>
       <c r="AH105">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AI105">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AJ105" t="s">
         <v>303</v>

--- a/jogos_2025-07-19.xlsx
+++ b/jogos_2025-07-19.xlsx
@@ -232,30 +232,30 @@
     <t>Australia New South Wales NPL</t>
   </si>
   <si>
+    <t>South Korea K League 1</t>
+  </si>
+  <si>
     <t>South Korea K League 2</t>
   </si>
   <si>
-    <t>South Korea K League 1</t>
+    <t>China China League One</t>
   </si>
   <si>
     <t>Japan J1 League</t>
   </si>
   <si>
-    <t>China China League One</t>
-  </si>
-  <si>
     <t>China Chinese Super League</t>
   </si>
   <si>
     <t>Norway Eliteserien</t>
   </si>
   <si>
+    <t>Sweden Superettan</t>
+  </si>
+  <si>
     <t>Kazakhstan Kazakhstan Premier League</t>
   </si>
   <si>
-    <t>Sweden Superettan</t>
-  </si>
-  <si>
     <t>Sweden Allsvenskan</t>
   </si>
   <si>
@@ -280,18 +280,18 @@
     <t>Argentina Prim B Nacional</t>
   </si>
   <si>
+    <t>Brazil Serie B</t>
+  </si>
+  <si>
     <t>Brazil Serie A</t>
   </si>
   <si>
-    <t>Brazil Serie B</t>
+    <t>Brazil Serie C</t>
   </si>
   <si>
     <t>USA USL Championship</t>
   </si>
   <si>
-    <t>Brazil Serie C</t>
-  </si>
-  <si>
     <t>Canada Canadian Premier League</t>
   </si>
   <si>
@@ -316,45 +316,45 @@
     <t>Sutherland Sharks</t>
   </si>
   <si>
+    <t>Pohang Steelers</t>
+  </si>
+  <si>
+    <t>Gangwon</t>
+  </si>
+  <si>
+    <t>Seoul E-Land</t>
+  </si>
+  <si>
+    <t>Hwaseong</t>
+  </si>
+  <si>
+    <t>Yanbian Longding</t>
+  </si>
+  <si>
+    <t>Gimpo Citizen</t>
+  </si>
+  <si>
+    <t>Shonan Bellmare</t>
+  </si>
+  <si>
+    <t>Jeju United</t>
+  </si>
+  <si>
     <t>Jeonnam Dragons</t>
   </si>
   <si>
-    <t>Jeju United</t>
-  </si>
-  <si>
-    <t>Hwaseong</t>
-  </si>
-  <si>
-    <t>Gimpo Citizen</t>
-  </si>
-  <si>
-    <t>Gangwon</t>
-  </si>
-  <si>
-    <t>Pohang Steelers</t>
-  </si>
-  <si>
-    <t>Shonan Bellmare</t>
-  </si>
-  <si>
-    <t>Yanbian Longding</t>
-  </si>
-  <si>
-    <t>Seoul E-Land</t>
-  </si>
-  <si>
     <t>Tokyo</t>
   </si>
   <si>
+    <t>Dalian Zhixing</t>
+  </si>
+  <si>
+    <t>Shenyang Urban</t>
+  </si>
+  <si>
     <t>Suzhou Dongwu</t>
   </si>
   <si>
-    <t>Shenyang Urban</t>
-  </si>
-  <si>
-    <t>Dalian Zhixing</t>
-  </si>
-  <si>
     <t>Hebei Kungfu</t>
   </si>
   <si>
@@ -364,39 +364,39 @@
     <t>Beijing Guoan</t>
   </si>
   <si>
+    <t>Henan Jianye</t>
+  </si>
+  <si>
     <t>KFUM</t>
   </si>
   <si>
-    <t>Henan Jianye</t>
+    <t>Oddevold</t>
+  </si>
+  <si>
+    <t>Umeå</t>
+  </si>
+  <si>
+    <t>Kairat</t>
+  </si>
+  <si>
+    <t>Djurgården</t>
   </si>
   <si>
     <t>Yelimay Semey</t>
   </si>
   <si>
-    <t>Oddevold</t>
-  </si>
-  <si>
-    <t>Kairat</t>
-  </si>
-  <si>
     <t>Öster</t>
   </si>
   <si>
-    <t>Umeå</t>
-  </si>
-  <si>
     <t>Östersunds FK</t>
   </si>
   <si>
-    <t>Djurgården</t>
+    <t>VPS</t>
   </si>
   <si>
     <t>Molde</t>
   </si>
   <si>
-    <t>VPS</t>
-  </si>
-  <si>
     <t>Breidablik</t>
   </si>
   <si>
@@ -412,12 +412,12 @@
     <t>Harju Jalgpallikool</t>
   </si>
   <si>
+    <t>Viking</t>
+  </si>
+  <si>
     <t>Tallinna FC Levadia</t>
   </si>
   <si>
-    <t>Viking</t>
-  </si>
-  <si>
     <t>Unión Española</t>
   </si>
   <si>
@@ -427,99 +427,99 @@
     <t>San Lorenzo</t>
   </si>
   <si>
+    <t>Club Atlético Mitre</t>
+  </si>
+  <si>
     <t>Talleres Remedios</t>
   </si>
   <si>
-    <t>Club Atlético Mitre</t>
+    <t>Deportes Santa Cruz</t>
+  </si>
+  <si>
+    <t>Goiás</t>
+  </si>
+  <si>
+    <t>Colo-Colo</t>
   </si>
   <si>
     <t>Fortaleza</t>
   </si>
   <si>
-    <t>Deportes Santa Cruz</t>
-  </si>
-  <si>
-    <t>Colo-Colo</t>
-  </si>
-  <si>
-    <t>Goiás</t>
-  </si>
-  <si>
     <t>Lanús</t>
   </si>
   <si>
+    <t>Deportivo Morón</t>
+  </si>
+  <si>
+    <t>Tristán Suárez</t>
+  </si>
+  <si>
+    <t>Deportivo Madryn</t>
+  </si>
+  <si>
     <t>All Boys</t>
   </si>
   <si>
+    <t>Ituano</t>
+  </si>
+  <si>
+    <t>Deportivo Maipú</t>
+  </si>
+  <si>
+    <t>ABC</t>
+  </si>
+  <si>
+    <t>Rhode Island</t>
+  </si>
+  <si>
+    <t>Temperley</t>
+  </si>
+  <si>
+    <t>Colón</t>
+  </si>
+  <si>
     <t>Chaco For Ever</t>
   </si>
   <si>
-    <t>Rhode Island</t>
-  </si>
-  <si>
-    <t>ABC</t>
-  </si>
-  <si>
-    <t>Ituano</t>
-  </si>
-  <si>
-    <t>Deportivo Maipú</t>
+    <t>Estudiantes Río Cuarto</t>
+  </si>
+  <si>
+    <t>Arsenal de Sarandí</t>
+  </si>
+  <si>
+    <t>York9 FC</t>
+  </si>
+  <si>
+    <t>Gimnasia y Tiro</t>
+  </si>
+  <si>
+    <t>Alvarado</t>
+  </si>
+  <si>
+    <t>Defensores Unidos</t>
   </si>
   <si>
     <t>Colegiales</t>
   </si>
   <si>
-    <t>York9 FC</t>
-  </si>
-  <si>
-    <t>Arsenal de Sarandí</t>
-  </si>
-  <si>
-    <t>Colón</t>
-  </si>
-  <si>
-    <t>Estudiantes Río Cuarto</t>
-  </si>
-  <si>
-    <t>Tristán Suárez</t>
+    <t>Estudiantes Caseros</t>
   </si>
   <si>
     <t>Atlanta</t>
   </si>
   <si>
-    <t>Estudiantes Caseros</t>
-  </si>
-  <si>
-    <t>Gimnasia y Tiro</t>
-  </si>
-  <si>
-    <t>Temperley</t>
-  </si>
-  <si>
-    <t>Alvarado</t>
-  </si>
-  <si>
-    <t>Defensores Unidos</t>
-  </si>
-  <si>
-    <t>Deportivo Madryn</t>
-  </si>
-  <si>
-    <t>Deportivo Morón</t>
-  </si>
-  <si>
     <t>Vasco da Gama</t>
   </si>
   <si>
+    <t>Coritiba</t>
+  </si>
+  <si>
+    <t>Mirassol</t>
+  </si>
+  <si>
     <t>Avaí</t>
   </si>
   <si>
-    <t>Coritiba</t>
-  </si>
-  <si>
-    <t>Mirassol</t>
-  </si>
-  <si>
     <t>Coquimbo Unido</t>
   </si>
   <si>
@@ -529,10 +529,16 @@
     <t>Godoy Cruz</t>
   </si>
   <si>
+    <t>Londrina</t>
+  </si>
+  <si>
     <t>Ponte Preta</t>
   </si>
   <si>
-    <t>Londrina</t>
+    <t>Chattanooga FC</t>
+  </si>
+  <si>
+    <t>Concepción</t>
   </si>
   <si>
     <t>Crown Legacy</t>
@@ -541,60 +547,54 @@
     <t>Loudoun United</t>
   </si>
   <si>
-    <t>Concepción</t>
-  </si>
-  <si>
-    <t>Chattanooga FC</t>
+    <t>New York RB</t>
+  </si>
+  <si>
+    <t>Charleston Battery</t>
+  </si>
+  <si>
+    <t>Atlanta United FC</t>
+  </si>
+  <si>
+    <t>Volta Redonda</t>
   </si>
   <si>
     <t>Columbus Crew</t>
   </si>
   <si>
+    <t>Montreal Impact</t>
+  </si>
+  <si>
+    <t>New England Revolution</t>
+  </si>
+  <si>
     <t>Carolina Core</t>
   </si>
   <si>
-    <t>Atlanta United FC</t>
-  </si>
-  <si>
-    <t>New York RB</t>
-  </si>
-  <si>
-    <t>Montreal Impact</t>
-  </si>
-  <si>
-    <t>Volta Redonda</t>
-  </si>
-  <si>
-    <t>Charleston Battery</t>
-  </si>
-  <si>
-    <t>New England Revolution</t>
-  </si>
-  <si>
     <t>São Paulo</t>
   </si>
   <si>
+    <t>Birmingham Legion</t>
+  </si>
+  <si>
     <t>Instituto</t>
   </si>
   <si>
-    <t>Birmingham Legion</t>
-  </si>
-  <si>
     <t>Louisville City</t>
   </si>
   <si>
+    <t>Sporting KC</t>
+  </si>
+  <si>
     <t>FC Dallas</t>
   </si>
   <si>
+    <t>Seattle Sounders</t>
+  </si>
+  <si>
     <t>Nashville SC</t>
   </si>
   <si>
-    <t>Sporting KC</t>
-  </si>
-  <si>
-    <t>Seattle Sounders</t>
-  </si>
-  <si>
     <t>Houston Dynamo</t>
   </si>
   <si>
@@ -604,15 +604,15 @@
     <t>Orange County SC</t>
   </si>
   <si>
+    <t>San Diego</t>
+  </si>
+  <si>
+    <t>Portland Timbers</t>
+  </si>
+  <si>
     <t>Los Angeles FC</t>
   </si>
   <si>
-    <t>San Diego</t>
-  </si>
-  <si>
-    <t>Portland Timbers</t>
-  </si>
-  <si>
     <t>Minnesota United II</t>
   </si>
   <si>
@@ -628,45 +628,45 @@
     <t>Blacktown City</t>
   </si>
   <si>
+    <t>Jeonbuk Motors</t>
+  </si>
+  <si>
+    <t>Daejeon Citizen</t>
+  </si>
+  <si>
+    <t>Seongnam</t>
+  </si>
+  <si>
+    <t>Busan I'Park</t>
+  </si>
+  <si>
+    <t>Qingdao Red Lions</t>
+  </si>
+  <si>
+    <t>Ansan Greeners</t>
+  </si>
+  <si>
+    <t>Cerezo Osaka</t>
+  </si>
+  <si>
+    <t>Anyang</t>
+  </si>
+  <si>
     <t>Suwon Bluewings</t>
   </si>
   <si>
-    <t>Anyang</t>
-  </si>
-  <si>
-    <t>Busan I'Park</t>
-  </si>
-  <si>
-    <t>Ansan Greeners</t>
-  </si>
-  <si>
-    <t>Daejeon Citizen</t>
-  </si>
-  <si>
-    <t>Jeonbuk Motors</t>
-  </si>
-  <si>
-    <t>Cerezo Osaka</t>
-  </si>
-  <si>
-    <t>Qingdao Red Lions</t>
-  </si>
-  <si>
-    <t>Seongnam</t>
-  </si>
-  <si>
     <t>Urawa Reds</t>
   </si>
   <si>
+    <t>Shandong Luneng</t>
+  </si>
+  <si>
+    <t>Chongqing Tongliang Long</t>
+  </si>
+  <si>
     <t>Dongguan United</t>
   </si>
   <si>
-    <t>Chongqing Tongliang Long</t>
-  </si>
-  <si>
-    <t>Shandong Luneng</t>
-  </si>
-  <si>
     <t>Nantong Zhiyun</t>
   </si>
   <si>
@@ -676,39 +676,39 @@
     <t>Shanghai Shenhua</t>
   </si>
   <si>
+    <t>Meizhou Hakka</t>
+  </si>
+  <si>
     <t>Brann</t>
   </si>
   <si>
-    <t>Meizhou Hakka</t>
+    <t>Örgryte</t>
+  </si>
+  <si>
+    <t>Örebro</t>
+  </si>
+  <si>
+    <t>Kaisar</t>
+  </si>
+  <si>
+    <t>Elfsborg</t>
   </si>
   <si>
     <t>Zhenys</t>
   </si>
   <si>
-    <t>Örgryte</t>
-  </si>
-  <si>
-    <t>Kaisar</t>
-  </si>
-  <si>
     <t>Malmö FF</t>
   </si>
   <si>
-    <t>Örebro</t>
-  </si>
-  <si>
     <t>Falkenberg</t>
   </si>
   <si>
-    <t>Elfsborg</t>
+    <t>KuPS</t>
   </si>
   <si>
     <t>Strømsgodset</t>
   </si>
   <si>
-    <t>KuPS</t>
-  </si>
-  <si>
     <t>Vestri</t>
   </si>
   <si>
@@ -733,99 +733,99 @@
     <t>Gimnasia La Plata</t>
   </si>
   <si>
+    <t>Central Norte</t>
+  </si>
+  <si>
     <t>Defensores de Belgrano</t>
   </si>
   <si>
-    <t>Central Norte</t>
+    <t>Recoleta</t>
+  </si>
+  <si>
+    <t>Cuiabá</t>
+  </si>
+  <si>
+    <t>La Serena</t>
   </si>
   <si>
     <t>Bahia</t>
   </si>
   <si>
-    <t>Recoleta</t>
-  </si>
-  <si>
-    <t>La Serena</t>
-  </si>
-  <si>
-    <t>Cuiabá</t>
-  </si>
-  <si>
     <t>Rosario Central</t>
   </si>
   <si>
+    <t>Chacarita Juniors</t>
+  </si>
+  <si>
+    <t>Los Andes</t>
+  </si>
+  <si>
+    <t>Patronato</t>
+  </si>
+  <si>
     <t>Almagro</t>
   </si>
   <si>
+    <t>Botafogo PB</t>
+  </si>
+  <si>
+    <t>Club Atlético Güemes</t>
+  </si>
+  <si>
+    <t>Maringá</t>
+  </si>
+  <si>
+    <t>Hartford Athletic</t>
+  </si>
+  <si>
+    <t>Gimnasia Jujuy</t>
+  </si>
+  <si>
+    <t>Gimnasia Mendoza</t>
+  </si>
+  <si>
     <t>Almirante Brown</t>
   </si>
   <si>
-    <t>Hartford Athletic</t>
-  </si>
-  <si>
-    <t>Maringá</t>
-  </si>
-  <si>
-    <t>Botafogo PB</t>
-  </si>
-  <si>
-    <t>Club Atlético Güemes</t>
+    <t>Nueva Chicago</t>
+  </si>
+  <si>
+    <t>San Miguel</t>
+  </si>
+  <si>
+    <t>Vancouver FC</t>
+  </si>
+  <si>
+    <t>San Martín Tucumán</t>
+  </si>
+  <si>
+    <t>Ferro Carril Oeste</t>
+  </si>
+  <si>
+    <t>Agropecuario</t>
   </si>
   <si>
     <t>Quilmes</t>
   </si>
   <si>
-    <t>Vancouver FC</t>
-  </si>
-  <si>
-    <t>San Miguel</t>
-  </si>
-  <si>
-    <t>Gimnasia Mendoza</t>
-  </si>
-  <si>
-    <t>Nueva Chicago</t>
-  </si>
-  <si>
-    <t>Los Andes</t>
+    <t>San Telmo</t>
   </si>
   <si>
     <t>Racing Córdoba</t>
   </si>
   <si>
-    <t>San Telmo</t>
-  </si>
-  <si>
-    <t>San Martín Tucumán</t>
-  </si>
-  <si>
-    <t>Gimnasia Jujuy</t>
-  </si>
-  <si>
-    <t>Ferro Carril Oeste</t>
-  </si>
-  <si>
-    <t>Agropecuario</t>
-  </si>
-  <si>
-    <t>Patronato</t>
-  </si>
-  <si>
-    <t>Chacarita Juniors</t>
-  </si>
-  <si>
     <t>Grêmio</t>
   </si>
   <si>
+    <t>Paysandu</t>
+  </si>
+  <si>
+    <t>Santos</t>
+  </si>
+  <si>
     <t>Vila Nova</t>
   </si>
   <si>
-    <t>Paysandu</t>
-  </si>
-  <si>
-    <t>Santos</t>
-  </si>
-  <si>
     <t>Deportes Iquique</t>
   </si>
   <si>
@@ -835,10 +835,16 @@
     <t>Sarmiento</t>
   </si>
   <si>
+    <t>Itabaiana</t>
+  </si>
+  <si>
     <t>Floresta</t>
   </si>
   <si>
-    <t>Itabaiana</t>
+    <t>Inter Miami II</t>
+  </si>
+  <si>
+    <t>Antofagasta</t>
   </si>
   <si>
     <t>Philadelphia Union II</t>
@@ -847,60 +853,54 @@
     <t>Oakland Roots</t>
   </si>
   <si>
-    <t>Antofagasta</t>
-  </si>
-  <si>
-    <t>Inter Miami II</t>
+    <t>Inter Miami</t>
+  </si>
+  <si>
+    <t>Miami FC II</t>
+  </si>
+  <si>
+    <t>Charlotte</t>
+  </si>
+  <si>
+    <t>Atlético PR</t>
   </si>
   <si>
     <t>DC United</t>
   </si>
   <si>
+    <t>Chicago Fire</t>
+  </si>
+  <si>
+    <t>Orlando City</t>
+  </si>
+  <si>
     <t>Atlanta United II</t>
   </si>
   <si>
-    <t>Charlotte</t>
-  </si>
-  <si>
-    <t>Inter Miami</t>
-  </si>
-  <si>
-    <t>Chicago Fire</t>
-  </si>
-  <si>
-    <t>Atlético PR</t>
-  </si>
-  <si>
-    <t>Miami FC II</t>
-  </si>
-  <si>
-    <t>Orlando City</t>
-  </si>
-  <si>
     <t>Corinthians</t>
   </si>
   <si>
+    <t>Colorado Springs</t>
+  </si>
+  <si>
     <t>River Plate</t>
   </si>
   <si>
-    <t>Colorado Springs</t>
-  </si>
-  <si>
     <t>Tulsa Roughnecks</t>
   </si>
   <si>
+    <t>New York City</t>
+  </si>
+  <si>
     <t>St. Louis City</t>
   </si>
   <si>
+    <t>SJ Earthquakes</t>
+  </si>
+  <si>
     <t>Toronto</t>
   </si>
   <si>
-    <t>New York City</t>
-  </si>
-  <si>
-    <t>SJ Earthquakes</t>
-  </si>
-  <si>
     <t>Philadelphia Union</t>
   </si>
   <si>
@@ -910,13 +910,13 @@
     <t>Las Vegas Lights</t>
   </si>
   <si>
+    <t>Vancouver Whitecaps</t>
+  </si>
+  <si>
+    <t>Minnesota United</t>
+  </si>
+  <si>
     <t>LA Galaxy</t>
-  </si>
-  <si>
-    <t>Vancouver Whitecaps</t>
-  </si>
-  <si>
-    <t>Minnesota United</t>
   </si>
   <si>
     <t>incomplete</t>
@@ -1467,10 +1467,10 @@
         <v>3.3</v>
       </c>
       <c r="T2">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="U2">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="V2">
         <v>5</v>
@@ -1485,7 +1485,7 @@
         <v>0</v>
       </c>
       <c r="Z2">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AA2">
         <v>5.3</v>
@@ -1494,25 +1494,25 @@
         <v>1.55</v>
       </c>
       <c r="AC2">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="AD2">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AE2">
         <v>1.55</v>
       </c>
       <c r="AF2">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AG2">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AH2">
-        <v>3.25</v>
+        <v>3.98</v>
       </c>
       <c r="AI2">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AJ2" t="s">
         <v>303</v>
@@ -1559,13 +1559,13 @@
         <v>301</v>
       </c>
       <c r="L3">
-        <v>3.3</v>
+        <v>2.02</v>
       </c>
       <c r="M3">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="N3">
-        <v>1.91</v>
+        <v>2.75</v>
       </c>
       <c r="O3">
         <v>2</v>
@@ -1577,58 +1577,58 @@
         <v>1.8</v>
       </c>
       <c r="R3">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="S3">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="T3">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="U3">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="V3">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="W3">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X3">
         <v>1.02</v>
       </c>
       <c r="Y3">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Z3">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AA3">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="AB3">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AC3">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="AD3">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AE3">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AF3">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="AG3">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="AH3">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="AI3">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AJ3" t="s">
         <v>303</v>
@@ -1693,58 +1693,58 @@
         <v>2.25</v>
       </c>
       <c r="R4">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S4">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="T4">
         <v>2.46</v>
       </c>
       <c r="U4">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="V4">
-        <v>5.7</v>
+        <v>5.75</v>
       </c>
       <c r="W4">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X4">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y4">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Z4">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AA4">
-        <v>4</v>
+        <v>3.94</v>
       </c>
       <c r="AB4">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AC4">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AD4">
         <v>2.62</v>
       </c>
       <c r="AE4">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AF4">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AG4">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH4">
         <v>4.8</v>
       </c>
       <c r="AI4">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AJ4" t="s">
         <v>303</v>
@@ -1791,13 +1791,13 @@
         <v>301</v>
       </c>
       <c r="L5">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="M5">
-        <v>3.79</v>
+        <v>4</v>
       </c>
       <c r="N5">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="O5">
         <v>2.3</v>
@@ -1839,10 +1839,10 @@
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AC5">
-        <v>2.35</v>
+        <v>2.17</v>
       </c>
       <c r="AD5">
         <v>0</v>
@@ -1907,13 +1907,13 @@
         <v>301</v>
       </c>
       <c r="L6">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="M6">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="N6">
-        <v>1.66</v>
+        <v>1.46</v>
       </c>
       <c r="O6">
         <v>1.33</v>
@@ -1931,10 +1931,10 @@
         <v>3.2</v>
       </c>
       <c r="T6">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="U6">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="V6">
         <v>5.5</v>
@@ -1946,19 +1946,19 @@
         <v>1.03</v>
       </c>
       <c r="Y6">
-        <v>12.3</v>
+        <v>11</v>
       </c>
       <c r="Z6">
         <v>1.16</v>
       </c>
       <c r="AA6">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AB6">
         <v>1.65</v>
       </c>
       <c r="AC6">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="AD6">
         <v>2.59</v>
@@ -1973,7 +1973,7 @@
         <v>1.93</v>
       </c>
       <c r="AH6">
-        <v>4.85</v>
+        <v>4.75</v>
       </c>
       <c r="AI6">
         <v>1.11</v>
@@ -2023,76 +2023,76 @@
         <v>301</v>
       </c>
       <c r="L7">
-        <v>3.74</v>
+        <v>2.85</v>
       </c>
       <c r="M7">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="N7">
-        <v>1.77</v>
+        <v>2.3</v>
       </c>
       <c r="O7">
         <v>2.25</v>
       </c>
       <c r="P7">
-        <v>13.75</v>
+        <v>7</v>
       </c>
       <c r="Q7">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="R7">
+        <v>1.48</v>
+      </c>
+      <c r="S7">
+        <v>2.45</v>
+      </c>
+      <c r="T7">
+        <v>3.2</v>
+      </c>
+      <c r="U7">
         <v>1.3</v>
       </c>
-      <c r="S7">
-        <v>3.3</v>
-      </c>
-      <c r="T7">
-        <v>2.45</v>
-      </c>
-      <c r="U7">
-        <v>1.5</v>
-      </c>
       <c r="V7">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="W7">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X7">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="Y7">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="Z7">
-        <v>1.16</v>
+        <v>1.42</v>
       </c>
       <c r="AA7">
-        <v>4.05</v>
+        <v>2.8</v>
       </c>
       <c r="AB7">
-        <v>1.65</v>
+        <v>1.91</v>
       </c>
       <c r="AC7">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="AD7">
-        <v>2.69</v>
+        <v>4.2</v>
       </c>
       <c r="AE7">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AF7">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AG7">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AH7">
-        <v>5.15</v>
+        <v>8.5</v>
       </c>
       <c r="AI7">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AJ7" t="s">
         <v>303</v>
@@ -2112,7 +2112,7 @@
         <v>43</v>
       </c>
       <c r="C8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D8" t="s">
         <v>94</v>
@@ -2139,22 +2139,22 @@
         <v>301</v>
       </c>
       <c r="L8">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="M8">
-        <v>3.03</v>
+        <v>3.12</v>
       </c>
       <c r="N8">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="O8">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="P8">
         <v>8</v>
       </c>
       <c r="Q8">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="R8">
         <v>1.42</v>
@@ -2181,34 +2181,34 @@
         <v>8</v>
       </c>
       <c r="Z8">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AA8">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="AB8">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AC8">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="AD8">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="AE8">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AF8">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AG8">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AH8">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="AI8">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AJ8" t="s">
         <v>303</v>
@@ -2228,7 +2228,7 @@
         <v>43</v>
       </c>
       <c r="C9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D9" t="s">
         <v>94</v>
@@ -2255,76 +2255,76 @@
         <v>301</v>
       </c>
       <c r="L9">
-        <v>3.41</v>
+        <v>1.83</v>
       </c>
       <c r="M9">
-        <v>3.32</v>
+        <v>3.11</v>
       </c>
       <c r="N9">
-        <v>1.9</v>
+        <v>3.97</v>
       </c>
       <c r="O9">
-        <v>2.42</v>
+        <v>1.67</v>
       </c>
       <c r="P9">
-        <v>7.1</v>
+        <v>12</v>
       </c>
       <c r="Q9">
-        <v>1.78</v>
+        <v>2.31</v>
       </c>
       <c r="R9">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="S9">
-        <v>2.62</v>
+        <v>3.01</v>
       </c>
       <c r="T9">
-        <v>3.25</v>
+        <v>2.84</v>
       </c>
       <c r="U9">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="V9">
-        <v>10</v>
+        <v>6.5</v>
       </c>
       <c r="W9">
         <v>1.05</v>
       </c>
       <c r="X9">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>7.1</v>
+        <v>11</v>
       </c>
       <c r="Z9">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="AA9">
-        <v>2.52</v>
+        <v>3.6</v>
       </c>
       <c r="AB9">
-        <v>2.2</v>
+        <v>1.87</v>
       </c>
       <c r="AC9">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="AD9">
-        <v>4.3</v>
+        <v>3.2</v>
       </c>
       <c r="AE9">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AF9">
-        <v>2.05</v>
+        <v>1.67</v>
       </c>
       <c r="AG9">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="AH9">
-        <v>8.4</v>
+        <v>6.5</v>
       </c>
       <c r="AI9">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AJ9" t="s">
         <v>303</v>
@@ -2344,7 +2344,7 @@
         <v>43</v>
       </c>
       <c r="C10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D10" t="s">
         <v>94</v>
@@ -2371,76 +2371,76 @@
         <v>301</v>
       </c>
       <c r="L10">
-        <v>1.74</v>
+        <v>3.41</v>
       </c>
       <c r="M10">
-        <v>3.28</v>
+        <v>3.32</v>
       </c>
       <c r="N10">
-        <v>4.2</v>
+        <v>1.9</v>
       </c>
       <c r="O10">
+        <v>2.42</v>
+      </c>
+      <c r="P10">
+        <v>7.1</v>
+      </c>
+      <c r="Q10">
+        <v>1.78</v>
+      </c>
+      <c r="R10">
+        <v>1.44</v>
+      </c>
+      <c r="S10">
+        <v>2.62</v>
+      </c>
+      <c r="T10">
+        <v>3.25</v>
+      </c>
+      <c r="U10">
+        <v>1.3</v>
+      </c>
+      <c r="V10">
+        <v>10</v>
+      </c>
+      <c r="W10">
+        <v>1.05</v>
+      </c>
+      <c r="X10">
+        <v>1.04</v>
+      </c>
+      <c r="Y10">
+        <v>7.1</v>
+      </c>
+      <c r="Z10">
+        <v>1.41</v>
+      </c>
+      <c r="AA10">
+        <v>2.52</v>
+      </c>
+      <c r="AB10">
+        <v>2.2</v>
+      </c>
+      <c r="AC10">
         <v>1.53</v>
       </c>
-      <c r="P10">
-        <v>6.75</v>
-      </c>
-      <c r="Q10">
-        <v>3.18</v>
-      </c>
-      <c r="R10">
-        <v>1.48</v>
-      </c>
-      <c r="S10">
-        <v>2.56</v>
-      </c>
-      <c r="T10">
-        <v>3.34</v>
-      </c>
-      <c r="U10">
-        <v>1.28</v>
-      </c>
-      <c r="V10">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="W10">
-        <v>1.02</v>
-      </c>
-      <c r="X10">
-        <v>1.05</v>
-      </c>
-      <c r="Y10">
-        <v>8</v>
-      </c>
-      <c r="Z10">
-        <v>1.4</v>
-      </c>
-      <c r="AA10">
-        <v>2.75</v>
-      </c>
-      <c r="AB10">
-        <v>2.3</v>
-      </c>
-      <c r="AC10">
-        <v>1.5</v>
-      </c>
       <c r="AD10">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="AE10">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF10">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AG10">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AH10">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AI10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AJ10" t="s">
         <v>303</v>
@@ -2460,7 +2460,7 @@
         <v>43</v>
       </c>
       <c r="C11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D11" t="s">
         <v>94</v>
@@ -2487,76 +2487,76 @@
         <v>301</v>
       </c>
       <c r="L11">
-        <v>2.29</v>
+        <v>1.48</v>
       </c>
       <c r="M11">
-        <v>3.12</v>
+        <v>3.85</v>
       </c>
       <c r="N11">
-        <v>2.75</v>
+        <v>5.6</v>
       </c>
       <c r="O11">
-        <v>2</v>
+        <v>1.38</v>
       </c>
       <c r="P11">
-        <v>8</v>
+        <v>8.9</v>
       </c>
       <c r="Q11">
+        <v>3.58</v>
+      </c>
+      <c r="R11">
+        <v>1.35</v>
+      </c>
+      <c r="S11">
+        <v>2.85</v>
+      </c>
+      <c r="T11">
+        <v>2.65</v>
+      </c>
+      <c r="U11">
+        <v>1.4</v>
+      </c>
+      <c r="V11">
+        <v>7.3</v>
+      </c>
+      <c r="W11">
+        <v>1.05</v>
+      </c>
+      <c r="X11">
+        <v>1.03</v>
+      </c>
+      <c r="Y11">
+        <v>7.4</v>
+      </c>
+      <c r="Z11">
+        <v>1.29</v>
+      </c>
+      <c r="AA11">
+        <v>3.4</v>
+      </c>
+      <c r="AB11">
+        <v>1.88</v>
+      </c>
+      <c r="AC11">
+        <v>1.85</v>
+      </c>
+      <c r="AD11">
+        <v>3.6</v>
+      </c>
+      <c r="AE11">
+        <v>1.21</v>
+      </c>
+      <c r="AF11">
         <v>2.1</v>
       </c>
-      <c r="R11">
-        <v>1.42</v>
-      </c>
-      <c r="S11">
-        <v>2.65</v>
-      </c>
-      <c r="T11">
-        <v>2.88</v>
-      </c>
-      <c r="U11">
-        <v>1.36</v>
-      </c>
-      <c r="V11">
+      <c r="AG11">
+        <v>1.66</v>
+      </c>
+      <c r="AH11">
         <v>7</v>
       </c>
-      <c r="W11">
-        <v>1.08</v>
-      </c>
-      <c r="X11">
-        <v>1.07</v>
-      </c>
-      <c r="Y11">
-        <v>8</v>
-      </c>
-      <c r="Z11">
-        <v>1.33</v>
-      </c>
-      <c r="AA11">
-        <v>3.25</v>
-      </c>
-      <c r="AB11">
-        <v>1.93</v>
-      </c>
-      <c r="AC11">
-        <v>1.77</v>
-      </c>
-      <c r="AD11">
-        <v>3.45</v>
-      </c>
-      <c r="AE11">
-        <v>1.3</v>
-      </c>
-      <c r="AF11">
-        <v>1.7</v>
-      </c>
-      <c r="AG11">
-        <v>2</v>
-      </c>
-      <c r="AH11">
-        <v>6.5</v>
-      </c>
       <c r="AI11">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AJ11" t="s">
         <v>303</v>
@@ -2603,76 +2603,76 @@
         <v>301</v>
       </c>
       <c r="L12">
-        <v>2.85</v>
+        <v>1.74</v>
       </c>
       <c r="M12">
-        <v>3</v>
+        <v>3.28</v>
       </c>
       <c r="N12">
-        <v>2.3</v>
+        <v>4.2</v>
       </c>
       <c r="O12">
-        <v>2.25</v>
+        <v>1.53</v>
       </c>
       <c r="P12">
-        <v>7</v>
+        <v>6.75</v>
       </c>
       <c r="Q12">
-        <v>1.95</v>
+        <v>3.18</v>
       </c>
       <c r="R12">
         <v>1.48</v>
       </c>
       <c r="S12">
-        <v>2.45</v>
+        <v>2.56</v>
       </c>
       <c r="T12">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="U12">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="V12">
-        <v>7.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W12">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X12">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="Y12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z12">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AA12">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AB12">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="AC12">
-        <v>1.79</v>
+        <v>1.5</v>
       </c>
       <c r="AD12">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="AE12">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AF12">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AG12">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AH12">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="AI12">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AJ12" t="s">
         <v>303</v>
@@ -2692,7 +2692,7 @@
         <v>43</v>
       </c>
       <c r="C13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D13" t="s">
         <v>94</v>
@@ -2808,7 +2808,7 @@
         <v>43</v>
       </c>
       <c r="C14" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D14" t="s">
         <v>94</v>
@@ -2835,76 +2835,76 @@
         <v>301</v>
       </c>
       <c r="L14">
-        <v>1.66</v>
+        <v>2.32</v>
       </c>
       <c r="M14">
-        <v>3.55</v>
+        <v>3.03</v>
       </c>
       <c r="N14">
-        <v>5.4</v>
+        <v>2.79</v>
       </c>
       <c r="O14">
-        <v>1.38</v>
+        <v>1.91</v>
       </c>
       <c r="P14">
-        <v>8.9</v>
+        <v>8</v>
       </c>
       <c r="Q14">
-        <v>3.58</v>
+        <v>2.25</v>
       </c>
       <c r="R14">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S14">
-        <v>2.52</v>
+        <v>2.65</v>
       </c>
       <c r="T14">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="U14">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="V14">
-        <v>7.3</v>
+        <v>7</v>
       </c>
       <c r="W14">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X14">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y14">
         <v>8</v>
       </c>
       <c r="Z14">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AA14">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="AB14">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AC14">
         <v>1.65</v>
       </c>
       <c r="AD14">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AE14">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AF14">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="AG14">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AH14">
-        <v>5.3</v>
+        <v>7.5</v>
       </c>
       <c r="AI14">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AJ14" t="s">
         <v>303</v>
@@ -2924,7 +2924,7 @@
         <v>43</v>
       </c>
       <c r="C15" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D15" t="s">
         <v>94</v>
@@ -2951,40 +2951,40 @@
         <v>301</v>
       </c>
       <c r="L15">
-        <v>1.83</v>
+        <v>3.74</v>
       </c>
       <c r="M15">
-        <v>3.11</v>
+        <v>3.5</v>
       </c>
       <c r="N15">
-        <v>3.97</v>
+        <v>1.77</v>
       </c>
       <c r="O15">
+        <v>2.25</v>
+      </c>
+      <c r="P15">
+        <v>13.75</v>
+      </c>
+      <c r="Q15">
         <v>1.67</v>
       </c>
-      <c r="P15">
-        <v>12</v>
-      </c>
-      <c r="Q15">
-        <v>2.31</v>
-      </c>
       <c r="R15">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="S15">
-        <v>3.01</v>
+        <v>3.3</v>
       </c>
       <c r="T15">
-        <v>2.84</v>
+        <v>2.45</v>
       </c>
       <c r="U15">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="V15">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="W15">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="X15">
         <v>1.01</v>
@@ -2993,34 +2993,34 @@
         <v>11</v>
       </c>
       <c r="Z15">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AA15">
-        <v>3.6</v>
+        <v>4.05</v>
       </c>
       <c r="AB15">
-        <v>1.87</v>
+        <v>1.65</v>
       </c>
       <c r="AC15">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AD15">
-        <v>3.2</v>
+        <v>2.69</v>
       </c>
       <c r="AE15">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AF15">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG15">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AH15">
-        <v>6.5</v>
+        <v>5.15</v>
       </c>
       <c r="AI15">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AJ15" t="s">
         <v>303</v>
@@ -3040,7 +3040,7 @@
         <v>43</v>
       </c>
       <c r="C16" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D16" t="s">
         <v>94</v>
@@ -3156,7 +3156,7 @@
         <v>44</v>
       </c>
       <c r="C17" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D17" t="s">
         <v>94</v>
@@ -3183,76 +3183,76 @@
         <v>301</v>
       </c>
       <c r="L17">
-        <v>1.48</v>
+        <v>2.98</v>
       </c>
       <c r="M17">
-        <v>3.9</v>
+        <v>3.74</v>
       </c>
       <c r="N17">
-        <v>5.85</v>
+        <v>2.01</v>
       </c>
       <c r="O17">
+        <v>2.4</v>
+      </c>
+      <c r="P17">
+        <v>18.75</v>
+      </c>
+      <c r="Q17">
+        <v>1.57</v>
+      </c>
+      <c r="R17">
+        <v>1.25</v>
+      </c>
+      <c r="S17">
+        <v>3.75</v>
+      </c>
+      <c r="T17">
+        <v>2.25</v>
+      </c>
+      <c r="U17">
+        <v>1.57</v>
+      </c>
+      <c r="V17">
+        <v>5.5</v>
+      </c>
+      <c r="W17">
+        <v>1.14</v>
+      </c>
+      <c r="X17">
+        <v>1.01</v>
+      </c>
+      <c r="Y17">
+        <v>13</v>
+      </c>
+      <c r="Z17">
+        <v>1.1</v>
+      </c>
+      <c r="AA17">
+        <v>5</v>
+      </c>
+      <c r="AB17">
         <v>1.53</v>
       </c>
-      <c r="P17">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="Q17">
-        <v>2.88</v>
-      </c>
-      <c r="R17">
-        <v>1.39</v>
-      </c>
-      <c r="S17">
-        <v>2.5</v>
-      </c>
-      <c r="T17">
-        <v>3</v>
-      </c>
-      <c r="U17">
-        <v>1.32</v>
-      </c>
-      <c r="V17">
-        <v>7.9</v>
-      </c>
-      <c r="W17">
-        <v>1.05</v>
-      </c>
-      <c r="X17">
-        <v>1</v>
-      </c>
-      <c r="Y17">
-        <v>9</v>
-      </c>
-      <c r="Z17">
-        <v>1.33</v>
-      </c>
-      <c r="AA17">
-        <v>3.04</v>
-      </c>
-      <c r="AB17">
-        <v>2</v>
-      </c>
       <c r="AC17">
-        <v>1.73</v>
+        <v>2.25</v>
       </c>
       <c r="AD17">
-        <v>3.58</v>
+        <v>2.35</v>
       </c>
       <c r="AE17">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="AF17">
-        <v>1.97</v>
+        <v>1.53</v>
       </c>
       <c r="AG17">
-        <v>1.72</v>
+        <v>2.38</v>
       </c>
       <c r="AH17">
-        <v>7.4</v>
+        <v>4.05</v>
       </c>
       <c r="AI17">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="AJ17" t="s">
         <v>303</v>
@@ -3272,7 +3272,7 @@
         <v>44</v>
       </c>
       <c r="C18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D18" t="s">
         <v>94</v>
@@ -3299,13 +3299,13 @@
         <v>301</v>
       </c>
       <c r="L18">
-        <v>2.55</v>
+        <v>1.97</v>
       </c>
       <c r="M18">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="N18">
-        <v>2.84</v>
+        <v>3.3</v>
       </c>
       <c r="O18">
         <v>1.73</v>
@@ -3317,7 +3317,7 @@
         <v>2.25</v>
       </c>
       <c r="R18">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="S18">
         <v>2.65</v>
@@ -3335,10 +3335,10 @@
         <v>1.08</v>
       </c>
       <c r="X18">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y18">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z18">
         <v>1.27</v>
@@ -3347,13 +3347,13 @@
         <v>3.34</v>
       </c>
       <c r="AB18">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AC18">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AD18">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="AE18">
         <v>1.31</v>
@@ -3368,7 +3368,7 @@
         <v>5.55</v>
       </c>
       <c r="AI18">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AJ18" t="s">
         <v>303</v>
@@ -3388,7 +3388,7 @@
         <v>44</v>
       </c>
       <c r="C19" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D19" t="s">
         <v>94</v>
@@ -3415,76 +3415,76 @@
         <v>301</v>
       </c>
       <c r="L19">
-        <v>3.1</v>
+        <v>1.71</v>
       </c>
       <c r="M19">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="N19">
-        <v>2.09</v>
+        <v>4.3</v>
       </c>
       <c r="O19">
-        <v>2.4</v>
+        <v>1.53</v>
       </c>
       <c r="P19">
-        <v>18.75</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q19">
-        <v>1.57</v>
+        <v>2.88</v>
       </c>
       <c r="R19">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="S19">
-        <v>3.75</v>
+        <v>2.5</v>
       </c>
       <c r="T19">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="U19">
-        <v>1.57</v>
+        <v>1.32</v>
       </c>
       <c r="V19">
-        <v>5.5</v>
+        <v>7.9</v>
       </c>
       <c r="W19">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="X19">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y19">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="Z19">
-        <v>1.1</v>
+        <v>1.33</v>
       </c>
       <c r="AA19">
-        <v>5</v>
+        <v>3.04</v>
       </c>
       <c r="AB19">
-        <v>1.53</v>
+        <v>2</v>
       </c>
       <c r="AC19">
-        <v>2.25</v>
+        <v>1.72</v>
       </c>
       <c r="AD19">
-        <v>2.35</v>
+        <v>3.58</v>
       </c>
       <c r="AE19">
-        <v>1.57</v>
+        <v>1.22</v>
       </c>
       <c r="AF19">
-        <v>1.53</v>
+        <v>1.97</v>
       </c>
       <c r="AG19">
-        <v>2.38</v>
+        <v>1.72</v>
       </c>
       <c r="AH19">
-        <v>4.05</v>
+        <v>7.4</v>
       </c>
       <c r="AI19">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AJ19" t="s">
         <v>303</v>
@@ -3504,7 +3504,7 @@
         <v>45</v>
       </c>
       <c r="C20" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D20" t="s">
         <v>94</v>
@@ -3531,13 +3531,13 @@
         <v>301</v>
       </c>
       <c r="L20">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="M20">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="N20">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="O20">
         <v>1.73</v>
@@ -3558,13 +3558,13 @@
         <v>3.22</v>
       </c>
       <c r="U20">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="V20">
         <v>8</v>
       </c>
       <c r="W20">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X20">
         <v>1.04</v>
@@ -3576,7 +3576,7 @@
         <v>1.42</v>
       </c>
       <c r="AA20">
-        <v>2.62</v>
+        <v>3.1</v>
       </c>
       <c r="AB20">
         <v>2.25</v>
@@ -3588,16 +3588,16 @@
         <v>4.1</v>
       </c>
       <c r="AE20">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AF20">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AG20">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AH20">
-        <v>7.9</v>
+        <v>6.5</v>
       </c>
       <c r="AI20">
         <v>1.08</v>
@@ -3763,13 +3763,13 @@
         <v>301</v>
       </c>
       <c r="L22">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="M22">
-        <v>3.05</v>
+        <v>3.58</v>
       </c>
       <c r="N22">
-        <v>3</v>
+        <v>2.73</v>
       </c>
       <c r="O22">
         <v>1.83</v>
@@ -3811,10 +3811,10 @@
         <v>3.88</v>
       </c>
       <c r="AB22">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AC22">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AD22">
         <v>2.53</v>
@@ -3852,7 +3852,7 @@
         <v>47</v>
       </c>
       <c r="C23" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D23" t="s">
         <v>94</v>
@@ -3879,76 +3879,76 @@
         <v>301</v>
       </c>
       <c r="L23">
-        <v>2.88</v>
+        <v>1.44</v>
       </c>
       <c r="M23">
-        <v>3.11</v>
+        <v>4.5</v>
       </c>
       <c r="N23">
-        <v>2.22</v>
+        <v>5.3</v>
       </c>
       <c r="O23">
-        <v>2.15</v>
+        <v>1.33</v>
       </c>
       <c r="P23">
-        <v>8.5</v>
+        <v>22</v>
       </c>
       <c r="Q23">
-        <v>1.93</v>
+        <v>3.25</v>
       </c>
       <c r="R23">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="S23">
-        <v>2.7</v>
+        <v>4</v>
       </c>
       <c r="T23">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="U23">
-        <v>1.38</v>
+        <v>1.67</v>
       </c>
       <c r="V23">
-        <v>7.3</v>
+        <v>4.5</v>
       </c>
       <c r="W23">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="X23">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>8.5</v>
+        <v>17</v>
       </c>
       <c r="Z23">
-        <v>1.3</v>
+        <v>1.08</v>
       </c>
       <c r="AA23">
-        <v>3.45</v>
+        <v>5.55</v>
       </c>
       <c r="AB23">
-        <v>1.89</v>
+        <v>1.43</v>
       </c>
       <c r="AC23">
-        <v>1.81</v>
+        <v>2.62</v>
       </c>
       <c r="AD23">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="AE23">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="AF23">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG23">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AH23">
-        <v>6.25</v>
+        <v>3.44</v>
       </c>
       <c r="AI23">
-        <v>1.11</v>
+        <v>1.23</v>
       </c>
       <c r="AJ23" t="s">
         <v>303</v>
@@ -3968,7 +3968,7 @@
         <v>47</v>
       </c>
       <c r="C24" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D24" t="s">
         <v>94</v>
@@ -3995,76 +3995,76 @@
         <v>301</v>
       </c>
       <c r="L24">
-        <v>1.45</v>
+        <v>2.88</v>
       </c>
       <c r="M24">
-        <v>4.8</v>
+        <v>3.11</v>
       </c>
       <c r="N24">
-        <v>5.8</v>
+        <v>2.22</v>
       </c>
       <c r="O24">
+        <v>2.15</v>
+      </c>
+      <c r="P24">
+        <v>8.5</v>
+      </c>
+      <c r="Q24">
+        <v>1.93</v>
+      </c>
+      <c r="R24">
+        <v>1.4</v>
+      </c>
+      <c r="S24">
+        <v>2.7</v>
+      </c>
+      <c r="T24">
+        <v>2.8</v>
+      </c>
+      <c r="U24">
+        <v>1.38</v>
+      </c>
+      <c r="V24">
+        <v>7.3</v>
+      </c>
+      <c r="W24">
+        <v>1.03</v>
+      </c>
+      <c r="X24">
+        <v>1.06</v>
+      </c>
+      <c r="Y24">
+        <v>8.5</v>
+      </c>
+      <c r="Z24">
+        <v>1.3</v>
+      </c>
+      <c r="AA24">
+        <v>3.45</v>
+      </c>
+      <c r="AB24">
+        <v>1.89</v>
+      </c>
+      <c r="AC24">
+        <v>1.81</v>
+      </c>
+      <c r="AD24">
+        <v>3.2</v>
+      </c>
+      <c r="AE24">
         <v>1.33</v>
       </c>
-      <c r="P24">
-        <v>22</v>
-      </c>
-      <c r="Q24">
-        <v>3.25</v>
-      </c>
-      <c r="R24">
-        <v>1.22</v>
-      </c>
-      <c r="S24">
-        <v>4</v>
-      </c>
-      <c r="T24">
-        <v>2.1</v>
-      </c>
-      <c r="U24">
-        <v>1.67</v>
-      </c>
-      <c r="V24">
-        <v>4.5</v>
-      </c>
-      <c r="W24">
-        <v>1.18</v>
-      </c>
-      <c r="X24">
-        <v>1.01</v>
-      </c>
-      <c r="Y24">
-        <v>17</v>
-      </c>
-      <c r="Z24">
-        <v>1.08</v>
-      </c>
-      <c r="AA24">
-        <v>5.55</v>
-      </c>
-      <c r="AB24">
-        <v>1.48</v>
-      </c>
-      <c r="AC24">
-        <v>2.6</v>
-      </c>
-      <c r="AD24">
-        <v>2.1</v>
-      </c>
-      <c r="AE24">
-        <v>1.6</v>
-      </c>
       <c r="AF24">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG24">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AH24">
-        <v>3.44</v>
+        <v>6.25</v>
       </c>
       <c r="AI24">
-        <v>1.23</v>
+        <v>1.11</v>
       </c>
       <c r="AJ24" t="s">
         <v>303</v>
@@ -4111,76 +4111,76 @@
         <v>301</v>
       </c>
       <c r="L25">
+        <v>2.57</v>
+      </c>
+      <c r="M25">
+        <v>3.3</v>
+      </c>
+      <c r="N25">
+        <v>2.34</v>
+      </c>
+      <c r="O25">
+        <v>2.05</v>
+      </c>
+      <c r="P25">
+        <v>10</v>
+      </c>
+      <c r="Q25">
         <v>1.8</v>
       </c>
-      <c r="M25">
-        <v>3.15</v>
-      </c>
-      <c r="N25">
-        <v>4.3</v>
-      </c>
-      <c r="O25">
-        <v>1.61</v>
-      </c>
-      <c r="P25">
-        <v>6.7</v>
-      </c>
-      <c r="Q25">
-        <v>2.89</v>
-      </c>
       <c r="R25">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="S25">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="T25">
-        <v>3.14</v>
+        <v>2.5</v>
       </c>
       <c r="U25">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="V25">
-        <v>7.7</v>
+        <v>6</v>
       </c>
       <c r="W25">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="X25">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y25">
-        <v>6.75</v>
+        <v>10</v>
       </c>
       <c r="Z25">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AA25">
-        <v>2.8</v>
+        <v>4.33</v>
       </c>
       <c r="AB25">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="AC25">
-        <v>1.62</v>
+        <v>2.1</v>
       </c>
       <c r="AD25">
-        <v>3.74</v>
+        <v>2.26</v>
       </c>
       <c r="AE25">
-        <v>1.22</v>
+        <v>1.51</v>
       </c>
       <c r="AF25">
-        <v>2</v>
+        <v>1.57</v>
       </c>
       <c r="AG25">
-        <v>1.7</v>
+        <v>2.25</v>
       </c>
       <c r="AH25">
-        <v>7.2</v>
+        <v>4.75</v>
       </c>
       <c r="AI25">
-        <v>1.05</v>
+        <v>1.2</v>
       </c>
       <c r="AJ25" t="s">
         <v>303</v>
@@ -4200,7 +4200,7 @@
         <v>48</v>
       </c>
       <c r="C26" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D26" t="s">
         <v>94</v>
@@ -4227,28 +4227,28 @@
         <v>301</v>
       </c>
       <c r="L26">
-        <v>2.57</v>
+        <v>2.73</v>
       </c>
       <c r="M26">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="N26">
-        <v>2.34</v>
+        <v>2.23</v>
       </c>
       <c r="O26">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="P26">
         <v>10</v>
       </c>
       <c r="Q26">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="R26">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S26">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="T26">
         <v>2.5</v>
@@ -4269,22 +4269,22 @@
         <v>10</v>
       </c>
       <c r="Z26">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AA26">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="AB26">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AC26">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AD26">
-        <v>2.26</v>
+        <v>2.8</v>
       </c>
       <c r="AE26">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="AF26">
         <v>1.57</v>
@@ -4293,10 +4293,10 @@
         <v>2.25</v>
       </c>
       <c r="AH26">
-        <v>4.75</v>
+        <v>5.25</v>
       </c>
       <c r="AI26">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AJ26" t="s">
         <v>303</v>
@@ -4316,7 +4316,7 @@
         <v>48</v>
       </c>
       <c r="C27" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D27" t="s">
         <v>94</v>
@@ -4346,7 +4346,7 @@
         <v>1.22</v>
       </c>
       <c r="M27">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="N27">
         <v>12</v>
@@ -4361,58 +4361,58 @@
         <v>5.65</v>
       </c>
       <c r="R27">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="S27">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="T27">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="U27">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="V27">
-        <v>6.05</v>
+        <v>5.8</v>
       </c>
       <c r="W27">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X27">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y27">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="Z27">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AA27">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="AB27">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="AC27">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="AD27">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="AE27">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AF27">
-        <v>2.51</v>
+        <v>2.3</v>
       </c>
       <c r="AG27">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AH27">
-        <v>5.15</v>
+        <v>5</v>
       </c>
       <c r="AI27">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AJ27" t="s">
         <v>303</v>
@@ -4459,43 +4459,43 @@
         <v>301</v>
       </c>
       <c r="L28">
-        <v>5.9</v>
+        <v>2.09</v>
       </c>
       <c r="M28">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="N28">
-        <v>1.4</v>
+        <v>2.98</v>
       </c>
       <c r="O28">
-        <v>3.35</v>
+        <v>1.67</v>
       </c>
       <c r="P28">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Q28">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="R28">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S28">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T28">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="U28">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="V28">
-        <v>5.75</v>
+        <v>7</v>
       </c>
       <c r="W28">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X28">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y28">
         <v>11</v>
@@ -4504,31 +4504,31 @@
         <v>1.22</v>
       </c>
       <c r="AA28">
-        <v>4.33</v>
+        <v>3.64</v>
       </c>
       <c r="AB28">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="AC28">
+        <v>1.93</v>
+      </c>
+      <c r="AD28">
+        <v>2.88</v>
+      </c>
+      <c r="AE28">
+        <v>1.34</v>
+      </c>
+      <c r="AF28">
+        <v>1.67</v>
+      </c>
+      <c r="AG28">
         <v>2.1</v>
       </c>
-      <c r="AD28">
-        <v>2.65</v>
-      </c>
-      <c r="AE28">
-        <v>1.48</v>
-      </c>
-      <c r="AF28">
-        <v>1.77</v>
-      </c>
-      <c r="AG28">
-        <v>1.9</v>
-      </c>
       <c r="AH28">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AI28">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="AJ28" t="s">
         <v>303</v>
@@ -4575,76 +4575,76 @@
         <v>301</v>
       </c>
       <c r="L29">
-        <v>2.73</v>
+        <v>1.8</v>
       </c>
       <c r="M29">
-        <v>3.29</v>
+        <v>3.15</v>
       </c>
       <c r="N29">
-        <v>2.23</v>
+        <v>4.3</v>
       </c>
       <c r="O29">
-        <v>2.2</v>
+        <v>1.61</v>
       </c>
       <c r="P29">
-        <v>10</v>
+        <v>6.7</v>
       </c>
       <c r="Q29">
-        <v>1.73</v>
+        <v>2.89</v>
       </c>
       <c r="R29">
-        <v>1.33</v>
+        <v>1.51</v>
       </c>
       <c r="S29">
-        <v>3.25</v>
+        <v>2.38</v>
       </c>
       <c r="T29">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="U29">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="V29">
-        <v>6</v>
+        <v>7.9</v>
       </c>
       <c r="W29">
-        <v>1.13</v>
+        <v>1.02</v>
       </c>
       <c r="X29">
         <v>1.05</v>
       </c>
       <c r="Y29">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Z29">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="AA29">
+        <v>2.62</v>
+      </c>
+      <c r="AB29">
+        <v>2.22</v>
+      </c>
+      <c r="AC29">
+        <v>1.63</v>
+      </c>
+      <c r="AD29">
         <v>4</v>
       </c>
-      <c r="AB29">
+      <c r="AE29">
+        <v>1.2</v>
+      </c>
+      <c r="AF29">
+        <v>2.1</v>
+      </c>
+      <c r="AG29">
         <v>1.67</v>
       </c>
-      <c r="AC29">
-        <v>2</v>
-      </c>
-      <c r="AD29">
-        <v>2.8</v>
-      </c>
-      <c r="AE29">
-        <v>1.44</v>
-      </c>
-      <c r="AF29">
-        <v>1.57</v>
-      </c>
-      <c r="AG29">
-        <v>2.25</v>
-      </c>
       <c r="AH29">
-        <v>5.25</v>
+        <v>7.5</v>
       </c>
       <c r="AI29">
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="AJ29" t="s">
         <v>303</v>
@@ -4664,7 +4664,7 @@
         <v>48</v>
       </c>
       <c r="C30" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D30" t="s">
         <v>94</v>
@@ -4691,76 +4691,76 @@
         <v>301</v>
       </c>
       <c r="L30">
-        <v>2.4</v>
+        <v>5.9</v>
       </c>
       <c r="M30">
-        <v>3.15</v>
+        <v>4.2</v>
       </c>
       <c r="N30">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="O30">
-        <v>1.8</v>
+        <v>3.35</v>
       </c>
       <c r="P30">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Q30">
+        <v>1.4</v>
+      </c>
+      <c r="R30">
+        <v>1.3</v>
+      </c>
+      <c r="S30">
+        <v>3.2</v>
+      </c>
+      <c r="T30">
+        <v>2.38</v>
+      </c>
+      <c r="U30">
+        <v>1.53</v>
+      </c>
+      <c r="V30">
+        <v>5.75</v>
+      </c>
+      <c r="W30">
+        <v>1.07</v>
+      </c>
+      <c r="X30">
+        <v>1.04</v>
+      </c>
+      <c r="Y30">
+        <v>11</v>
+      </c>
+      <c r="Z30">
+        <v>1.22</v>
+      </c>
+      <c r="AA30">
+        <v>4.33</v>
+      </c>
+      <c r="AB30">
+        <v>1.65</v>
+      </c>
+      <c r="AC30">
         <v>2.1</v>
       </c>
-      <c r="R30">
-        <v>1.36</v>
-      </c>
-      <c r="S30">
-        <v>3</v>
-      </c>
-      <c r="T30">
-        <v>2.63</v>
-      </c>
-      <c r="U30">
-        <v>1.44</v>
-      </c>
-      <c r="V30">
-        <v>7</v>
-      </c>
-      <c r="W30">
-        <v>1.1</v>
-      </c>
-      <c r="X30">
-        <v>1.06</v>
-      </c>
-      <c r="Y30">
-        <v>9</v>
-      </c>
-      <c r="Z30">
-        <v>1.3</v>
-      </c>
-      <c r="AA30">
-        <v>3.55</v>
-      </c>
-      <c r="AB30">
-        <v>1.81</v>
-      </c>
-      <c r="AC30">
-        <v>1.89</v>
-      </c>
       <c r="AD30">
-        <v>3.25</v>
+        <v>2.65</v>
       </c>
       <c r="AE30">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="AF30">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AG30">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AH30">
-        <v>6.25</v>
+        <v>5</v>
       </c>
       <c r="AI30">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AJ30" t="s">
         <v>303</v>
@@ -4780,7 +4780,7 @@
         <v>48</v>
       </c>
       <c r="C31" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D31" t="s">
         <v>94</v>
@@ -4807,28 +4807,28 @@
         <v>301</v>
       </c>
       <c r="L31">
-        <v>2.09</v>
+        <v>2.4</v>
       </c>
       <c r="M31">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N31">
-        <v>2.98</v>
+        <v>2.6</v>
       </c>
       <c r="O31">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="P31">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="Q31">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="R31">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S31">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="T31">
         <v>2.63</v>
@@ -4843,28 +4843,28 @@
         <v>1.1</v>
       </c>
       <c r="X31">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y31">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Z31">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AA31">
-        <v>3.64</v>
+        <v>3.55</v>
       </c>
       <c r="AB31">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="AC31">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AD31">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="AE31">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AF31">
         <v>1.67</v>
@@ -4873,10 +4873,10 @@
         <v>2.1</v>
       </c>
       <c r="AH31">
-        <v>5.3</v>
+        <v>6.25</v>
       </c>
       <c r="AI31">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AJ31" t="s">
         <v>303</v>
@@ -4896,7 +4896,7 @@
         <v>49</v>
       </c>
       <c r="C32" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D32" t="s">
         <v>94</v>
@@ -4923,76 +4923,76 @@
         <v>301</v>
       </c>
       <c r="L32">
-        <v>1.47</v>
+        <v>3</v>
       </c>
       <c r="M32">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="N32">
-        <v>4.9</v>
+        <v>2.27</v>
       </c>
       <c r="O32">
-        <v>1.39</v>
+        <v>2.3</v>
       </c>
       <c r="P32">
-        <v>25</v>
+        <v>13.75</v>
       </c>
       <c r="Q32">
-        <v>3</v>
+        <v>1.67</v>
       </c>
       <c r="R32">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="S32">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="T32">
-        <v>2.03</v>
+        <v>2.45</v>
       </c>
       <c r="U32">
-        <v>1.7</v>
+        <v>1.48</v>
       </c>
       <c r="V32">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="W32">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X32">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y32">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="Z32">
-        <v>1.06</v>
+        <v>1.22</v>
       </c>
       <c r="AA32">
-        <v>6.25</v>
+        <v>3.8</v>
       </c>
       <c r="AB32">
-        <v>1.55</v>
+        <v>1.74</v>
       </c>
       <c r="AC32">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AD32">
-        <v>1.95</v>
+        <v>2.78</v>
       </c>
       <c r="AE32">
-        <v>1.75</v>
+        <v>1.36</v>
       </c>
       <c r="AF32">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="AG32">
-        <v>2.39</v>
+        <v>2.26</v>
       </c>
       <c r="AH32">
-        <v>3.25</v>
+        <v>5</v>
       </c>
       <c r="AI32">
-        <v>1.27</v>
+        <v>1.13</v>
       </c>
       <c r="AJ32" t="s">
         <v>303</v>
@@ -5012,7 +5012,7 @@
         <v>49</v>
       </c>
       <c r="C33" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D33" t="s">
         <v>94</v>
@@ -5039,76 +5039,76 @@
         <v>301</v>
       </c>
       <c r="L33">
-        <v>2.95</v>
+        <v>1.47</v>
       </c>
       <c r="M33">
-        <v>3.46</v>
+        <v>4.2</v>
       </c>
       <c r="N33">
-        <v>2.33</v>
+        <v>4.9</v>
       </c>
       <c r="O33">
-        <v>2.3</v>
+        <v>1.39</v>
       </c>
       <c r="P33">
-        <v>13.75</v>
+        <v>25</v>
       </c>
       <c r="Q33">
-        <v>1.67</v>
+        <v>3</v>
       </c>
       <c r="R33">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="S33">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="T33">
-        <v>2.45</v>
+        <v>2.03</v>
       </c>
       <c r="U33">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="V33">
-        <v>6</v>
+        <v>4.4</v>
       </c>
       <c r="W33">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X33">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="Z33">
-        <v>1.22</v>
+        <v>1.06</v>
       </c>
       <c r="AA33">
-        <v>3.92</v>
+        <v>6.25</v>
       </c>
       <c r="AB33">
-        <v>1.74</v>
+        <v>1.55</v>
       </c>
       <c r="AC33">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="AD33">
-        <v>2.78</v>
+        <v>1.95</v>
       </c>
       <c r="AE33">
-        <v>1.36</v>
+        <v>1.75</v>
       </c>
       <c r="AF33">
-        <v>1.62</v>
+        <v>1.51</v>
       </c>
       <c r="AG33">
-        <v>2.2</v>
+        <v>2.39</v>
       </c>
       <c r="AH33">
-        <v>5</v>
+        <v>3.25</v>
       </c>
       <c r="AI33">
-        <v>1.13</v>
+        <v>1.27</v>
       </c>
       <c r="AJ33" t="s">
         <v>303</v>
@@ -5155,13 +5155,13 @@
         <v>301</v>
       </c>
       <c r="L34">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="M34">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="N34">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="O34">
         <v>1.37</v>
@@ -5173,16 +5173,16 @@
         <v>3.1</v>
       </c>
       <c r="R34">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="S34">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="T34">
         <v>2.1</v>
       </c>
       <c r="U34">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="V34">
         <v>4.2</v>
@@ -5197,28 +5197,28 @@
         <v>10</v>
       </c>
       <c r="Z34">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AA34">
-        <v>5.32</v>
+        <v>5</v>
       </c>
       <c r="AB34">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="AC34">
-        <v>2.47</v>
+        <v>2.65</v>
       </c>
       <c r="AD34">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AE34">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AF34">
         <v>1.62</v>
       </c>
       <c r="AG34">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="AH34">
         <v>3.6</v>
@@ -5244,7 +5244,7 @@
         <v>50</v>
       </c>
       <c r="C35" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D35" t="s">
         <v>94</v>
@@ -5289,58 +5289,58 @@
         <v>2.74</v>
       </c>
       <c r="R35">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S35">
         <v>2.62</v>
       </c>
       <c r="T35">
-        <v>2.88</v>
+        <v>2.93</v>
       </c>
       <c r="U35">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="V35">
-        <v>7</v>
+        <v>8.1</v>
       </c>
       <c r="W35">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X35">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y35">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="Z35">
         <v>1.27</v>
       </c>
       <c r="AA35">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AB35">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AC35">
         <v>1.73</v>
       </c>
       <c r="AD35">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AE35">
         <v>1.29</v>
       </c>
       <c r="AF35">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AG35">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AH35">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI35">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AJ35" t="s">
         <v>303</v>
@@ -5360,7 +5360,7 @@
         <v>50</v>
       </c>
       <c r="C36" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D36" t="s">
         <v>94</v>
@@ -5601,7 +5601,7 @@
         <v>131</v>
       </c>
       <c r="F38" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -5708,7 +5708,7 @@
         <v>52</v>
       </c>
       <c r="C39" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="D39" t="s">
         <v>94</v>
@@ -5717,7 +5717,7 @@
         <v>132</v>
       </c>
       <c r="F39" t="s">
-        <v>131</v>
+        <v>235</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -5735,76 +5735,76 @@
         <v>301</v>
       </c>
       <c r="L39">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="M39">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="T39">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V39">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="W39">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X39">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Z39">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AA39">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AB39">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AC39">
+        <v>2.45</v>
+      </c>
+      <c r="AD39">
+        <v>2.08</v>
+      </c>
+      <c r="AE39">
+        <v>1.66</v>
+      </c>
+      <c r="AF39">
+        <v>1.42</v>
+      </c>
+      <c r="AG39">
         <v>2.62</v>
       </c>
-      <c r="AD39">
-        <v>0</v>
-      </c>
-      <c r="AE39">
-        <v>0</v>
-      </c>
-      <c r="AF39">
-        <v>0</v>
-      </c>
-      <c r="AG39">
-        <v>0</v>
-      </c>
       <c r="AH39">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AI39">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AJ39" t="s">
         <v>303</v>
@@ -5824,7 +5824,7 @@
         <v>52</v>
       </c>
       <c r="C40" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="D40" t="s">
         <v>94</v>
@@ -5833,7 +5833,7 @@
         <v>133</v>
       </c>
       <c r="F40" t="s">
-        <v>235</v>
+        <v>131</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -5851,76 +5851,76 @@
         <v>301</v>
       </c>
       <c r="L40">
-        <v>2.77</v>
+        <v>1.22</v>
       </c>
       <c r="M40">
-        <v>3.79</v>
+        <v>6.4</v>
       </c>
       <c r="N40">
-        <v>2.02</v>
+        <v>6.9</v>
       </c>
       <c r="O40">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P40">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Q40">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="R40">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="S40">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="T40">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="U40">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="V40">
-        <v>4.4</v>
+        <v>3.84</v>
       </c>
       <c r="W40">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="X40">
         <v>1.01</v>
       </c>
       <c r="Y40">
-        <v>15.5</v>
+        <v>20</v>
       </c>
       <c r="Z40">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="AA40">
-        <v>5.25</v>
+        <v>6</v>
       </c>
       <c r="AB40">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AC40">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="AD40">
-        <v>2.08</v>
+        <v>1.86</v>
       </c>
       <c r="AE40">
-        <v>1.66</v>
+        <v>1.84</v>
       </c>
       <c r="AF40">
-        <v>1.42</v>
+        <v>1.91</v>
       </c>
       <c r="AG40">
-        <v>2.62</v>
+        <v>1.8</v>
       </c>
       <c r="AH40">
-        <v>3.7</v>
+        <v>2.88</v>
       </c>
       <c r="AI40">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AJ40" t="s">
         <v>303</v>
@@ -6083,10 +6083,10 @@
         <v>301</v>
       </c>
       <c r="L42">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="M42">
-        <v>3.31</v>
+        <v>3.14</v>
       </c>
       <c r="N42">
         <v>3.19</v>
@@ -6113,7 +6113,7 @@
         <v>1.41</v>
       </c>
       <c r="V42">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="W42">
         <v>1.08</v>
@@ -6125,16 +6125,16 @@
         <v>9.1</v>
       </c>
       <c r="Z42">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AA42">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="AB42">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="AC42">
-        <v>1.91</v>
+        <v>1.76</v>
       </c>
       <c r="AD42">
         <v>2.97</v>
@@ -6143,7 +6143,7 @@
         <v>1.3</v>
       </c>
       <c r="AF42">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AG42">
         <v>2.1</v>
@@ -6520,7 +6520,7 @@
         <v>56</v>
       </c>
       <c r="C46" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D46" t="s">
         <v>94</v>
@@ -6547,76 +6547,76 @@
         <v>301</v>
       </c>
       <c r="L46">
-        <v>2.4</v>
+        <v>2.67</v>
       </c>
       <c r="M46">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="N46">
-        <v>2.75</v>
+        <v>2.43</v>
       </c>
       <c r="O46">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="P46">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="Q46">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="R46">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="S46">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="T46">
-        <v>3.2</v>
+        <v>3.02</v>
       </c>
       <c r="U46">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="V46">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="W46">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X46">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="Y46">
-        <v>7.1</v>
+        <v>7.8</v>
       </c>
       <c r="Z46">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="AA46">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="AB46">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AC46">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AD46">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="AE46">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AF46">
-        <v>1.92</v>
+        <v>1.71</v>
       </c>
       <c r="AG46">
         <v>1.85</v>
       </c>
       <c r="AH46">
-        <v>8.1</v>
+        <v>7</v>
       </c>
       <c r="AI46">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AJ46" t="s">
         <v>303</v>
@@ -6636,7 +6636,7 @@
         <v>56</v>
       </c>
       <c r="C47" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D47" t="s">
         <v>94</v>
@@ -6663,76 +6663,76 @@
         <v>301</v>
       </c>
       <c r="L47">
-        <v>2.09</v>
+        <v>1.73</v>
       </c>
       <c r="M47">
-        <v>3.16</v>
+        <v>3.06</v>
       </c>
       <c r="N47">
-        <v>3.35</v>
+        <v>4.7</v>
       </c>
       <c r="O47">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="P47">
-        <v>7.2</v>
+        <v>6</v>
       </c>
       <c r="Q47">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="R47">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="S47">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="T47">
-        <v>3.04</v>
+        <v>3.5</v>
       </c>
       <c r="U47">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="V47">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W47">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X47">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y47">
-        <v>8</v>
+        <v>6.2</v>
       </c>
       <c r="Z47">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AA47">
-        <v>2.83</v>
+        <v>2.43</v>
       </c>
       <c r="AB47">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AC47">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="AD47">
-        <v>3.6</v>
+        <v>4.75</v>
       </c>
       <c r="AE47">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AF47">
-        <v>1.71</v>
+        <v>2.25</v>
       </c>
       <c r="AG47">
-        <v>1.82</v>
+        <v>1.62</v>
       </c>
       <c r="AH47">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="AI47">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AJ47" t="s">
         <v>303</v>
@@ -6895,76 +6895,76 @@
         <v>301</v>
       </c>
       <c r="L49">
-        <v>1.91</v>
+        <v>2.4</v>
       </c>
       <c r="M49">
-        <v>3.15</v>
+        <v>2.96</v>
       </c>
       <c r="N49">
-        <v>4.18</v>
+        <v>2.75</v>
       </c>
       <c r="O49">
-        <v>1.57</v>
+        <v>1.95</v>
       </c>
       <c r="P49">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q49">
-        <v>3.1</v>
+        <v>2.15</v>
       </c>
       <c r="R49">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="S49">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="T49">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="U49">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="V49">
-        <v>11</v>
+        <v>8.5</v>
       </c>
       <c r="W49">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X49">
         <v>1.08</v>
       </c>
       <c r="Y49">
-        <v>6.64</v>
+        <v>7.5</v>
       </c>
       <c r="Z49">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AA49">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="AB49">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="AC49">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="AD49">
-        <v>4.75</v>
+        <v>4.2</v>
       </c>
       <c r="AE49">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AF49">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AG49">
-        <v>1.62</v>
+        <v>1.82</v>
       </c>
       <c r="AH49">
-        <v>10</v>
+        <v>8.1</v>
       </c>
       <c r="AI49">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="AJ49" t="s">
         <v>303</v>
@@ -7124,7 +7124,7 @@
         <v>0</v>
       </c>
       <c r="K51" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L51">
         <v>0</v>
@@ -7240,7 +7240,7 @@
         <v>0</v>
       </c>
       <c r="K52" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L52">
         <v>0</v>
@@ -7332,7 +7332,7 @@
         <v>58</v>
       </c>
       <c r="C53" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D53" t="s">
         <v>94</v>
@@ -7359,76 +7359,76 @@
         <v>301</v>
       </c>
       <c r="L53">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M53">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N53">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O53">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="P53">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Q53">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R53">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S53">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T53">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U53">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V53">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="W53">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X53">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y53">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="Z53">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AA53">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AB53">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC53">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AD53">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE53">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AF53">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG53">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AH53">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AI53">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AJ53" t="s">
         <v>303</v>
@@ -7448,7 +7448,7 @@
         <v>58</v>
       </c>
       <c r="C54" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D54" t="s">
         <v>94</v>
@@ -7475,76 +7475,76 @@
         <v>301</v>
       </c>
       <c r="L54">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M54">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N54">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O54">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="P54">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q54">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R54">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S54">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="T54">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U54">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V54">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="W54">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X54">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y54">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="Z54">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AA54">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AB54">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AC54">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AD54">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AE54">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AF54">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AG54">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH54">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AI54">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AJ54" t="s">
         <v>303</v>
@@ -7564,7 +7564,7 @@
         <v>58</v>
       </c>
       <c r="C55" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D55" t="s">
         <v>94</v>
@@ -7591,13 +7591,13 @@
         <v>301</v>
       </c>
       <c r="L55">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="M55">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="N55">
-        <v>3.75</v>
+        <v>3.83</v>
       </c>
       <c r="O55">
         <v>1.71</v>
@@ -7609,7 +7609,7 @@
         <v>2.6</v>
       </c>
       <c r="R55">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="S55">
         <v>2.33</v>
@@ -7621,28 +7621,28 @@
         <v>1.25</v>
       </c>
       <c r="V55">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W55">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X55">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Y55">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="Z55">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AA55">
         <v>2.48</v>
       </c>
       <c r="AB55">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="AC55">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AD55">
         <v>4.6</v>
@@ -7654,13 +7654,13 @@
         <v>2.2</v>
       </c>
       <c r="AG55">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AH55">
         <v>9</v>
       </c>
       <c r="AI55">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AJ55" t="s">
         <v>303</v>
@@ -7796,7 +7796,7 @@
         <v>58</v>
       </c>
       <c r="C57" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D57" t="s">
         <v>94</v>
@@ -7823,76 +7823,76 @@
         <v>301</v>
       </c>
       <c r="L57">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M57">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N57">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="O57">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="P57">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q57">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R57">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S57">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T57">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U57">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V57">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="W57">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X57">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y57">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z57">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AA57">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AB57">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC57">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD57">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AE57">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF57">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG57">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH57">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="AI57">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AJ57" t="s">
         <v>303</v>
@@ -7912,7 +7912,7 @@
         <v>58</v>
       </c>
       <c r="C58" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D58" t="s">
         <v>94</v>
@@ -7939,64 +7939,64 @@
         <v>301</v>
       </c>
       <c r="L58">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="M58">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="N58">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="O58">
         <v>1.53</v>
       </c>
       <c r="P58">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q58">
         <v>2.75</v>
       </c>
       <c r="R58">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S58">
         <v>3</v>
       </c>
       <c r="T58">
-        <v>2.63</v>
+        <v>2.52</v>
       </c>
       <c r="U58">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="V58">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="W58">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X58">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y58">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="Z58">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AA58">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AB58">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AC58">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AD58">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE58">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AF58">
         <v>1.8</v>
@@ -8005,10 +8005,10 @@
         <v>1.91</v>
       </c>
       <c r="AH58">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AI58">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AJ58" t="s">
         <v>303</v>
@@ -8284,7 +8284,7 @@
         <v>0</v>
       </c>
       <c r="K61" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L61">
         <v>0</v>
@@ -8608,7 +8608,7 @@
         <v>58</v>
       </c>
       <c r="C64" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D64" t="s">
         <v>94</v>
@@ -8632,79 +8632,79 @@
         <v>0</v>
       </c>
       <c r="K64" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L64">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M64">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N64">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O64">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="P64">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q64">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R64">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S64">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T64">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U64">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V64">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="W64">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X64">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y64">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Z64">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AA64">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AB64">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC64">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD64">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AE64">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AF64">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG64">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH64">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AI64">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ64" t="s">
         <v>303</v>
@@ -9212,7 +9212,7 @@
         <v>0</v>
       </c>
       <c r="K69" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L69">
         <v>0</v>
@@ -9328,7 +9328,7 @@
         <v>0</v>
       </c>
       <c r="K70" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L70">
         <v>0</v>
@@ -9420,7 +9420,7 @@
         <v>59</v>
       </c>
       <c r="C71" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D71" t="s">
         <v>94</v>
@@ -9447,13 +9447,13 @@
         <v>301</v>
       </c>
       <c r="L71">
-        <v>2.08</v>
+        <v>2.29</v>
       </c>
       <c r="M71">
-        <v>3.28</v>
+        <v>3.02</v>
       </c>
       <c r="N71">
-        <v>3.95</v>
+        <v>2.84</v>
       </c>
       <c r="O71">
         <v>1.67</v>
@@ -9468,16 +9468,16 @@
         <v>1.5</v>
       </c>
       <c r="S71">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="T71">
         <v>3.34</v>
       </c>
       <c r="U71">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="V71">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="W71">
         <v>1.05</v>
@@ -9495,25 +9495,25 @@
         <v>2.6</v>
       </c>
       <c r="AB71">
-        <v>2.42</v>
+        <v>2.37</v>
       </c>
       <c r="AC71">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AD71">
         <v>4.6</v>
       </c>
       <c r="AE71">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AF71">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AG71">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AH71">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AI71">
         <v>1.04</v>
@@ -9536,7 +9536,7 @@
         <v>60</v>
       </c>
       <c r="C72" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D72" t="s">
         <v>94</v>
@@ -9563,76 +9563,76 @@
         <v>301</v>
       </c>
       <c r="L72">
-        <v>2.11</v>
+        <v>1.6</v>
       </c>
       <c r="M72">
-        <v>2.88</v>
+        <v>3.31</v>
       </c>
       <c r="N72">
-        <v>3.5</v>
+        <v>5.2</v>
       </c>
       <c r="O72">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="P72">
-        <v>5.75</v>
+        <v>6.5</v>
       </c>
       <c r="Q72">
-        <v>2.37</v>
+        <v>3.3</v>
       </c>
       <c r="R72">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="S72">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="T72">
-        <v>3.66</v>
+        <v>3.3</v>
       </c>
       <c r="U72">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="V72">
-        <v>11.5</v>
+        <v>8.9</v>
       </c>
       <c r="W72">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X72">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="Y72">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z72">
-        <v>1.57</v>
+        <v>1.41</v>
       </c>
       <c r="AA72">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AB72">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="AC72">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AD72">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AE72">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AF72">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AG72">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AH72">
-        <v>10</v>
+        <v>9.1</v>
       </c>
       <c r="AI72">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AJ72" t="s">
         <v>303</v>
@@ -9679,76 +9679,76 @@
         <v>301</v>
       </c>
       <c r="L73">
-        <v>1.6</v>
+        <v>2.56</v>
       </c>
       <c r="M73">
-        <v>3.54</v>
+        <v>2.84</v>
       </c>
       <c r="N73">
-        <v>5</v>
+        <v>2.65</v>
       </c>
       <c r="O73">
+        <v>1.95</v>
+      </c>
+      <c r="P73">
+        <v>6.75</v>
+      </c>
+      <c r="Q73">
+        <v>2.2</v>
+      </c>
+      <c r="R73">
         <v>1.5</v>
       </c>
-      <c r="P73">
-        <v>6.5</v>
-      </c>
-      <c r="Q73">
-        <v>3.3</v>
-      </c>
-      <c r="R73">
-        <v>1.47</v>
-      </c>
       <c r="S73">
-        <v>2.52</v>
+        <v>2.32</v>
       </c>
       <c r="T73">
         <v>3.3</v>
       </c>
       <c r="U73">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="V73">
-        <v>9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W73">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X73">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="Y73">
-        <v>6.5</v>
+        <v>7.17</v>
       </c>
       <c r="Z73">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="AA73">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AB73">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="AC73">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AD73">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="AE73">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AF73">
-        <v>2.38</v>
+        <v>2.05</v>
       </c>
       <c r="AG73">
-        <v>1.53</v>
+        <v>1.72</v>
       </c>
       <c r="AH73">
         <v>9.5</v>
       </c>
       <c r="AI73">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AJ73" t="s">
         <v>303</v>
@@ -9795,76 +9795,76 @@
         <v>301</v>
       </c>
       <c r="L74">
-        <v>2.5</v>
+        <v>1.88</v>
       </c>
       <c r="M74">
-        <v>3.01</v>
+        <v>2.93</v>
       </c>
       <c r="N74">
-        <v>3</v>
+        <v>4.1</v>
       </c>
       <c r="O74">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="P74">
-        <v>6.75</v>
+        <v>5.75</v>
       </c>
       <c r="Q74">
+        <v>2.37</v>
+      </c>
+      <c r="R74">
+        <v>1.55</v>
+      </c>
+      <c r="S74">
         <v>2.2</v>
       </c>
-      <c r="R74">
+      <c r="T74">
+        <v>3.66</v>
+      </c>
+      <c r="U74">
+        <v>1.22</v>
+      </c>
+      <c r="V74">
+        <v>11.5</v>
+      </c>
+      <c r="W74">
+        <v>1.04</v>
+      </c>
+      <c r="X74">
+        <v>1.07</v>
+      </c>
+      <c r="Y74">
+        <v>6</v>
+      </c>
+      <c r="Z74">
         <v>1.53</v>
       </c>
-      <c r="S74">
-        <v>2.32</v>
-      </c>
-      <c r="T74">
-        <v>3.3</v>
-      </c>
-      <c r="U74">
-        <v>1.27</v>
-      </c>
-      <c r="V74">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="W74">
+      <c r="AA74">
+        <v>2.25</v>
+      </c>
+      <c r="AB74">
+        <v>2.73</v>
+      </c>
+      <c r="AC74">
+        <v>1.4</v>
+      </c>
+      <c r="AD74">
+        <v>5</v>
+      </c>
+      <c r="AE74">
+        <v>1.13</v>
+      </c>
+      <c r="AF74">
+        <v>2.25</v>
+      </c>
+      <c r="AG74">
+        <v>1.63</v>
+      </c>
+      <c r="AH74">
+        <v>10</v>
+      </c>
+      <c r="AI74">
         <v>1.03</v>
-      </c>
-      <c r="X74">
-        <v>1.1</v>
-      </c>
-      <c r="Y74">
-        <v>7.15</v>
-      </c>
-      <c r="Z74">
-        <v>1.44</v>
-      </c>
-      <c r="AA74">
-        <v>2.63</v>
-      </c>
-      <c r="AB74">
-        <v>2.4</v>
-      </c>
-      <c r="AC74">
-        <v>1.53</v>
-      </c>
-      <c r="AD74">
-        <v>4.75</v>
-      </c>
-      <c r="AE74">
-        <v>1.18</v>
-      </c>
-      <c r="AF74">
-        <v>2</v>
-      </c>
-      <c r="AG74">
-        <v>1.72</v>
-      </c>
-      <c r="AH74">
-        <v>9.5</v>
-      </c>
-      <c r="AI74">
-        <v>1.05</v>
       </c>
       <c r="AJ74" t="s">
         <v>303</v>
@@ -10232,7 +10232,7 @@
         <v>62</v>
       </c>
       <c r="C78" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D78" t="s">
         <v>94</v>
@@ -10262,73 +10262,73 @@
         <v>1.54</v>
       </c>
       <c r="M78">
-        <v>3.25</v>
+        <v>3.72</v>
       </c>
       <c r="N78">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="O78">
         <v>1.49</v>
       </c>
       <c r="P78">
-        <v>6.5</v>
+        <v>8.75</v>
       </c>
       <c r="Q78">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="R78">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="S78">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="T78">
-        <v>3.3</v>
+        <v>2.84</v>
       </c>
       <c r="U78">
+        <v>1.36</v>
+      </c>
+      <c r="V78">
+        <v>7</v>
+      </c>
+      <c r="W78">
+        <v>1.07</v>
+      </c>
+      <c r="X78">
+        <v>1.01</v>
+      </c>
+      <c r="Y78">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="Z78">
+        <v>1.28</v>
+      </c>
+      <c r="AA78">
+        <v>3.2</v>
+      </c>
+      <c r="AB78">
+        <v>1.94</v>
+      </c>
+      <c r="AC78">
+        <v>1.76</v>
+      </c>
+      <c r="AD78">
+        <v>3.4</v>
+      </c>
+      <c r="AE78">
         <v>1.29</v>
       </c>
-      <c r="V78">
-        <v>9</v>
-      </c>
-      <c r="W78">
-        <v>1.03</v>
-      </c>
-      <c r="X78">
-        <v>1.05</v>
-      </c>
-      <c r="Y78">
-        <v>6.75</v>
-      </c>
-      <c r="Z78">
-        <v>1.42</v>
-      </c>
-      <c r="AA78">
-        <v>2.5</v>
-      </c>
-      <c r="AB78">
-        <v>2.4</v>
-      </c>
-      <c r="AC78">
-        <v>1.52</v>
-      </c>
-      <c r="AD78">
-        <v>4.35</v>
-      </c>
-      <c r="AE78">
-        <v>1.14</v>
-      </c>
       <c r="AF78">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="AG78">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AH78">
-        <v>8.5</v>
+        <v>6.3</v>
       </c>
       <c r="AI78">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AJ78" t="s">
         <v>303</v>
@@ -10348,7 +10348,7 @@
         <v>62</v>
       </c>
       <c r="C79" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D79" t="s">
         <v>94</v>
@@ -10375,76 +10375,76 @@
         <v>301</v>
       </c>
       <c r="L79">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="M79">
-        <v>3.9</v>
+        <v>3.41</v>
       </c>
       <c r="N79">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="O79">
         <v>1.49</v>
       </c>
       <c r="P79">
-        <v>8.75</v>
+        <v>6.5</v>
       </c>
       <c r="Q79">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="R79">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="S79">
-        <v>2.68</v>
+        <v>2.35</v>
       </c>
       <c r="T79">
-        <v>2.84</v>
+        <v>3.3</v>
       </c>
       <c r="U79">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="V79">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W79">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X79">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="Y79">
-        <v>8.300000000000001</v>
+        <v>6.5</v>
       </c>
       <c r="Z79">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="AA79">
-        <v>3.2</v>
+        <v>2.55</v>
       </c>
       <c r="AB79">
-        <v>1.96</v>
+        <v>2.3</v>
       </c>
       <c r="AC79">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="AD79">
-        <v>3.4</v>
+        <v>4.75</v>
       </c>
       <c r="AE79">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="AF79">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AG79">
-        <v>1.69</v>
+        <v>1.48</v>
       </c>
       <c r="AH79">
-        <v>6.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AI79">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AJ79" t="s">
         <v>303</v>
@@ -10491,40 +10491,40 @@
         <v>301</v>
       </c>
       <c r="L80">
-        <v>2.75</v>
+        <v>1.55</v>
       </c>
       <c r="M80">
+        <v>4.1</v>
+      </c>
+      <c r="N80">
+        <v>4.5</v>
+      </c>
+      <c r="O80">
+        <v>1.4</v>
+      </c>
+      <c r="P80">
+        <v>0</v>
+      </c>
+      <c r="Q80">
+        <v>2.88</v>
+      </c>
+      <c r="R80">
+        <v>1.18</v>
+      </c>
+      <c r="S80">
+        <v>4.33</v>
+      </c>
+      <c r="T80">
+        <v>1.91</v>
+      </c>
+      <c r="U80">
+        <v>1.8</v>
+      </c>
+      <c r="V80">
         <v>3.8</v>
       </c>
-      <c r="N80">
-        <v>2.05</v>
-      </c>
-      <c r="O80">
-        <v>2.2</v>
-      </c>
-      <c r="P80">
-        <v>0</v>
-      </c>
-      <c r="Q80">
-        <v>1.67</v>
-      </c>
-      <c r="R80">
-        <v>1.25</v>
-      </c>
-      <c r="S80">
-        <v>3.6</v>
-      </c>
-      <c r="T80">
-        <v>2.1</v>
-      </c>
-      <c r="U80">
-        <v>1.65</v>
-      </c>
-      <c r="V80">
-        <v>4.5</v>
-      </c>
       <c r="W80">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="X80">
         <v>0</v>
@@ -10533,34 +10533,34 @@
         <v>0</v>
       </c>
       <c r="Z80">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AA80">
-        <v>5.25</v>
+        <v>6.5</v>
       </c>
       <c r="AB80">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="AC80">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="AD80">
-        <v>2.11</v>
+        <v>1.84</v>
       </c>
       <c r="AE80">
-        <v>1.64</v>
+        <v>1.85</v>
       </c>
       <c r="AF80">
         <v>1.48</v>
       </c>
       <c r="AG80">
-        <v>2.48</v>
+        <v>2.51</v>
       </c>
       <c r="AH80">
-        <v>3.55</v>
+        <v>2.83</v>
       </c>
       <c r="AI80">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AJ80" t="s">
         <v>303</v>
@@ -10580,7 +10580,7 @@
         <v>63</v>
       </c>
       <c r="C81" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D81" t="s">
         <v>94</v>
@@ -10607,76 +10607,76 @@
         <v>301</v>
       </c>
       <c r="L81">
-        <v>1.49</v>
+        <v>2.14</v>
       </c>
       <c r="M81">
-        <v>4.3</v>
+        <v>3.14</v>
       </c>
       <c r="N81">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="O81">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="P81">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q81">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="R81">
-        <v>1.24</v>
+        <v>1.45</v>
       </c>
       <c r="S81">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="T81">
-        <v>2.3</v>
+        <v>2.93</v>
       </c>
       <c r="U81">
-        <v>1.55</v>
+        <v>1.35</v>
       </c>
       <c r="V81">
-        <v>5.25</v>
+        <v>6.5</v>
       </c>
       <c r="W81">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X81">
         <v>1.04</v>
       </c>
       <c r="Y81">
-        <v>13</v>
+        <v>8.5</v>
       </c>
       <c r="Z81">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="AA81">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="AB81">
-        <v>1.67</v>
+        <v>1.92</v>
       </c>
       <c r="AC81">
-        <v>2.09</v>
+        <v>1.78</v>
       </c>
       <c r="AD81">
-        <v>2.74</v>
+        <v>3.42</v>
       </c>
       <c r="AE81">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AF81">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="AG81">
-        <v>2.08</v>
+        <v>1.91</v>
       </c>
       <c r="AH81">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI81">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AJ81" t="s">
         <v>303</v>
@@ -10696,7 +10696,7 @@
         <v>63</v>
       </c>
       <c r="C82" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="D82" t="s">
         <v>94</v>
@@ -10723,76 +10723,76 @@
         <v>301</v>
       </c>
       <c r="L82">
-        <v>2.22</v>
+        <v>2.75</v>
       </c>
       <c r="M82">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="N82">
-        <v>3.2</v>
+        <v>2.05</v>
       </c>
       <c r="O82">
-        <v>1.62</v>
+        <v>2.2</v>
       </c>
       <c r="P82">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q82">
-        <v>2.63</v>
+        <v>1.67</v>
       </c>
       <c r="R82">
-        <v>1.45</v>
+        <v>1.29</v>
       </c>
       <c r="S82">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="T82">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="U82">
-        <v>1.37</v>
+        <v>1.55</v>
       </c>
       <c r="V82">
-        <v>7.5</v>
+        <v>5.25</v>
       </c>
       <c r="W82">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X82">
         <v>1.01</v>
       </c>
       <c r="Y82">
-        <v>8.5</v>
+        <v>11</v>
       </c>
       <c r="Z82">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="AA82">
-        <v>3.08</v>
+        <v>4.33</v>
       </c>
       <c r="AB82">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AC82">
-        <v>1.75</v>
+        <v>2.16</v>
       </c>
       <c r="AD82">
-        <v>3.42</v>
+        <v>2.45</v>
       </c>
       <c r="AE82">
-        <v>1.29</v>
+        <v>1.48</v>
       </c>
       <c r="AF82">
-        <v>1.76</v>
+        <v>1.55</v>
       </c>
       <c r="AG82">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="AH82">
-        <v>6.9</v>
+        <v>3.8</v>
       </c>
       <c r="AI82">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="AJ82" t="s">
         <v>303</v>
@@ -10812,7 +10812,7 @@
         <v>63</v>
       </c>
       <c r="C83" t="s">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="D83" t="s">
         <v>94</v>
@@ -10839,76 +10839,76 @@
         <v>301</v>
       </c>
       <c r="L83">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="M83">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="N83">
-        <v>4.5</v>
+        <v>3.45</v>
       </c>
       <c r="O83">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="P83">
         <v>0</v>
       </c>
       <c r="Q83">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="R83">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S83">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="T83">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="U83">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="V83">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="W83">
+        <v>1.11</v>
+      </c>
+      <c r="X83">
+        <v>1.04</v>
+      </c>
+      <c r="Y83">
+        <v>13</v>
+      </c>
+      <c r="Z83">
+        <v>1.22</v>
+      </c>
+      <c r="AA83">
+        <v>4</v>
+      </c>
+      <c r="AB83">
+        <v>1.74</v>
+      </c>
+      <c r="AC83">
+        <v>1.97</v>
+      </c>
+      <c r="AD83">
+        <v>2.78</v>
+      </c>
+      <c r="AE83">
+        <v>1.42</v>
+      </c>
+      <c r="AF83">
+        <v>1.75</v>
+      </c>
+      <c r="AG83">
+        <v>2.05</v>
+      </c>
+      <c r="AH83">
+        <v>5</v>
+      </c>
+      <c r="AI83">
         <v>1.17</v>
-      </c>
-      <c r="X83">
-        <v>0</v>
-      </c>
-      <c r="Y83">
-        <v>0</v>
-      </c>
-      <c r="Z83">
-        <v>1.12</v>
-      </c>
-      <c r="AA83">
-        <v>5.25</v>
-      </c>
-      <c r="AB83">
-        <v>1.48</v>
-      </c>
-      <c r="AC83">
-        <v>2.52</v>
-      </c>
-      <c r="AD83">
-        <v>2.13</v>
-      </c>
-      <c r="AE83">
-        <v>1.62</v>
-      </c>
-      <c r="AF83">
-        <v>1.48</v>
-      </c>
-      <c r="AG83">
-        <v>2.4</v>
-      </c>
-      <c r="AH83">
-        <v>3.4</v>
-      </c>
-      <c r="AI83">
-        <v>1.29</v>
       </c>
       <c r="AJ83" t="s">
         <v>303</v>
@@ -10955,22 +10955,22 @@
         <v>301</v>
       </c>
       <c r="L84">
-        <v>1.45</v>
+        <v>2.98</v>
       </c>
       <c r="M84">
-        <v>3.8</v>
+        <v>3.07</v>
       </c>
       <c r="N84">
-        <v>6</v>
+        <v>2.18</v>
       </c>
       <c r="O84">
-        <v>1.36</v>
+        <v>2.2</v>
       </c>
       <c r="P84">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="Q84">
-        <v>3.1</v>
+        <v>1.73</v>
       </c>
       <c r="R84">
         <v>1.25</v>
@@ -10979,16 +10979,16 @@
         <v>3.75</v>
       </c>
       <c r="T84">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="U84">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="V84">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="W84">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="X84">
         <v>1.01</v>
@@ -10997,34 +10997,34 @@
         <v>17</v>
       </c>
       <c r="Z84">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AA84">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="AB84">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AC84">
-        <v>2.4</v>
+        <v>2.57</v>
       </c>
       <c r="AD84">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AE84">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AF84">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AG84">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="AH84">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AI84">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AJ84" t="s">
         <v>303</v>
@@ -11044,7 +11044,7 @@
         <v>64</v>
       </c>
       <c r="C85" t="s">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="D85" t="s">
         <v>94</v>
@@ -11071,76 +11071,76 @@
         <v>301</v>
       </c>
       <c r="L85">
-        <v>1.91</v>
+        <v>1.24</v>
       </c>
       <c r="M85">
-        <v>3.6</v>
+        <v>7</v>
       </c>
       <c r="N85">
+        <v>6.6</v>
+      </c>
+      <c r="O85">
+        <v>1.28</v>
+      </c>
+      <c r="P85">
+        <v>27</v>
+      </c>
+      <c r="Q85">
         <v>3.35</v>
       </c>
-      <c r="O85">
-        <v>1.57</v>
-      </c>
-      <c r="P85">
-        <v>0</v>
-      </c>
-      <c r="Q85">
-        <v>2.5</v>
-      </c>
       <c r="R85">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="S85">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="T85">
-        <v>2.33</v>
+        <v>2.05</v>
       </c>
       <c r="U85">
-        <v>1.52</v>
+        <v>1.75</v>
       </c>
       <c r="V85">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W85">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="X85">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y85">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="Z85">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AA85">
-        <v>4.25</v>
+        <v>5.5</v>
       </c>
       <c r="AB85">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AC85">
-        <v>2.25</v>
+        <v>2.81</v>
       </c>
       <c r="AD85">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="AE85">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="AF85">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AG85">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AH85">
-        <v>4</v>
+        <v>3.14</v>
       </c>
       <c r="AI85">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AJ85" t="s">
         <v>303</v>
@@ -11235,10 +11235,10 @@
         <v>5</v>
       </c>
       <c r="AB86">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AC86">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AD86">
         <v>2.05</v>
@@ -11276,7 +11276,7 @@
         <v>64</v>
       </c>
       <c r="C87" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="D87" t="s">
         <v>94</v>
@@ -11303,76 +11303,76 @@
         <v>301</v>
       </c>
       <c r="L87">
-        <v>2.98</v>
+        <v>2.97</v>
       </c>
       <c r="M87">
-        <v>3.07</v>
+        <v>3.11</v>
       </c>
       <c r="N87">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="O87">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="P87">
-        <v>11.5</v>
+        <v>6</v>
       </c>
       <c r="Q87">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="R87">
+        <v>1.57</v>
+      </c>
+      <c r="S87">
+        <v>2.3</v>
+      </c>
+      <c r="T87">
+        <v>3.66</v>
+      </c>
+      <c r="U87">
         <v>1.25</v>
       </c>
-      <c r="S87">
-        <v>3.75</v>
-      </c>
-      <c r="T87">
-        <v>2.25</v>
-      </c>
-      <c r="U87">
-        <v>1.57</v>
-      </c>
       <c r="V87">
-        <v>5.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W87">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="X87">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="Y87">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="Z87">
-        <v>1.18</v>
+        <v>1.48</v>
       </c>
       <c r="AA87">
-        <v>4.75</v>
+        <v>2.37</v>
       </c>
       <c r="AB87">
-        <v>1.53</v>
+        <v>2.52</v>
       </c>
       <c r="AC87">
-        <v>2.35</v>
+        <v>1.5</v>
       </c>
       <c r="AD87">
-        <v>2.25</v>
+        <v>5.2</v>
       </c>
       <c r="AE87">
-        <v>1.57</v>
+        <v>1.15</v>
       </c>
       <c r="AF87">
-        <v>1.44</v>
+        <v>2.05</v>
       </c>
       <c r="AG87">
-        <v>2.63</v>
+        <v>1.65</v>
       </c>
       <c r="AH87">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AI87">
-        <v>1.22</v>
+        <v>1.02</v>
       </c>
       <c r="AJ87" t="s">
         <v>303</v>
@@ -11419,22 +11419,22 @@
         <v>301</v>
       </c>
       <c r="L88">
-        <v>2.63</v>
+        <v>1.45</v>
       </c>
       <c r="M88">
+        <v>3.8</v>
+      </c>
+      <c r="N88">
+        <v>6</v>
+      </c>
+      <c r="O88">
+        <v>1.36</v>
+      </c>
+      <c r="P88">
+        <v>14</v>
+      </c>
+      <c r="Q88">
         <v>3.1</v>
-      </c>
-      <c r="N88">
-        <v>2.4</v>
-      </c>
-      <c r="O88">
-        <v>2.05</v>
-      </c>
-      <c r="P88">
-        <v>11.5</v>
-      </c>
-      <c r="Q88">
-        <v>1.8</v>
       </c>
       <c r="R88">
         <v>1.25</v>
@@ -11443,22 +11443,22 @@
         <v>3.75</v>
       </c>
       <c r="T88">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="U88">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="V88">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="W88">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X88">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y88">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="Z88">
         <v>1.17</v>
@@ -11467,22 +11467,22 @@
         <v>5</v>
       </c>
       <c r="AB88">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AC88">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="AD88">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AE88">
         <v>1.61</v>
       </c>
       <c r="AF88">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AG88">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="AH88">
         <v>3.8</v>
@@ -11508,7 +11508,7 @@
         <v>64</v>
       </c>
       <c r="C89" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D89" t="s">
         <v>94</v>
@@ -11535,76 +11535,76 @@
         <v>301</v>
       </c>
       <c r="L89">
-        <v>3.14</v>
+        <v>2.63</v>
       </c>
       <c r="M89">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="N89">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="O89">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="P89">
-        <v>6</v>
+        <v>11.5</v>
       </c>
       <c r="Q89">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="R89">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="S89">
-        <v>2.3</v>
+        <v>3.75</v>
       </c>
       <c r="T89">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="U89">
+        <v>1.62</v>
+      </c>
+      <c r="V89">
+        <v>5</v>
+      </c>
+      <c r="W89">
+        <v>1.17</v>
+      </c>
+      <c r="X89">
+        <v>1.04</v>
+      </c>
+      <c r="Y89">
+        <v>10</v>
+      </c>
+      <c r="Z89">
+        <v>1.17</v>
+      </c>
+      <c r="AA89">
+        <v>5</v>
+      </c>
+      <c r="AB89">
+        <v>1.54</v>
+      </c>
+      <c r="AC89">
+        <v>2.38</v>
+      </c>
+      <c r="AD89">
+        <v>2.2</v>
+      </c>
+      <c r="AE89">
+        <v>1.61</v>
+      </c>
+      <c r="AF89">
+        <v>1.44</v>
+      </c>
+      <c r="AG89">
+        <v>2.63</v>
+      </c>
+      <c r="AH89">
+        <v>3.8</v>
+      </c>
+      <c r="AI89">
         <v>1.25</v>
-      </c>
-      <c r="V89">
-        <v>7.5</v>
-      </c>
-      <c r="W89">
-        <v>1.01</v>
-      </c>
-      <c r="X89">
-        <v>1.12</v>
-      </c>
-      <c r="Y89">
-        <v>6.05</v>
-      </c>
-      <c r="Z89">
-        <v>1.53</v>
-      </c>
-      <c r="AA89">
-        <v>2.45</v>
-      </c>
-      <c r="AB89">
-        <v>2.6</v>
-      </c>
-      <c r="AC89">
-        <v>1.46</v>
-      </c>
-      <c r="AD89">
-        <v>5.2</v>
-      </c>
-      <c r="AE89">
-        <v>1.1</v>
-      </c>
-      <c r="AF89">
-        <v>2.05</v>
-      </c>
-      <c r="AG89">
-        <v>1.7</v>
-      </c>
-      <c r="AH89">
-        <v>10</v>
-      </c>
-      <c r="AI89">
-        <v>1.02</v>
       </c>
       <c r="AJ89" t="s">
         <v>303</v>
@@ -11624,7 +11624,7 @@
         <v>64</v>
       </c>
       <c r="C90" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D90" t="s">
         <v>94</v>
@@ -11651,76 +11651,76 @@
         <v>301</v>
       </c>
       <c r="L90">
-        <v>1.2</v>
+        <v>2.47</v>
       </c>
       <c r="M90">
-        <v>5.2</v>
+        <v>3.07</v>
       </c>
       <c r="N90">
-        <v>6.6</v>
+        <v>2.57</v>
       </c>
       <c r="O90">
-        <v>1.28</v>
+        <v>2.05</v>
       </c>
       <c r="P90">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="Q90">
-        <v>3.35</v>
+        <v>1.83</v>
       </c>
       <c r="R90">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="S90">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="T90">
-        <v>1.96</v>
+        <v>2.5</v>
       </c>
       <c r="U90">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="V90">
-        <v>4.3</v>
+        <v>6.5</v>
       </c>
       <c r="W90">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="X90">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y90">
-        <v>19</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Z90">
+        <v>1.21</v>
+      </c>
+      <c r="AA90">
+        <v>3.74</v>
+      </c>
+      <c r="AB90">
+        <v>1.8</v>
+      </c>
+      <c r="AC90">
+        <v>1.91</v>
+      </c>
+      <c r="AD90">
+        <v>2.74</v>
+      </c>
+      <c r="AE90">
+        <v>1.37</v>
+      </c>
+      <c r="AF90">
+        <v>1.57</v>
+      </c>
+      <c r="AG90">
+        <v>2.25</v>
+      </c>
+      <c r="AH90">
+        <v>4.95</v>
+      </c>
+      <c r="AI90">
         <v>1.11</v>
-      </c>
-      <c r="AA90">
-        <v>5.5</v>
-      </c>
-      <c r="AB90">
-        <v>1.33</v>
-      </c>
-      <c r="AC90">
-        <v>2.75</v>
-      </c>
-      <c r="AD90">
-        <v>2.04</v>
-      </c>
-      <c r="AE90">
-        <v>1.75</v>
-      </c>
-      <c r="AF90">
-        <v>1.67</v>
-      </c>
-      <c r="AG90">
-        <v>2.1</v>
-      </c>
-      <c r="AH90">
-        <v>3.14</v>
-      </c>
-      <c r="AI90">
-        <v>1.22</v>
       </c>
       <c r="AJ90" t="s">
         <v>303</v>
@@ -11740,7 +11740,7 @@
         <v>64</v>
       </c>
       <c r="C91" t="s">
-        <v>93</v>
+        <v>70</v>
       </c>
       <c r="D91" t="s">
         <v>94</v>
@@ -11767,76 +11767,76 @@
         <v>301</v>
       </c>
       <c r="L91">
-        <v>2.47</v>
+        <v>1.74</v>
       </c>
       <c r="M91">
-        <v>3.07</v>
+        <v>3.9</v>
       </c>
       <c r="N91">
-        <v>2.57</v>
+        <v>3.8</v>
       </c>
       <c r="O91">
-        <v>2.05</v>
+        <v>1.57</v>
       </c>
       <c r="P91">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q91">
-        <v>1.83</v>
+        <v>2.5</v>
       </c>
       <c r="R91">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="S91">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="T91">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="U91">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="V91">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="W91">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="X91">
         <v>1</v>
       </c>
       <c r="Y91">
-        <v>9.300000000000001</v>
+        <v>12</v>
       </c>
       <c r="Z91">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AA91">
-        <v>3.74</v>
+        <v>5</v>
       </c>
       <c r="AB91">
-        <v>1.8</v>
+        <v>1.48</v>
       </c>
       <c r="AC91">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="AD91">
-        <v>2.74</v>
+        <v>2.11</v>
       </c>
       <c r="AE91">
-        <v>1.37</v>
+        <v>1.65</v>
       </c>
       <c r="AF91">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AG91">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="AH91">
-        <v>4.95</v>
+        <v>3.34</v>
       </c>
       <c r="AI91">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AJ91" t="s">
         <v>303</v>
@@ -11856,7 +11856,7 @@
         <v>65</v>
       </c>
       <c r="C92" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D92" t="s">
         <v>94</v>
@@ -11883,13 +11883,13 @@
         <v>301</v>
       </c>
       <c r="L92">
-        <v>2.41</v>
+        <v>2.31</v>
       </c>
       <c r="M92">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="N92">
-        <v>3.63</v>
+        <v>2.87</v>
       </c>
       <c r="O92">
         <v>1.83</v>
@@ -11901,10 +11901,10 @@
         <v>2.38</v>
       </c>
       <c r="R92">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="S92">
-        <v>2.45</v>
+        <v>2.12</v>
       </c>
       <c r="T92">
         <v>3.6</v>
@@ -11925,28 +11925,28 @@
         <v>5.75</v>
       </c>
       <c r="Z92">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AA92">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="AB92">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="AC92">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AD92">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="AE92">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF92">
         <v>2.15</v>
       </c>
       <c r="AG92">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AH92">
         <v>8.800000000000001</v>
@@ -11972,7 +11972,7 @@
         <v>65</v>
       </c>
       <c r="C93" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D93" t="s">
         <v>94</v>
@@ -11999,76 +11999,76 @@
         <v>301</v>
       </c>
       <c r="L93">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="M93">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N93">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="O93">
-        <v>2.65</v>
+        <v>1.83</v>
       </c>
       <c r="P93">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="Q93">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="R93">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="S93">
-        <v>2.4</v>
+        <v>2.98</v>
       </c>
       <c r="T93">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="U93">
+        <v>1.39</v>
+      </c>
+      <c r="V93">
+        <v>7.2</v>
+      </c>
+      <c r="W93">
+        <v>1.03</v>
+      </c>
+      <c r="X93">
+        <v>1.05</v>
+      </c>
+      <c r="Y93">
+        <v>10</v>
+      </c>
+      <c r="Z93">
+        <v>1.24</v>
+      </c>
+      <c r="AA93">
+        <v>3.42</v>
+      </c>
+      <c r="AB93">
+        <v>1.9</v>
+      </c>
+      <c r="AC93">
+        <v>1.81</v>
+      </c>
+      <c r="AD93">
+        <v>3.24</v>
+      </c>
+      <c r="AE93">
         <v>1.3</v>
       </c>
-      <c r="V93">
-        <v>8</v>
-      </c>
-      <c r="W93">
-        <v>1.05</v>
-      </c>
-      <c r="X93">
-        <v>1.1</v>
-      </c>
-      <c r="Y93">
-        <v>6.5</v>
-      </c>
-      <c r="Z93">
-        <v>1.48</v>
-      </c>
-      <c r="AA93">
-        <v>2.65</v>
-      </c>
-      <c r="AB93">
-        <v>2.4</v>
-      </c>
-      <c r="AC93">
-        <v>1.55</v>
-      </c>
-      <c r="AD93">
-        <v>4.5</v>
-      </c>
-      <c r="AE93">
-        <v>1.2</v>
-      </c>
       <c r="AF93">
+        <v>1.73</v>
+      </c>
+      <c r="AG93">
         <v>2.05</v>
       </c>
-      <c r="AG93">
-        <v>1.7</v>
-      </c>
       <c r="AH93">
-        <v>9</v>
+        <v>5.5</v>
       </c>
       <c r="AI93">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AJ93" t="s">
         <v>303</v>
@@ -12088,7 +12088,7 @@
         <v>65</v>
       </c>
       <c r="C94" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D94" t="s">
         <v>94</v>
@@ -12115,76 +12115,76 @@
         <v>301</v>
       </c>
       <c r="L94">
-        <v>2.53</v>
+        <v>4</v>
       </c>
       <c r="M94">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="N94">
-        <v>2.53</v>
+        <v>2</v>
       </c>
       <c r="O94">
-        <v>1.83</v>
+        <v>2.65</v>
       </c>
       <c r="P94">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Q94">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="R94">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="S94">
-        <v>2.95</v>
+        <v>2.4</v>
       </c>
       <c r="T94">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="U94">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="V94">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="W94">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X94">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="Y94">
-        <v>10</v>
+        <v>6.5</v>
       </c>
       <c r="Z94">
-        <v>1.24</v>
+        <v>1.48</v>
       </c>
       <c r="AA94">
-        <v>3.42</v>
+        <v>2.65</v>
       </c>
       <c r="AB94">
-        <v>1.92</v>
+        <v>2.4</v>
       </c>
       <c r="AC94">
-        <v>1.85</v>
+        <v>1.55</v>
       </c>
       <c r="AD94">
-        <v>3.24</v>
+        <v>4.5</v>
       </c>
       <c r="AE94">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="AF94">
-        <v>1.73</v>
+        <v>2.05</v>
       </c>
       <c r="AG94">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AH94">
-        <v>5.8</v>
+        <v>9</v>
       </c>
       <c r="AI94">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AJ94" t="s">
         <v>303</v>
@@ -12204,7 +12204,7 @@
         <v>65</v>
       </c>
       <c r="C95" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D95" t="s">
         <v>94</v>
@@ -12231,13 +12231,13 @@
         <v>301</v>
       </c>
       <c r="L95">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="M95">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="N95">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="O95">
         <v>1.33</v>
@@ -12252,16 +12252,16 @@
         <v>1.36</v>
       </c>
       <c r="S95">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="T95">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="U95">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="V95">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="W95">
         <v>1.03</v>
@@ -12273,31 +12273,31 @@
         <v>10</v>
       </c>
       <c r="Z95">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AA95">
         <v>3.3</v>
       </c>
       <c r="AB95">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AC95">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AD95">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="AE95">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="AF95">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AG95">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AH95">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AI95">
         <v>1.1</v>
@@ -12347,76 +12347,76 @@
         <v>301</v>
       </c>
       <c r="L96">
-        <v>2.15</v>
+        <v>2.63</v>
       </c>
       <c r="M96">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N96">
-        <v>2.93</v>
+        <v>2.4</v>
       </c>
       <c r="O96">
+        <v>2</v>
+      </c>
+      <c r="P96">
+        <v>13.5</v>
+      </c>
+      <c r="Q96">
+        <v>1.8</v>
+      </c>
+      <c r="R96">
+        <v>1.22</v>
+      </c>
+      <c r="S96">
+        <v>4</v>
+      </c>
+      <c r="T96">
+        <v>2.1</v>
+      </c>
+      <c r="U96">
         <v>1.67</v>
       </c>
-      <c r="P96">
-        <v>11.5</v>
-      </c>
-      <c r="Q96">
-        <v>2.2</v>
-      </c>
-      <c r="R96">
-        <v>1.3</v>
-      </c>
-      <c r="S96">
-        <v>3.4</v>
-      </c>
-      <c r="T96">
-        <v>2.38</v>
-      </c>
-      <c r="U96">
-        <v>1.53</v>
-      </c>
       <c r="V96">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="W96">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="X96">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y96">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="Z96">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AA96">
-        <v>4.33</v>
+        <v>5.25</v>
       </c>
       <c r="AB96">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="AC96">
-        <v>2.15</v>
+        <v>2.75</v>
       </c>
       <c r="AD96">
-        <v>2.55</v>
+        <v>2.1</v>
       </c>
       <c r="AE96">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AF96">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AG96">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="AH96">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="AI96">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AJ96" t="s">
         <v>303</v>
@@ -12463,76 +12463,76 @@
         <v>301</v>
       </c>
       <c r="L97">
+        <v>2.15</v>
+      </c>
+      <c r="M97">
+        <v>3.2</v>
+      </c>
+      <c r="N97">
+        <v>2.93</v>
+      </c>
+      <c r="O97">
+        <v>1.67</v>
+      </c>
+      <c r="P97">
+        <v>11.5</v>
+      </c>
+      <c r="Q97">
+        <v>2.2</v>
+      </c>
+      <c r="R97">
+        <v>1.3</v>
+      </c>
+      <c r="S97">
+        <v>3.4</v>
+      </c>
+      <c r="T97">
+        <v>2.38</v>
+      </c>
+      <c r="U97">
         <v>1.53</v>
       </c>
-      <c r="M97">
-        <v>3.79</v>
-      </c>
-      <c r="N97">
-        <v>4.9</v>
-      </c>
-      <c r="O97">
-        <v>1.43</v>
-      </c>
-      <c r="P97">
-        <v>10.5</v>
-      </c>
-      <c r="Q97">
-        <v>3.2</v>
-      </c>
-      <c r="R97">
-        <v>1.32</v>
-      </c>
-      <c r="S97">
-        <v>3.1</v>
-      </c>
-      <c r="T97">
-        <v>2.45</v>
-      </c>
-      <c r="U97">
-        <v>1.49</v>
-      </c>
       <c r="V97">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="W97">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X97">
         <v>1.04</v>
       </c>
       <c r="Y97">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Z97">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AA97">
-        <v>3.7</v>
+        <v>4.33</v>
       </c>
       <c r="AB97">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AC97">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AD97">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="AE97">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="AF97">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AG97">
-        <v>1.83</v>
+        <v>2.38</v>
       </c>
       <c r="AH97">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AI97">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AJ97" t="s">
         <v>303</v>
@@ -12579,22 +12579,22 @@
         <v>301</v>
       </c>
       <c r="L98">
-        <v>2.63</v>
+        <v>1.56</v>
       </c>
       <c r="M98">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="N98">
-        <v>2.4</v>
+        <v>4.9</v>
       </c>
       <c r="O98">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="P98">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Q98">
-        <v>1.8</v>
+        <v>2.88</v>
       </c>
       <c r="R98">
         <v>1.22</v>
@@ -12627,25 +12627,25 @@
         <v>5.25</v>
       </c>
       <c r="AB98">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AC98">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="AD98">
         <v>2.1</v>
       </c>
       <c r="AE98">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AF98">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AG98">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="AH98">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AI98">
         <v>1.28</v>
@@ -12695,76 +12695,76 @@
         <v>301</v>
       </c>
       <c r="L99">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="M99">
-        <v>3.65</v>
+        <v>3.79</v>
       </c>
       <c r="N99">
         <v>4.9</v>
       </c>
       <c r="O99">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="P99">
-        <v>14</v>
+        <v>10.5</v>
       </c>
       <c r="Q99">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="R99">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="S99">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="T99">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="U99">
-        <v>1.67</v>
+        <v>1.49</v>
       </c>
       <c r="V99">
-        <v>4.5</v>
+        <v>5.75</v>
       </c>
       <c r="W99">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="X99">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y99">
-        <v>17</v>
+        <v>10.5</v>
       </c>
       <c r="Z99">
+        <v>1.23</v>
+      </c>
+      <c r="AA99">
+        <v>3.7</v>
+      </c>
+      <c r="AB99">
+        <v>1.7</v>
+      </c>
+      <c r="AC99">
+        <v>2</v>
+      </c>
+      <c r="AD99">
+        <v>2.75</v>
+      </c>
+      <c r="AE99">
+        <v>1.39</v>
+      </c>
+      <c r="AF99">
+        <v>1.85</v>
+      </c>
+      <c r="AG99">
+        <v>1.83</v>
+      </c>
+      <c r="AH99">
+        <v>5</v>
+      </c>
+      <c r="AI99">
         <v>1.15</v>
-      </c>
-      <c r="AA99">
-        <v>5.25</v>
-      </c>
-      <c r="AB99">
-        <v>1.45</v>
-      </c>
-      <c r="AC99">
-        <v>2.55</v>
-      </c>
-      <c r="AD99">
-        <v>2.1</v>
-      </c>
-      <c r="AE99">
-        <v>1.67</v>
-      </c>
-      <c r="AF99">
-        <v>1.5</v>
-      </c>
-      <c r="AG99">
-        <v>2.5</v>
-      </c>
-      <c r="AH99">
-        <v>3.6</v>
-      </c>
-      <c r="AI99">
-        <v>1.28</v>
       </c>
       <c r="AJ99" t="s">
         <v>303</v>
@@ -13016,7 +13016,7 @@
         <v>68</v>
       </c>
       <c r="C102" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D102" t="s">
         <v>94</v>
@@ -13043,13 +13043,13 @@
         <v>301</v>
       </c>
       <c r="L102">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="M102">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="N102">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="O102">
         <v>1.44</v>
@@ -13064,16 +13064,16 @@
         <v>1.33</v>
       </c>
       <c r="S102">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="T102">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="U102">
         <v>1.44</v>
       </c>
       <c r="V102">
-        <v>7.1</v>
+        <v>6.5</v>
       </c>
       <c r="W102">
         <v>1.1</v>
@@ -13082,7 +13082,7 @@
         <v>1.05</v>
       </c>
       <c r="Y102">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z102">
         <v>1.29</v>
@@ -13091,28 +13091,28 @@
         <v>3.5</v>
       </c>
       <c r="AB102">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AC102">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AD102">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="AE102">
         <v>1.3</v>
       </c>
       <c r="AF102">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AG102">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AH102">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AI102">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AJ102" t="s">
         <v>303</v>
@@ -13159,76 +13159,76 @@
         <v>301</v>
       </c>
       <c r="L103">
-        <v>1.52</v>
+        <v>1.79</v>
       </c>
       <c r="M103">
-        <v>3.74</v>
+        <v>3.32</v>
       </c>
       <c r="N103">
-        <v>5.1</v>
+        <v>3.87</v>
       </c>
       <c r="O103">
+        <v>0</v>
+      </c>
+      <c r="P103">
+        <v>0</v>
+      </c>
+      <c r="Q103">
+        <v>0</v>
+      </c>
+      <c r="R103">
+        <v>0</v>
+      </c>
+      <c r="S103">
+        <v>0</v>
+      </c>
+      <c r="T103">
+        <v>0</v>
+      </c>
+      <c r="U103">
+        <v>0</v>
+      </c>
+      <c r="V103">
+        <v>0</v>
+      </c>
+      <c r="W103">
+        <v>0</v>
+      </c>
+      <c r="X103">
+        <v>0</v>
+      </c>
+      <c r="Y103">
+        <v>0</v>
+      </c>
+      <c r="Z103">
+        <v>0</v>
+      </c>
+      <c r="AA103">
+        <v>0</v>
+      </c>
+      <c r="AB103">
         <v>1.4</v>
       </c>
-      <c r="P103">
-        <v>13.5</v>
-      </c>
-      <c r="Q103">
-        <v>3</v>
-      </c>
-      <c r="R103">
-        <v>1.25</v>
-      </c>
-      <c r="S103">
-        <v>3.75</v>
-      </c>
-      <c r="T103">
-        <v>2.2</v>
-      </c>
-      <c r="U103">
-        <v>1.62</v>
-      </c>
-      <c r="V103">
-        <v>5</v>
-      </c>
-      <c r="W103">
-        <v>1.17</v>
-      </c>
-      <c r="X103">
-        <v>1.01</v>
-      </c>
-      <c r="Y103">
-        <v>17</v>
-      </c>
-      <c r="Z103">
-        <v>1.18</v>
-      </c>
-      <c r="AA103">
-        <v>4.75</v>
-      </c>
-      <c r="AB103">
-        <v>1.53</v>
-      </c>
       <c r="AC103">
-        <v>2.35</v>
+        <v>2.75</v>
       </c>
       <c r="AD103">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AE103">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AF103">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG103">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH103">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AI103">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AJ103" t="s">
         <v>303</v>
@@ -13275,76 +13275,76 @@
         <v>301</v>
       </c>
       <c r="L104">
-        <v>1.79</v>
+        <v>2.4</v>
       </c>
       <c r="M104">
-        <v>3.32</v>
+        <v>3.1</v>
       </c>
       <c r="N104">
-        <v>3.87</v>
+        <v>2.63</v>
       </c>
       <c r="O104">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="P104">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Q104">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R104">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S104">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T104">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U104">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V104">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="W104">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X104">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y104">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z104">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AA104">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB104">
+        <v>1.45</v>
+      </c>
+      <c r="AC104">
+        <v>2.55</v>
+      </c>
+      <c r="AD104">
+        <v>2.15</v>
+      </c>
+      <c r="AE104">
+        <v>1.65</v>
+      </c>
+      <c r="AF104">
         <v>1.4</v>
       </c>
-      <c r="AC104">
+      <c r="AG104">
         <v>2.75</v>
       </c>
-      <c r="AD104">
-        <v>1.95</v>
-      </c>
-      <c r="AE104">
-        <v>1.75</v>
-      </c>
-      <c r="AF104">
-        <v>0</v>
-      </c>
-      <c r="AG104">
-        <v>0</v>
-      </c>
       <c r="AH104">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AI104">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AJ104" t="s">
         <v>303</v>
@@ -13391,22 +13391,22 @@
         <v>301</v>
       </c>
       <c r="L105">
-        <v>2.4</v>
+        <v>1.52</v>
       </c>
       <c r="M105">
-        <v>3.1</v>
+        <v>3.74</v>
       </c>
       <c r="N105">
-        <v>2.63</v>
+        <v>5.1</v>
       </c>
       <c r="O105">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="P105">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="Q105">
-        <v>2.05</v>
+        <v>3</v>
       </c>
       <c r="R105">
         <v>1.25</v>
@@ -13415,16 +13415,16 @@
         <v>3.75</v>
       </c>
       <c r="T105">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="U105">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="V105">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="W105">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X105">
         <v>1.01</v>
@@ -13433,34 +13433,34 @@
         <v>17</v>
       </c>
       <c r="Z105">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AA105">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="AB105">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="AC105">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="AD105">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AE105">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AF105">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="AG105">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="AH105">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="AI105">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AJ105" t="s">
         <v>303</v>

--- a/jogos_2025-07-19.xlsx
+++ b/jogos_2025-07-19.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="870" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="870" uniqueCount="315">
   <si>
     <t>Date</t>
   </si>
@@ -232,30 +232,30 @@
     <t>Australia New South Wales NPL</t>
   </si>
   <si>
+    <t>South Korea K League 2</t>
+  </si>
+  <si>
     <t>Japan J1 League</t>
   </si>
   <si>
+    <t>South Korea K League 1</t>
+  </si>
+  <si>
     <t>China China League One</t>
   </si>
   <si>
-    <t>South Korea K League 1</t>
-  </si>
-  <si>
-    <t>South Korea K League 2</t>
-  </si>
-  <si>
     <t>China Chinese Super League</t>
   </si>
   <si>
     <t>Norway Eliteserien</t>
   </si>
   <si>
+    <t>Sweden Allsvenskan</t>
+  </si>
+  <si>
     <t>Sweden Superettan</t>
   </si>
   <si>
-    <t>Sweden Allsvenskan</t>
-  </si>
-  <si>
     <t>Kazakhstan Kazakhstan Premier League</t>
   </si>
   <si>
@@ -268,30 +268,30 @@
     <t>Estonia Meistriliiga</t>
   </si>
   <si>
+    <t>Chile Primera B</t>
+  </si>
+  <si>
     <t>Chile Primera División</t>
   </si>
   <si>
-    <t>Chile Primera B</t>
-  </si>
-  <si>
     <t>Argentina Primera División</t>
   </si>
   <si>
     <t>Argentina Prim B Nacional</t>
   </si>
   <si>
+    <t>Brazil Serie B</t>
+  </si>
+  <si>
     <t>Brazil Serie A</t>
   </si>
   <si>
-    <t>Brazil Serie B</t>
+    <t>Brazil Serie C</t>
   </si>
   <si>
     <t>USA USL Championship</t>
   </si>
   <si>
-    <t>Brazil Serie C</t>
-  </si>
-  <si>
     <t>Canada Canadian Premier League</t>
   </si>
   <si>
@@ -316,42 +316,42 @@
     <t>Sutherland Sharks</t>
   </si>
   <si>
+    <t>Seoul E-Land</t>
+  </si>
+  <si>
+    <t>Tokyo</t>
+  </si>
+  <si>
+    <t>Hwaseong</t>
+  </si>
+  <si>
+    <t>Gangwon</t>
+  </si>
+  <si>
+    <t>Gimpo Citizen</t>
+  </si>
+  <si>
     <t>Shonan Bellmare</t>
   </si>
   <si>
+    <t>Jeju United</t>
+  </si>
+  <si>
+    <t>Jeonnam Dragons</t>
+  </si>
+  <si>
+    <t>Pohang Steelers</t>
+  </si>
+  <si>
     <t>Yanbian Longding</t>
   </si>
   <si>
-    <t>Pohang Steelers</t>
-  </si>
-  <si>
-    <t>Jeju United</t>
-  </si>
-  <si>
-    <t>Tokyo</t>
-  </si>
-  <si>
-    <t>Hwaseong</t>
-  </si>
-  <si>
-    <t>Seoul E-Land</t>
-  </si>
-  <si>
-    <t>Gangwon</t>
-  </si>
-  <si>
-    <t>Jeonnam Dragons</t>
-  </si>
-  <si>
-    <t>Gimpo Citizen</t>
+    <t>Suzhou Dongwu</t>
   </si>
   <si>
     <t>Dalian Zhixing</t>
   </si>
   <si>
-    <t>Suzhou Dongwu</t>
-  </si>
-  <si>
     <t>Shenyang Urban</t>
   </si>
   <si>
@@ -370,27 +370,27 @@
     <t>KFUM</t>
   </si>
   <si>
+    <t>Öster</t>
+  </si>
+  <si>
+    <t>Oddevold</t>
+  </si>
+  <si>
     <t>Östersunds FK</t>
   </si>
   <si>
+    <t>Kairat</t>
+  </si>
+  <si>
     <t>Djurgården</t>
   </si>
   <si>
     <t>Yelimay Semey</t>
   </si>
   <si>
-    <t>Oddevold</t>
-  </si>
-  <si>
-    <t>Kairat</t>
-  </si>
-  <si>
     <t>Umeå</t>
   </si>
   <si>
-    <t>Öster</t>
-  </si>
-  <si>
     <t>Molde</t>
   </si>
   <si>
@@ -409,28 +409,34 @@
     <t>Degerfors</t>
   </si>
   <si>
+    <t>Harju Jalgpallikool</t>
+  </si>
+  <si>
     <t>Viking</t>
   </si>
   <si>
-    <t>Harju Jalgpallikool</t>
-  </si>
-  <si>
     <t>Tallinna FC Levadia</t>
   </si>
   <si>
+    <t>Cobreloa</t>
+  </si>
+  <si>
     <t>Unión Española</t>
   </si>
   <si>
-    <t>Cobreloa</t>
-  </si>
-  <si>
     <t>San Lorenzo</t>
   </si>
   <si>
+    <t>Talleres Remedios</t>
+  </si>
+  <si>
     <t>Club Atlético Mitre</t>
   </si>
   <si>
-    <t>Talleres Remedios</t>
+    <t>Colo-Colo</t>
+  </si>
+  <si>
+    <t>Goiás</t>
   </si>
   <si>
     <t>Fortaleza</t>
@@ -439,180 +445,174 @@
     <t>Deportes Santa Cruz</t>
   </si>
   <si>
-    <t>Colo-Colo</t>
-  </si>
-  <si>
-    <t>Goiás</t>
-  </si>
-  <si>
     <t>Lanús</t>
   </si>
   <si>
+    <t>Chaco For Ever</t>
+  </si>
+  <si>
+    <t>Deportivo Maipú</t>
+  </si>
+  <si>
+    <t>Colón</t>
+  </si>
+  <si>
+    <t>Atlanta</t>
+  </si>
+  <si>
+    <t>Temperley</t>
+  </si>
+  <si>
+    <t>Gimnasia y Tiro</t>
+  </si>
+  <si>
+    <t>Arsenal de Sarandí</t>
+  </si>
+  <si>
+    <t>Deportivo Madryn</t>
+  </si>
+  <si>
     <t>Colegiales</t>
   </si>
   <si>
-    <t>Deportivo Madryn</t>
+    <t>Alvarado</t>
+  </si>
+  <si>
+    <t>Ituano</t>
+  </si>
+  <si>
+    <t>Estudiantes Caseros</t>
+  </si>
+  <si>
+    <t>All Boys</t>
+  </si>
+  <si>
+    <t>Deportivo Morón</t>
+  </si>
+  <si>
+    <t>Tristán Suárez</t>
   </si>
   <si>
     <t>Rhode Island</t>
   </si>
   <si>
+    <t>Defensores Unidos</t>
+  </si>
+  <si>
     <t>ABC</t>
   </si>
   <si>
-    <t>Alvarado</t>
-  </si>
-  <si>
-    <t>Deportivo Morón</t>
-  </si>
-  <si>
-    <t>Tristán Suárez</t>
+    <t>York9 FC</t>
   </si>
   <si>
     <t>Estudiantes Río Cuarto</t>
   </si>
   <si>
-    <t>Gimnasia y Tiro</t>
-  </si>
-  <si>
-    <t>Estudiantes Caseros</t>
-  </si>
-  <si>
-    <t>Colón</t>
-  </si>
-  <si>
-    <t>Chaco For Ever</t>
-  </si>
-  <si>
-    <t>Temperley</t>
-  </si>
-  <si>
-    <t>Deportivo Maipú</t>
-  </si>
-  <si>
-    <t>York9 FC</t>
-  </si>
-  <si>
-    <t>Defensores Unidos</t>
-  </si>
-  <si>
-    <t>Ituano</t>
-  </si>
-  <si>
-    <t>Atlanta</t>
-  </si>
-  <si>
-    <t>All Boys</t>
-  </si>
-  <si>
-    <t>Arsenal de Sarandí</t>
-  </si>
-  <si>
     <t>Vasco da Gama</t>
   </si>
   <si>
+    <t>Coritiba</t>
+  </si>
+  <si>
+    <t>Coquimbo Unido</t>
+  </si>
+  <si>
     <t>Mirassol</t>
   </si>
   <si>
     <t>Avaí</t>
   </si>
   <si>
-    <t>Coquimbo Unido</t>
-  </si>
-  <si>
-    <t>Coritiba</t>
+    <t>Platense</t>
   </si>
   <si>
     <t>Godoy Cruz</t>
   </si>
   <si>
-    <t>Platense</t>
-  </si>
-  <si>
     <t>Ponte Preta</t>
   </si>
   <si>
     <t>Londrina</t>
   </si>
   <si>
+    <t>Crown Legacy</t>
+  </si>
+  <si>
+    <t>Concepción</t>
+  </si>
+  <si>
     <t>Loudoun United</t>
   </si>
   <si>
-    <t>Concepción</t>
-  </si>
-  <si>
     <t>Chattanooga FC</t>
   </si>
   <si>
-    <t>Crown Legacy</t>
+    <t>Montreal Impact</t>
   </si>
   <si>
     <t>Charleston Battery</t>
   </si>
   <si>
+    <t>New England Revolution</t>
+  </si>
+  <si>
     <t>Atlanta United FC</t>
   </si>
   <si>
-    <t>Montreal Impact</t>
+    <t>Carolina Core</t>
+  </si>
+  <si>
+    <t>Columbus Crew</t>
   </si>
   <si>
     <t>Volta Redonda</t>
   </si>
   <si>
-    <t>Carolina Core</t>
-  </si>
-  <si>
-    <t>New England Revolution</t>
-  </si>
-  <si>
     <t>New York RB</t>
   </si>
   <si>
-    <t>Columbus Crew</t>
-  </si>
-  <si>
     <t>Birmingham Legion</t>
   </si>
   <si>
+    <t>Louisville City</t>
+  </si>
+  <si>
     <t>Instituto</t>
   </si>
   <si>
-    <t>Louisville City</t>
-  </si>
-  <si>
     <t>São Paulo</t>
   </si>
   <si>
     <t>Houston Dynamo</t>
   </si>
   <si>
+    <t>Sporting KC</t>
+  </si>
+  <si>
     <t>Seattle Sounders</t>
   </si>
   <si>
+    <t>Nashville SC</t>
+  </si>
+  <si>
     <t>FC Dallas</t>
   </si>
   <si>
-    <t>Sporting KC</t>
-  </si>
-  <si>
-    <t>Nashville SC</t>
-  </si>
-  <si>
     <t>Real Salt Lake</t>
   </si>
   <si>
     <t>Orange County SC</t>
   </si>
   <si>
+    <t>Los Angeles FC</t>
+  </si>
+  <si>
+    <t>Portland Timbers</t>
+  </si>
+  <si>
     <t>San Diego</t>
   </si>
   <si>
-    <t>Los Angeles FC</t>
-  </si>
-  <si>
-    <t>Portland Timbers</t>
-  </si>
-  <si>
     <t>Minnesota United II</t>
   </si>
   <si>
@@ -628,42 +628,42 @@
     <t>Blacktown City</t>
   </si>
   <si>
+    <t>Seongnam</t>
+  </si>
+  <si>
+    <t>Urawa Reds</t>
+  </si>
+  <si>
+    <t>Busan I'Park</t>
+  </si>
+  <si>
+    <t>Daejeon Citizen</t>
+  </si>
+  <si>
+    <t>Ansan Greeners</t>
+  </si>
+  <si>
     <t>Cerezo Osaka</t>
   </si>
   <si>
+    <t>Anyang</t>
+  </si>
+  <si>
+    <t>Suwon Bluewings</t>
+  </si>
+  <si>
+    <t>Jeonbuk Motors</t>
+  </si>
+  <si>
     <t>Qingdao Red Lions</t>
   </si>
   <si>
-    <t>Jeonbuk Motors</t>
-  </si>
-  <si>
-    <t>Anyang</t>
-  </si>
-  <si>
-    <t>Urawa Reds</t>
-  </si>
-  <si>
-    <t>Busan I'Park</t>
-  </si>
-  <si>
-    <t>Seongnam</t>
-  </si>
-  <si>
-    <t>Daejeon Citizen</t>
-  </si>
-  <si>
-    <t>Suwon Bluewings</t>
-  </si>
-  <si>
-    <t>Ansan Greeners</t>
+    <t>Dongguan United</t>
   </si>
   <si>
     <t>Shandong Luneng</t>
   </si>
   <si>
-    <t>Dongguan United</t>
-  </si>
-  <si>
     <t>Chongqing Tongliang Long</t>
   </si>
   <si>
@@ -682,27 +682,27 @@
     <t>Brann</t>
   </si>
   <si>
+    <t>Malmö FF</t>
+  </si>
+  <si>
+    <t>Örgryte</t>
+  </si>
+  <si>
     <t>Falkenberg</t>
   </si>
   <si>
+    <t>Kaisar</t>
+  </si>
+  <si>
     <t>Elfsborg</t>
   </si>
   <si>
     <t>Zhenys</t>
   </si>
   <si>
-    <t>Örgryte</t>
-  </si>
-  <si>
-    <t>Kaisar</t>
-  </si>
-  <si>
     <t>Örebro</t>
   </si>
   <si>
-    <t>Malmö FF</t>
-  </si>
-  <si>
     <t>Strømsgodset</t>
   </si>
   <si>
@@ -724,19 +724,25 @@
     <t>FK Bodo - Glimt</t>
   </si>
   <si>
+    <t>San Marcos</t>
+  </si>
+  <si>
     <t>Unión La Calera</t>
   </si>
   <si>
-    <t>San Marcos</t>
-  </si>
-  <si>
     <t>Gimnasia La Plata</t>
   </si>
   <si>
+    <t>Defensores de Belgrano</t>
+  </si>
+  <si>
     <t>Central Norte</t>
   </si>
   <si>
-    <t>Defensores de Belgrano</t>
+    <t>La Serena</t>
+  </si>
+  <si>
+    <t>Cuiabá</t>
   </si>
   <si>
     <t>Bahia</t>
@@ -745,180 +751,174 @@
     <t>Recoleta</t>
   </si>
   <si>
-    <t>La Serena</t>
-  </si>
-  <si>
-    <t>Cuiabá</t>
-  </si>
-  <si>
     <t>Rosario Central</t>
   </si>
   <si>
+    <t>Almirante Brown</t>
+  </si>
+  <si>
+    <t>Club Atlético Güemes</t>
+  </si>
+  <si>
+    <t>Gimnasia Mendoza</t>
+  </si>
+  <si>
+    <t>Racing Córdoba</t>
+  </si>
+  <si>
+    <t>Gimnasia Jujuy</t>
+  </si>
+  <si>
+    <t>San Martín Tucumán</t>
+  </si>
+  <si>
+    <t>San Miguel</t>
+  </si>
+  <si>
+    <t>Patronato</t>
+  </si>
+  <si>
     <t>Quilmes</t>
   </si>
   <si>
-    <t>Patronato</t>
+    <t>Ferro Carril Oeste</t>
+  </si>
+  <si>
+    <t>Botafogo PB</t>
+  </si>
+  <si>
+    <t>San Telmo</t>
+  </si>
+  <si>
+    <t>Almagro</t>
+  </si>
+  <si>
+    <t>Chacarita Juniors</t>
+  </si>
+  <si>
+    <t>Los Andes</t>
   </si>
   <si>
     <t>Hartford Athletic</t>
   </si>
   <si>
+    <t>Agropecuario</t>
+  </si>
+  <si>
     <t>Maringá</t>
   </si>
   <si>
-    <t>Ferro Carril Oeste</t>
-  </si>
-  <si>
-    <t>Chacarita Juniors</t>
-  </si>
-  <si>
-    <t>Los Andes</t>
+    <t>Vancouver FC</t>
   </si>
   <si>
     <t>Nueva Chicago</t>
   </si>
   <si>
-    <t>San Martín Tucumán</t>
-  </si>
-  <si>
-    <t>San Telmo</t>
-  </si>
-  <si>
-    <t>Gimnasia Mendoza</t>
-  </si>
-  <si>
-    <t>Almirante Brown</t>
-  </si>
-  <si>
-    <t>Gimnasia Jujuy</t>
-  </si>
-  <si>
-    <t>Club Atlético Güemes</t>
-  </si>
-  <si>
-    <t>Vancouver FC</t>
-  </si>
-  <si>
-    <t>Agropecuario</t>
-  </si>
-  <si>
-    <t>Botafogo PB</t>
-  </si>
-  <si>
-    <t>Racing Córdoba</t>
-  </si>
-  <si>
-    <t>Almagro</t>
-  </si>
-  <si>
-    <t>San Miguel</t>
-  </si>
-  <si>
     <t>Grêmio</t>
   </si>
   <si>
+    <t>Paysandu</t>
+  </si>
+  <si>
+    <t>Deportes Iquique</t>
+  </si>
+  <si>
     <t>Santos</t>
   </si>
   <si>
     <t>Vila Nova</t>
   </si>
   <si>
-    <t>Deportes Iquique</t>
-  </si>
-  <si>
-    <t>Paysandu</t>
+    <t>Vélez Sarsfield</t>
   </si>
   <si>
     <t>Sarmiento</t>
   </si>
   <si>
-    <t>Vélez Sarsfield</t>
-  </si>
-  <si>
     <t>Floresta</t>
   </si>
   <si>
     <t>Itabaiana</t>
   </si>
   <si>
+    <t>Philadelphia Union II</t>
+  </si>
+  <si>
+    <t>Antofagasta</t>
+  </si>
+  <si>
     <t>Oakland Roots</t>
   </si>
   <si>
-    <t>Antofagasta</t>
-  </si>
-  <si>
     <t>Inter Miami II</t>
   </si>
   <si>
-    <t>Philadelphia Union II</t>
+    <t>Chicago Fire</t>
   </si>
   <si>
     <t>Miami FC II</t>
   </si>
   <si>
+    <t>Orlando City</t>
+  </si>
+  <si>
     <t>Charlotte</t>
   </si>
   <si>
-    <t>Chicago Fire</t>
+    <t>Atlanta United II</t>
+  </si>
+  <si>
+    <t>DC United</t>
   </si>
   <si>
     <t>Atlético PR</t>
   </si>
   <si>
-    <t>Atlanta United II</t>
-  </si>
-  <si>
-    <t>Orlando City</t>
-  </si>
-  <si>
     <t>Inter Miami</t>
   </si>
   <si>
-    <t>DC United</t>
-  </si>
-  <si>
     <t>Colorado Springs</t>
   </si>
   <si>
+    <t>Tulsa Roughnecks</t>
+  </si>
+  <si>
     <t>River Plate</t>
   </si>
   <si>
-    <t>Tulsa Roughnecks</t>
-  </si>
-  <si>
     <t>Corinthians</t>
   </si>
   <si>
     <t>Philadelphia Union</t>
   </si>
   <si>
+    <t>New York City</t>
+  </si>
+  <si>
     <t>SJ Earthquakes</t>
   </si>
   <si>
+    <t>Toronto</t>
+  </si>
+  <si>
     <t>St. Louis City</t>
   </si>
   <si>
-    <t>New York City</t>
-  </si>
-  <si>
-    <t>Toronto</t>
-  </si>
-  <si>
     <t>FC Cincinnati</t>
   </si>
   <si>
     <t>Las Vegas Lights</t>
   </si>
   <si>
+    <t>LA Galaxy</t>
+  </si>
+  <si>
+    <t>Minnesota United</t>
+  </si>
+  <si>
     <t>Vancouver Whitecaps</t>
   </si>
   <si>
-    <t>LA Galaxy</t>
-  </si>
-  <si>
-    <t>Minnesota United</t>
-  </si>
-  <si>
     <t>complete</t>
   </si>
   <si>
@@ -934,13 +934,31 @@
     <t>['12', '15', '43', '29', '69', '79']</t>
   </si>
   <si>
+    <t>['57', '81']</t>
+  </si>
+  <si>
+    <t>['59', '89']</t>
+  </si>
+  <si>
+    <t>['50']</t>
+  </si>
+  <si>
     <t>[]</t>
   </si>
   <si>
+    <t>['17']</t>
+  </si>
+  <si>
     <t>['45']</t>
   </si>
   <si>
     <t>['48', '64', '86']</t>
+  </si>
+  <si>
+    <t>['22']</t>
+  </si>
+  <si>
+    <t>['34', '27']</t>
   </si>
 </sst>
 </file>
@@ -1533,7 +1551,7 @@
         <v>304</v>
       </c>
       <c r="AK2" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="AL2" s="3">
         <v>45857</v>
@@ -1649,7 +1667,7 @@
         <v>305</v>
       </c>
       <c r="AK3" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="AL3" s="3">
         <v>45857.1875</v>
@@ -1675,7 +1693,7 @@
         <v>201</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -1687,7 +1705,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L4">
         <v>1.7</v>
@@ -1765,7 +1783,7 @@
         <v>306</v>
       </c>
       <c r="AK4" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL4" s="3">
         <v>45857.20833333334</v>
@@ -1791,19 +1809,19 @@
         <v>202</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5">
         <v>0</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L5">
         <v>2.8</v>
@@ -1878,10 +1896,10 @@
         <v>1.07</v>
       </c>
       <c r="AJ5" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AK5" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="AL5" s="3">
         <v>45857.26041666666</v>
@@ -1907,19 +1925,19 @@
         <v>203</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6">
         <v>0</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L6">
         <v>3.99</v>
@@ -1994,10 +2012,10 @@
         <v>1.15</v>
       </c>
       <c r="AJ6" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AK6" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="AL6" s="3">
         <v>45857.27083333334</v>
@@ -2038,82 +2056,82 @@
         <v>302</v>
       </c>
       <c r="L7">
-        <v>2.74</v>
+        <v>1.83</v>
       </c>
       <c r="M7">
-        <v>3.41</v>
+        <v>3.11</v>
       </c>
       <c r="N7">
-        <v>2.16</v>
+        <v>3.97</v>
       </c>
       <c r="O7">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="P7">
-        <v>9.5</v>
+        <v>12</v>
       </c>
       <c r="Q7">
-        <v>1.9</v>
+        <v>2.31</v>
       </c>
       <c r="R7">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="S7">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="T7">
-        <v>2.45</v>
+        <v>2.84</v>
       </c>
       <c r="U7">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="V7">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="W7">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="X7">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>9.5</v>
+        <v>11</v>
       </c>
       <c r="Z7">
         <v>1.25</v>
       </c>
       <c r="AA7">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="AB7">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="AC7">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="AD7">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="AE7">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="AF7">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AG7">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AH7">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="AI7">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AJ7" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK7" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL7" s="3">
         <v>45857.29166666666</v>
@@ -2154,31 +2172,31 @@
         <v>302</v>
       </c>
       <c r="L8">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="M8">
-        <v>3.45</v>
+        <v>3.26</v>
       </c>
       <c r="N8">
-        <v>5.4</v>
+        <v>2.52</v>
       </c>
       <c r="O8">
-        <v>1.38</v>
+        <v>2.05</v>
       </c>
       <c r="P8">
-        <v>8.9</v>
+        <v>8.5</v>
       </c>
       <c r="Q8">
-        <v>3.58</v>
+        <v>2.05</v>
       </c>
       <c r="R8">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S8">
         <v>2.75</v>
       </c>
       <c r="T8">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="U8">
         <v>1.38</v>
@@ -2190,46 +2208,46 @@
         <v>1.08</v>
       </c>
       <c r="X8">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y8">
         <v>8.5</v>
       </c>
       <c r="Z8">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AA8">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="AB8">
-        <v>2.07</v>
+        <v>1.87</v>
       </c>
       <c r="AC8">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AD8">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AE8">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AF8">
-        <v>2.04</v>
+        <v>1.7</v>
       </c>
       <c r="AG8">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AH8">
         <v>6.5</v>
       </c>
       <c r="AI8">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AJ8" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK8" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL8" s="3">
         <v>45857.29166666666</v>
@@ -2243,7 +2261,7 @@
         <v>43</v>
       </c>
       <c r="C9" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D9" t="s">
         <v>94</v>
@@ -2270,82 +2288,82 @@
         <v>302</v>
       </c>
       <c r="L9">
-        <v>2.85</v>
+        <v>3.41</v>
       </c>
       <c r="M9">
-        <v>3</v>
+        <v>3.32</v>
       </c>
       <c r="N9">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="O9">
-        <v>2.25</v>
+        <v>2.42</v>
       </c>
       <c r="P9">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="Q9">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="R9">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="S9">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="T9">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U9">
         <v>1.3</v>
       </c>
       <c r="V9">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="W9">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X9">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="Y9">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="Z9">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AA9">
-        <v>2.8</v>
+        <v>2.52</v>
       </c>
       <c r="AB9">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AC9">
-        <v>1.79</v>
+        <v>1.53</v>
       </c>
       <c r="AD9">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AE9">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AF9">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AG9">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AH9">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="AI9">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AJ9" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK9" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL9" s="3">
         <v>45857.29166666666</v>
@@ -2386,22 +2404,22 @@
         <v>302</v>
       </c>
       <c r="L10">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="M10">
-        <v>3.03</v>
+        <v>3.12</v>
       </c>
       <c r="N10">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="O10">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="P10">
         <v>8</v>
       </c>
       <c r="Q10">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="R10">
         <v>1.42</v>
@@ -2428,40 +2446,40 @@
         <v>8</v>
       </c>
       <c r="Z10">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AA10">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="AB10">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AC10">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="AD10">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="AE10">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AF10">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AG10">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AH10">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="AI10">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AJ10" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK10" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL10" s="3">
         <v>45857.29166666666</v>
@@ -2502,82 +2520,82 @@
         <v>302</v>
       </c>
       <c r="L11">
+        <v>1.74</v>
+      </c>
+      <c r="M11">
+        <v>3.28</v>
+      </c>
+      <c r="N11">
+        <v>4.2</v>
+      </c>
+      <c r="O11">
+        <v>1.53</v>
+      </c>
+      <c r="P11">
+        <v>6.75</v>
+      </c>
+      <c r="Q11">
+        <v>3.18</v>
+      </c>
+      <c r="R11">
+        <v>1.48</v>
+      </c>
+      <c r="S11">
+        <v>2.56</v>
+      </c>
+      <c r="T11">
+        <v>3.34</v>
+      </c>
+      <c r="U11">
+        <v>1.28</v>
+      </c>
+      <c r="V11">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="W11">
+        <v>1.02</v>
+      </c>
+      <c r="X11">
+        <v>1.05</v>
+      </c>
+      <c r="Y11">
+        <v>8</v>
+      </c>
+      <c r="Z11">
+        <v>1.5</v>
+      </c>
+      <c r="AA11">
         <v>2.4</v>
       </c>
-      <c r="M11">
-        <v>3.26</v>
-      </c>
-      <c r="N11">
-        <v>2.52</v>
-      </c>
-      <c r="O11">
-        <v>2.05</v>
-      </c>
-      <c r="P11">
-        <v>8.5</v>
-      </c>
-      <c r="Q11">
-        <v>2.05</v>
-      </c>
-      <c r="R11">
-        <v>1.4</v>
-      </c>
-      <c r="S11">
-        <v>2.75</v>
-      </c>
-      <c r="T11">
-        <v>2.8</v>
-      </c>
-      <c r="U11">
-        <v>1.38</v>
-      </c>
-      <c r="V11">
-        <v>7</v>
-      </c>
-      <c r="W11">
-        <v>1.08</v>
-      </c>
-      <c r="X11">
-        <v>1.06</v>
-      </c>
-      <c r="Y11">
-        <v>8.5</v>
-      </c>
-      <c r="Z11">
-        <v>1.3</v>
-      </c>
-      <c r="AA11">
-        <v>3.35</v>
-      </c>
       <c r="AB11">
-        <v>1.87</v>
+        <v>2.3</v>
       </c>
       <c r="AC11">
-        <v>1.83</v>
+        <v>1.5</v>
       </c>
       <c r="AD11">
-        <v>3.4</v>
+        <v>4.8</v>
       </c>
       <c r="AE11">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AF11">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="AG11">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AH11">
-        <v>6.5</v>
+        <v>9</v>
       </c>
       <c r="AI11">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="AJ11" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK11" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL11" s="3">
         <v>45857.29166666666</v>
@@ -2591,7 +2609,7 @@
         <v>43</v>
       </c>
       <c r="C12" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D12" t="s">
         <v>94</v>
@@ -2618,82 +2636,82 @@
         <v>302</v>
       </c>
       <c r="L12">
+        <v>2.74</v>
+      </c>
+      <c r="M12">
         <v>3.41</v>
       </c>
-      <c r="M12">
-        <v>3.32</v>
-      </c>
       <c r="N12">
+        <v>2.16</v>
+      </c>
+      <c r="O12">
+        <v>2.1</v>
+      </c>
+      <c r="P12">
+        <v>9.5</v>
+      </c>
+      <c r="Q12">
         <v>1.9</v>
       </c>
-      <c r="O12">
-        <v>2.42</v>
-      </c>
-      <c r="P12">
-        <v>7.1</v>
-      </c>
-      <c r="Q12">
-        <v>1.78</v>
-      </c>
       <c r="R12">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="S12">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="T12">
-        <v>3.25</v>
+        <v>2.45</v>
       </c>
       <c r="U12">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="V12">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W12">
+        <v>1.12</v>
+      </c>
+      <c r="X12">
         <v>1.05</v>
       </c>
-      <c r="X12">
-        <v>1.04</v>
-      </c>
       <c r="Y12">
-        <v>7.1</v>
+        <v>9.5</v>
       </c>
       <c r="Z12">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="AA12">
-        <v>2.52</v>
+        <v>3.95</v>
       </c>
       <c r="AB12">
-        <v>2.2</v>
+        <v>1.76</v>
       </c>
       <c r="AC12">
-        <v>1.53</v>
+        <v>1.94</v>
       </c>
       <c r="AD12">
-        <v>4.3</v>
+        <v>2.8</v>
       </c>
       <c r="AE12">
-        <v>1.15</v>
+        <v>1.42</v>
       </c>
       <c r="AF12">
-        <v>2.05</v>
+        <v>1.55</v>
       </c>
       <c r="AG12">
-        <v>1.73</v>
+        <v>2.25</v>
       </c>
       <c r="AH12">
-        <v>8.4</v>
+        <v>5</v>
       </c>
       <c r="AI12">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AJ12" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK12" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL12" s="3">
         <v>45857.29166666666</v>
@@ -2707,7 +2725,7 @@
         <v>43</v>
       </c>
       <c r="C13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D13" t="s">
         <v>94</v>
@@ -2734,82 +2752,82 @@
         <v>302</v>
       </c>
       <c r="L13">
-        <v>1.83</v>
+        <v>2.32</v>
       </c>
       <c r="M13">
-        <v>3.11</v>
+        <v>3.03</v>
       </c>
       <c r="N13">
-        <v>3.97</v>
+        <v>2.79</v>
       </c>
       <c r="O13">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="P13">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="Q13">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="R13">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="S13">
-        <v>3.01</v>
+        <v>2.65</v>
       </c>
       <c r="T13">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="U13">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="V13">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="W13">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X13">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="Y13">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="Z13">
+        <v>1.38</v>
+      </c>
+      <c r="AA13">
+        <v>3</v>
+      </c>
+      <c r="AB13">
+        <v>2.1</v>
+      </c>
+      <c r="AC13">
+        <v>1.65</v>
+      </c>
+      <c r="AD13">
+        <v>3.8</v>
+      </c>
+      <c r="AE13">
         <v>1.25</v>
       </c>
-      <c r="AA13">
-        <v>3.6</v>
-      </c>
-      <c r="AB13">
-        <v>1.87</v>
-      </c>
-      <c r="AC13">
-        <v>1.83</v>
-      </c>
-      <c r="AD13">
-        <v>3.2</v>
-      </c>
-      <c r="AE13">
-        <v>1.3</v>
-      </c>
       <c r="AF13">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AG13">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AH13">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="AI13">
         <v>1.08</v>
       </c>
       <c r="AJ13" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK13" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL13" s="3">
         <v>45857.29166666666</v>
@@ -2823,7 +2841,7 @@
         <v>43</v>
       </c>
       <c r="C14" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D14" t="s">
         <v>94</v>
@@ -2850,82 +2868,82 @@
         <v>302</v>
       </c>
       <c r="L14">
-        <v>2.29</v>
+        <v>3.74</v>
       </c>
       <c r="M14">
-        <v>3.12</v>
+        <v>3.5</v>
       </c>
       <c r="N14">
-        <v>2.75</v>
+        <v>1.77</v>
       </c>
       <c r="O14">
+        <v>2.25</v>
+      </c>
+      <c r="P14">
+        <v>13.75</v>
+      </c>
+      <c r="Q14">
+        <v>1.67</v>
+      </c>
+      <c r="R14">
+        <v>1.3</v>
+      </c>
+      <c r="S14">
+        <v>3.3</v>
+      </c>
+      <c r="T14">
+        <v>2.45</v>
+      </c>
+      <c r="U14">
+        <v>1.5</v>
+      </c>
+      <c r="V14">
+        <v>6</v>
+      </c>
+      <c r="W14">
+        <v>1.12</v>
+      </c>
+      <c r="X14">
+        <v>1.01</v>
+      </c>
+      <c r="Y14">
+        <v>11</v>
+      </c>
+      <c r="Z14">
+        <v>1.16</v>
+      </c>
+      <c r="AA14">
+        <v>4.05</v>
+      </c>
+      <c r="AB14">
+        <v>1.65</v>
+      </c>
+      <c r="AC14">
         <v>2</v>
       </c>
-      <c r="P14">
-        <v>8</v>
-      </c>
-      <c r="Q14">
-        <v>2.1</v>
-      </c>
-      <c r="R14">
-        <v>1.42</v>
-      </c>
-      <c r="S14">
-        <v>2.65</v>
-      </c>
-      <c r="T14">
-        <v>2.88</v>
-      </c>
-      <c r="U14">
+      <c r="AD14">
+        <v>2.69</v>
+      </c>
+      <c r="AE14">
         <v>1.36</v>
       </c>
-      <c r="V14">
-        <v>7</v>
-      </c>
-      <c r="W14">
-        <v>1.08</v>
-      </c>
-      <c r="X14">
-        <v>1.07</v>
-      </c>
-      <c r="Y14">
-        <v>8</v>
-      </c>
-      <c r="Z14">
-        <v>1.33</v>
-      </c>
-      <c r="AA14">
-        <v>3.25</v>
-      </c>
-      <c r="AB14">
-        <v>1.93</v>
-      </c>
-      <c r="AC14">
-        <v>1.77</v>
-      </c>
-      <c r="AD14">
-        <v>3.45</v>
-      </c>
-      <c r="AE14">
-        <v>1.3</v>
-      </c>
       <c r="AF14">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AG14">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AH14">
-        <v>6.5</v>
+        <v>5.15</v>
       </c>
       <c r="AI14">
         <v>1.1</v>
       </c>
       <c r="AJ14" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK14" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL14" s="3">
         <v>45857.29166666666</v>
@@ -2939,7 +2957,7 @@
         <v>43</v>
       </c>
       <c r="C15" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D15" t="s">
         <v>94</v>
@@ -2966,82 +2984,82 @@
         <v>302</v>
       </c>
       <c r="L15">
-        <v>3.74</v>
+        <v>2.85</v>
       </c>
       <c r="M15">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="N15">
-        <v>1.77</v>
+        <v>2.3</v>
       </c>
       <c r="O15">
         <v>2.25</v>
       </c>
       <c r="P15">
-        <v>13.75</v>
+        <v>7</v>
       </c>
       <c r="Q15">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="R15">
+        <v>1.48</v>
+      </c>
+      <c r="S15">
+        <v>2.45</v>
+      </c>
+      <c r="T15">
+        <v>3.2</v>
+      </c>
+      <c r="U15">
         <v>1.3</v>
       </c>
-      <c r="S15">
-        <v>3.3</v>
-      </c>
-      <c r="T15">
-        <v>2.45</v>
-      </c>
-      <c r="U15">
-        <v>1.5</v>
-      </c>
       <c r="V15">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="W15">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X15">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="Y15">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="Z15">
-        <v>1.16</v>
+        <v>1.42</v>
       </c>
       <c r="AA15">
-        <v>4.05</v>
+        <v>2.8</v>
       </c>
       <c r="AB15">
-        <v>1.65</v>
+        <v>1.91</v>
       </c>
       <c r="AC15">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="AD15">
-        <v>2.69</v>
+        <v>4.2</v>
       </c>
       <c r="AE15">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AF15">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AG15">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AH15">
-        <v>5.15</v>
+        <v>8.5</v>
       </c>
       <c r="AI15">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AJ15" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK15" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL15" s="3">
         <v>45857.29166666666</v>
@@ -3067,97 +3085,97 @@
         <v>213</v>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16">
         <v>0</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16">
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L16">
-        <v>1.74</v>
+        <v>1.6</v>
       </c>
       <c r="M16">
-        <v>3.28</v>
+        <v>3.44</v>
       </c>
       <c r="N16">
-        <v>4.2</v>
+        <v>5.03</v>
       </c>
       <c r="O16">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="P16">
-        <v>6.75</v>
+        <v>8.9</v>
       </c>
       <c r="Q16">
-        <v>3.18</v>
+        <v>3.58</v>
       </c>
       <c r="R16">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="S16">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="T16">
-        <v>3.34</v>
+        <v>2.65</v>
       </c>
       <c r="U16">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="V16">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="W16">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X16">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y16">
         <v>8</v>
       </c>
       <c r="Z16">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AA16">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="AB16">
-        <v>2.3</v>
+        <v>2.13</v>
       </c>
       <c r="AC16">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AD16">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="AE16">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AF16">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AG16">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AH16">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="AI16">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AJ16" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="AK16" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL16" s="3">
         <v>45857.29166666666</v>
@@ -3171,7 +3189,7 @@
         <v>44</v>
       </c>
       <c r="C17" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D17" t="s">
         <v>94</v>
@@ -3198,82 +3216,82 @@
         <v>302</v>
       </c>
       <c r="L17">
-        <v>2.98</v>
+        <v>1.6</v>
       </c>
       <c r="M17">
-        <v>3.74</v>
+        <v>3.5</v>
       </c>
       <c r="N17">
+        <v>4.8</v>
+      </c>
+      <c r="O17">
+        <v>1.53</v>
+      </c>
+      <c r="P17">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="Q17">
+        <v>2.88</v>
+      </c>
+      <c r="R17">
+        <v>1.4</v>
+      </c>
+      <c r="S17">
+        <v>2.5</v>
+      </c>
+      <c r="T17">
+        <v>3</v>
+      </c>
+      <c r="U17">
+        <v>1.31</v>
+      </c>
+      <c r="V17">
+        <v>7.75</v>
+      </c>
+      <c r="W17">
+        <v>1.02</v>
+      </c>
+      <c r="X17">
+        <v>1.04</v>
+      </c>
+      <c r="Y17">
+        <v>8.5</v>
+      </c>
+      <c r="Z17">
+        <v>1.33</v>
+      </c>
+      <c r="AA17">
+        <v>3</v>
+      </c>
+      <c r="AB17">
+        <v>2.07</v>
+      </c>
+      <c r="AC17">
+        <v>1.67</v>
+      </c>
+      <c r="AD17">
+        <v>3.6</v>
+      </c>
+      <c r="AE17">
+        <v>1.25</v>
+      </c>
+      <c r="AF17">
         <v>2.01</v>
       </c>
-      <c r="O17">
-        <v>2.4</v>
-      </c>
-      <c r="P17">
-        <v>18.75</v>
-      </c>
-      <c r="Q17">
-        <v>1.57</v>
-      </c>
-      <c r="R17">
-        <v>1.25</v>
-      </c>
-      <c r="S17">
-        <v>3.75</v>
-      </c>
-      <c r="T17">
-        <v>2.25</v>
-      </c>
-      <c r="U17">
-        <v>1.57</v>
-      </c>
-      <c r="V17">
-        <v>5.5</v>
-      </c>
-      <c r="W17">
-        <v>1.14</v>
-      </c>
-      <c r="X17">
-        <v>1.01</v>
-      </c>
-      <c r="Y17">
-        <v>13</v>
-      </c>
-      <c r="Z17">
-        <v>1.1</v>
-      </c>
-      <c r="AA17">
-        <v>5</v>
-      </c>
-      <c r="AB17">
-        <v>1.53</v>
-      </c>
-      <c r="AC17">
-        <v>2.25</v>
-      </c>
-      <c r="AD17">
-        <v>2.35</v>
-      </c>
-      <c r="AE17">
-        <v>1.57</v>
-      </c>
-      <c r="AF17">
-        <v>1.53</v>
-      </c>
       <c r="AG17">
-        <v>2.38</v>
+        <v>1.73</v>
       </c>
       <c r="AH17">
-        <v>4.05</v>
+        <v>7</v>
       </c>
       <c r="AI17">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="AJ17" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK17" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL17" s="3">
         <v>45857.33333333334</v>
@@ -3287,7 +3305,7 @@
         <v>44</v>
       </c>
       <c r="C18" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D18" t="s">
         <v>94</v>
@@ -3314,82 +3332,82 @@
         <v>302</v>
       </c>
       <c r="L18">
-        <v>1.64</v>
+        <v>2.98</v>
       </c>
       <c r="M18">
-        <v>3.39</v>
+        <v>3.74</v>
       </c>
       <c r="N18">
-        <v>5.1</v>
+        <v>2.01</v>
       </c>
       <c r="O18">
+        <v>2.4</v>
+      </c>
+      <c r="P18">
+        <v>18.75</v>
+      </c>
+      <c r="Q18">
+        <v>1.57</v>
+      </c>
+      <c r="R18">
+        <v>1.25</v>
+      </c>
+      <c r="S18">
+        <v>3.75</v>
+      </c>
+      <c r="T18">
+        <v>2.25</v>
+      </c>
+      <c r="U18">
+        <v>1.57</v>
+      </c>
+      <c r="V18">
+        <v>5.5</v>
+      </c>
+      <c r="W18">
+        <v>1.14</v>
+      </c>
+      <c r="X18">
+        <v>1.01</v>
+      </c>
+      <c r="Y18">
+        <v>13</v>
+      </c>
+      <c r="Z18">
+        <v>1.1</v>
+      </c>
+      <c r="AA18">
+        <v>5</v>
+      </c>
+      <c r="AB18">
         <v>1.53</v>
       </c>
-      <c r="P18">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="Q18">
-        <v>2.88</v>
-      </c>
-      <c r="R18">
-        <v>1.43</v>
-      </c>
-      <c r="S18">
-        <v>2.66</v>
-      </c>
-      <c r="T18">
-        <v>3.1</v>
-      </c>
-      <c r="U18">
-        <v>1.35</v>
-      </c>
-      <c r="V18">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="W18">
-        <v>1.02</v>
-      </c>
-      <c r="X18">
-        <v>1.06</v>
-      </c>
-      <c r="Y18">
-        <v>8.25</v>
-      </c>
-      <c r="Z18">
-        <v>1.36</v>
-      </c>
-      <c r="AA18">
-        <v>3</v>
-      </c>
-      <c r="AB18">
-        <v>2</v>
-      </c>
       <c r="AC18">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="AD18">
-        <v>3.6</v>
+        <v>2.35</v>
       </c>
       <c r="AE18">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="AF18">
-        <v>2.05</v>
+        <v>1.53</v>
       </c>
       <c r="AG18">
-        <v>1.68</v>
+        <v>2.38</v>
       </c>
       <c r="AH18">
-        <v>7.7</v>
+        <v>4.05</v>
       </c>
       <c r="AI18">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="AJ18" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK18" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL18" s="3">
         <v>45857.33333333334</v>
@@ -3403,7 +3421,7 @@
         <v>44</v>
       </c>
       <c r="C19" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D19" t="s">
         <v>94</v>
@@ -3433,10 +3451,10 @@
         <v>2.5</v>
       </c>
       <c r="M19">
-        <v>2.74</v>
+        <v>2.95</v>
       </c>
       <c r="N19">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="O19">
         <v>1.73</v>
@@ -3448,22 +3466,22 @@
         <v>2.25</v>
       </c>
       <c r="R19">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="S19">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="T19">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="U19">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="V19">
-        <v>7.75</v>
+        <v>7.1</v>
       </c>
       <c r="W19">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X19">
         <v>1.08</v>
@@ -3478,34 +3496,34 @@
         <v>2.9</v>
       </c>
       <c r="AB19">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="AC19">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AD19">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="AE19">
         <v>1.22</v>
       </c>
       <c r="AF19">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AG19">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="AH19">
-        <v>8.5</v>
+        <v>6.15</v>
       </c>
       <c r="AI19">
         <v>1.06</v>
       </c>
       <c r="AJ19" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK19" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL19" s="3">
         <v>45857.33333333334</v>
@@ -3519,7 +3537,7 @@
         <v>45</v>
       </c>
       <c r="C20" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D20" t="s">
         <v>94</v>
@@ -3546,13 +3564,13 @@
         <v>302</v>
       </c>
       <c r="L20">
-        <v>2.49</v>
+        <v>2.39</v>
       </c>
       <c r="M20">
         <v>3.19</v>
       </c>
       <c r="N20">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="O20">
         <v>1.73</v>
@@ -3564,64 +3582,64 @@
         <v>2.3</v>
       </c>
       <c r="R20">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S20">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="T20">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="U20">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="V20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W20">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X20">
         <v>1.05</v>
       </c>
       <c r="Y20">
-        <v>7.75</v>
+        <v>8</v>
       </c>
       <c r="Z20">
         <v>1.36</v>
       </c>
       <c r="AA20">
-        <v>2.95</v>
+        <v>2.83</v>
       </c>
       <c r="AB20">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AC20">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="AD20">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="AE20">
         <v>1.25</v>
       </c>
       <c r="AF20">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AG20">
         <v>1.85</v>
       </c>
       <c r="AH20">
-        <v>7.5</v>
+        <v>7.25</v>
       </c>
       <c r="AI20">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AJ20" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK20" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL20" s="3">
         <v>45857.35416666666</v>
@@ -3734,10 +3752,10 @@
         <v>1.06</v>
       </c>
       <c r="AJ21" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK21" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL21" s="3">
         <v>45857.35763888889</v>
@@ -3850,10 +3868,10 @@
         <v>1.13</v>
       </c>
       <c r="AJ22" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK22" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL22" s="3">
         <v>45857.35763888889</v>
@@ -3966,10 +3984,10 @@
         <v>1.23</v>
       </c>
       <c r="AJ23" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK23" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL23" s="3">
         <v>45857.375</v>
@@ -4082,10 +4100,10 @@
         <v>1.11</v>
       </c>
       <c r="AJ24" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK24" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL24" s="3">
         <v>45857.375</v>
@@ -4126,82 +4144,82 @@
         <v>302</v>
       </c>
       <c r="L25">
-        <v>2.4</v>
+        <v>5.9</v>
       </c>
       <c r="M25">
-        <v>3.15</v>
+        <v>4.2</v>
       </c>
       <c r="N25">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="O25">
-        <v>1.8</v>
+        <v>3.35</v>
       </c>
       <c r="P25">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Q25">
+        <v>1.4</v>
+      </c>
+      <c r="R25">
+        <v>1.3</v>
+      </c>
+      <c r="S25">
+        <v>3.2</v>
+      </c>
+      <c r="T25">
+        <v>2.38</v>
+      </c>
+      <c r="U25">
+        <v>1.53</v>
+      </c>
+      <c r="V25">
+        <v>5.75</v>
+      </c>
+      <c r="W25">
+        <v>1.07</v>
+      </c>
+      <c r="X25">
+        <v>1.04</v>
+      </c>
+      <c r="Y25">
+        <v>11</v>
+      </c>
+      <c r="Z25">
+        <v>1.22</v>
+      </c>
+      <c r="AA25">
+        <v>4.33</v>
+      </c>
+      <c r="AB25">
+        <v>1.65</v>
+      </c>
+      <c r="AC25">
         <v>2.1</v>
       </c>
-      <c r="R25">
-        <v>1.36</v>
-      </c>
-      <c r="S25">
-        <v>3</v>
-      </c>
-      <c r="T25">
-        <v>2.63</v>
-      </c>
-      <c r="U25">
-        <v>1.44</v>
-      </c>
-      <c r="V25">
-        <v>7</v>
-      </c>
-      <c r="W25">
-        <v>1.1</v>
-      </c>
-      <c r="X25">
-        <v>1.06</v>
-      </c>
-      <c r="Y25">
-        <v>9</v>
-      </c>
-      <c r="Z25">
-        <v>1.3</v>
-      </c>
-      <c r="AA25">
-        <v>3.55</v>
-      </c>
-      <c r="AB25">
-        <v>1.81</v>
-      </c>
-      <c r="AC25">
-        <v>1.89</v>
-      </c>
       <c r="AD25">
-        <v>3.25</v>
+        <v>2.65</v>
       </c>
       <c r="AE25">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="AF25">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AG25">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AH25">
-        <v>6.25</v>
+        <v>5</v>
       </c>
       <c r="AI25">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AJ25" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK25" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL25" s="3">
         <v>45857.41666666666</v>
@@ -4242,82 +4260,82 @@
         <v>302</v>
       </c>
       <c r="L26">
-        <v>2.09</v>
+        <v>2.57</v>
       </c>
       <c r="M26">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="N26">
-        <v>2.98</v>
+        <v>2.34</v>
       </c>
       <c r="O26">
-        <v>1.67</v>
+        <v>2.05</v>
       </c>
       <c r="P26">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Q26">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="R26">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S26">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="T26">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="U26">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="V26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W26">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X26">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y26">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Z26">
         <v>1.22</v>
       </c>
       <c r="AA26">
-        <v>3.64</v>
+        <v>4.33</v>
       </c>
       <c r="AB26">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="AC26">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AD26">
-        <v>2.88</v>
+        <v>2.26</v>
       </c>
       <c r="AE26">
-        <v>1.34</v>
+        <v>1.51</v>
       </c>
       <c r="AF26">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AG26">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AH26">
-        <v>5.3</v>
+        <v>4.75</v>
       </c>
       <c r="AI26">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="AJ26" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK26" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL26" s="3">
         <v>45857.41666666666</v>
@@ -4331,7 +4349,7 @@
         <v>48</v>
       </c>
       <c r="C27" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D27" t="s">
         <v>94</v>
@@ -4358,82 +4376,82 @@
         <v>302</v>
       </c>
       <c r="L27">
-        <v>1.77</v>
+        <v>2.4</v>
       </c>
       <c r="M27">
+        <v>3.15</v>
+      </c>
+      <c r="N27">
+        <v>2.6</v>
+      </c>
+      <c r="O27">
+        <v>1.8</v>
+      </c>
+      <c r="P27">
+        <v>9</v>
+      </c>
+      <c r="Q27">
+        <v>2.1</v>
+      </c>
+      <c r="R27">
+        <v>1.36</v>
+      </c>
+      <c r="S27">
+        <v>3</v>
+      </c>
+      <c r="T27">
+        <v>2.63</v>
+      </c>
+      <c r="U27">
+        <v>1.44</v>
+      </c>
+      <c r="V27">
+        <v>7</v>
+      </c>
+      <c r="W27">
+        <v>1.1</v>
+      </c>
+      <c r="X27">
+        <v>1.06</v>
+      </c>
+      <c r="Y27">
+        <v>9</v>
+      </c>
+      <c r="Z27">
+        <v>1.3</v>
+      </c>
+      <c r="AA27">
+        <v>3.55</v>
+      </c>
+      <c r="AB27">
+        <v>1.81</v>
+      </c>
+      <c r="AC27">
+        <v>1.89</v>
+      </c>
+      <c r="AD27">
         <v>3.25</v>
       </c>
-      <c r="N27">
-        <v>4.4</v>
-      </c>
-      <c r="O27">
-        <v>1.61</v>
-      </c>
-      <c r="P27">
-        <v>6.7</v>
-      </c>
-      <c r="Q27">
-        <v>2.89</v>
-      </c>
-      <c r="R27">
-        <v>1.4</v>
-      </c>
-      <c r="S27">
-        <v>2.55</v>
-      </c>
-      <c r="T27">
-        <v>3.2</v>
-      </c>
-      <c r="U27">
-        <v>1.3</v>
-      </c>
-      <c r="V27">
-        <v>8</v>
-      </c>
-      <c r="W27">
-        <v>1.03</v>
-      </c>
-      <c r="X27">
-        <v>1.03</v>
-      </c>
-      <c r="Y27">
-        <v>7.4</v>
-      </c>
-      <c r="Z27">
-        <v>1.32</v>
-      </c>
-      <c r="AA27">
-        <v>2.88</v>
-      </c>
-      <c r="AB27">
-        <v>2.25</v>
-      </c>
-      <c r="AC27">
-        <v>1.53</v>
-      </c>
-      <c r="AD27">
-        <v>3.8</v>
-      </c>
       <c r="AE27">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AF27">
-        <v>2.05</v>
+        <v>1.67</v>
       </c>
       <c r="AG27">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="AH27">
-        <v>6.7</v>
+        <v>6.25</v>
       </c>
       <c r="AI27">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="AJ27" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK27" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL27" s="3">
         <v>45857.41666666666</v>
@@ -4447,7 +4465,7 @@
         <v>48</v>
       </c>
       <c r="C28" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D28" t="s">
         <v>94</v>
@@ -4474,82 +4492,82 @@
         <v>302</v>
       </c>
       <c r="L28">
-        <v>2.57</v>
+        <v>1.26</v>
       </c>
       <c r="M28">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="N28">
-        <v>2.34</v>
+        <v>10</v>
       </c>
       <c r="O28">
-        <v>2.05</v>
+        <v>1.23</v>
       </c>
       <c r="P28">
-        <v>10</v>
+        <v>7.9</v>
       </c>
       <c r="Q28">
-        <v>1.8</v>
+        <v>5.65</v>
       </c>
       <c r="R28">
         <v>1.3</v>
       </c>
       <c r="S28">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="T28">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="U28">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="V28">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="W28">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="X28">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y28">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Z28">
         <v>1.22</v>
       </c>
       <c r="AA28">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="AB28">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AC28">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AD28">
-        <v>2.26</v>
+        <v>2.62</v>
       </c>
       <c r="AE28">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="AF28">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AG28">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="AH28">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="AI28">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AJ28" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK28" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL28" s="3">
         <v>45857.41666666666</v>
@@ -4563,7 +4581,7 @@
         <v>48</v>
       </c>
       <c r="C29" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D29" t="s">
         <v>94</v>
@@ -4590,82 +4608,82 @@
         <v>302</v>
       </c>
       <c r="L29">
-        <v>1.26</v>
+        <v>2.09</v>
       </c>
       <c r="M29">
-        <v>4.8</v>
+        <v>3.25</v>
       </c>
       <c r="N29">
-        <v>10</v>
+        <v>2.98</v>
       </c>
       <c r="O29">
-        <v>1.23</v>
+        <v>1.67</v>
       </c>
       <c r="P29">
-        <v>7.9</v>
+        <v>10.5</v>
       </c>
       <c r="Q29">
-        <v>5.65</v>
+        <v>2.3</v>
       </c>
       <c r="R29">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S29">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T29">
-        <v>2.47</v>
+        <v>2.63</v>
       </c>
       <c r="U29">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="V29">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="W29">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X29">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z29">
         <v>1.22</v>
       </c>
       <c r="AA29">
-        <v>4</v>
+        <v>3.64</v>
       </c>
       <c r="AB29">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AC29">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AD29">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="AE29">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AF29">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AG29">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AH29">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AI29">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="AJ29" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK29" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL29" s="3">
         <v>45857.41666666666</v>
@@ -4679,7 +4697,7 @@
         <v>48</v>
       </c>
       <c r="C30" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D30" t="s">
         <v>94</v>
@@ -4706,82 +4724,82 @@
         <v>302</v>
       </c>
       <c r="L30">
-        <v>2.73</v>
+        <v>1.77</v>
       </c>
       <c r="M30">
-        <v>3.29</v>
+        <v>3.25</v>
       </c>
       <c r="N30">
-        <v>2.23</v>
+        <v>4.4</v>
       </c>
       <c r="O30">
-        <v>2.2</v>
+        <v>1.61</v>
       </c>
       <c r="P30">
-        <v>10</v>
+        <v>6.7</v>
       </c>
       <c r="Q30">
-        <v>1.73</v>
+        <v>2.89</v>
       </c>
       <c r="R30">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="S30">
-        <v>3.25</v>
+        <v>2.55</v>
       </c>
       <c r="T30">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="U30">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="V30">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W30">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="X30">
+        <v>1.03</v>
+      </c>
+      <c r="Y30">
+        <v>7.4</v>
+      </c>
+      <c r="Z30">
+        <v>1.32</v>
+      </c>
+      <c r="AA30">
+        <v>2.88</v>
+      </c>
+      <c r="AB30">
+        <v>2.25</v>
+      </c>
+      <c r="AC30">
+        <v>1.53</v>
+      </c>
+      <c r="AD30">
+        <v>3.8</v>
+      </c>
+      <c r="AE30">
+        <v>1.22</v>
+      </c>
+      <c r="AF30">
+        <v>2.05</v>
+      </c>
+      <c r="AG30">
+        <v>1.7</v>
+      </c>
+      <c r="AH30">
+        <v>6.7</v>
+      </c>
+      <c r="AI30">
         <v>1.05</v>
       </c>
-      <c r="Y30">
-        <v>10</v>
-      </c>
-      <c r="Z30">
-        <v>1.25</v>
-      </c>
-      <c r="AA30">
-        <v>4</v>
-      </c>
-      <c r="AB30">
-        <v>1.67</v>
-      </c>
-      <c r="AC30">
-        <v>2</v>
-      </c>
-      <c r="AD30">
-        <v>2.8</v>
-      </c>
-      <c r="AE30">
-        <v>1.44</v>
-      </c>
-      <c r="AF30">
-        <v>1.57</v>
-      </c>
-      <c r="AG30">
-        <v>2.25</v>
-      </c>
-      <c r="AH30">
-        <v>5.25</v>
-      </c>
-      <c r="AI30">
-        <v>1.17</v>
-      </c>
       <c r="AJ30" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK30" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL30" s="3">
         <v>45857.41666666666</v>
@@ -4822,82 +4840,82 @@
         <v>302</v>
       </c>
       <c r="L31">
-        <v>5.9</v>
+        <v>2.73</v>
       </c>
       <c r="M31">
-        <v>4.2</v>
+        <v>3.29</v>
       </c>
       <c r="N31">
-        <v>1.4</v>
+        <v>2.23</v>
       </c>
       <c r="O31">
-        <v>3.35</v>
+        <v>2.2</v>
       </c>
       <c r="P31">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q31">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="R31">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S31">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T31">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="U31">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="V31">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="W31">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X31">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y31">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Z31">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AA31">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="AB31">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AC31">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AD31">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="AE31">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AF31">
-        <v>1.77</v>
+        <v>1.57</v>
       </c>
       <c r="AG31">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="AH31">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="AI31">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AJ31" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK31" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL31" s="3">
         <v>45857.41666666666</v>
@@ -5010,10 +5028,10 @@
         <v>1.27</v>
       </c>
       <c r="AJ32" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK32" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL32" s="3">
         <v>45857.45833333334</v>
@@ -5126,10 +5144,10 @@
         <v>1.13</v>
       </c>
       <c r="AJ33" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK33" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL33" s="3">
         <v>45857.45833333334</v>
@@ -5242,10 +5260,10 @@
         <v>1.29</v>
       </c>
       <c r="AJ34" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK34" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL34" s="3">
         <v>45857.45833333334</v>
@@ -5259,7 +5277,7 @@
         <v>50</v>
       </c>
       <c r="C35" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D35" t="s">
         <v>94</v>
@@ -5358,10 +5376,10 @@
         <v>1.2</v>
       </c>
       <c r="AJ35" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK35" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL35" s="3">
         <v>45857.5</v>
@@ -5474,10 +5492,10 @@
         <v>1.06</v>
       </c>
       <c r="AJ36" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK36" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL36" s="3">
         <v>45857.5</v>
@@ -5491,7 +5509,7 @@
         <v>51</v>
       </c>
       <c r="C37" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D37" t="s">
         <v>94</v>
@@ -5590,10 +5608,10 @@
         <v>1.13</v>
       </c>
       <c r="AJ37" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK37" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL37" s="3">
         <v>45857.52083333334</v>
@@ -5607,7 +5625,7 @@
         <v>52</v>
       </c>
       <c r="C38" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="D38" t="s">
         <v>94</v>
@@ -5616,7 +5634,7 @@
         <v>131</v>
       </c>
       <c r="F38" t="s">
-        <v>235</v>
+        <v>133</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -5631,85 +5649,85 @@
         <v>0</v>
       </c>
       <c r="K38" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="L38">
-        <v>2.77</v>
+        <v>11</v>
       </c>
       <c r="M38">
-        <v>3.79</v>
+        <v>6.75</v>
       </c>
       <c r="N38">
-        <v>2.02</v>
+        <v>1.13</v>
       </c>
       <c r="O38">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P38">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Q38">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="R38">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S38">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="T38">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U38">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V38">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="W38">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X38">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y38">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="Z38">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AA38">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AB38">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AC38">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AD38">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AE38">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF38">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AG38">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AH38">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AI38">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AJ38" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK38" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL38" s="3">
         <v>45857.54166666666</v>
@@ -5723,7 +5741,7 @@
         <v>52</v>
       </c>
       <c r="C39" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="D39" t="s">
         <v>94</v>
@@ -5732,7 +5750,7 @@
         <v>132</v>
       </c>
       <c r="F39" t="s">
-        <v>133</v>
+        <v>235</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -5747,85 +5765,85 @@
         <v>0</v>
       </c>
       <c r="K39" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="L39">
-        <v>11</v>
+        <v>2.77</v>
       </c>
       <c r="M39">
-        <v>6.75</v>
+        <v>3.79</v>
       </c>
       <c r="N39">
-        <v>1.13</v>
+        <v>2.02</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="T39">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V39">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="W39">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X39">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Z39">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AA39">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AB39">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC39">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD39">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AE39">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF39">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AG39">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AH39">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AI39">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AJ39" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK39" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL39" s="3">
         <v>45857.54166666666</v>
@@ -5848,7 +5866,7 @@
         <v>133</v>
       </c>
       <c r="F40" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -5938,10 +5956,10 @@
         <v>1.4</v>
       </c>
       <c r="AJ40" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK40" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL40" s="3">
         <v>45857.54166666666</v>
@@ -5982,82 +6000,82 @@
         <v>302</v>
       </c>
       <c r="L41">
-        <v>2.53</v>
+        <v>2.05</v>
       </c>
       <c r="M41">
-        <v>3.21</v>
+        <v>3.14</v>
       </c>
       <c r="N41">
-        <v>2.85</v>
+        <v>3.19</v>
       </c>
       <c r="O41">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="P41">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="Q41">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="R41">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="S41">
-        <v>2.63</v>
+        <v>3</v>
       </c>
       <c r="T41">
-        <v>3.25</v>
+        <v>2.62</v>
       </c>
       <c r="U41">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="V41">
-        <v>9</v>
+        <v>5.75</v>
       </c>
       <c r="W41">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X41">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y41">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="Z41">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AA41">
-        <v>2.84</v>
+        <v>3.6</v>
       </c>
       <c r="AB41">
-        <v>2.15</v>
+        <v>1.94</v>
       </c>
       <c r="AC41">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="AD41">
-        <v>3.6</v>
+        <v>2.83</v>
       </c>
       <c r="AE41">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="AF41">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="AG41">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AH41">
-        <v>7.1</v>
+        <v>5.25</v>
       </c>
       <c r="AI41">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AJ41" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK41" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL41" s="3">
         <v>45857.5625</v>
@@ -6098,82 +6116,82 @@
         <v>302</v>
       </c>
       <c r="L42">
-        <v>2.05</v>
+        <v>2.53</v>
       </c>
       <c r="M42">
-        <v>3.14</v>
+        <v>3.21</v>
       </c>
       <c r="N42">
-        <v>3.19</v>
+        <v>2.85</v>
       </c>
       <c r="O42">
+        <v>1.83</v>
+      </c>
+      <c r="P42">
+        <v>7.4</v>
+      </c>
+      <c r="Q42">
+        <v>2.2</v>
+      </c>
+      <c r="R42">
+        <v>1.44</v>
+      </c>
+      <c r="S42">
+        <v>2.63</v>
+      </c>
+      <c r="T42">
+        <v>3.25</v>
+      </c>
+      <c r="U42">
+        <v>1.33</v>
+      </c>
+      <c r="V42">
+        <v>9</v>
+      </c>
+      <c r="W42">
+        <v>1.07</v>
+      </c>
+      <c r="X42">
+        <v>1.03</v>
+      </c>
+      <c r="Y42">
+        <v>7.4</v>
+      </c>
+      <c r="Z42">
+        <v>1.33</v>
+      </c>
+      <c r="AA42">
+        <v>2.84</v>
+      </c>
+      <c r="AB42">
+        <v>2.15</v>
+      </c>
+      <c r="AC42">
         <v>1.67</v>
       </c>
-      <c r="P42">
-        <v>8.4</v>
-      </c>
-      <c r="Q42">
-        <v>2.5</v>
-      </c>
-      <c r="R42">
-        <v>1.33</v>
-      </c>
-      <c r="S42">
-        <v>3</v>
-      </c>
-      <c r="T42">
-        <v>2.62</v>
-      </c>
-      <c r="U42">
-        <v>1.43</v>
-      </c>
-      <c r="V42">
-        <v>5.75</v>
-      </c>
-      <c r="W42">
-        <v>1.1</v>
-      </c>
-      <c r="X42">
-        <v>1.02</v>
-      </c>
-      <c r="Y42">
-        <v>10</v>
-      </c>
-      <c r="Z42">
-        <v>1.32</v>
-      </c>
-      <c r="AA42">
+      <c r="AD42">
         <v>3.6</v>
       </c>
-      <c r="AB42">
-        <v>1.94</v>
-      </c>
-      <c r="AC42">
-        <v>1.76</v>
-      </c>
-      <c r="AD42">
-        <v>2.83</v>
-      </c>
       <c r="AE42">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="AF42">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="AG42">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AH42">
-        <v>5.25</v>
+        <v>7.1</v>
       </c>
       <c r="AI42">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="AJ42" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK42" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL42" s="3">
         <v>45857.5625</v>
@@ -6286,10 +6304,10 @@
         <v>1.03</v>
       </c>
       <c r="AJ43" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK43" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL43" s="3">
         <v>45857.60416666666</v>
@@ -6402,10 +6420,10 @@
         <v>0</v>
       </c>
       <c r="AJ44" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK44" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL44" s="3">
         <v>45857.64583333334</v>
@@ -6518,10 +6536,10 @@
         <v>0</v>
       </c>
       <c r="AJ45" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK45" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL45" s="3">
         <v>45857.64583333334</v>
@@ -6535,7 +6553,7 @@
         <v>56</v>
       </c>
       <c r="C46" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D46" t="s">
         <v>94</v>
@@ -6562,82 +6580,82 @@
         <v>302</v>
       </c>
       <c r="L46">
-        <v>2.4</v>
+        <v>1.34</v>
       </c>
       <c r="M46">
-        <v>2.96</v>
+        <v>4.96</v>
       </c>
       <c r="N46">
+        <v>8.35</v>
+      </c>
+      <c r="O46">
+        <v>1.25</v>
+      </c>
+      <c r="P46">
+        <v>15.25</v>
+      </c>
+      <c r="Q46">
+        <v>4.33</v>
+      </c>
+      <c r="R46">
+        <v>1.3</v>
+      </c>
+      <c r="S46">
+        <v>3.4</v>
+      </c>
+      <c r="T46">
+        <v>2.5</v>
+      </c>
+      <c r="U46">
+        <v>1.5</v>
+      </c>
+      <c r="V46">
+        <v>6</v>
+      </c>
+      <c r="W46">
+        <v>1.13</v>
+      </c>
+      <c r="X46">
+        <v>1.01</v>
+      </c>
+      <c r="Y46">
+        <v>11</v>
+      </c>
+      <c r="Z46">
+        <v>1.17</v>
+      </c>
+      <c r="AA46">
+        <v>4</v>
+      </c>
+      <c r="AB46">
+        <v>1.73</v>
+      </c>
+      <c r="AC46">
+        <v>2.08</v>
+      </c>
+      <c r="AD46">
         <v>2.75</v>
       </c>
-      <c r="O46">
-        <v>1.95</v>
-      </c>
-      <c r="P46">
-        <v>7</v>
-      </c>
-      <c r="Q46">
-        <v>2.15</v>
-      </c>
-      <c r="R46">
-        <v>1.49</v>
-      </c>
-      <c r="S46">
-        <v>2.48</v>
-      </c>
-      <c r="T46">
-        <v>3.14</v>
-      </c>
-      <c r="U46">
-        <v>1.3</v>
-      </c>
-      <c r="V46">
-        <v>8</v>
-      </c>
-      <c r="W46">
-        <v>1.05</v>
-      </c>
-      <c r="X46">
-        <v>1.07</v>
-      </c>
-      <c r="Y46">
-        <v>7</v>
-      </c>
-      <c r="Z46">
-        <v>1.38</v>
-      </c>
-      <c r="AA46">
-        <v>2.8</v>
-      </c>
-      <c r="AB46">
-        <v>2.19</v>
-      </c>
-      <c r="AC46">
-        <v>1.6</v>
-      </c>
-      <c r="AD46">
-        <v>4.2</v>
-      </c>
       <c r="AE46">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="AF46">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AG46">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AH46">
-        <v>8</v>
+        <v>5.3</v>
       </c>
       <c r="AI46">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AJ46" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK46" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL46" s="3">
         <v>45857.66666666666</v>
@@ -6651,7 +6669,7 @@
         <v>56</v>
       </c>
       <c r="C47" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D47" t="s">
         <v>94</v>
@@ -6678,82 +6696,82 @@
         <v>302</v>
       </c>
       <c r="L47">
-        <v>2.67</v>
+        <v>1.73</v>
       </c>
       <c r="M47">
-        <v>3</v>
+        <v>3.06</v>
       </c>
       <c r="N47">
-        <v>2.43</v>
+        <v>4.7</v>
       </c>
       <c r="O47">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="P47">
-        <v>7.2</v>
+        <v>6</v>
       </c>
       <c r="Q47">
+        <v>3.1</v>
+      </c>
+      <c r="R47">
+        <v>1.55</v>
+      </c>
+      <c r="S47">
+        <v>2.3</v>
+      </c>
+      <c r="T47">
+        <v>3.6</v>
+      </c>
+      <c r="U47">
+        <v>1.25</v>
+      </c>
+      <c r="V47">
+        <v>9</v>
+      </c>
+      <c r="W47">
+        <v>1.03</v>
+      </c>
+      <c r="X47">
+        <v>1.09</v>
+      </c>
+      <c r="Y47">
+        <v>5.95</v>
+      </c>
+      <c r="Z47">
+        <v>1.5</v>
+      </c>
+      <c r="AA47">
+        <v>2.4</v>
+      </c>
+      <c r="AB47">
+        <v>2.3</v>
+      </c>
+      <c r="AC47">
+        <v>1.5</v>
+      </c>
+      <c r="AD47">
+        <v>5</v>
+      </c>
+      <c r="AE47">
+        <v>1.15</v>
+      </c>
+      <c r="AF47">
         <v>2.2</v>
       </c>
-      <c r="R47">
-        <v>1.45</v>
-      </c>
-      <c r="S47">
-        <v>2.55</v>
-      </c>
-      <c r="T47">
-        <v>3.04</v>
-      </c>
-      <c r="U47">
-        <v>1.33</v>
-      </c>
-      <c r="V47">
-        <v>8</v>
-      </c>
-      <c r="W47">
-        <v>1.05</v>
-      </c>
-      <c r="X47">
-        <v>1.03</v>
-      </c>
-      <c r="Y47">
-        <v>7.3</v>
-      </c>
-      <c r="Z47">
-        <v>1.35</v>
-      </c>
-      <c r="AA47">
-        <v>3.01</v>
-      </c>
-      <c r="AB47">
-        <v>2.05</v>
-      </c>
-      <c r="AC47">
-        <v>1.65</v>
-      </c>
-      <c r="AD47">
-        <v>3.35</v>
-      </c>
-      <c r="AE47">
-        <v>1.26</v>
-      </c>
-      <c r="AF47">
-        <v>1.78</v>
-      </c>
       <c r="AG47">
-        <v>1.83</v>
+        <v>1.59</v>
       </c>
       <c r="AH47">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AI47">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AJ47" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK47" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL47" s="3">
         <v>45857.66666666666</v>
@@ -6767,7 +6785,7 @@
         <v>56</v>
       </c>
       <c r="C48" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D48" t="s">
         <v>94</v>
@@ -6794,82 +6812,82 @@
         <v>302</v>
       </c>
       <c r="L48">
-        <v>1.34</v>
+        <v>2.4</v>
       </c>
       <c r="M48">
-        <v>4.96</v>
+        <v>2.96</v>
       </c>
       <c r="N48">
-        <v>8.35</v>
+        <v>2.75</v>
       </c>
       <c r="O48">
-        <v>1.25</v>
+        <v>1.95</v>
       </c>
       <c r="P48">
-        <v>15.25</v>
+        <v>7</v>
       </c>
       <c r="Q48">
-        <v>4.33</v>
+        <v>2.15</v>
       </c>
       <c r="R48">
+        <v>1.49</v>
+      </c>
+      <c r="S48">
+        <v>2.48</v>
+      </c>
+      <c r="T48">
+        <v>3.14</v>
+      </c>
+      <c r="U48">
         <v>1.3</v>
       </c>
-      <c r="S48">
-        <v>3.4</v>
-      </c>
-      <c r="T48">
-        <v>2.5</v>
-      </c>
-      <c r="U48">
-        <v>1.5</v>
-      </c>
       <c r="V48">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W48">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="X48">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="Y48">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="Z48">
-        <v>1.17</v>
+        <v>1.38</v>
       </c>
       <c r="AA48">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="AB48">
-        <v>1.73</v>
+        <v>2.19</v>
       </c>
       <c r="AC48">
-        <v>2.08</v>
+        <v>1.6</v>
       </c>
       <c r="AD48">
-        <v>2.75</v>
+        <v>4.2</v>
       </c>
       <c r="AE48">
-        <v>1.35</v>
+        <v>1.18</v>
       </c>
       <c r="AF48">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AG48">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AH48">
-        <v>5.3</v>
+        <v>8</v>
       </c>
       <c r="AI48">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AJ48" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK48" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL48" s="3">
         <v>45857.66666666666</v>
@@ -6883,7 +6901,7 @@
         <v>56</v>
       </c>
       <c r="C49" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D49" t="s">
         <v>94</v>
@@ -6910,82 +6928,82 @@
         <v>302</v>
       </c>
       <c r="L49">
-        <v>1.73</v>
+        <v>2.67</v>
       </c>
       <c r="M49">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="N49">
-        <v>4.7</v>
+        <v>2.43</v>
       </c>
       <c r="O49">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="P49">
+        <v>7.2</v>
+      </c>
+      <c r="Q49">
+        <v>2.2</v>
+      </c>
+      <c r="R49">
+        <v>1.45</v>
+      </c>
+      <c r="S49">
+        <v>2.55</v>
+      </c>
+      <c r="T49">
+        <v>3.04</v>
+      </c>
+      <c r="U49">
+        <v>1.33</v>
+      </c>
+      <c r="V49">
+        <v>8</v>
+      </c>
+      <c r="W49">
+        <v>1.05</v>
+      </c>
+      <c r="X49">
+        <v>1.03</v>
+      </c>
+      <c r="Y49">
+        <v>7.3</v>
+      </c>
+      <c r="Z49">
+        <v>1.35</v>
+      </c>
+      <c r="AA49">
+        <v>3.01</v>
+      </c>
+      <c r="AB49">
+        <v>2.05</v>
+      </c>
+      <c r="AC49">
+        <v>1.65</v>
+      </c>
+      <c r="AD49">
+        <v>3.35</v>
+      </c>
+      <c r="AE49">
+        <v>1.26</v>
+      </c>
+      <c r="AF49">
+        <v>1.78</v>
+      </c>
+      <c r="AG49">
+        <v>1.83</v>
+      </c>
+      <c r="AH49">
         <v>6</v>
       </c>
-      <c r="Q49">
-        <v>3.1</v>
-      </c>
-      <c r="R49">
-        <v>1.55</v>
-      </c>
-      <c r="S49">
-        <v>2.3</v>
-      </c>
-      <c r="T49">
-        <v>3.6</v>
-      </c>
-      <c r="U49">
-        <v>1.25</v>
-      </c>
-      <c r="V49">
-        <v>9</v>
-      </c>
-      <c r="W49">
-        <v>1.03</v>
-      </c>
-      <c r="X49">
-        <v>1.09</v>
-      </c>
-      <c r="Y49">
-        <v>5.95</v>
-      </c>
-      <c r="Z49">
-        <v>1.5</v>
-      </c>
-      <c r="AA49">
-        <v>2.4</v>
-      </c>
-      <c r="AB49">
-        <v>2.3</v>
-      </c>
-      <c r="AC49">
-        <v>1.5</v>
-      </c>
-      <c r="AD49">
-        <v>5</v>
-      </c>
-      <c r="AE49">
-        <v>1.15</v>
-      </c>
-      <c r="AF49">
-        <v>2.2</v>
-      </c>
-      <c r="AG49">
-        <v>1.59</v>
-      </c>
-      <c r="AH49">
-        <v>12</v>
-      </c>
       <c r="AI49">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AJ49" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK49" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL49" s="3">
         <v>45857.66666666666</v>
@@ -7098,10 +7116,10 @@
         <v>1.03</v>
       </c>
       <c r="AJ50" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK50" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL50" s="3">
         <v>45857.6875</v>
@@ -7139,7 +7157,7 @@
         <v>0</v>
       </c>
       <c r="K51" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="L51">
         <v>0</v>
@@ -7214,10 +7232,10 @@
         <v>0</v>
       </c>
       <c r="AJ51" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK51" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL51" s="3">
         <v>45857.70833333334</v>
@@ -7330,10 +7348,10 @@
         <v>0</v>
       </c>
       <c r="AJ52" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK52" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL52" s="3">
         <v>45857.70833333334</v>
@@ -7347,7 +7365,7 @@
         <v>58</v>
       </c>
       <c r="C53" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D53" t="s">
         <v>94</v>
@@ -7374,82 +7392,82 @@
         <v>302</v>
       </c>
       <c r="L53">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="M53">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N53">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O53">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="P53">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Q53">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R53">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S53">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T53">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U53">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V53">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="W53">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X53">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y53">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z53">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AA53">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AB53">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC53">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AD53">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AE53">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF53">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG53">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH53">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AI53">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AJ53" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK53" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL53" s="3">
         <v>45857.70833333334</v>
@@ -7463,7 +7481,7 @@
         <v>58</v>
       </c>
       <c r="C54" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D54" t="s">
         <v>94</v>
@@ -7490,82 +7508,82 @@
         <v>302</v>
       </c>
       <c r="L54">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M54">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N54">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="O54">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="P54">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q54">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R54">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="S54">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="T54">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U54">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V54">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="W54">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X54">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y54">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="Z54">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AA54">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AB54">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC54">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD54">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AE54">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AF54">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG54">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AH54">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AI54">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AJ54" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK54" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL54" s="3">
         <v>45857.70833333334</v>
@@ -7678,10 +7696,10 @@
         <v>0</v>
       </c>
       <c r="AJ55" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK55" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL55" s="3">
         <v>45857.70833333334</v>
@@ -7719,7 +7737,7 @@
         <v>0</v>
       </c>
       <c r="K56" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="L56">
         <v>0</v>
@@ -7794,10 +7812,10 @@
         <v>0</v>
       </c>
       <c r="AJ56" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK56" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL56" s="3">
         <v>45857.70833333334</v>
@@ -7910,10 +7928,10 @@
         <v>0</v>
       </c>
       <c r="AJ57" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK57" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL57" s="3">
         <v>45857.70833333334</v>
@@ -8026,10 +8044,10 @@
         <v>0</v>
       </c>
       <c r="AJ58" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK58" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL58" s="3">
         <v>45857.70833333334</v>
@@ -8142,10 +8160,10 @@
         <v>0</v>
       </c>
       <c r="AJ59" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK59" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL59" s="3">
         <v>45857.70833333334</v>
@@ -8183,7 +8201,7 @@
         <v>0</v>
       </c>
       <c r="K60" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="L60">
         <v>0</v>
@@ -8258,10 +8276,10 @@
         <v>0</v>
       </c>
       <c r="AJ60" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK60" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL60" s="3">
         <v>45857.70833333334</v>
@@ -8275,7 +8293,7 @@
         <v>58</v>
       </c>
       <c r="C61" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D61" t="s">
         <v>94</v>
@@ -8302,82 +8320,82 @@
         <v>302</v>
       </c>
       <c r="L61">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="M61">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N61">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="O61">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="P61">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="Q61">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R61">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S61">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T61">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="U61">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="V61">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="W61">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X61">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y61">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="Z61">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA61">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB61">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC61">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AD61">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AE61">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF61">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG61">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AH61">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AI61">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AJ61" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK61" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL61" s="3">
         <v>45857.70833333334</v>
@@ -8490,10 +8508,10 @@
         <v>0</v>
       </c>
       <c r="AJ62" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK62" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL62" s="3">
         <v>45857.70833333334</v>
@@ -8606,10 +8624,10 @@
         <v>0</v>
       </c>
       <c r="AJ63" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK63" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL63" s="3">
         <v>45857.70833333334</v>
@@ -8647,7 +8665,7 @@
         <v>0</v>
       </c>
       <c r="K64" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="L64">
         <v>0</v>
@@ -8722,10 +8740,10 @@
         <v>0</v>
       </c>
       <c r="AJ64" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK64" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL64" s="3">
         <v>45857.70833333334</v>
@@ -8739,7 +8757,7 @@
         <v>58</v>
       </c>
       <c r="C65" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D65" t="s">
         <v>94</v>
@@ -8766,82 +8784,82 @@
         <v>302</v>
       </c>
       <c r="L65">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M65">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N65">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O65">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="P65">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q65">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R65">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S65">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="T65">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U65">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="V65">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W65">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X65">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y65">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Z65">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AA65">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AB65">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC65">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD65">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AE65">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AF65">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG65">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH65">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AI65">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AJ65" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK65" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL65" s="3">
         <v>45857.70833333334</v>
@@ -8855,7 +8873,7 @@
         <v>58</v>
       </c>
       <c r="C66" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D66" t="s">
         <v>94</v>
@@ -8882,82 +8900,82 @@
         <v>302</v>
       </c>
       <c r="L66">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="M66">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N66">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O66">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="P66">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q66">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R66">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S66">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T66">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U66">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V66">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W66">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X66">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y66">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z66">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AA66">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AB66">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC66">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD66">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AE66">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF66">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG66">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH66">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AI66">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AJ66" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK66" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL66" s="3">
         <v>45857.70833333334</v>
@@ -8971,7 +8989,7 @@
         <v>58</v>
       </c>
       <c r="C67" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D67" t="s">
         <v>94</v>
@@ -8998,82 +9016,82 @@
         <v>302</v>
       </c>
       <c r="L67">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="M67">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N67">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="O67">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="P67">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="Q67">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="R67">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="S67">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="T67">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="U67">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="V67">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="W67">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X67">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Y67">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="Z67">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA67">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB67">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AC67">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AD67">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AE67">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF67">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AG67">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AH67">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AI67">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AJ67" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK67" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL67" s="3">
         <v>45857.70833333334</v>
@@ -9087,7 +9105,7 @@
         <v>58</v>
       </c>
       <c r="C68" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D68" t="s">
         <v>94</v>
@@ -9114,82 +9132,82 @@
         <v>302</v>
       </c>
       <c r="L68">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M68">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N68">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="O68">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="P68">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q68">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R68">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S68">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T68">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U68">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V68">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="W68">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X68">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y68">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Z68">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AA68">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB68">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC68">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD68">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AE68">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF68">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG68">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH68">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AI68">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AJ68" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK68" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL68" s="3">
         <v>45857.70833333334</v>
@@ -9203,7 +9221,7 @@
         <v>58</v>
       </c>
       <c r="C69" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D69" t="s">
         <v>94</v>
@@ -9230,82 +9248,82 @@
         <v>302</v>
       </c>
       <c r="L69">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M69">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N69">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O69">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="P69">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q69">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R69">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S69">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T69">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U69">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V69">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W69">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X69">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y69">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z69">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AA69">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AB69">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC69">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD69">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE69">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF69">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG69">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH69">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AI69">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ69" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK69" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL69" s="3">
         <v>45857.70833333334</v>
@@ -9418,10 +9436,10 @@
         <v>0</v>
       </c>
       <c r="AJ70" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK70" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL70" s="3">
         <v>45857.70833333334</v>
@@ -9435,7 +9453,7 @@
         <v>59</v>
       </c>
       <c r="C71" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D71" t="s">
         <v>94</v>
@@ -9534,10 +9552,10 @@
         <v>1.03</v>
       </c>
       <c r="AJ71" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK71" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL71" s="3">
         <v>45857.72916666666</v>
@@ -9578,25 +9596,25 @@
         <v>302</v>
       </c>
       <c r="L72">
-        <v>2.56</v>
+        <v>1.6</v>
       </c>
       <c r="M72">
-        <v>2.84</v>
+        <v>3.31</v>
       </c>
       <c r="N72">
-        <v>2.65</v>
+        <v>5.2</v>
       </c>
       <c r="O72">
-        <v>1.95</v>
+        <v>1.5</v>
       </c>
       <c r="P72">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="Q72">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="R72">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="S72">
         <v>2.4</v>
@@ -9611,49 +9629,49 @@
         <v>9</v>
       </c>
       <c r="W72">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X72">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y72">
         <v>6.5</v>
       </c>
       <c r="Z72">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AA72">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AB72">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AC72">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AD72">
-        <v>4.8</v>
+        <v>4.33</v>
       </c>
       <c r="AE72">
         <v>1.18</v>
       </c>
       <c r="AF72">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="AG72">
-        <v>1.71</v>
+        <v>1.55</v>
       </c>
       <c r="AH72">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="AI72">
         <v>1.03</v>
       </c>
       <c r="AJ72" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK72" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL72" s="3">
         <v>45857.77083333334</v>
@@ -9667,7 +9685,7 @@
         <v>60</v>
       </c>
       <c r="C73" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D73" t="s">
         <v>94</v>
@@ -9694,82 +9712,82 @@
         <v>302</v>
       </c>
       <c r="L73">
-        <v>1.88</v>
+        <v>1.47</v>
       </c>
       <c r="M73">
-        <v>2.93</v>
+        <v>4.25</v>
       </c>
       <c r="N73">
-        <v>4.1</v>
+        <v>6.55</v>
       </c>
       <c r="O73">
-        <v>1.9</v>
+        <v>1.36</v>
       </c>
       <c r="P73">
-        <v>5.75</v>
+        <v>12</v>
       </c>
       <c r="Q73">
-        <v>2.37</v>
+        <v>3.5</v>
       </c>
       <c r="R73">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="S73">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="T73">
-        <v>3.64</v>
+        <v>2.63</v>
       </c>
       <c r="U73">
+        <v>1.44</v>
+      </c>
+      <c r="V73">
+        <v>7</v>
+      </c>
+      <c r="W73">
+        <v>1.1</v>
+      </c>
+      <c r="X73">
+        <v>1.01</v>
+      </c>
+      <c r="Y73">
+        <v>11</v>
+      </c>
+      <c r="Z73">
         <v>1.22</v>
       </c>
-      <c r="V73">
-        <v>10</v>
-      </c>
-      <c r="W73">
-        <v>1.02</v>
-      </c>
-      <c r="X73">
+      <c r="AA73">
+        <v>3.52</v>
+      </c>
+      <c r="AB73">
+        <v>1.85</v>
+      </c>
+      <c r="AC73">
+        <v>1.95</v>
+      </c>
+      <c r="AD73">
+        <v>2.98</v>
+      </c>
+      <c r="AE73">
+        <v>1.3</v>
+      </c>
+      <c r="AF73">
+        <v>1.91</v>
+      </c>
+      <c r="AG73">
+        <v>1.8</v>
+      </c>
+      <c r="AH73">
+        <v>5.8</v>
+      </c>
+      <c r="AI73">
         <v>1.07</v>
       </c>
-      <c r="Y73">
-        <v>5.75</v>
-      </c>
-      <c r="Z73">
-        <v>1.53</v>
-      </c>
-      <c r="AA73">
-        <v>2.25</v>
-      </c>
-      <c r="AB73">
-        <v>2.73</v>
-      </c>
-      <c r="AC73">
-        <v>1.4</v>
-      </c>
-      <c r="AD73">
-        <v>5.69</v>
-      </c>
-      <c r="AE73">
-        <v>1.13</v>
-      </c>
-      <c r="AF73">
-        <v>2.2</v>
-      </c>
-      <c r="AG73">
-        <v>1.64</v>
-      </c>
-      <c r="AH73">
-        <v>10</v>
-      </c>
-      <c r="AI73">
-        <v>1.02</v>
-      </c>
       <c r="AJ73" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK73" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL73" s="3">
         <v>45857.77083333334</v>
@@ -9783,7 +9801,7 @@
         <v>60</v>
       </c>
       <c r="C74" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D74" t="s">
         <v>94</v>
@@ -9810,82 +9828,82 @@
         <v>302</v>
       </c>
       <c r="L74">
-        <v>1.47</v>
+        <v>2.56</v>
       </c>
       <c r="M74">
-        <v>4.25</v>
+        <v>2.84</v>
       </c>
       <c r="N74">
-        <v>6.55</v>
+        <v>2.65</v>
       </c>
       <c r="O74">
-        <v>1.36</v>
+        <v>1.95</v>
       </c>
       <c r="P74">
-        <v>12</v>
+        <v>6.75</v>
       </c>
       <c r="Q74">
-        <v>3.5</v>
+        <v>2.2</v>
       </c>
       <c r="R74">
-        <v>1.36</v>
+        <v>1.51</v>
       </c>
       <c r="S74">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="T74">
-        <v>2.63</v>
+        <v>3.3</v>
       </c>
       <c r="U74">
+        <v>1.29</v>
+      </c>
+      <c r="V74">
+        <v>9</v>
+      </c>
+      <c r="W74">
+        <v>1.03</v>
+      </c>
+      <c r="X74">
+        <v>1.06</v>
+      </c>
+      <c r="Y74">
+        <v>6.5</v>
+      </c>
+      <c r="Z74">
         <v>1.44</v>
       </c>
-      <c r="V74">
-        <v>7</v>
-      </c>
-      <c r="W74">
-        <v>1.1</v>
-      </c>
-      <c r="X74">
-        <v>1.01</v>
-      </c>
-      <c r="Y74">
-        <v>11</v>
-      </c>
-      <c r="Z74">
-        <v>1.22</v>
-      </c>
       <c r="AA74">
-        <v>3.52</v>
+        <v>2.6</v>
       </c>
       <c r="AB74">
-        <v>1.85</v>
+        <v>2.5</v>
       </c>
       <c r="AC74">
-        <v>1.95</v>
+        <v>1.46</v>
       </c>
       <c r="AD74">
-        <v>2.98</v>
+        <v>4.8</v>
       </c>
       <c r="AE74">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AF74">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="AG74">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="AH74">
-        <v>5.8</v>
+        <v>9</v>
       </c>
       <c r="AI74">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AJ74" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK74" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL74" s="3">
         <v>45857.77083333334</v>
@@ -9899,7 +9917,7 @@
         <v>60</v>
       </c>
       <c r="C75" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D75" t="s">
         <v>94</v>
@@ -9926,82 +9944,82 @@
         <v>302</v>
       </c>
       <c r="L75">
-        <v>1.6</v>
+        <v>1.88</v>
       </c>
       <c r="M75">
-        <v>3.31</v>
+        <v>2.93</v>
       </c>
       <c r="N75">
-        <v>5.2</v>
+        <v>4.1</v>
       </c>
       <c r="O75">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="P75">
-        <v>6.5</v>
+        <v>5.75</v>
       </c>
       <c r="Q75">
-        <v>3.3</v>
+        <v>2.37</v>
       </c>
       <c r="R75">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="S75">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="T75">
-        <v>3.3</v>
+        <v>3.64</v>
       </c>
       <c r="U75">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="V75">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W75">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X75">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Y75">
-        <v>6.5</v>
+        <v>5.75</v>
       </c>
       <c r="Z75">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AA75">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="AB75">
-        <v>2.3</v>
+        <v>2.73</v>
       </c>
       <c r="AC75">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AD75">
-        <v>4.33</v>
+        <v>5.69</v>
       </c>
       <c r="AE75">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AF75">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AG75">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="AH75">
-        <v>9.1</v>
+        <v>10</v>
       </c>
       <c r="AI75">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AJ75" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK75" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL75" s="3">
         <v>45857.77083333334</v>
@@ -10042,70 +10060,70 @@
         <v>302</v>
       </c>
       <c r="L76">
-        <v>1.9</v>
+        <v>2.55</v>
       </c>
       <c r="M76">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="N76">
+        <v>3.1</v>
+      </c>
+      <c r="O76">
+        <v>1.95</v>
+      </c>
+      <c r="P76">
+        <v>5</v>
+      </c>
+      <c r="Q76">
+        <v>2.5</v>
+      </c>
+      <c r="R76">
+        <v>1.73</v>
+      </c>
+      <c r="S76">
+        <v>2</v>
+      </c>
+      <c r="T76">
         <v>4.5</v>
       </c>
-      <c r="O76">
-        <v>1.62</v>
-      </c>
-      <c r="P76">
-        <v>6.25</v>
-      </c>
-      <c r="Q76">
-        <v>3</v>
-      </c>
-      <c r="R76">
-        <v>1.57</v>
-      </c>
-      <c r="S76">
-        <v>2.25</v>
-      </c>
-      <c r="T76">
-        <v>3.75</v>
-      </c>
       <c r="U76">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="V76">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="W76">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X76">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="Y76">
-        <v>6.25</v>
+        <v>5</v>
       </c>
       <c r="Z76">
-        <v>1.53</v>
+        <v>1.77</v>
       </c>
       <c r="AA76">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="AB76">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="AC76">
+        <v>1.3</v>
+      </c>
+      <c r="AD76">
+        <v>7.5</v>
+      </c>
+      <c r="AE76">
+        <v>1.08</v>
+      </c>
+      <c r="AF76">
+        <v>2.63</v>
+      </c>
+      <c r="AG76">
         <v>1.44</v>
-      </c>
-      <c r="AD76">
-        <v>5.25</v>
-      </c>
-      <c r="AE76">
-        <v>1.15</v>
-      </c>
-      <c r="AF76">
-        <v>2.25</v>
-      </c>
-      <c r="AG76">
-        <v>1.57</v>
       </c>
       <c r="AH76">
         <v>10</v>
@@ -10114,10 +10132,10 @@
         <v>1.04</v>
       </c>
       <c r="AJ76" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK76" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL76" s="3">
         <v>45857.78125</v>
@@ -10158,70 +10176,70 @@
         <v>302</v>
       </c>
       <c r="L77">
-        <v>2.55</v>
+        <v>1.9</v>
       </c>
       <c r="M77">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="N77">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="O77">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="P77">
-        <v>5</v>
+        <v>6.25</v>
       </c>
       <c r="Q77">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="R77">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="S77">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="T77">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="U77">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="V77">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="W77">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X77">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="Y77">
-        <v>5</v>
+        <v>6.25</v>
       </c>
       <c r="Z77">
-        <v>1.77</v>
+        <v>1.53</v>
       </c>
       <c r="AA77">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="AB77">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="AC77">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AD77">
-        <v>7.5</v>
+        <v>5.25</v>
       </c>
       <c r="AE77">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AF77">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="AG77">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AH77">
         <v>10</v>
@@ -10230,10 +10248,10 @@
         <v>1.04</v>
       </c>
       <c r="AJ77" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK77" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL77" s="3">
         <v>45857.78125</v>
@@ -10247,7 +10265,7 @@
         <v>62</v>
       </c>
       <c r="C78" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D78" t="s">
         <v>94</v>
@@ -10346,10 +10364,10 @@
         <v>1.01</v>
       </c>
       <c r="AJ78" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK78" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL78" s="3">
         <v>45857.8125</v>
@@ -10363,7 +10381,7 @@
         <v>62</v>
       </c>
       <c r="C79" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D79" t="s">
         <v>94</v>
@@ -10462,10 +10480,10 @@
         <v>1.06</v>
       </c>
       <c r="AJ79" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK79" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL79" s="3">
         <v>45857.8125</v>
@@ -10479,7 +10497,7 @@
         <v>63</v>
       </c>
       <c r="C80" t="s">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="D80" t="s">
         <v>94</v>
@@ -10506,82 +10524,82 @@
         <v>302</v>
       </c>
       <c r="L80">
-        <v>1.51</v>
+        <v>2.75</v>
       </c>
       <c r="M80">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="N80">
-        <v>4.6</v>
+        <v>2.05</v>
       </c>
       <c r="O80">
+        <v>2.2</v>
+      </c>
+      <c r="P80">
+        <v>0</v>
+      </c>
+      <c r="Q80">
+        <v>1.67</v>
+      </c>
+      <c r="R80">
+        <v>1.25</v>
+      </c>
+      <c r="S80">
+        <v>3.6</v>
+      </c>
+      <c r="T80">
+        <v>2.2</v>
+      </c>
+      <c r="U80">
+        <v>1.62</v>
+      </c>
+      <c r="V80">
+        <v>4.75</v>
+      </c>
+      <c r="W80">
+        <v>1.15</v>
+      </c>
+      <c r="X80">
+        <v>1</v>
+      </c>
+      <c r="Y80">
+        <v>12</v>
+      </c>
+      <c r="Z80">
+        <v>1.15</v>
+      </c>
+      <c r="AA80">
+        <v>4.75</v>
+      </c>
+      <c r="AB80">
         <v>1.5</v>
       </c>
-      <c r="P80">
-        <v>0</v>
-      </c>
-      <c r="Q80">
-        <v>2.75</v>
-      </c>
-      <c r="R80">
-        <v>1.3</v>
-      </c>
-      <c r="S80">
-        <v>3.2</v>
-      </c>
-      <c r="T80">
+      <c r="AC80">
         <v>2.4</v>
       </c>
-      <c r="U80">
-        <v>1.5</v>
-      </c>
-      <c r="V80">
-        <v>5.5</v>
-      </c>
-      <c r="W80">
-        <v>1.1</v>
-      </c>
-      <c r="X80">
-        <v>1.02</v>
-      </c>
-      <c r="Y80">
-        <v>10</v>
-      </c>
-      <c r="Z80">
-        <v>1.23</v>
-      </c>
-      <c r="AA80">
-        <v>3.9</v>
-      </c>
-      <c r="AB80">
-        <v>1.65</v>
-      </c>
-      <c r="AC80">
-        <v>2.05</v>
-      </c>
       <c r="AD80">
-        <v>2.9</v>
+        <v>2.25</v>
       </c>
       <c r="AE80">
-        <v>1.41</v>
+        <v>1.57</v>
       </c>
       <c r="AF80">
-        <v>1.8</v>
+        <v>1.47</v>
       </c>
       <c r="AG80">
-        <v>1.93</v>
+        <v>2.4</v>
       </c>
       <c r="AH80">
-        <v>5.2</v>
+        <v>3.6</v>
       </c>
       <c r="AI80">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AJ80" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK80" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL80" s="3">
         <v>45857.83333333334</v>
@@ -10595,7 +10613,7 @@
         <v>63</v>
       </c>
       <c r="C81" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D81" t="s">
         <v>94</v>
@@ -10694,10 +10712,10 @@
         <v>1.1</v>
       </c>
       <c r="AJ81" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK81" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL81" s="3">
         <v>45857.83333333334</v>
@@ -10711,7 +10729,7 @@
         <v>63</v>
       </c>
       <c r="C82" t="s">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="D82" t="s">
         <v>94</v>
@@ -10738,82 +10756,82 @@
         <v>302</v>
       </c>
       <c r="L82">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="M82">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="N82">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O82">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="P82">
         <v>0</v>
       </c>
       <c r="Q82">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="R82">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="S82">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="T82">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="U82">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="V82">
-        <v>3.8</v>
+        <v>5.5</v>
       </c>
       <c r="W82">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="X82">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y82">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z82">
-        <v>1.09</v>
+        <v>1.23</v>
       </c>
       <c r="AA82">
-        <v>6</v>
+        <v>3.9</v>
       </c>
       <c r="AB82">
-        <v>1.36</v>
+        <v>1.65</v>
       </c>
       <c r="AC82">
+        <v>2.05</v>
+      </c>
+      <c r="AD82">
         <v>2.9</v>
       </c>
-      <c r="AD82">
-        <v>1.91</v>
-      </c>
       <c r="AE82">
-        <v>1.82</v>
+        <v>1.41</v>
       </c>
       <c r="AF82">
-        <v>1.44</v>
+        <v>1.8</v>
       </c>
       <c r="AG82">
-        <v>2.6</v>
+        <v>1.93</v>
       </c>
       <c r="AH82">
-        <v>2.92</v>
+        <v>5.2</v>
       </c>
       <c r="AI82">
-        <v>1.31</v>
+        <v>1.12</v>
       </c>
       <c r="AJ82" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK82" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL82" s="3">
         <v>45857.83333333334</v>
@@ -10854,82 +10872,82 @@
         <v>302</v>
       </c>
       <c r="L83">
-        <v>2.75</v>
+        <v>1.55</v>
       </c>
       <c r="M83">
+        <v>4.1</v>
+      </c>
+      <c r="N83">
+        <v>4.5</v>
+      </c>
+      <c r="O83">
+        <v>1.4</v>
+      </c>
+      <c r="P83">
+        <v>0</v>
+      </c>
+      <c r="Q83">
+        <v>2.88</v>
+      </c>
+      <c r="R83">
+        <v>1.2</v>
+      </c>
+      <c r="S83">
+        <v>4</v>
+      </c>
+      <c r="T83">
+        <v>1.95</v>
+      </c>
+      <c r="U83">
+        <v>1.75</v>
+      </c>
+      <c r="V83">
         <v>3.8</v>
       </c>
-      <c r="N83">
-        <v>2.05</v>
-      </c>
-      <c r="O83">
-        <v>2.2</v>
-      </c>
-      <c r="P83">
-        <v>0</v>
-      </c>
-      <c r="Q83">
-        <v>1.67</v>
-      </c>
-      <c r="R83">
-        <v>1.25</v>
-      </c>
-      <c r="S83">
-        <v>3.6</v>
-      </c>
-      <c r="T83">
-        <v>2.2</v>
-      </c>
-      <c r="U83">
-        <v>1.62</v>
-      </c>
-      <c r="V83">
-        <v>4.75</v>
-      </c>
       <c r="W83">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="X83">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y83">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Z83">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="AA83">
-        <v>4.75</v>
+        <v>6</v>
       </c>
       <c r="AB83">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AC83">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="AD83">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="AE83">
-        <v>1.57</v>
+        <v>1.82</v>
       </c>
       <c r="AF83">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AG83">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AH83">
-        <v>3.6</v>
+        <v>2.92</v>
       </c>
       <c r="AI83">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AJ83" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK83" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL83" s="3">
         <v>45857.83333333334</v>
@@ -10943,7 +10961,7 @@
         <v>64</v>
       </c>
       <c r="C84" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D84" t="s">
         <v>94</v>
@@ -10970,82 +10988,82 @@
         <v>302</v>
       </c>
       <c r="L84">
-        <v>1.28</v>
+        <v>2.63</v>
       </c>
       <c r="M84">
-        <v>6.3</v>
+        <v>3.1</v>
       </c>
       <c r="N84">
-        <v>6.2</v>
+        <v>2.4</v>
       </c>
       <c r="O84">
-        <v>1.28</v>
+        <v>2.05</v>
       </c>
       <c r="P84">
-        <v>27</v>
+        <v>11.5</v>
       </c>
       <c r="Q84">
-        <v>3.35</v>
+        <v>1.8</v>
       </c>
       <c r="R84">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="S84">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="T84">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="U84">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="V84">
-        <v>3.88</v>
+        <v>5</v>
       </c>
       <c r="W84">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="X84">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y84">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="Z84">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="AA84">
-        <v>5.9</v>
+        <v>5</v>
       </c>
       <c r="AB84">
-        <v>1.38</v>
+        <v>1.54</v>
       </c>
       <c r="AC84">
-        <v>2.81</v>
+        <v>2.38</v>
       </c>
       <c r="AD84">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AE84">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AF84">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="AG84">
-        <v>2.1</v>
+        <v>2.63</v>
       </c>
       <c r="AH84">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="AI84">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AJ84" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK84" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL84" s="3">
         <v>45857.85416666666</v>
@@ -11059,7 +11077,7 @@
         <v>64</v>
       </c>
       <c r="C85" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D85" t="s">
         <v>94</v>
@@ -11086,22 +11104,22 @@
         <v>302</v>
       </c>
       <c r="L85">
-        <v>2.11</v>
+        <v>1.28</v>
       </c>
       <c r="M85">
-        <v>3.12</v>
+        <v>6.3</v>
       </c>
       <c r="N85">
-        <v>3.08</v>
+        <v>6.2</v>
       </c>
       <c r="O85">
-        <v>1.67</v>
+        <v>1.28</v>
       </c>
       <c r="P85">
-        <v>12.5</v>
+        <v>27</v>
       </c>
       <c r="Q85">
-        <v>2.2</v>
+        <v>3.35</v>
       </c>
       <c r="R85">
         <v>1.22</v>
@@ -11110,58 +11128,58 @@
         <v>4</v>
       </c>
       <c r="T85">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="U85">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="V85">
-        <v>4.5</v>
+        <v>3.88</v>
       </c>
       <c r="W85">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X85">
         <v>1.01</v>
       </c>
       <c r="Y85">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="Z85">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="AA85">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="AB85">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AC85">
-        <v>2.63</v>
+        <v>2.81</v>
       </c>
       <c r="AD85">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AE85">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="AF85">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AG85">
-        <v>2.75</v>
+        <v>2.1</v>
       </c>
       <c r="AH85">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="AI85">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AJ85" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK85" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL85" s="3">
         <v>45857.85416666666</v>
@@ -11202,82 +11220,82 @@
         <v>302</v>
       </c>
       <c r="L86">
-        <v>2.63</v>
+        <v>2.47</v>
       </c>
       <c r="M86">
-        <v>3.1</v>
+        <v>3.07</v>
       </c>
       <c r="N86">
-        <v>2.4</v>
+        <v>2.57</v>
       </c>
       <c r="O86">
         <v>2.05</v>
       </c>
       <c r="P86">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="Q86">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="R86">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="S86">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="T86">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="U86">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="V86">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="W86">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="X86">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y86">
-        <v>10</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Z86">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AA86">
-        <v>5</v>
+        <v>3.74</v>
       </c>
       <c r="AB86">
         <v>1.54</v>
       </c>
       <c r="AC86">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AD86">
-        <v>2.33</v>
+        <v>2.74</v>
       </c>
       <c r="AE86">
-        <v>1.53</v>
+        <v>1.37</v>
       </c>
       <c r="AF86">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AG86">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="AH86">
-        <v>3.8</v>
+        <v>4.95</v>
       </c>
       <c r="AI86">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AJ86" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK86" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL86" s="3">
         <v>45857.85416666666</v>
@@ -11291,7 +11309,7 @@
         <v>64</v>
       </c>
       <c r="C87" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D87" t="s">
         <v>94</v>
@@ -11318,82 +11336,82 @@
         <v>302</v>
       </c>
       <c r="L87">
-        <v>2.97</v>
+        <v>2.11</v>
       </c>
       <c r="M87">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="N87">
-        <v>2.17</v>
+        <v>3.08</v>
       </c>
       <c r="O87">
-        <v>2.3</v>
+        <v>1.67</v>
       </c>
       <c r="P87">
-        <v>6</v>
+        <v>12.5</v>
       </c>
       <c r="Q87">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="R87">
-        <v>1.62</v>
+        <v>1.22</v>
       </c>
       <c r="S87">
+        <v>4</v>
+      </c>
+      <c r="T87">
+        <v>2.1</v>
+      </c>
+      <c r="U87">
+        <v>1.67</v>
+      </c>
+      <c r="V87">
+        <v>4.5</v>
+      </c>
+      <c r="W87">
+        <v>1.18</v>
+      </c>
+      <c r="X87">
+        <v>1.01</v>
+      </c>
+      <c r="Y87">
+        <v>17</v>
+      </c>
+      <c r="Z87">
+        <v>1.17</v>
+      </c>
+      <c r="AA87">
+        <v>5</v>
+      </c>
+      <c r="AB87">
+        <v>1.45</v>
+      </c>
+      <c r="AC87">
+        <v>2.63</v>
+      </c>
+      <c r="AD87">
         <v>2.2</v>
       </c>
-      <c r="T87">
-        <v>3.6</v>
-      </c>
-      <c r="U87">
-        <v>1.22</v>
-      </c>
-      <c r="V87">
-        <v>10</v>
-      </c>
-      <c r="W87">
-        <v>1.02</v>
-      </c>
-      <c r="X87">
-        <v>1.11</v>
-      </c>
-      <c r="Y87">
-        <v>5.75</v>
-      </c>
-      <c r="Z87">
-        <v>1.48</v>
-      </c>
-      <c r="AA87">
-        <v>2.37</v>
-      </c>
-      <c r="AB87">
-        <v>2.52</v>
-      </c>
-      <c r="AC87">
-        <v>1.5</v>
-      </c>
-      <c r="AD87">
-        <v>5.2</v>
-      </c>
       <c r="AE87">
-        <v>1.13</v>
+        <v>1.59</v>
       </c>
       <c r="AF87">
-        <v>2.17</v>
+        <v>1.4</v>
       </c>
       <c r="AG87">
-        <v>1.65</v>
+        <v>2.75</v>
       </c>
       <c r="AH87">
-        <v>11.5</v>
+        <v>3.65</v>
       </c>
       <c r="AI87">
-        <v>1.02</v>
+        <v>1.28</v>
       </c>
       <c r="AJ87" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK87" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL87" s="3">
         <v>45857.85416666666</v>
@@ -11506,10 +11524,10 @@
         <v>1.25</v>
       </c>
       <c r="AJ88" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK88" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL88" s="3">
         <v>45857.85416666666</v>
@@ -11550,64 +11568,64 @@
         <v>302</v>
       </c>
       <c r="L89">
-        <v>2.47</v>
+        <v>1.45</v>
       </c>
       <c r="M89">
-        <v>3.07</v>
+        <v>3.8</v>
       </c>
       <c r="N89">
-        <v>2.57</v>
+        <v>6</v>
       </c>
       <c r="O89">
-        <v>2.05</v>
+        <v>1.36</v>
       </c>
       <c r="P89">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Q89">
-        <v>1.83</v>
+        <v>3.1</v>
       </c>
       <c r="R89">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="S89">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="T89">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="U89">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="V89">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="W89">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="X89">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y89">
-        <v>9.300000000000001</v>
+        <v>17</v>
       </c>
       <c r="Z89">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AA89">
-        <v>3.74</v>
+        <v>5</v>
       </c>
       <c r="AB89">
+        <v>1.45</v>
+      </c>
+      <c r="AC89">
+        <v>2.63</v>
+      </c>
+      <c r="AD89">
+        <v>2.3</v>
+      </c>
+      <c r="AE89">
         <v>1.54</v>
-      </c>
-      <c r="AC89">
-        <v>2.3</v>
-      </c>
-      <c r="AD89">
-        <v>2.74</v>
-      </c>
-      <c r="AE89">
-        <v>1.37</v>
       </c>
       <c r="AF89">
         <v>1.57</v>
@@ -11616,16 +11634,16 @@
         <v>2.25</v>
       </c>
       <c r="AH89">
-        <v>4.95</v>
+        <v>3.8</v>
       </c>
       <c r="AI89">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AJ89" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK89" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL89" s="3">
         <v>45857.85416666666</v>
@@ -11639,7 +11657,7 @@
         <v>64</v>
       </c>
       <c r="C90" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="D90" t="s">
         <v>94</v>
@@ -11666,82 +11684,82 @@
         <v>302</v>
       </c>
       <c r="L90">
-        <v>2.98</v>
+        <v>2.97</v>
       </c>
       <c r="M90">
-        <v>3.07</v>
+        <v>3.11</v>
       </c>
       <c r="N90">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="O90">
+        <v>2.3</v>
+      </c>
+      <c r="P90">
+        <v>6</v>
+      </c>
+      <c r="Q90">
+        <v>1.91</v>
+      </c>
+      <c r="R90">
+        <v>1.62</v>
+      </c>
+      <c r="S90">
         <v>2.2</v>
       </c>
-      <c r="P90">
+      <c r="T90">
+        <v>3.6</v>
+      </c>
+      <c r="U90">
+        <v>1.22</v>
+      </c>
+      <c r="V90">
+        <v>10</v>
+      </c>
+      <c r="W90">
+        <v>1.02</v>
+      </c>
+      <c r="X90">
+        <v>1.11</v>
+      </c>
+      <c r="Y90">
+        <v>5.75</v>
+      </c>
+      <c r="Z90">
+        <v>1.48</v>
+      </c>
+      <c r="AA90">
+        <v>2.37</v>
+      </c>
+      <c r="AB90">
+        <v>2.52</v>
+      </c>
+      <c r="AC90">
+        <v>1.5</v>
+      </c>
+      <c r="AD90">
+        <v>5.2</v>
+      </c>
+      <c r="AE90">
+        <v>1.13</v>
+      </c>
+      <c r="AF90">
+        <v>2.17</v>
+      </c>
+      <c r="AG90">
+        <v>1.65</v>
+      </c>
+      <c r="AH90">
         <v>11.5</v>
       </c>
-      <c r="Q90">
-        <v>1.73</v>
-      </c>
-      <c r="R90">
-        <v>1.25</v>
-      </c>
-      <c r="S90">
-        <v>3.75</v>
-      </c>
-      <c r="T90">
-        <v>2.25</v>
-      </c>
-      <c r="U90">
-        <v>1.57</v>
-      </c>
-      <c r="V90">
-        <v>5.5</v>
-      </c>
-      <c r="W90">
-        <v>1.14</v>
-      </c>
-      <c r="X90">
-        <v>1.01</v>
-      </c>
-      <c r="Y90">
-        <v>17</v>
-      </c>
-      <c r="Z90">
-        <v>1.18</v>
-      </c>
-      <c r="AA90">
-        <v>4.75</v>
-      </c>
-      <c r="AB90">
-        <v>1.47</v>
-      </c>
-      <c r="AC90">
-        <v>2.57</v>
-      </c>
-      <c r="AD90">
-        <v>2.15</v>
-      </c>
-      <c r="AE90">
-        <v>1.62</v>
-      </c>
-      <c r="AF90">
-        <v>1.44</v>
-      </c>
-      <c r="AG90">
-        <v>2.63</v>
-      </c>
-      <c r="AH90">
-        <v>4</v>
-      </c>
       <c r="AI90">
-        <v>1.22</v>
+        <v>1.02</v>
       </c>
       <c r="AJ90" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK90" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL90" s="3">
         <v>45857.85416666666</v>
@@ -11782,22 +11800,22 @@
         <v>302</v>
       </c>
       <c r="L91">
-        <v>1.45</v>
+        <v>2.98</v>
       </c>
       <c r="M91">
-        <v>3.8</v>
+        <v>3.07</v>
       </c>
       <c r="N91">
-        <v>6</v>
+        <v>2.18</v>
       </c>
       <c r="O91">
-        <v>1.36</v>
+        <v>2.2</v>
       </c>
       <c r="P91">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="Q91">
-        <v>3.1</v>
+        <v>1.73</v>
       </c>
       <c r="R91">
         <v>1.25</v>
@@ -11806,16 +11824,16 @@
         <v>3.75</v>
       </c>
       <c r="T91">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="U91">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="V91">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="W91">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="X91">
         <v>1.01</v>
@@ -11824,40 +11842,40 @@
         <v>17</v>
       </c>
       <c r="Z91">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AA91">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="AB91">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AC91">
+        <v>2.57</v>
+      </c>
+      <c r="AD91">
+        <v>2.15</v>
+      </c>
+      <c r="AE91">
+        <v>1.62</v>
+      </c>
+      <c r="AF91">
+        <v>1.44</v>
+      </c>
+      <c r="AG91">
         <v>2.63</v>
       </c>
-      <c r="AD91">
-        <v>2.3</v>
-      </c>
-      <c r="AE91">
-        <v>1.54</v>
-      </c>
-      <c r="AF91">
-        <v>1.57</v>
-      </c>
-      <c r="AG91">
-        <v>2.25</v>
-      </c>
       <c r="AH91">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AI91">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AJ91" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK91" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL91" s="3">
         <v>45857.85416666666</v>
@@ -11871,7 +11889,7 @@
         <v>65</v>
       </c>
       <c r="C92" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D92" t="s">
         <v>94</v>
@@ -11970,10 +11988,10 @@
         <v>1.11</v>
       </c>
       <c r="AJ92" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK92" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL92" s="3">
         <v>45857.875</v>
@@ -11987,7 +12005,7 @@
         <v>65</v>
       </c>
       <c r="C93" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D93" t="s">
         <v>94</v>
@@ -12014,82 +12032,82 @@
         <v>302</v>
       </c>
       <c r="L93">
-        <v>4</v>
+        <v>1.87</v>
       </c>
       <c r="M93">
-        <v>3.1</v>
+        <v>3.53</v>
       </c>
       <c r="N93">
+        <v>3.56</v>
+      </c>
+      <c r="O93">
+        <v>1.33</v>
+      </c>
+      <c r="P93">
+        <v>14.75</v>
+      </c>
+      <c r="Q93">
+        <v>3.5</v>
+      </c>
+      <c r="R93">
+        <v>1.33</v>
+      </c>
+      <c r="S93">
+        <v>3</v>
+      </c>
+      <c r="T93">
+        <v>2.58</v>
+      </c>
+      <c r="U93">
+        <v>1.48</v>
+      </c>
+      <c r="V93">
+        <v>5.75</v>
+      </c>
+      <c r="W93">
+        <v>1.1</v>
+      </c>
+      <c r="X93">
+        <v>1.02</v>
+      </c>
+      <c r="Y93">
+        <v>10</v>
+      </c>
+      <c r="Z93">
+        <v>1.22</v>
+      </c>
+      <c r="AA93">
+        <v>3.6</v>
+      </c>
+      <c r="AB93">
+        <v>1.77</v>
+      </c>
+      <c r="AC93">
+        <v>1.93</v>
+      </c>
+      <c r="AD93">
+        <v>2.85</v>
+      </c>
+      <c r="AE93">
+        <v>1.38</v>
+      </c>
+      <c r="AF93">
+        <v>1.67</v>
+      </c>
+      <c r="AG93">
         <v>2</v>
       </c>
-      <c r="O93">
-        <v>2.65</v>
-      </c>
-      <c r="P93">
-        <v>6.5</v>
-      </c>
-      <c r="Q93">
-        <v>1.75</v>
-      </c>
-      <c r="R93">
-        <v>1.5</v>
-      </c>
-      <c r="S93">
-        <v>2.4</v>
-      </c>
-      <c r="T93">
-        <v>3.2</v>
-      </c>
-      <c r="U93">
-        <v>1.3</v>
-      </c>
-      <c r="V93">
-        <v>8</v>
-      </c>
-      <c r="W93">
-        <v>1.05</v>
-      </c>
-      <c r="X93">
-        <v>1.1</v>
-      </c>
-      <c r="Y93">
-        <v>6.5</v>
-      </c>
-      <c r="Z93">
-        <v>1.48</v>
-      </c>
-      <c r="AA93">
-        <v>2.65</v>
-      </c>
-      <c r="AB93">
-        <v>2.4</v>
-      </c>
-      <c r="AC93">
-        <v>1.55</v>
-      </c>
-      <c r="AD93">
-        <v>4.5</v>
-      </c>
-      <c r="AE93">
-        <v>1.2</v>
-      </c>
-      <c r="AF93">
-        <v>2.05</v>
-      </c>
-      <c r="AG93">
-        <v>1.7</v>
-      </c>
       <c r="AH93">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AI93">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="AJ93" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK93" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL93" s="3">
         <v>45857.875</v>
@@ -12103,7 +12121,7 @@
         <v>65</v>
       </c>
       <c r="C94" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D94" t="s">
         <v>94</v>
@@ -12130,82 +12148,82 @@
         <v>302</v>
       </c>
       <c r="L94">
-        <v>1.87</v>
+        <v>4</v>
       </c>
       <c r="M94">
-        <v>3.53</v>
+        <v>3.1</v>
       </c>
       <c r="N94">
-        <v>3.56</v>
+        <v>2</v>
       </c>
       <c r="O94">
-        <v>1.33</v>
+        <v>2.65</v>
       </c>
       <c r="P94">
-        <v>14.75</v>
+        <v>6.5</v>
       </c>
       <c r="Q94">
-        <v>3.5</v>
+        <v>1.75</v>
       </c>
       <c r="R94">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="S94">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="T94">
-        <v>2.58</v>
+        <v>3.2</v>
       </c>
       <c r="U94">
+        <v>1.3</v>
+      </c>
+      <c r="V94">
+        <v>8</v>
+      </c>
+      <c r="W94">
+        <v>1.05</v>
+      </c>
+      <c r="X94">
+        <v>1.1</v>
+      </c>
+      <c r="Y94">
+        <v>6.5</v>
+      </c>
+      <c r="Z94">
         <v>1.48</v>
       </c>
-      <c r="V94">
-        <v>5.75</v>
-      </c>
-      <c r="W94">
-        <v>1.1</v>
-      </c>
-      <c r="X94">
-        <v>1.02</v>
-      </c>
-      <c r="Y94">
-        <v>10</v>
-      </c>
-      <c r="Z94">
-        <v>1.22</v>
-      </c>
       <c r="AA94">
-        <v>3.6</v>
+        <v>2.65</v>
       </c>
       <c r="AB94">
-        <v>1.77</v>
+        <v>2.4</v>
       </c>
       <c r="AC94">
-        <v>1.93</v>
+        <v>1.55</v>
       </c>
       <c r="AD94">
-        <v>2.85</v>
+        <v>4.5</v>
       </c>
       <c r="AE94">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="AF94">
-        <v>1.67</v>
+        <v>2.05</v>
       </c>
       <c r="AG94">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AH94">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AI94">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AJ94" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK94" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL94" s="3">
         <v>45857.875</v>
@@ -12219,7 +12237,7 @@
         <v>65</v>
       </c>
       <c r="C95" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D95" t="s">
         <v>94</v>
@@ -12318,10 +12336,10 @@
         <v>1.02</v>
       </c>
       <c r="AJ95" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK95" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL95" s="3">
         <v>45857.875</v>
@@ -12434,10 +12452,10 @@
         <v>1.17</v>
       </c>
       <c r="AJ96" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK96" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL96" s="3">
         <v>45857.89583333334</v>
@@ -12478,22 +12496,22 @@
         <v>302</v>
       </c>
       <c r="L97">
-        <v>1.56</v>
+        <v>2.63</v>
       </c>
       <c r="M97">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="N97">
-        <v>4.9</v>
+        <v>2.4</v>
       </c>
       <c r="O97">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="P97">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Q97">
-        <v>2.88</v>
+        <v>1.8</v>
       </c>
       <c r="R97">
         <v>1.22</v>
@@ -12526,34 +12544,34 @@
         <v>5.25</v>
       </c>
       <c r="AB97">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="AC97">
-        <v>2.9</v>
+        <v>2.29</v>
       </c>
       <c r="AD97">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AE97">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AF97">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AG97">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="AH97">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AI97">
         <v>1.28</v>
       </c>
       <c r="AJ97" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK97" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL97" s="3">
         <v>45857.89583333334</v>
@@ -12594,82 +12612,82 @@
         <v>302</v>
       </c>
       <c r="L98">
-        <v>2.15</v>
+        <v>1.56</v>
       </c>
       <c r="M98">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="N98">
-        <v>2.93</v>
+        <v>4.9</v>
       </c>
       <c r="O98">
+        <v>1.4</v>
+      </c>
+      <c r="P98">
+        <v>14</v>
+      </c>
+      <c r="Q98">
+        <v>2.88</v>
+      </c>
+      <c r="R98">
+        <v>1.22</v>
+      </c>
+      <c r="S98">
+        <v>4</v>
+      </c>
+      <c r="T98">
+        <v>2.1</v>
+      </c>
+      <c r="U98">
         <v>1.67</v>
       </c>
-      <c r="P98">
-        <v>11.5</v>
-      </c>
-      <c r="Q98">
-        <v>2.2</v>
-      </c>
-      <c r="R98">
-        <v>1.3</v>
-      </c>
-      <c r="S98">
-        <v>3.4</v>
-      </c>
-      <c r="T98">
-        <v>2.38</v>
-      </c>
-      <c r="U98">
-        <v>1.53</v>
-      </c>
       <c r="V98">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="W98">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="X98">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y98">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="Z98">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AA98">
-        <v>4.33</v>
+        <v>5.25</v>
       </c>
       <c r="AB98">
-        <v>1.62</v>
+        <v>1.38</v>
       </c>
       <c r="AC98">
-        <v>2.15</v>
+        <v>2.9</v>
       </c>
       <c r="AD98">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="AE98">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="AF98">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG98">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AH98">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="AI98">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AJ98" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK98" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL98" s="3">
         <v>45857.89583333334</v>
@@ -12710,82 +12728,82 @@
         <v>302</v>
       </c>
       <c r="L99">
-        <v>2.63</v>
+        <v>1.53</v>
       </c>
       <c r="M99">
+        <v>3.79</v>
+      </c>
+      <c r="N99">
+        <v>4.9</v>
+      </c>
+      <c r="O99">
+        <v>1.43</v>
+      </c>
+      <c r="P99">
+        <v>10.5</v>
+      </c>
+      <c r="Q99">
+        <v>3.2</v>
+      </c>
+      <c r="R99">
+        <v>1.32</v>
+      </c>
+      <c r="S99">
         <v>3.1</v>
       </c>
-      <c r="N99">
-        <v>2.4</v>
-      </c>
-      <c r="O99">
-        <v>2</v>
-      </c>
-      <c r="P99">
-        <v>13.5</v>
-      </c>
-      <c r="Q99">
-        <v>1.8</v>
-      </c>
-      <c r="R99">
-        <v>1.22</v>
-      </c>
-      <c r="S99">
-        <v>4</v>
-      </c>
       <c r="T99">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="U99">
-        <v>1.67</v>
+        <v>1.49</v>
       </c>
       <c r="V99">
-        <v>4.5</v>
+        <v>5.75</v>
       </c>
       <c r="W99">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="X99">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y99">
-        <v>17</v>
+        <v>10.5</v>
       </c>
       <c r="Z99">
+        <v>1.23</v>
+      </c>
+      <c r="AA99">
+        <v>3.7</v>
+      </c>
+      <c r="AB99">
+        <v>1.61</v>
+      </c>
+      <c r="AC99">
+        <v>2.17</v>
+      </c>
+      <c r="AD99">
+        <v>2.75</v>
+      </c>
+      <c r="AE99">
+        <v>1.39</v>
+      </c>
+      <c r="AF99">
+        <v>1.85</v>
+      </c>
+      <c r="AG99">
+        <v>1.83</v>
+      </c>
+      <c r="AH99">
+        <v>5</v>
+      </c>
+      <c r="AI99">
         <v>1.15</v>
       </c>
-      <c r="AA99">
-        <v>5.25</v>
-      </c>
-      <c r="AB99">
-        <v>1.55</v>
-      </c>
-      <c r="AC99">
-        <v>2.29</v>
-      </c>
-      <c r="AD99">
-        <v>2.1</v>
-      </c>
-      <c r="AE99">
-        <v>1.65</v>
-      </c>
-      <c r="AF99">
-        <v>1.4</v>
-      </c>
-      <c r="AG99">
-        <v>2.75</v>
-      </c>
-      <c r="AH99">
-        <v>3.5</v>
-      </c>
-      <c r="AI99">
-        <v>1.28</v>
-      </c>
       <c r="AJ99" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK99" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL99" s="3">
         <v>45857.89583333334</v>
@@ -12826,82 +12844,82 @@
         <v>302</v>
       </c>
       <c r="L100">
+        <v>2.15</v>
+      </c>
+      <c r="M100">
+        <v>3.2</v>
+      </c>
+      <c r="N100">
+        <v>2.93</v>
+      </c>
+      <c r="O100">
+        <v>1.67</v>
+      </c>
+      <c r="P100">
+        <v>11.5</v>
+      </c>
+      <c r="Q100">
+        <v>2.2</v>
+      </c>
+      <c r="R100">
+        <v>1.3</v>
+      </c>
+      <c r="S100">
+        <v>3.4</v>
+      </c>
+      <c r="T100">
+        <v>2.38</v>
+      </c>
+      <c r="U100">
         <v>1.53</v>
       </c>
-      <c r="M100">
-        <v>3.79</v>
-      </c>
-      <c r="N100">
-        <v>4.9</v>
-      </c>
-      <c r="O100">
-        <v>1.43</v>
-      </c>
-      <c r="P100">
-        <v>10.5</v>
-      </c>
-      <c r="Q100">
-        <v>3.2</v>
-      </c>
-      <c r="R100">
-        <v>1.32</v>
-      </c>
-      <c r="S100">
-        <v>3.1</v>
-      </c>
-      <c r="T100">
-        <v>2.45</v>
-      </c>
-      <c r="U100">
-        <v>1.49</v>
-      </c>
       <c r="V100">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="W100">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X100">
         <v>1.04</v>
       </c>
       <c r="Y100">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Z100">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AA100">
-        <v>3.7</v>
+        <v>4.33</v>
       </c>
       <c r="AB100">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AC100">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AD100">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="AE100">
-        <v>1.39</v>
+        <v>1.57</v>
       </c>
       <c r="AF100">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AG100">
-        <v>1.83</v>
+        <v>2.38</v>
       </c>
       <c r="AH100">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AI100">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AJ100" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK100" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL100" s="3">
         <v>45857.89583333334</v>
@@ -13014,10 +13032,10 @@
         <v>1.18</v>
       </c>
       <c r="AJ101" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK101" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL101" s="3">
         <v>45857.9375</v>
@@ -13031,7 +13049,7 @@
         <v>68</v>
       </c>
       <c r="C102" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D102" t="s">
         <v>94</v>
@@ -13130,10 +13148,10 @@
         <v>1.09</v>
       </c>
       <c r="AJ102" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK102" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL102" s="3">
         <v>45857.95833333334</v>
@@ -13174,82 +13192,82 @@
         <v>302</v>
       </c>
       <c r="L103">
-        <v>1.79</v>
+        <v>1.52</v>
       </c>
       <c r="M103">
-        <v>3.32</v>
+        <v>3.74</v>
       </c>
       <c r="N103">
-        <v>3.87</v>
+        <v>5.1</v>
       </c>
       <c r="O103">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="P103">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Q103">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R103">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S103">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T103">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U103">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V103">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W103">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X103">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y103">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z103">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AA103">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AB103">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AC103">
-        <v>2.31</v>
+        <v>2.54</v>
       </c>
       <c r="AD103">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="AE103">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AF103">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG103">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH103">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AI103">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AJ103" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK103" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL103" s="3">
         <v>45857.97916666666</v>
@@ -13290,22 +13308,22 @@
         <v>302</v>
       </c>
       <c r="L104">
-        <v>1.52</v>
+        <v>2.4</v>
       </c>
       <c r="M104">
-        <v>3.74</v>
+        <v>3.1</v>
       </c>
       <c r="N104">
-        <v>5.1</v>
+        <v>2.63</v>
       </c>
       <c r="O104">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="P104">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="Q104">
-        <v>3</v>
+        <v>2.05</v>
       </c>
       <c r="R104">
         <v>1.25</v>
@@ -13314,16 +13332,16 @@
         <v>3.75</v>
       </c>
       <c r="T104">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="U104">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="V104">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="W104">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X104">
         <v>1.01</v>
@@ -13332,40 +13350,40 @@
         <v>17</v>
       </c>
       <c r="Z104">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AA104">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="AB104">
-        <v>1.48</v>
+        <v>1.72</v>
       </c>
       <c r="AC104">
-        <v>2.54</v>
+        <v>2</v>
       </c>
       <c r="AD104">
-        <v>2.29</v>
+        <v>2.15</v>
       </c>
       <c r="AE104">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AF104">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="AG104">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="AH104">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="AI104">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AJ104" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK104" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL104" s="3">
         <v>45857.97916666666</v>
@@ -13406,82 +13424,82 @@
         <v>302</v>
       </c>
       <c r="L105">
-        <v>2.4</v>
+        <v>1.79</v>
       </c>
       <c r="M105">
-        <v>3.1</v>
+        <v>3.32</v>
       </c>
       <c r="N105">
-        <v>2.63</v>
+        <v>3.87</v>
       </c>
       <c r="O105">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="P105">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="Q105">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="R105">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S105">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="T105">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U105">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="V105">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="W105">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X105">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y105">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Z105">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AA105">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AB105">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="AC105">
-        <v>2</v>
+        <v>2.31</v>
       </c>
       <c r="AD105">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AE105">
-        <v>1.65</v>
+        <v>1.54</v>
       </c>
       <c r="AF105">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AG105">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AH105">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AI105">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AJ105" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AK105" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL105" s="3">
         <v>45857.97916666666</v>
